--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B4A08B6-5F1E-4850-96F8-1CB89521C203}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1378,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D417"/>
+  <dimension ref="A1:D416"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.77734375" bestFit="1" customWidth="1"/>
@@ -6498,27 +6499,27 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B366" s="4">
-        <v>-23.469118999999999</v>
+        <v>-23.944847236431929</v>
       </c>
       <c r="C366" s="4">
-        <v>-46.478465</v>
+        <v>-46.325583061907672</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B367" s="4">
-        <v>-23.944847236431929</v>
+        <v>-23.531849347808581</v>
       </c>
       <c r="C367" s="4">
-        <v>-46.325583061907672</v>
+        <v>-46.735724065610007</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>286</v>
@@ -6526,13 +6527,13 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B368" s="4">
-        <v>-23.531849347808581</v>
+        <v>-23.55294247630945</v>
       </c>
       <c r="C368" s="4">
-        <v>-46.735724065610007</v>
+        <v>-46.619393166946679</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>286</v>
@@ -6540,13 +6541,13 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B369" s="4">
-        <v>-23.55294247630945</v>
+        <v>-23.472979486390759</v>
       </c>
       <c r="C369" s="4">
-        <v>-46.619393166946679</v>
+        <v>-46.523945212141733</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>286</v>
@@ -6554,13 +6555,13 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B370" s="4">
-        <v>-23.472979486390759</v>
+        <v>-23.564769691418221</v>
       </c>
       <c r="C370" s="4">
-        <v>-46.523945212141733</v>
+        <v>-46.501131225825851</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>286</v>
@@ -6568,13 +6569,13 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B371" s="4">
-        <v>-23.564769691418221</v>
+        <v>-23.944992958284949</v>
       </c>
       <c r="C371" s="4">
-        <v>-46.501131225825851</v>
+        <v>-46.325577395823011</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>286</v>
@@ -6582,13 +6583,13 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B372" s="4">
-        <v>-23.944992958284949</v>
+        <v>-23.654672045553511</v>
       </c>
       <c r="C372" s="4">
-        <v>-46.325577395823011</v>
+        <v>-46.532770484183843</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>286</v>
@@ -6596,13 +6597,13 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B373" s="4">
-        <v>-23.654672045553511</v>
+        <v>-23.571564505363789</v>
       </c>
       <c r="C373" s="4">
-        <v>-46.532770484183843</v>
+        <v>-46.674319619591728</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>286</v>
@@ -6610,13 +6611,13 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B374" s="4">
-        <v>-23.571564505363789</v>
+        <v>-23.67088218599541</v>
       </c>
       <c r="C374" s="4">
-        <v>-46.674319619591728</v>
+        <v>-46.703460322836527</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>286</v>
@@ -6624,13 +6625,13 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B375" s="4">
-        <v>-23.67088218599541</v>
+        <v>-23.198517529504979</v>
       </c>
       <c r="C375" s="4">
-        <v>-46.703460322836527</v>
+        <v>-45.878332076374498</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>286</v>
@@ -6638,13 +6639,13 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B376" s="4">
-        <v>-23.198517529504979</v>
+        <v>-23.614815151746999</v>
       </c>
       <c r="C376" s="4">
-        <v>-45.878332076374498</v>
+        <v>-46.667774402652867</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>286</v>
@@ -6652,13 +6653,13 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B377" s="4">
-        <v>-23.614815151746999</v>
+        <v>-23.570646581729552</v>
       </c>
       <c r="C377" s="4">
-        <v>-46.667774402652867</v>
+        <v>-46.700654586311067</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>286</v>
@@ -6666,13 +6667,13 @@
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B378" s="4">
-        <v>-23.570646581729552</v>
+        <v>-23.531889646879669</v>
       </c>
       <c r="C378" s="4">
-        <v>-46.700654586311067</v>
+        <v>-46.735696404249197</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>286</v>
@@ -6680,13 +6681,13 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B379" s="4">
-        <v>-23.531889646879669</v>
+        <v>-23.514655011467308</v>
       </c>
       <c r="C379" s="4">
-        <v>-46.735696404249197</v>
+        <v>-46.69731055044749</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>286</v>
@@ -6694,13 +6695,13 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B380" s="4">
-        <v>-23.514655011467308</v>
+        <v>-23.533991495405971</v>
       </c>
       <c r="C380" s="4">
-        <v>-46.69731055044749</v>
+        <v>-46.213424755631287</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>286</v>
@@ -6708,13 +6709,13 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B381" s="4">
-        <v>-23.533991495405971</v>
+        <v>-23.601480756898351</v>
       </c>
       <c r="C381" s="4">
-        <v>-46.213424755631287</v>
+        <v>-46.660196519590862</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>286</v>
@@ -6722,13 +6723,13 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B382" s="4">
-        <v>-23.601480756898351</v>
+        <v>-23.617863095353002</v>
       </c>
       <c r="C382" s="4">
-        <v>-46.660196519590862</v>
+        <v>-46.703053701914143</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>286</v>
@@ -6736,13 +6737,13 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B383" s="4">
-        <v>-23.617863095353002</v>
+        <v>-23.53076941855366</v>
       </c>
       <c r="C383" s="4">
-        <v>-46.703053701914143</v>
+        <v>-46.661219004249162</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>286</v>
@@ -6750,13 +6751,13 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="B384" s="4">
-        <v>-23.53076941855366</v>
+        <v>-23.687290402466761</v>
       </c>
       <c r="C384" s="4">
-        <v>-46.661219004249162</v>
+        <v>-46.547322733080051</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>286</v>
@@ -6764,13 +6765,13 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="B385" s="4">
-        <v>-23.687290402466761</v>
+        <v>-23.55050696354467</v>
       </c>
       <c r="C385" s="4">
-        <v>-46.547322733080051</v>
+        <v>-46.567435488904863</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>286</v>
@@ -6792,13 +6793,13 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B387" s="4">
-        <v>-23.55050696354467</v>
+        <v>-23.51602162022504</v>
       </c>
       <c r="C387" s="4">
-        <v>-46.567435488904863</v>
+        <v>-46.60905822012348</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>286</v>
@@ -6806,13 +6807,13 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="B388" s="4">
-        <v>-23.51602162022504</v>
+        <v>-23.515997996484789</v>
       </c>
       <c r="C388" s="4">
-        <v>-46.60905822012348</v>
+        <v>-46.609125690757487</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>286</v>
@@ -6820,13 +6821,13 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="B389" s="4">
-        <v>-23.515997996484789</v>
+        <v>-23.58698385549571</v>
       </c>
       <c r="C389" s="4">
-        <v>-46.609125690757487</v>
+        <v>-46.671689406111518</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>286</v>
@@ -6834,13 +6835,13 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" s="3" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B390" s="4">
-        <v>-23.58698385549571</v>
+        <v>-23.650150268594871</v>
       </c>
       <c r="C390" s="4">
-        <v>-46.671689406111518</v>
+        <v>-46.677958860065658</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>286</v>
@@ -6848,27 +6849,27 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B391" s="4">
-        <v>-23.650150268594871</v>
+        <v>-23.47289117254504</v>
       </c>
       <c r="C391" s="4">
-        <v>-46.677958860065658</v>
+        <v>-46.52207849143646</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B392" s="4">
-        <v>-23.47289117254504</v>
+        <v>-23.56536077118389</v>
       </c>
       <c r="C392" s="4">
-        <v>-46.52207849143646</v>
+        <v>-46.500440332261029</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>303</v>
@@ -6876,13 +6877,13 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B393" s="4">
-        <v>-23.56536077118389</v>
+        <v>-23.661359333585541</v>
       </c>
       <c r="C393" s="4">
-        <v>-46.500440332261029</v>
+        <v>-46.520574457269959</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>303</v>
@@ -6890,13 +6891,13 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B394" s="4">
-        <v>-23.661359333585541</v>
+        <v>-23.570707330093601</v>
       </c>
       <c r="C394" s="4">
-        <v>-46.520574457269959</v>
+        <v>-46.720379967917701</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>303</v>
@@ -6904,13 +6905,13 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B395" s="4">
-        <v>-23.570707330093601</v>
+        <v>-23.045459699579109</v>
       </c>
       <c r="C395" s="4">
-        <v>-46.720379967917701</v>
+        <v>-45.583268119608519</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>303</v>
@@ -6918,13 +6919,13 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B396" s="4">
-        <v>-23.045459699579109</v>
+        <v>-23.489014112668329</v>
       </c>
       <c r="C396" s="4">
-        <v>-45.583268119608519</v>
+        <v>-46.654199878853412</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>303</v>
@@ -6935,10 +6936,10 @@
         <v>308</v>
       </c>
       <c r="B397" s="4">
-        <v>-23.489014112668329</v>
+        <v>-23.517930442486811</v>
       </c>
       <c r="C397" s="4">
-        <v>-46.654199878853412</v>
+        <v>-46.609561860842398</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>303</v>
@@ -6946,13 +6947,13 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B398" s="4">
-        <v>-23.517930442486811</v>
+        <v>-23.936341835223541</v>
       </c>
       <c r="C398" s="4">
-        <v>-46.609561860842398</v>
+        <v>-46.330332980981289</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>303</v>
@@ -6963,10 +6964,10 @@
         <v>309</v>
       </c>
       <c r="B399" s="4">
-        <v>-23.936341835223541</v>
+        <v>-23.936241361134488</v>
       </c>
       <c r="C399" s="4">
-        <v>-46.330332980981289</v>
+        <v>-46.329994816600603</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>303</v>
@@ -6974,13 +6975,13 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B400" s="4">
-        <v>-23.936241361134488</v>
+        <v>-23.542180443534122</v>
       </c>
       <c r="C400" s="4">
-        <v>-46.329994816600603</v>
+        <v>-46.547794314314849</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>303</v>
@@ -6988,13 +6989,13 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B401" s="4">
-        <v>-23.542180443534122</v>
+        <v>-23.21299542490172</v>
       </c>
       <c r="C401" s="4">
-        <v>-46.547794314314849</v>
+        <v>-45.891634145689373</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>303</v>
@@ -7002,13 +7003,13 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B402" s="4">
-        <v>-23.21299542490172</v>
+        <v>-23.616689913358801</v>
       </c>
       <c r="C402" s="4">
-        <v>-45.891634145689373</v>
+        <v>-46.73115851773855</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>303</v>
@@ -7016,13 +7017,13 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B403" s="4">
-        <v>-23.616689913358801</v>
+        <v>-23.61617950543452</v>
       </c>
       <c r="C403" s="4">
-        <v>-46.73115851773855</v>
+        <v>-46.55514996348554</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>303</v>
@@ -7030,13 +7031,13 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B404" s="4">
-        <v>-23.61617950543452</v>
+        <v>-23.659527372292189</v>
       </c>
       <c r="C404" s="4">
-        <v>-46.55514996348554</v>
+        <v>-46.679324804160899</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>303</v>
@@ -7044,13 +7045,13 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B405" s="4">
-        <v>-23.659527372292189</v>
+        <v>-23.528986648887749</v>
       </c>
       <c r="C405" s="4">
-        <v>-46.679324804160899</v>
+        <v>-46.202061720611603</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>303</v>
@@ -7058,13 +7059,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B406" s="4">
-        <v>-23.528986648887749</v>
+        <v>-23.6165818644177</v>
       </c>
       <c r="C406" s="4">
-        <v>-46.202061720611603</v>
+        <v>-46.609124019590261</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>303</v>
@@ -7072,13 +7073,13 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B407" s="4">
-        <v>-23.6165818644177</v>
+        <v>-23.614889538343611</v>
       </c>
       <c r="C407" s="4">
-        <v>-46.609124019590261</v>
+        <v>-45.43082713953082</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>303</v>
@@ -7086,13 +7087,13 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B408" s="4">
-        <v>-23.614889538343611</v>
+        <v>-23.583207587411191</v>
       </c>
       <c r="C408" s="4">
-        <v>-45.43082713953082</v>
+        <v>-46.575700250279112</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>303</v>
@@ -7100,13 +7101,13 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B409" s="4">
-        <v>-23.583207587411191</v>
+        <v>-23.52333118643968</v>
       </c>
       <c r="C409" s="4">
-        <v>-46.575700250279112</v>
+        <v>-46.687814811526337</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>303</v>
@@ -7114,13 +7115,13 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B410" s="4">
-        <v>-23.52333118643968</v>
+        <v>-23.512812952205699</v>
       </c>
       <c r="C410" s="4">
-        <v>-46.687814811526337</v>
+        <v>-46.703434205721571</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>303</v>
@@ -7128,13 +7129,13 @@
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B411" s="4">
-        <v>-23.512812952205699</v>
+        <v>-23.600163797091621</v>
       </c>
       <c r="C411" s="4">
-        <v>-46.703434205721571</v>
+        <v>-46.647396065554943</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>303</v>
@@ -7142,13 +7143,13 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B412" s="4">
-        <v>-23.600163797091621</v>
+        <v>-23.529221288285211</v>
       </c>
       <c r="C412" s="4">
-        <v>-46.647396065554943</v>
+        <v>-46.202022417007768</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>303</v>
@@ -7156,13 +7157,13 @@
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B413" s="4">
-        <v>-23.529221288285211</v>
+        <v>-23.592473033312061</v>
       </c>
       <c r="C413" s="4">
-        <v>-46.202022417007768</v>
+        <v>-46.621634868423968</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>303</v>
@@ -7170,13 +7171,13 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A414" s="3" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B414" s="4">
-        <v>-23.592473033312061</v>
+        <v>-23.49786360950602</v>
       </c>
       <c r="C414" s="4">
-        <v>-46.621634868423968</v>
+        <v>-46.455292573149649</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>303</v>
@@ -7184,13 +7185,13 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B415" s="4">
-        <v>-23.49786360950602</v>
+        <v>-23.674672154258179</v>
       </c>
       <c r="C415" s="4">
-        <v>-46.455292573149649</v>
+        <v>-46.55702542861637</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>303</v>
@@ -7198,34 +7199,44 @@
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B416" s="4">
-        <v>-23.674672154258179</v>
+        <v>-23.66215145705554</v>
       </c>
       <c r="C416" s="4">
-        <v>-46.55702542861637</v>
+        <v>-46.518995308408897</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A417" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B417" s="4">
-        <v>-23.66215145705554</v>
-      </c>
-      <c r="C417" s="4">
-        <v>-46.518995308408897</v>
-      </c>
-      <c r="D417" s="4" t="s">
-        <v>303</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563561C5-EB2B-425D-9BA6-51C4516000DC}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="4">
+        <v>-23.469118999999999</v>
+      </c>
+      <c r="C1" s="4">
+        <v>-46.478465</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B4A08B6-5F1E-4850-96F8-1CB89521C203}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8022FD0C-A521-4811-851B-E11DDBD2DE7F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="322">
   <si>
     <t>nome</t>
   </si>
@@ -886,12 +885,6 @@
   </si>
   <si>
     <t>FLORA MOTORS LTDA</t>
-  </si>
-  <si>
-    <t>SPG ✅</t>
-  </si>
-  <si>
-    <t>vermelho</t>
   </si>
   <si>
     <t>EVEREST COMERCIO DE VEICULOS S/A</t>
@@ -6499,7 +6492,7 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B366" s="4">
         <v>-23.944847236431929</v>
@@ -6508,12 +6501,12 @@
         <v>-46.325583061907672</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B367" s="4">
         <v>-23.531849347808581</v>
@@ -6522,12 +6515,12 @@
         <v>-46.735724065610007</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B368" s="4">
         <v>-23.55294247630945</v>
@@ -6536,12 +6529,12 @@
         <v>-46.619393166946679</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B369" s="4">
         <v>-23.472979486390759</v>
@@ -6550,12 +6543,12 @@
         <v>-46.523945212141733</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B370" s="4">
         <v>-23.564769691418221</v>
@@ -6564,12 +6557,12 @@
         <v>-46.501131225825851</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B371" s="4">
         <v>-23.944992958284949</v>
@@ -6578,12 +6571,12 @@
         <v>-46.325577395823011</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B372" s="4">
         <v>-23.654672045553511</v>
@@ -6592,12 +6585,12 @@
         <v>-46.532770484183843</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B373" s="4">
         <v>-23.571564505363789</v>
@@ -6606,12 +6599,12 @@
         <v>-46.674319619591728</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B374" s="4">
         <v>-23.67088218599541</v>
@@ -6620,12 +6613,12 @@
         <v>-46.703460322836527</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B375" s="4">
         <v>-23.198517529504979</v>
@@ -6634,12 +6627,12 @@
         <v>-45.878332076374498</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B376" s="4">
         <v>-23.614815151746999</v>
@@ -6648,12 +6641,12 @@
         <v>-46.667774402652867</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B377" s="4">
         <v>-23.570646581729552</v>
@@ -6662,12 +6655,12 @@
         <v>-46.700654586311067</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B378" s="4">
         <v>-23.531889646879669</v>
@@ -6676,12 +6669,12 @@
         <v>-46.735696404249197</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B379" s="4">
         <v>-23.514655011467308</v>
@@ -6690,12 +6683,12 @@
         <v>-46.69731055044749</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B380" s="4">
         <v>-23.533991495405971</v>
@@ -6704,12 +6697,12 @@
         <v>-46.213424755631287</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B381" s="4">
         <v>-23.601480756898351</v>
@@ -6718,12 +6711,12 @@
         <v>-46.660196519590862</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B382" s="4">
         <v>-23.617863095353002</v>
@@ -6732,12 +6725,12 @@
         <v>-46.703053701914143</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B383" s="4">
         <v>-23.53076941855366</v>
@@ -6746,12 +6739,12 @@
         <v>-46.661219004249162</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B384" s="4">
         <v>-23.687290402466761</v>
@@ -6760,12 +6753,12 @@
         <v>-46.547322733080051</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B385" s="4">
         <v>-23.55050696354467</v>
@@ -6774,12 +6767,12 @@
         <v>-46.567435488904863</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A386" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B386" s="4">
         <v>-23.55050696354467</v>
@@ -6788,12 +6781,12 @@
         <v>-46.567435488904863</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B387" s="4">
         <v>-23.51602162022504</v>
@@ -6802,12 +6795,12 @@
         <v>-46.60905822012348</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B388" s="4">
         <v>-23.515997996484789</v>
@@ -6816,12 +6809,12 @@
         <v>-46.609125690757487</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B389" s="4">
         <v>-23.58698385549571</v>
@@ -6830,12 +6823,12 @@
         <v>-46.671689406111518</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B390" s="4">
         <v>-23.650150268594871</v>
@@ -6844,12 +6837,12 @@
         <v>-46.677958860065658</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B391" s="4">
         <v>-23.47289117254504</v>
@@ -6858,12 +6851,12 @@
         <v>-46.52207849143646</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B392" s="4">
         <v>-23.56536077118389</v>
@@ -6872,12 +6865,12 @@
         <v>-46.500440332261029</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B393" s="4">
         <v>-23.661359333585541</v>
@@ -6886,12 +6879,12 @@
         <v>-46.520574457269959</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B394" s="4">
         <v>-23.570707330093601</v>
@@ -6900,12 +6893,12 @@
         <v>-46.720379967917701</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B395" s="4">
         <v>-23.045459699579109</v>
@@ -6914,12 +6907,12 @@
         <v>-45.583268119608519</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B396" s="4">
         <v>-23.489014112668329</v>
@@ -6928,12 +6921,12 @@
         <v>-46.654199878853412</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B397" s="4">
         <v>-23.517930442486811</v>
@@ -6942,12 +6935,12 @@
         <v>-46.609561860842398</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B398" s="4">
         <v>-23.936341835223541</v>
@@ -6956,12 +6949,12 @@
         <v>-46.330332980981289</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B399" s="4">
         <v>-23.936241361134488</v>
@@ -6970,12 +6963,12 @@
         <v>-46.329994816600603</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B400" s="4">
         <v>-23.542180443534122</v>
@@ -6984,12 +6977,12 @@
         <v>-46.547794314314849</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B401" s="4">
         <v>-23.21299542490172</v>
@@ -6998,12 +6991,12 @@
         <v>-45.891634145689373</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B402" s="4">
         <v>-23.616689913358801</v>
@@ -7012,12 +7005,12 @@
         <v>-46.73115851773855</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B403" s="4">
         <v>-23.61617950543452</v>
@@ -7026,12 +7019,12 @@
         <v>-46.55514996348554</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B404" s="4">
         <v>-23.659527372292189</v>
@@ -7040,12 +7033,12 @@
         <v>-46.679324804160899</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B405" s="4">
         <v>-23.528986648887749</v>
@@ -7054,12 +7047,12 @@
         <v>-46.202061720611603</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B406" s="4">
         <v>-23.6165818644177</v>
@@ -7068,12 +7061,12 @@
         <v>-46.609124019590261</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B407" s="4">
         <v>-23.614889538343611</v>
@@ -7082,12 +7075,12 @@
         <v>-45.43082713953082</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B408" s="4">
         <v>-23.583207587411191</v>
@@ -7096,12 +7089,12 @@
         <v>-46.575700250279112</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B409" s="4">
         <v>-23.52333118643968</v>
@@ -7110,12 +7103,12 @@
         <v>-46.687814811526337</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B410" s="4">
         <v>-23.512812952205699</v>
@@ -7124,12 +7117,12 @@
         <v>-46.703434205721571</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B411" s="4">
         <v>-23.600163797091621</v>
@@ -7138,12 +7131,12 @@
         <v>-46.647396065554943</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B412" s="4">
         <v>-23.529221288285211</v>
@@ -7152,12 +7145,12 @@
         <v>-46.202022417007768</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B413" s="4">
         <v>-23.592473033312061</v>
@@ -7166,12 +7159,12 @@
         <v>-46.621634868423968</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A414" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B414" s="4">
         <v>-23.49786360950602</v>
@@ -7180,12 +7173,12 @@
         <v>-46.455292573149649</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B415" s="4">
         <v>-23.674672154258179</v>
@@ -7194,12 +7187,12 @@
         <v>-46.55702542861637</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B416" s="4">
         <v>-23.66215145705554</v>
@@ -7208,35 +7201,11 @@
         <v>-46.518995308408897</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563561C5-EB2B-425D-9BA6-51C4516000DC}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B1" s="4">
-        <v>-23.469118999999999</v>
-      </c>
-      <c r="C1" s="4">
-        <v>-46.478465</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8022FD0C-A521-4811-851B-E11DDBD2DE7F}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{071265FB-2687-458B-9229-D958A77D2F93}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="324">
   <si>
     <t>nome</t>
   </si>
@@ -1002,6 +1002,12 @@
   </si>
   <si>
     <t>Ok - Distribuidora De Veiculos E Pe</t>
+  </si>
+  <si>
+    <t>SPG ✅</t>
+  </si>
+  <si>
+    <t>vermelho</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D416"/>
+  <dimension ref="A1:D417"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.77734375" bestFit="1" customWidth="1"/>
@@ -7204,6 +7210,20 @@
         <v>301</v>
       </c>
     </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>322</v>
+      </c>
+      <c r="B417">
+        <v>-23.469118999999999</v>
+      </c>
+      <c r="C417">
+        <v>-46.478465</v>
+      </c>
+      <c r="D417" t="s">
+        <v>323</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{071265FB-2687-458B-9229-D958A77D2F93}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59A9E207-2268-4C4A-BDA5-27BFD3E6B6AC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1064,7 +1064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1075,6 +1075,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1378,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D417"/>
+  <dimension ref="A1:D418"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.77734375" bestFit="1" customWidth="1"/>
@@ -7211,18 +7214,24 @@
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A417" t="s">
+      <c r="A417" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="B417">
+      <c r="B417" s="4">
         <v>-23.469118999999999</v>
       </c>
-      <c r="C417">
+      <c r="C417" s="4">
         <v>-46.478465</v>
       </c>
-      <c r="D417" t="s">
+      <c r="D417" s="4" t="s">
         <v>323</v>
       </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A418" s="4"/>
+      <c r="B418" s="4"/>
+      <c r="C418" s="4"/>
+      <c r="D418" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59A9E207-2268-4C4A-BDA5-27BFD3E6B6AC}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C756E28-B28B-4A15-A467-AFCB8EA5ACC3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="322">
   <si>
     <t>nome</t>
   </si>
@@ -1002,12 +1002,6 @@
   </si>
   <si>
     <t>Ok - Distribuidora De Veiculos E Pe</t>
-  </si>
-  <si>
-    <t>SPG ✅</t>
-  </si>
-  <si>
-    <t>vermelho</t>
   </si>
 </sst>
 </file>
@@ -1064,7 +1058,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1078,6 +1072,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1385,7 +1385,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7214,23 +7215,15 @@
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A417" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="B417" s="4">
-        <v>-23.469118999999999</v>
-      </c>
-      <c r="C417" s="4">
-        <v>-46.478465</v>
-      </c>
-      <c r="D417" s="4" t="s">
-        <v>323</v>
-      </c>
+      <c r="A417" s="5"/>
+      <c r="B417" s="4"/>
+      <c r="C417" s="4"/>
+      <c r="D417" s="4"/>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A418" s="4"/>
-      <c r="B418" s="4"/>
-      <c r="C418" s="4"/>
+      <c r="B418" s="6"/>
+      <c r="C418" s="7"/>
       <c r="D418" s="4"/>
     </row>
   </sheetData>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C756E28-B28B-4A15-A467-AFCB8EA5ACC3}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B532667D-AEC3-4948-8934-CF4FA5859E96}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="324">
   <si>
     <t>nome</t>
   </si>
@@ -1002,6 +1002,12 @@
   </si>
   <si>
     <t>Ok - Distribuidora De Veiculos E Pe</t>
+  </si>
+  <si>
+    <t>SPG ✅</t>
+  </si>
+  <si>
+    <t>vermelho</t>
   </si>
 </sst>
 </file>
@@ -7215,10 +7221,18 @@
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A417" s="5"/>
-      <c r="B417" s="4"/>
-      <c r="C417" s="4"/>
-      <c r="D417" s="4"/>
+      <c r="A417" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B417" s="4">
+        <v>-23.469118999999999</v>
+      </c>
+      <c r="C417" s="4">
+        <v>-46.478465</v>
+      </c>
+      <c r="D417" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A418" s="4"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B532667D-AEC3-4948-8934-CF4FA5859E96}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753C7EF0-9FF8-44C4-BD71-443314040C6E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="334">
   <si>
     <t>nome</t>
   </si>
@@ -1008,6 +1008,36 @@
   </si>
   <si>
     <t>vermelho</t>
+  </si>
+  <si>
+    <t>rosa</t>
+  </si>
+  <si>
+    <t>-23.453774345473747</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.558983148431594</t>
+  </si>
+  <si>
+    <t>Jorge Felix Monteiro</t>
+  </si>
+  <si>
+    <t>-23.57251653927414</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.6660423195917</t>
+  </si>
+  <si>
+    <t>Convatec Medical Care</t>
+  </si>
+  <si>
+    <t>-23.02519394724738</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.564070713412825</t>
+  </si>
+  <si>
+    <t>Maisnove Med Diagnostica Ltda</t>
   </si>
 </sst>
 </file>
@@ -1064,26 +1094,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1387,37 +1418,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D418"/>
+  <dimension ref="A1:D602"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="149.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="85.77734375" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="7">
         <v>-23.488315</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="7">
         <v>-46.548983</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -1425,13 +1456,13 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="7">
         <v>-23.443432999999999</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="7">
         <v>-46.539954999999999</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -1439,13 +1470,13 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="7">
         <v>-23.56146</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="7">
         <v>-46.560160000000003</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -1453,13 +1484,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="7">
         <v>-23.579740000000001</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="7">
         <v>-46.594245999999998</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -1467,13 +1498,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="7">
         <v>-23.572645999999999</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="7">
         <v>-46.695819</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -1481,13 +1512,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="7">
         <v>-23.479626</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="7">
         <v>-46.602395999999999</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -1495,13 +1526,13 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="7">
         <v>-23.563962</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="7">
         <v>-46.652904999999997</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -1509,13 +1540,13 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="7">
         <v>-23.577199</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="7">
         <v>-46.688048000000002</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -1523,13 +1554,13 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="7">
         <v>-23.591363999999999</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="7">
         <v>-46.689765999999999</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -1537,13 +1568,13 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="7">
         <v>-23.678487000000001</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="7">
         <v>-46.699168999999998</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -1551,13 +1582,13 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="7">
         <v>-23.538999</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="7">
         <v>-46.576335999999998</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -1565,13 +1596,13 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="7">
         <v>-23.541689000000002</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="7">
         <v>-46.577046000000003</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -1579,13 +1610,13 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="7">
         <v>-23.558211</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="7">
         <v>-46.658684999999998</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -1593,13 +1624,13 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="7">
         <v>-23.554179999999999</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="7">
         <v>-46.652403999999997</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -1607,13 +1638,13 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="7">
         <v>-23.57077</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="7">
         <v>-46.643185000000003</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -1621,13 +1652,13 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="7">
         <v>-23.482817000000001</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="7">
         <v>-46.644765</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -1635,13 +1666,13 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="7">
         <v>-23.551082000000001</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="7">
         <v>-46.722143000000003</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -1649,13 +1680,13 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="7">
         <v>-23.595493999999999</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="7">
         <v>-46.686731000000002</v>
       </c>
       <c r="D19" s="4" t="s">
@@ -1663,13 +1694,13 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="7">
         <v>-23.521588999999999</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="7">
         <v>-46.623797000000003</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -1677,13 +1708,13 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="7">
         <v>-23.610192999999999</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="7">
         <v>-46.666874</v>
       </c>
       <c r="D21" s="4" t="s">
@@ -1691,13 +1722,13 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="7">
         <v>-23.540752999999999</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="7">
         <v>-46.470533000000003</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -1705,13 +1736,13 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="7">
         <v>-23.625706999999998</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="7">
         <v>-46.705692999999997</v>
       </c>
       <c r="D23" s="4" t="s">
@@ -1719,13 +1750,13 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="7">
         <v>-23.546695</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="7">
         <v>-46.638584000000002</v>
       </c>
       <c r="D24" s="4" t="s">
@@ -1733,13 +1764,13 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="7">
         <v>-23.653185000000001</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="7">
         <v>-46.710213000000003</v>
       </c>
       <c r="D25" s="4" t="s">
@@ -1747,13 +1778,13 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="7">
         <v>-23.623417</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="7">
         <v>-46.698543999999998</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -1761,13 +1792,13 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="7">
         <v>-23.599135</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="7">
         <v>-46.637210000000003</v>
       </c>
       <c r="D27" s="4" t="s">
@@ -1775,13 +1806,13 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="7">
         <v>-23.527429000000001</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="7">
         <v>-46.674795000000003</v>
       </c>
       <c r="D28" s="4" t="s">
@@ -1789,13 +1820,13 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="7">
         <v>-23.588070999999999</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="7">
         <v>-46.751193999999998</v>
       </c>
       <c r="D29" s="4" t="s">
@@ -1803,13 +1834,13 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="7">
         <v>-23.631077000000001</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="7">
         <v>-46.735916000000003</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -1817,13 +1848,13 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="7">
         <v>-23.506409999999999</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="7">
         <v>-46.718114</v>
       </c>
       <c r="D31" s="4" t="s">
@@ -1831,13 +1862,13 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="7">
         <v>-23.599032999999999</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="7">
         <v>-46.697569999999999</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -1845,13 +1876,13 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="7">
         <v>-23.515812</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="7">
         <v>-46.618219000000003</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -1859,13 +1890,13 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="7">
         <v>-23.649725</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="7">
         <v>-46.757517999999997</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -1873,13 +1904,13 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="7">
         <v>-23.619785</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="7">
         <v>-46.626846999999998</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -1887,13 +1918,13 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="7">
         <v>-23.542124000000001</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="7">
         <v>-46.657392999999999</v>
       </c>
       <c r="D36" s="4" t="s">
@@ -1901,13 +1932,13 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="7">
         <v>-23.565902000000001</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="7">
         <v>-46.503075000000003</v>
       </c>
       <c r="D37" s="4" t="s">
@@ -1915,13 +1946,13 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="7">
         <v>-23.676286999999999</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="7">
         <v>-46.676811000000001</v>
       </c>
       <c r="D38" s="4" t="s">
@@ -1929,13 +1960,13 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="7">
         <v>-23.648716</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="7">
         <v>-46.53192</v>
       </c>
       <c r="D39" s="4" t="s">
@@ -1943,13 +1974,13 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="7">
         <v>-23.667739000000001</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="7">
         <v>-46.533405000000002</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -1957,13 +1988,13 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="7">
         <v>-23.66366</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="7">
         <v>-46.507441</v>
       </c>
       <c r="D41" s="4" t="s">
@@ -1971,13 +2002,13 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="7">
         <v>-23.692691</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="7">
         <v>-46.550325999999998</v>
       </c>
       <c r="D42" s="4" t="s">
@@ -1985,13 +2016,13 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="7">
         <v>-23.683627999999999</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="7">
         <v>-46.557174000000003</v>
       </c>
       <c r="D43" s="4" t="s">
@@ -1999,13 +2030,13 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="7">
         <v>-23.723153</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="7">
         <v>-46.543081000000001</v>
       </c>
       <c r="D44" s="4" t="s">
@@ -2013,13 +2044,13 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="7">
         <v>-23.62524174829716</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="7">
         <v>-46.579337125848518</v>
       </c>
       <c r="D45" s="4" t="s">
@@ -2027,13 +2058,13 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="7">
         <v>-23.691476000000002</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="7">
         <v>-46.623373000000001</v>
       </c>
       <c r="D46" s="4" t="s">
@@ -2041,13 +2072,13 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="7">
         <v>-23.664166999999999</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="7">
         <v>-46.460864000000001</v>
       </c>
       <c r="D47" s="4" t="s">
@@ -2055,13 +2086,13 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="7">
         <v>-23.199942</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="7">
         <v>-45.881328000000003</v>
       </c>
       <c r="D48" s="4" t="s">
@@ -2069,13 +2100,13 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="7">
         <v>-23.217275000000001</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="7">
         <v>-45.891328999999999</v>
       </c>
       <c r="D49" s="4" t="s">
@@ -2083,13 +2114,13 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="7">
         <v>-23.204297</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="7">
         <v>-45.908647000000002</v>
       </c>
       <c r="D50" s="4" t="s">
@@ -2097,13 +2128,13 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="7">
         <v>-23.023564</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="7">
         <v>-45.58175</v>
       </c>
       <c r="D51" s="4" t="s">
@@ -2111,13 +2142,13 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="7">
         <v>-23.977830000000001</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="7">
         <v>-46.308711000000002</v>
       </c>
       <c r="D52" s="4" t="s">
@@ -2125,13 +2156,13 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="7">
         <v>-23.968945999999999</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="7">
         <v>-46.332338</v>
       </c>
       <c r="D53" s="4" t="s">
@@ -2139,13 +2170,13 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="7">
         <v>-23.997776000000002</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="7">
         <v>-46.406599999999997</v>
       </c>
       <c r="D54" s="4" t="s">
@@ -2153,13 +2184,13 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="7">
         <v>-23.968004000000001</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="7">
         <v>-46.383924</v>
       </c>
       <c r="D55" s="4" t="s">
@@ -2167,13 +2198,13 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="7">
         <v>-23.654187</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="7">
         <v>-45.437063999999999</v>
       </c>
       <c r="D56" s="4" t="s">
@@ -2181,13 +2212,13 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="7">
         <v>-23.623825</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="7">
         <v>-45.410716999999998</v>
       </c>
       <c r="D57" s="4" t="s">
@@ -2195,13 +2226,13 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="7">
         <v>-23.451029999999999</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="7">
         <v>-45.066152000000002</v>
       </c>
       <c r="D58" s="4" t="s">
@@ -2209,13 +2240,13 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="7">
         <v>-23.451029999999999</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="7">
         <v>-45.066152000000002</v>
       </c>
       <c r="D59" s="4" t="s">
@@ -2223,13 +2254,13 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="7">
         <v>-23.515775000000001</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="7">
         <v>-46.179687000000001</v>
       </c>
       <c r="D60" s="4" t="s">
@@ -2237,13 +2268,13 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="7">
         <v>-23.525369999999999</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="7">
         <v>-46.199418000000001</v>
       </c>
       <c r="D61" s="4" t="s">
@@ -2251,13 +2282,13 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="7">
         <v>-23.542863000000001</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="7">
         <v>-46.318485000000003</v>
       </c>
       <c r="D62" s="4" t="s">
@@ -2265,13 +2296,13 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="7">
         <v>-23.475434</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="7">
         <v>-46.326332000000001</v>
       </c>
       <c r="D63" s="4" t="s">
@@ -2279,13 +2310,13 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="7">
         <v>-23.433228</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="7">
         <v>-46.272283999999999</v>
       </c>
       <c r="D64" s="4" t="s">
@@ -2293,13 +2324,13 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="7">
         <v>-23.434073000000001</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="7">
         <v>-46.403787999999999</v>
       </c>
       <c r="D65" s="4" t="s">
@@ -2307,13 +2338,13 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="7">
         <v>-23.106290000000001</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="7">
         <v>-45.707639999999998</v>
       </c>
       <c r="D66" s="4" t="s">
@@ -2321,13 +2352,13 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="7">
         <v>-23.103555</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="7">
         <v>-45.685161000000001</v>
       </c>
       <c r="D67" s="4" t="s">
@@ -2335,13 +2366,13 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="7">
         <v>-22.718788</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="7">
         <v>-45.567636999999998</v>
       </c>
       <c r="D68" s="4" t="s">
@@ -2349,13 +2380,13 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="7">
         <v>-22.718989000000001</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="7">
         <v>-45.566285999999998</v>
       </c>
       <c r="D69" s="4" t="s">
@@ -2363,13 +2394,13 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="7">
         <v>-22.718833</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="7">
         <v>-45.566991000000002</v>
       </c>
       <c r="D70" s="4" t="s">
@@ -2377,13 +2408,13 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="7">
         <v>-22.720191</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="7">
         <v>-45.568637000000003</v>
       </c>
       <c r="D71" s="4" t="s">
@@ -2391,13 +2422,13 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="7">
         <v>-22.719995000000001</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="7">
         <v>-45.568159999999999</v>
       </c>
       <c r="D72" s="4" t="s">
@@ -2405,13 +2436,13 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="7">
         <v>-22.812314000000001</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="7">
         <v>-45.197495000000004</v>
       </c>
       <c r="D73" s="4" t="s">
@@ -2419,13 +2450,13 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="7">
         <v>-23.999110999999999</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="7">
         <v>-46.260528999999998</v>
       </c>
       <c r="D74" s="4" t="s">
@@ -2433,13 +2464,13 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75" s="7">
         <v>-23.521166999999998</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75" s="7">
         <v>-46.700789999999998</v>
       </c>
       <c r="D75" s="4" t="s">
@@ -2447,13 +2478,13 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="7">
         <v>-23.525178</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="7">
         <v>-46.546751999999998</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -2461,13 +2492,13 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77" s="7">
         <v>-23.437859</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="7">
         <v>-46.480556</v>
       </c>
       <c r="D77" s="4" t="s">
@@ -2475,13 +2506,13 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="7">
         <v>-23.627414999999999</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="7">
         <v>-46.655560999999999</v>
       </c>
       <c r="D78" s="4" t="s">
@@ -2489,13 +2520,13 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79" s="7">
         <v>-23.63166</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="7">
         <v>-46.737563000000002</v>
       </c>
       <c r="D79" s="4" t="s">
@@ -2503,13 +2534,13 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="7">
         <v>-23.484327</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80" s="7">
         <v>-46.642066999999997</v>
       </c>
       <c r="D80" s="4" t="s">
@@ -2517,13 +2548,13 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81" s="7">
         <v>-23.584136000000001</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81" s="7">
         <v>-46.725045000000001</v>
       </c>
       <c r="D81" s="4" t="s">
@@ -2531,13 +2562,13 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="7">
         <v>-23.621504000000002</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82" s="7">
         <v>-46.699919000000001</v>
       </c>
       <c r="D82" s="4" t="s">
@@ -2545,13 +2576,13 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83" s="7">
         <v>-23.591676</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83" s="7">
         <v>-46.586267999999997</v>
       </c>
       <c r="D83" s="4" t="s">
@@ -2559,13 +2590,13 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="7">
         <v>-23.52676274205535</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84" s="7">
         <v>-46.619144962589843</v>
       </c>
       <c r="D84" s="4" t="s">
@@ -2573,13 +2604,13 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85" s="7">
         <v>-23.565246992894739</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85" s="7">
         <v>-46.65051887671855</v>
       </c>
       <c r="D85" s="4" t="s">
@@ -2587,13 +2618,13 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="7">
         <v>-23.72301356505324</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86" s="7">
         <v>-46.543113180420171</v>
       </c>
       <c r="D86" s="4" t="s">
@@ -2601,13 +2632,13 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87" s="7">
         <v>-23.54382381180768</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87" s="7">
         <v>-46.638819200492357</v>
       </c>
       <c r="D87" s="4" t="s">
@@ -2615,13 +2646,13 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
+      <c r="A88" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="7">
         <v>-23.555561999999998</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C88" s="7">
         <v>-46.600524999999998</v>
       </c>
       <c r="D88" s="4" t="s">
@@ -2629,13 +2660,13 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89" s="7">
         <v>-23.714396000000001</v>
       </c>
-      <c r="C89" s="4">
+      <c r="C89" s="7">
         <v>-46.549258000000002</v>
       </c>
       <c r="D89" s="4" t="s">
@@ -2643,13 +2674,13 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="7">
         <v>-23.494792</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90" s="7">
         <v>-46.571232999999999</v>
       </c>
       <c r="D90" s="4" t="s">
@@ -2657,13 +2688,13 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91" s="7">
         <v>-23.510097999999999</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C91" s="7">
         <v>-46.366622</v>
       </c>
       <c r="D91" s="4" t="s">
@@ -2671,13 +2702,13 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="7">
         <v>-23.561454000000001</v>
       </c>
-      <c r="C92" s="4">
+      <c r="C92" s="7">
         <v>-46.557878000000002</v>
       </c>
       <c r="D92" s="4" t="s">
@@ -2685,13 +2716,13 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B93" s="4">
+      <c r="B93" s="7">
         <v>-23.513169999999999</v>
       </c>
-      <c r="C93" s="4">
+      <c r="C93" s="7">
         <v>-46.653599</v>
       </c>
       <c r="D93" s="4" t="s">
@@ -2699,13 +2730,13 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="7">
         <v>-23.606002</v>
       </c>
-      <c r="C94" s="4">
+      <c r="C94" s="7">
         <v>-46.668900999999998</v>
       </c>
       <c r="D94" s="4" t="s">
@@ -2713,13 +2744,13 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
+      <c r="A95" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="4">
+      <c r="B95" s="7">
         <v>-23.602588000000001</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95" s="7">
         <v>-46.673183999999999</v>
       </c>
       <c r="D95" s="4" t="s">
@@ -2727,13 +2758,13 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="7">
         <v>-23.562083000000001</v>
       </c>
-      <c r="C96" s="4">
+      <c r="C96" s="7">
         <v>-46.659592000000004</v>
       </c>
       <c r="D96" s="4" t="s">
@@ -2741,13 +2772,13 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
+      <c r="A97" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B97" s="4">
+      <c r="B97" s="7">
         <v>-23.559954000000001</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97" s="7">
         <v>-46.695656</v>
       </c>
       <c r="D97" s="4" t="s">
@@ -2755,13 +2786,13 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="7">
         <v>-23.469597</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98" s="7">
         <v>-46.694237000000001</v>
       </c>
       <c r="D98" s="4" t="s">
@@ -2769,13 +2800,13 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B99" s="4">
+      <c r="B99" s="7">
         <v>-23.500527000000002</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99" s="7">
         <v>-46.625770000000003</v>
       </c>
       <c r="D99" s="4" t="s">
@@ -2783,13 +2814,13 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="7">
         <v>-23.562685999999999</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100" s="7">
         <v>-46.554555999999998</v>
       </c>
       <c r="D100" s="4" t="s">
@@ -2797,13 +2828,13 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="3" t="s">
+      <c r="A101" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B101" s="4">
+      <c r="B101" s="7">
         <v>-23.469698000000001</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101" s="7">
         <v>-46.527177000000002</v>
       </c>
       <c r="D101" s="4" t="s">
@@ -2811,13 +2842,13 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
+      <c r="A102" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="7">
         <v>-23.503102999999999</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102" s="7">
         <v>-46.625295000000001</v>
       </c>
       <c r="D102" s="4" t="s">
@@ -2825,13 +2856,13 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
+      <c r="A103" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103" s="7">
         <v>-23.488278000000001</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103" s="7">
         <v>-46.574466000000001</v>
       </c>
       <c r="D103" s="4" t="s">
@@ -2839,13 +2870,13 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
+      <c r="A104" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="7">
         <v>-23.637298000000001</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104" s="7">
         <v>-46.768484999999998</v>
       </c>
       <c r="D104" s="4" t="s">
@@ -2853,13 +2884,13 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
+      <c r="A105" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105" s="7">
         <v>-23.54588</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105" s="7">
         <v>-46.471882999999998</v>
       </c>
       <c r="D105" s="4" t="s">
@@ -2867,13 +2898,13 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="3" t="s">
+      <c r="A106" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="7">
         <v>-23.54588</v>
       </c>
-      <c r="C106" s="4">
+      <c r="C106" s="7">
         <v>-46.471882999999998</v>
       </c>
       <c r="D106" s="4" t="s">
@@ -2881,13 +2912,13 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
+      <c r="A107" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B107" s="4">
+      <c r="B107" s="7">
         <v>-23.756208999999998</v>
       </c>
-      <c r="C107" s="4">
+      <c r="C107" s="7">
         <v>-46.708300999999999</v>
       </c>
       <c r="D107" s="4" t="s">
@@ -2895,13 +2926,13 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="7">
         <v>-23.550651999999999</v>
       </c>
-      <c r="C108" s="4">
+      <c r="C108" s="7">
         <v>-46.691231000000002</v>
       </c>
       <c r="D108" s="4" t="s">
@@ -2909,13 +2940,13 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="3" t="s">
+      <c r="A109" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B109" s="4">
+      <c r="B109" s="7">
         <v>-23.554106000000001</v>
       </c>
-      <c r="C109" s="4">
+      <c r="C109" s="7">
         <v>-46.649504</v>
       </c>
       <c r="D109" s="4" t="s">
@@ -2923,13 +2954,13 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="3" t="s">
+      <c r="A110" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="7">
         <v>-23.494074000000001</v>
       </c>
-      <c r="C110" s="4">
+      <c r="C110" s="7">
         <v>-46.646492000000002</v>
       </c>
       <c r="D110" s="4" t="s">
@@ -2937,13 +2968,13 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="3" t="s">
+      <c r="A111" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111" s="7">
         <v>-23.984368</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111" s="7">
         <v>-46.301693999999998</v>
       </c>
       <c r="D111" s="4" t="s">
@@ -2951,13 +2982,13 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="3" t="s">
+      <c r="A112" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="7">
         <v>-23.599646</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C112" s="7">
         <v>-46.600575999999997</v>
       </c>
       <c r="D112" s="4" t="s">
@@ -2965,13 +2996,13 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="3" t="s">
+      <c r="A113" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B113" s="4">
+      <c r="B113" s="7">
         <v>-23.605931999999999</v>
       </c>
-      <c r="C113" s="4">
+      <c r="C113" s="7">
         <v>-46.663786999999999</v>
       </c>
       <c r="D113" s="4" t="s">
@@ -2979,13 +3010,13 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="3" t="s">
+      <c r="A114" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="7">
         <v>-23.470124999999999</v>
       </c>
-      <c r="C114" s="4">
+      <c r="C114" s="7">
         <v>-46.529440999999998</v>
       </c>
       <c r="D114" s="4" t="s">
@@ -2993,13 +3024,13 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="3" t="s">
+      <c r="A115" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B115" s="4">
+      <c r="B115" s="7">
         <v>-23.523295999999998</v>
       </c>
-      <c r="C115" s="4">
+      <c r="C115" s="7">
         <v>-46.705745</v>
       </c>
       <c r="D115" s="4" t="s">
@@ -3007,13 +3038,13 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="3" t="s">
+      <c r="A116" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="7">
         <v>-23.622205000000001</v>
       </c>
-      <c r="C116" s="4">
+      <c r="C116" s="7">
         <v>-46.759484999999998</v>
       </c>
       <c r="D116" s="4" t="s">
@@ -3021,13 +3052,13 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="3" t="s">
+      <c r="A117" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117" s="7">
         <v>-23.526185999999999</v>
       </c>
-      <c r="C117" s="4">
+      <c r="C117" s="7">
         <v>-46.549695999999997</v>
       </c>
       <c r="D117" s="4" t="s">
@@ -3035,13 +3066,13 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="3" t="s">
+      <c r="A118" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="7">
         <v>-23.596549</v>
       </c>
-      <c r="C118" s="4">
+      <c r="C118" s="7">
         <v>-46.523448999999999</v>
       </c>
       <c r="D118" s="4" t="s">
@@ -3049,13 +3080,13 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="3" t="s">
+      <c r="A119" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119" s="7">
         <v>-23.406977999999999</v>
       </c>
-      <c r="C119" s="4">
+      <c r="C119" s="7">
         <v>-46.756115000000001</v>
       </c>
       <c r="D119" s="4" t="s">
@@ -3063,13 +3094,13 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="3" t="s">
+      <c r="A120" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="7">
         <v>-23.565166999999999</v>
       </c>
-      <c r="C120" s="4">
+      <c r="C120" s="7">
         <v>-46.666550999999998</v>
       </c>
       <c r="D120" s="4" t="s">
@@ -3077,13 +3108,13 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="3" t="s">
+      <c r="A121" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121" s="7">
         <v>-23.565166999999999</v>
       </c>
-      <c r="C121" s="4">
+      <c r="C121" s="7">
         <v>-46.666550999999998</v>
       </c>
       <c r="D121" s="4" t="s">
@@ -3091,13 +3122,13 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="3" t="s">
+      <c r="A122" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="7">
         <v>-23.503034</v>
       </c>
-      <c r="C122" s="4">
+      <c r="C122" s="7">
         <v>-46.625726</v>
       </c>
       <c r="D122" s="4" t="s">
@@ -3105,13 +3136,13 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="3" t="s">
+      <c r="A123" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123" s="7">
         <v>-23.503034</v>
       </c>
-      <c r="C123" s="4">
+      <c r="C123" s="7">
         <v>-46.625726</v>
       </c>
       <c r="D123" s="4" t="s">
@@ -3119,13 +3150,13 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="3" t="s">
+      <c r="A124" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="7">
         <v>-23.503034</v>
       </c>
-      <c r="C124" s="4">
+      <c r="C124" s="7">
         <v>-46.625726</v>
       </c>
       <c r="D124" s="4" t="s">
@@ -3133,13 +3164,13 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
+      <c r="A125" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125" s="7">
         <v>-23.516596</v>
       </c>
-      <c r="C125" s="4">
+      <c r="C125" s="7">
         <v>-46.624099999999999</v>
       </c>
       <c r="D125" s="4" t="s">
@@ -3147,13 +3178,13 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="3" t="s">
+      <c r="A126" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="7">
         <v>-23.561976999999999</v>
       </c>
-      <c r="C126" s="4">
+      <c r="C126" s="7">
         <v>-46.667828999999998</v>
       </c>
       <c r="D126" s="4" t="s">
@@ -3161,13 +3192,13 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
+      <c r="A127" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B127" s="4">
+      <c r="B127" s="7">
         <v>-23.561976999999999</v>
       </c>
-      <c r="C127" s="4">
+      <c r="C127" s="7">
         <v>-46.667828999999998</v>
       </c>
       <c r="D127" s="4" t="s">
@@ -3175,13 +3206,13 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="3" t="s">
+      <c r="A128" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="7">
         <v>-23.597560000000001</v>
       </c>
-      <c r="C128" s="4">
+      <c r="C128" s="7">
         <v>-46.453480999999996</v>
       </c>
       <c r="D128" s="4" t="s">
@@ -3189,13 +3220,13 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
+      <c r="A129" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B129" s="4">
+      <c r="B129" s="7">
         <v>-23.492291000000002</v>
       </c>
-      <c r="C129" s="4">
+      <c r="C129" s="7">
         <v>-46.442864999999998</v>
       </c>
       <c r="D129" s="4" t="s">
@@ -3203,13 +3234,13 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="3" t="s">
+      <c r="A130" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="7">
         <v>-23.492125999999999</v>
       </c>
-      <c r="C130" s="4">
+      <c r="C130" s="7">
         <v>-46.443055000000001</v>
       </c>
       <c r="D130" s="4" t="s">
@@ -3217,13 +3248,13 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="3" t="s">
+      <c r="A131" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B131" s="4">
+      <c r="B131" s="7">
         <v>-23.491990999999999</v>
       </c>
-      <c r="C131" s="4">
+      <c r="C131" s="7">
         <v>-46.443178000000003</v>
       </c>
       <c r="D131" s="4" t="s">
@@ -3231,13 +3262,13 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
+      <c r="A132" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="7">
         <v>-23.562175</v>
       </c>
-      <c r="C132" s="4">
+      <c r="C132" s="7">
         <v>-46.664454999999997</v>
       </c>
       <c r="D132" s="4" t="s">
@@ -3245,13 +3276,13 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
+      <c r="A133" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133" s="7">
         <v>-23.557445999999999</v>
       </c>
-      <c r="C133" s="4">
+      <c r="C133" s="7">
         <v>-46.659495</v>
       </c>
       <c r="D133" s="4" t="s">
@@ -3259,13 +3290,13 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="3" t="s">
+      <c r="A134" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="7">
         <v>-23.562539999999998</v>
       </c>
-      <c r="C134" s="4">
+      <c r="C134" s="7">
         <v>-46.664945000000003</v>
       </c>
       <c r="D134" s="4" t="s">
@@ -3273,13 +3304,13 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="3" t="s">
+      <c r="A135" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B135" s="4">
+      <c r="B135" s="7">
         <v>-23.544989000000001</v>
       </c>
-      <c r="C135" s="4">
+      <c r="C135" s="7">
         <v>-46.436619</v>
       </c>
       <c r="D135" s="4" t="s">
@@ -3287,13 +3318,13 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="3" t="s">
+      <c r="A136" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="7">
         <v>-23.572396000000001</v>
       </c>
-      <c r="C136" s="4">
+      <c r="C136" s="7">
         <v>-46.643099999999997</v>
       </c>
       <c r="D136" s="4" t="s">
@@ -3301,13 +3332,13 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="3" t="s">
+      <c r="A137" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B137" s="4">
+      <c r="B137" s="7">
         <v>-23.544201999999999</v>
       </c>
-      <c r="C137" s="4">
+      <c r="C137" s="7">
         <v>-46.520671999999998</v>
       </c>
       <c r="D137" s="4" t="s">
@@ -3315,13 +3346,13 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="3" t="s">
+      <c r="A138" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="7">
         <v>-23.545075000000001</v>
       </c>
-      <c r="C138" s="4">
+      <c r="C138" s="7">
         <v>-46.639964999999997</v>
       </c>
       <c r="D138" s="4" t="s">
@@ -3329,13 +3360,13 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="3" t="s">
+      <c r="A139" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B139" s="4">
+      <c r="B139" s="7">
         <v>-23.545041999999999</v>
       </c>
-      <c r="C139" s="4">
+      <c r="C139" s="7">
         <v>-46.640019000000002</v>
       </c>
       <c r="D139" s="4" t="s">
@@ -3343,13 +3374,13 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
+      <c r="A140" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140" s="7">
         <v>-23.558700000000002</v>
       </c>
-      <c r="C140" s="4">
+      <c r="C140" s="7">
         <v>-46.680200999999997</v>
       </c>
       <c r="D140" s="4" t="s">
@@ -3357,13 +3388,13 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="3" t="s">
+      <c r="A141" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B141" s="4">
+      <c r="B141" s="7">
         <v>-23.655239999999999</v>
       </c>
-      <c r="C141" s="4">
+      <c r="C141" s="7">
         <v>-46.528075000000001</v>
       </c>
       <c r="D141" s="4" t="s">
@@ -3371,13 +3402,13 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="3" t="s">
+      <c r="A142" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142" s="7">
         <v>-23.661394000000001</v>
       </c>
-      <c r="C142" s="4">
+      <c r="C142" s="7">
         <v>-46.753459999999997</v>
       </c>
       <c r="D142" s="4" t="s">
@@ -3385,13 +3416,13 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="3" t="s">
+      <c r="A143" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B143" s="4">
+      <c r="B143" s="7">
         <v>-23.661394000000001</v>
       </c>
-      <c r="C143" s="4">
+      <c r="C143" s="7">
         <v>-46.753459999999997</v>
       </c>
       <c r="D143" s="4" t="s">
@@ -3399,13 +3430,13 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="3" t="s">
+      <c r="A144" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144" s="7">
         <v>-23.468406000000002</v>
       </c>
-      <c r="C144" s="4">
+      <c r="C144" s="7">
         <v>-46.530954999999999</v>
       </c>
       <c r="D144" s="4" t="s">
@@ -3413,13 +3444,13 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="3" t="s">
+      <c r="A145" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B145" s="4">
+      <c r="B145" s="7">
         <v>-23.475971999999999</v>
       </c>
-      <c r="C145" s="4">
+      <c r="C145" s="7">
         <v>-46.352730000000001</v>
       </c>
       <c r="D145" s="4" t="s">
@@ -3427,13 +3458,13 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="3" t="s">
+      <c r="A146" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="7">
         <v>-23.475971999999999</v>
       </c>
-      <c r="C146" s="4">
+      <c r="C146" s="7">
         <v>-46.352730000000001</v>
       </c>
       <c r="D146" s="4" t="s">
@@ -3441,13 +3472,13 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
+      <c r="A147" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B147" s="7">
         <v>-23.741067999999999</v>
       </c>
-      <c r="C147" s="4">
+      <c r="C147" s="7">
         <v>-46.707394999999998</v>
       </c>
       <c r="D147" s="4" t="s">
@@ -3455,13 +3486,13 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="3" t="s">
+      <c r="A148" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148" s="7">
         <v>-23.741067999999999</v>
       </c>
-      <c r="C148" s="4">
+      <c r="C148" s="7">
         <v>-46.707394999999998</v>
       </c>
       <c r="D148" s="4" t="s">
@@ -3469,13 +3500,13 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
+      <c r="A149" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B149" s="4">
+      <c r="B149" s="7">
         <v>-23.521871000000001</v>
       </c>
-      <c r="C149" s="4">
+      <c r="C149" s="7">
         <v>-46.194389999999999</v>
       </c>
       <c r="D149" s="4" t="s">
@@ -3483,13 +3514,13 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="3" t="s">
+      <c r="A150" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="7">
         <v>-23.458227999999998</v>
       </c>
-      <c r="C150" s="4">
+      <c r="C150" s="7">
         <v>-46.602440999999999</v>
       </c>
       <c r="D150" s="4" t="s">
@@ -3497,13 +3528,13 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
+      <c r="A151" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B151" s="4">
+      <c r="B151" s="7">
         <v>-23.539591000000001</v>
       </c>
-      <c r="C151" s="4">
+      <c r="C151" s="7">
         <v>-46.609389999999998</v>
       </c>
       <c r="D151" s="4" t="s">
@@ -3511,13 +3542,13 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="3" t="s">
+      <c r="A152" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="7">
         <v>-23.529101000000001</v>
       </c>
-      <c r="C152" s="4">
+      <c r="C152" s="7">
         <v>-46.643954000000001</v>
       </c>
       <c r="D152" s="4" t="s">
@@ -3525,13 +3556,13 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" s="3" t="s">
+      <c r="A153" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153" s="7">
         <v>-23.529852999999999</v>
       </c>
-      <c r="C153" s="4">
+      <c r="C153" s="7">
         <v>-46.643543999999999</v>
       </c>
       <c r="D153" s="4" t="s">
@@ -3539,13 +3570,13 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" s="3" t="s">
+      <c r="A154" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="7">
         <v>-23.693193000000001</v>
       </c>
-      <c r="C154" s="4">
+      <c r="C154" s="7">
         <v>-46.595128000000003</v>
       </c>
       <c r="D154" s="4" t="s">
@@ -3553,13 +3584,13 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="3" t="s">
+      <c r="A155" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B155" s="4">
+      <c r="B155" s="7">
         <v>-23.552043000000001</v>
       </c>
-      <c r="C155" s="4">
+      <c r="C155" s="7">
         <v>-46.529882000000001</v>
       </c>
       <c r="D155" s="4" t="s">
@@ -3567,13 +3598,13 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" s="3" t="s">
+      <c r="A156" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156" s="7">
         <v>-23.65457</v>
       </c>
-      <c r="C156" s="4">
+      <c r="C156" s="7">
         <v>-46.526654999999998</v>
       </c>
       <c r="D156" s="4" t="s">
@@ -3581,13 +3612,13 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="3" t="s">
+      <c r="A157" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B157" s="4">
+      <c r="B157" s="7">
         <v>-23.655583</v>
       </c>
-      <c r="C157" s="4">
+      <c r="C157" s="7">
         <v>-46.527033000000003</v>
       </c>
       <c r="D157" s="4" t="s">
@@ -3595,13 +3626,13 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A158" s="3" t="s">
+      <c r="A158" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158" s="7">
         <v>-23.459781</v>
       </c>
-      <c r="C158" s="4">
+      <c r="C158" s="7">
         <v>-46.602575999999999</v>
       </c>
       <c r="D158" s="4" t="s">
@@ -3609,13 +3640,13 @@
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A159" s="3" t="s">
+      <c r="A159" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B159" s="4">
+      <c r="B159" s="7">
         <v>-23.494917000000001</v>
       </c>
-      <c r="C159" s="4">
+      <c r="C159" s="7">
         <v>-46.401294</v>
       </c>
       <c r="D159" s="4" t="s">
@@ -3623,13 +3654,13 @@
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A160" s="3" t="s">
+      <c r="A160" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="7">
         <v>-23.470124999999999</v>
       </c>
-      <c r="C160" s="4">
+      <c r="C160" s="7">
         <v>-46.529440999999998</v>
       </c>
       <c r="D160" s="4" t="s">
@@ -3637,13 +3668,13 @@
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="3" t="s">
+      <c r="A161" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B161" s="4">
+      <c r="B161" s="7">
         <v>-23.470124999999999</v>
       </c>
-      <c r="C161" s="4">
+      <c r="C161" s="7">
         <v>-46.529440999999998</v>
       </c>
       <c r="D161" s="4" t="s">
@@ -3651,13 +3682,13 @@
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
+      <c r="A162" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162" s="7">
         <v>-23.435561</v>
       </c>
-      <c r="C162" s="4">
+      <c r="C162" s="7">
         <v>-46.728448999999998</v>
       </c>
       <c r="D162" s="4" t="s">
@@ -3665,13 +3696,13 @@
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A163" s="3" t="s">
+      <c r="A163" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B163" s="4">
+      <c r="B163" s="7">
         <v>-23.469306</v>
       </c>
-      <c r="C163" s="4">
+      <c r="C163" s="7">
         <v>-46.677028</v>
       </c>
       <c r="D163" s="4" t="s">
@@ -3679,13 +3710,13 @@
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="3" t="s">
+      <c r="A164" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164" s="7">
         <v>-23.469306</v>
       </c>
-      <c r="C164" s="4">
+      <c r="C164" s="7">
         <v>-46.677028</v>
       </c>
       <c r="D164" s="4" t="s">
@@ -3693,13 +3724,13 @@
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="3" t="s">
+      <c r="A165" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B165" s="4">
+      <c r="B165" s="7">
         <v>-23.548327</v>
       </c>
-      <c r="C165" s="4">
+      <c r="C165" s="7">
         <v>-46.635429000000002</v>
       </c>
       <c r="D165" s="4" t="s">
@@ -3707,13 +3738,13 @@
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="3" t="s">
+      <c r="A166" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166" s="7">
         <v>-23.519480000000001</v>
       </c>
-      <c r="C166" s="4">
+      <c r="C166" s="7">
         <v>-46.695329000000001</v>
       </c>
       <c r="D166" s="4" t="s">
@@ -3721,13 +3752,13 @@
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A167" s="3" t="s">
+      <c r="A167" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B167" s="4">
+      <c r="B167" s="7">
         <v>-23.518322999999999</v>
       </c>
-      <c r="C167" s="4">
+      <c r="C167" s="7">
         <v>-46.695678999999998</v>
       </c>
       <c r="D167" s="4" t="s">
@@ -3735,13 +3766,13 @@
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="3" t="s">
+      <c r="A168" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="7">
         <v>-23.519119</v>
       </c>
-      <c r="C168" s="4">
+      <c r="C168" s="7">
         <v>-46.695405999999998</v>
       </c>
       <c r="D168" s="4" t="s">
@@ -3749,13 +3780,13 @@
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A169" s="3" t="s">
+      <c r="A169" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B169" s="4">
+      <c r="B169" s="7">
         <v>-23.53669</v>
       </c>
-      <c r="C169" s="4">
+      <c r="C169" s="7">
         <v>-46.404201</v>
       </c>
       <c r="D169" s="4" t="s">
@@ -3763,13 +3794,13 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="3" t="s">
+      <c r="A170" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170" s="7">
         <v>-23.470124999999999</v>
       </c>
-      <c r="C170" s="4">
+      <c r="C170" s="7">
         <v>-46.529440999999998</v>
       </c>
       <c r="D170" s="4" t="s">
@@ -3777,13 +3808,13 @@
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="3" t="s">
+      <c r="A171" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B171" s="4">
+      <c r="B171" s="7">
         <v>-23.470099999999999</v>
       </c>
-      <c r="C171" s="4">
+      <c r="C171" s="7">
         <v>-46.529328999999997</v>
       </c>
       <c r="D171" s="4" t="s">
@@ -3791,13 +3822,13 @@
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="3" t="s">
+      <c r="A172" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172" s="7">
         <v>-23.736751000000002</v>
       </c>
-      <c r="C172" s="4">
+      <c r="C172" s="7">
         <v>-46.693855999999997</v>
       </c>
       <c r="D172" s="4" t="s">
@@ -3805,13 +3836,13 @@
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="3" t="s">
+      <c r="A173" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B173" s="4">
+      <c r="B173" s="7">
         <v>-23.755013999999999</v>
       </c>
-      <c r="C173" s="4">
+      <c r="C173" s="7">
         <v>-46.675722</v>
       </c>
       <c r="D173" s="4" t="s">
@@ -3819,13 +3850,13 @@
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="3" t="s">
+      <c r="A174" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174" s="7">
         <v>-23.522544</v>
       </c>
-      <c r="C174" s="4">
+      <c r="C174" s="7">
         <v>-46.644922000000001</v>
       </c>
       <c r="D174" s="4" t="s">
@@ -3833,13 +3864,13 @@
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" s="3" t="s">
+      <c r="A175" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B175" s="4">
+      <c r="B175" s="7">
         <v>-23.526613000000001</v>
       </c>
-      <c r="C175" s="4">
+      <c r="C175" s="7">
         <v>-46.193955000000003</v>
       </c>
       <c r="D175" s="4" t="s">
@@ -3847,13 +3878,13 @@
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="3" t="s">
+      <c r="A176" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B176" s="4">
+      <c r="B176" s="7">
         <v>-23.499783000000001</v>
       </c>
-      <c r="C176" s="4">
+      <c r="C176" s="7">
         <v>-46.625141999999997</v>
       </c>
       <c r="D176" s="4" t="s">
@@ -3861,13 +3892,13 @@
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="3" t="s">
+      <c r="A177" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B177" s="4">
+      <c r="B177" s="7">
         <v>-23.733097000000001</v>
       </c>
-      <c r="C177" s="4">
+      <c r="C177" s="7">
         <v>-46.693812999999999</v>
       </c>
       <c r="D177" s="4" t="s">
@@ -3875,13 +3906,13 @@
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" s="3" t="s">
+      <c r="A178" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B178" s="4">
+      <c r="B178" s="7">
         <v>-22.733649</v>
       </c>
-      <c r="C178" s="4">
+      <c r="C178" s="7">
         <v>-45.119166999999997</v>
       </c>
       <c r="D178" s="4" t="s">
@@ -3889,13 +3920,13 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" s="3" t="s">
+      <c r="A179" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B179" s="4">
+      <c r="B179" s="7">
         <v>-23.519703</v>
       </c>
-      <c r="C179" s="4">
+      <c r="C179" s="7">
         <v>-46.704081000000002</v>
       </c>
       <c r="D179" s="4" t="s">
@@ -3903,13 +3934,13 @@
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A180" s="3" t="s">
+      <c r="A180" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B180" s="4">
+      <c r="B180" s="7">
         <v>-23.520734999999998</v>
       </c>
-      <c r="C180" s="4">
+      <c r="C180" s="7">
         <v>-46.704563</v>
       </c>
       <c r="D180" s="4" t="s">
@@ -3917,13 +3948,13 @@
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A181" s="3" t="s">
+      <c r="A181" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B181" s="4">
+      <c r="B181" s="7">
         <v>-23.520002999999999</v>
       </c>
-      <c r="C181" s="4">
+      <c r="C181" s="7">
         <v>-46.703935999999999</v>
       </c>
       <c r="D181" s="4" t="s">
@@ -3931,13 +3962,13 @@
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A182" s="3" t="s">
+      <c r="A182" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B182" s="4">
+      <c r="B182" s="7">
         <v>-23.520631999999999</v>
       </c>
-      <c r="C182" s="4">
+      <c r="C182" s="7">
         <v>-46.704483000000003</v>
       </c>
       <c r="D182" s="4" t="s">
@@ -3945,13 +3976,13 @@
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A183" s="3" t="s">
+      <c r="A183" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B183" s="4">
+      <c r="B183" s="7">
         <v>-23.521661999999999</v>
       </c>
-      <c r="C183" s="4">
+      <c r="C183" s="7">
         <v>-46.704793000000002</v>
       </c>
       <c r="D183" s="4" t="s">
@@ -3959,13 +3990,13 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="3" t="s">
+      <c r="A184" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B184" s="4">
+      <c r="B184" s="7">
         <v>-23.521661999999999</v>
       </c>
-      <c r="C184" s="4">
+      <c r="C184" s="7">
         <v>-46.704793000000002</v>
       </c>
       <c r="D184" s="4" t="s">
@@ -3973,13 +4004,13 @@
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="3" t="s">
+      <c r="A185" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B185" s="4">
+      <c r="B185" s="7">
         <v>-23.503533999999998</v>
       </c>
-      <c r="C185" s="4">
+      <c r="C185" s="7">
         <v>-46.672266</v>
       </c>
       <c r="D185" s="4" t="s">
@@ -3987,13 +4018,13 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="3" t="s">
+      <c r="A186" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B186" s="4">
+      <c r="B186" s="7">
         <v>-23.406860000000002</v>
       </c>
-      <c r="C186" s="4">
+      <c r="C186" s="7">
         <v>-46.756663000000003</v>
       </c>
       <c r="D186" s="4" t="s">
@@ -4001,13 +4032,13 @@
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="3" t="s">
+      <c r="A187" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B187" s="4">
+      <c r="B187" s="7">
         <v>-23.609956</v>
       </c>
-      <c r="C187" s="4">
+      <c r="C187" s="7">
         <v>-46.476108000000004</v>
       </c>
       <c r="D187" s="4" t="s">
@@ -4015,13 +4046,13 @@
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A188" s="3" t="s">
+      <c r="A188" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B188" s="4">
+      <c r="B188" s="7">
         <v>-23.660606701714588</v>
       </c>
-      <c r="C188" s="4">
+      <c r="C188" s="7">
         <v>-46.767486152162142</v>
       </c>
       <c r="D188" s="4" t="s">
@@ -4029,13 +4060,13 @@
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A189" s="3" t="s">
+      <c r="A189" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B189" s="4">
+      <c r="B189" s="7">
         <v>-23.539924978956019</v>
       </c>
-      <c r="C189" s="4">
+      <c r="C189" s="7">
         <v>-46.310160546576952</v>
       </c>
       <c r="D189" s="4" t="s">
@@ -4043,13 +4074,13 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A190" s="3" t="s">
+      <c r="A190" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B190" s="4">
+      <c r="B190" s="7">
         <v>-23.53731758262683</v>
       </c>
-      <c r="C190" s="4">
+      <c r="C190" s="7">
         <v>-46.309459746577119</v>
       </c>
       <c r="D190" s="4" t="s">
@@ -4057,13 +4088,13 @@
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A191" s="3" t="s">
+      <c r="A191" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B191" s="4">
+      <c r="B191" s="7">
         <v>-23.64675304792809</v>
       </c>
-      <c r="C191" s="4">
+      <c r="C191" s="7">
         <v>-46.729094359128602</v>
       </c>
       <c r="D191" s="4" t="s">
@@ -4071,13 +4102,13 @@
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A192" s="3" t="s">
+      <c r="A192" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B192" s="4">
+      <c r="B192" s="7">
         <v>-23.484664151834739</v>
       </c>
-      <c r="C192" s="4">
+      <c r="C192" s="7">
         <v>-46.69159361149547</v>
       </c>
       <c r="D192" s="4" t="s">
@@ -4085,13 +4116,13 @@
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A193" s="3" t="s">
+      <c r="A193" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B193" s="4">
+      <c r="B193" s="7">
         <v>-23.47372985842701</v>
       </c>
-      <c r="C193" s="4">
+      <c r="C193" s="7">
         <v>-46.668424555663513</v>
       </c>
       <c r="D193" s="4" t="s">
@@ -4099,13 +4130,13 @@
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A194" s="3" t="s">
+      <c r="A194" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B194" s="4">
+      <c r="B194" s="7">
         <v>-23.605656809354851</v>
       </c>
-      <c r="C194" s="4">
+      <c r="C194" s="7">
         <v>-46.663669343975343</v>
       </c>
       <c r="D194" s="4" t="s">
@@ -4113,13 +4144,13 @@
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A195" s="3" t="s">
+      <c r="A195" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B195" s="4">
+      <c r="B195" s="7">
         <v>-23.658374695817731</v>
       </c>
-      <c r="C195" s="4">
+      <c r="C195" s="7">
         <v>-46.705814192197657</v>
       </c>
       <c r="D195" s="4" t="s">
@@ -4127,13 +4158,13 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" s="3" t="s">
+      <c r="A196" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B196" s="4">
+      <c r="B196" s="7">
         <v>-23.658374695817731</v>
       </c>
-      <c r="C196" s="4">
+      <c r="C196" s="7">
         <v>-46.705814192197657</v>
       </c>
       <c r="D196" s="4" t="s">
@@ -4141,13 +4172,13 @@
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A197" s="3" t="s">
+      <c r="A197" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B197" s="4">
+      <c r="B197" s="7">
         <v>-23.652234458640169</v>
       </c>
-      <c r="C197" s="4">
+      <c r="C197" s="7">
         <v>-46.705969282649349</v>
       </c>
       <c r="D197" s="4" t="s">
@@ -4155,13 +4186,13 @@
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A198" s="3" t="s">
+      <c r="A198" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B198" s="4">
+      <c r="B198" s="7">
         <v>-23.540313917903632</v>
       </c>
-      <c r="C198" s="4">
+      <c r="C198" s="7">
         <v>-46.49159496668279</v>
       </c>
       <c r="D198" s="4" t="s">
@@ -4169,13 +4200,13 @@
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A199" s="3" t="s">
+      <c r="A199" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B199" s="4">
+      <c r="B199" s="7">
         <v>-23.540313917903632</v>
       </c>
-      <c r="C199" s="4">
+      <c r="C199" s="7">
         <v>-46.49159496668279</v>
       </c>
       <c r="D199" s="4" t="s">
@@ -4183,13 +4214,13 @@
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A200" s="3" t="s">
+      <c r="A200" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B200" s="4">
+      <c r="B200" s="7">
         <v>-23.492096178032551</v>
       </c>
-      <c r="C200" s="4">
+      <c r="C200" s="7">
         <v>-46.444885575461022</v>
       </c>
       <c r="D200" s="4" t="s">
@@ -4197,13 +4228,13 @@
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A201" s="3" t="s">
+      <c r="A201" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B201" s="4">
+      <c r="B201" s="7">
         <v>-23.609300894812812</v>
       </c>
-      <c r="C201" s="4">
+      <c r="C201" s="7">
         <v>-46.453317422745023</v>
       </c>
       <c r="D201" s="4" t="s">
@@ -4211,13 +4242,13 @@
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A202" s="3" t="s">
+      <c r="A202" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B202" s="4">
+      <c r="B202" s="7">
         <v>-23.708358096732361</v>
       </c>
-      <c r="C202" s="4">
+      <c r="C202" s="7">
         <v>-46.551051577452697</v>
       </c>
       <c r="D202" s="4" t="s">
@@ -4225,13 +4256,13 @@
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A203" s="3" t="s">
+      <c r="A203" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B203" s="4">
+      <c r="B203" s="7">
         <v>-23.708738588809439</v>
       </c>
-      <c r="C203" s="4">
+      <c r="C203" s="7">
         <v>-46.550794104243572</v>
       </c>
       <c r="D203" s="4" t="s">
@@ -4239,13 +4270,13 @@
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A204" s="3" t="s">
+      <c r="A204" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B204" s="4">
+      <c r="B204" s="7">
         <v>-23.70957889440616</v>
       </c>
-      <c r="C204" s="4">
+      <c r="C204" s="7">
         <v>-46.550877495148093</v>
       </c>
       <c r="D204" s="4" t="s">
@@ -4253,13 +4284,13 @@
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A205" s="3" t="s">
+      <c r="A205" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B205" s="4">
+      <c r="B205" s="7">
         <v>-23.710389561010238</v>
       </c>
-      <c r="C205" s="4">
+      <c r="C205" s="7">
         <v>-46.550815133079382</v>
       </c>
       <c r="D205" s="4" t="s">
@@ -4267,13 +4298,13 @@
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A206" s="3" t="s">
+      <c r="A206" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B206" s="4">
+      <c r="B206" s="7">
         <v>-23.496737584590239</v>
       </c>
-      <c r="C206" s="4">
+      <c r="C206" s="7">
         <v>-46.401155342390901</v>
       </c>
       <c r="D206" s="4" t="s">
@@ -4281,13 +4312,13 @@
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A207" s="3" t="s">
+      <c r="A207" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B207" s="4">
+      <c r="B207" s="7">
         <v>-23.496737584590239</v>
       </c>
-      <c r="C207" s="4">
+      <c r="C207" s="7">
         <v>-46.401155342390901</v>
       </c>
       <c r="D207" s="4" t="s">
@@ -4295,13 +4326,13 @@
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A208" s="3" t="s">
+      <c r="A208" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B208" s="4">
+      <c r="B208" s="7">
         <v>-23.539047183534741</v>
       </c>
-      <c r="C208" s="4">
+      <c r="C208" s="7">
         <v>-46.616023382911479</v>
       </c>
       <c r="D208" s="4" t="s">
@@ -4309,13 +4340,13 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" s="3" t="s">
+      <c r="A209" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B209" s="4">
+      <c r="B209" s="7">
         <v>-23.536874385810339</v>
       </c>
-      <c r="C209" s="4">
+      <c r="C209" s="7">
         <v>-46.616492087847853</v>
       </c>
       <c r="D209" s="4" t="s">
@@ -4323,13 +4354,13 @@
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A210" s="3" t="s">
+      <c r="A210" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B210" s="4">
+      <c r="B210" s="7">
         <v>-23.518669906765421</v>
       </c>
-      <c r="C210" s="4">
+      <c r="C210" s="7">
         <v>-46.675228110365637</v>
       </c>
       <c r="D210" s="4" t="s">
@@ -4337,13 +4368,13 @@
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A211" s="3" t="s">
+      <c r="A211" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B211" s="4">
+      <c r="B211" s="7">
         <v>-23.965608472200159</v>
       </c>
-      <c r="C211" s="4">
+      <c r="C211" s="7">
         <v>-46.385128858267322</v>
       </c>
       <c r="D211" s="4" t="s">
@@ -4351,13 +4382,13 @@
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A212" s="3" t="s">
+      <c r="A212" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B212" s="4">
+      <c r="B212" s="7">
         <v>-23.96553812194453</v>
       </c>
-      <c r="C212" s="4">
+      <c r="C212" s="7">
         <v>-46.384590128552361</v>
       </c>
       <c r="D212" s="4" t="s">
@@ -4365,13 +4396,13 @@
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A213" s="3" t="s">
+      <c r="A213" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B213" s="4">
+      <c r="B213" s="7">
         <v>-23.5989110180399</v>
       </c>
-      <c r="C213" s="4">
+      <c r="C213" s="7">
         <v>-46.4855585030813</v>
       </c>
       <c r="D213" s="4" t="s">
@@ -4379,13 +4410,13 @@
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A214" s="3" t="s">
+      <c r="A214" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B214" s="4">
+      <c r="B214" s="7">
         <v>-23.60233116159338</v>
       </c>
-      <c r="C214" s="4">
+      <c r="C214" s="7">
         <v>-46.482378222899449</v>
       </c>
       <c r="D214" s="4" t="s">
@@ -4393,13 +4424,13 @@
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A215" s="3" t="s">
+      <c r="A215" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B215" s="4">
+      <c r="B215" s="7">
         <v>-23.610841826422771</v>
       </c>
-      <c r="C215" s="4">
+      <c r="C215" s="7">
         <v>-46.475993473559093</v>
       </c>
       <c r="D215" s="4" t="s">
@@ -4407,13 +4438,13 @@
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A216" s="3" t="s">
+      <c r="A216" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B216" s="4">
+      <c r="B216" s="7">
         <v>-23.564547605983439</v>
       </c>
-      <c r="C216" s="4">
+      <c r="C216" s="7">
         <v>-46.683848837533823</v>
       </c>
       <c r="D216" s="4" t="s">
@@ -4421,13 +4452,13 @@
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A217" s="3" t="s">
+      <c r="A217" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B217" s="4">
+      <c r="B217" s="7">
         <v>-23.494308645089401</v>
       </c>
-      <c r="C217" s="4">
+      <c r="C217" s="7">
         <v>-46.438042465316279</v>
       </c>
       <c r="D217" s="4" t="s">
@@ -4435,13 +4466,13 @@
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A218" s="3" t="s">
+      <c r="A218" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B218" s="4">
+      <c r="B218" s="7">
         <v>-23.49049476602092</v>
       </c>
-      <c r="C218" s="4">
+      <c r="C218" s="7">
         <v>-46.574311906102317</v>
       </c>
       <c r="D218" s="4" t="s">
@@ -4449,13 +4480,13 @@
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A219" s="3" t="s">
+      <c r="A219" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B219" s="4">
+      <c r="B219" s="7">
         <v>-23.540611852108881</v>
       </c>
-      <c r="C219" s="4">
+      <c r="C219" s="7">
         <v>-46.615877046576891</v>
       </c>
       <c r="D219" s="4" t="s">
@@ -4463,13 +4494,13 @@
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A220" s="3" t="s">
+      <c r="A220" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B220" s="4">
+      <c r="B220" s="7">
         <v>-23.54104567003424</v>
       </c>
-      <c r="C220" s="4">
+      <c r="C220" s="7">
         <v>-46.616292986317468</v>
       </c>
       <c r="D220" s="4" t="s">
@@ -4477,13 +4508,13 @@
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A221" s="3" t="s">
+      <c r="A221" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B221" s="4">
+      <c r="B221" s="7">
         <v>-23.54104567003424</v>
       </c>
-      <c r="C221" s="4">
+      <c r="C221" s="7">
         <v>-46.616292986317468</v>
       </c>
       <c r="D221" s="4" t="s">
@@ -4491,13 +4522,13 @@
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A222" s="3" t="s">
+      <c r="A222" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B222" s="4">
+      <c r="B222" s="7">
         <v>-23.711593162640639</v>
       </c>
-      <c r="C222" s="4">
+      <c r="C222" s="7">
         <v>-46.549321304243463</v>
       </c>
       <c r="D222" s="4" t="s">
@@ -4505,13 +4536,13 @@
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A223" s="3" t="s">
+      <c r="A223" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B223" s="4">
+      <c r="B223" s="7">
         <v>-23.59158793865717</v>
       </c>
-      <c r="C223" s="4">
+      <c r="C223" s="7">
         <v>-46.549625792837169</v>
       </c>
       <c r="D223" s="4" t="s">
@@ -4519,13 +4550,13 @@
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A224" s="3" t="s">
+      <c r="A224" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B224" s="4">
+      <c r="B224" s="7">
         <v>-23.602453784707158</v>
       </c>
-      <c r="C224" s="4">
+      <c r="C224" s="7">
         <v>-46.527617916976602</v>
       </c>
       <c r="D224" s="4" t="s">
@@ -4533,13 +4564,13 @@
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A225" s="3" t="s">
+      <c r="A225" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B225" s="4">
+      <c r="B225" s="7">
         <v>-23.564888203022939</v>
       </c>
-      <c r="C225" s="4">
+      <c r="C225" s="7">
         <v>-46.666451814809101</v>
       </c>
       <c r="D225" s="4" t="s">
@@ -4547,13 +4578,13 @@
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A226" s="3" t="s">
+      <c r="A226" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B226" s="4">
+      <c r="B226" s="7">
         <v>-23.562636970172001</v>
       </c>
-      <c r="C226" s="4">
+      <c r="C226" s="7">
         <v>-46.669587112092309</v>
       </c>
       <c r="D226" s="4" t="s">
@@ -4561,13 +4592,13 @@
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A227" s="3" t="s">
+      <c r="A227" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B227" s="4">
+      <c r="B227" s="7">
         <v>-23.562611189434861</v>
       </c>
-      <c r="C227" s="4">
+      <c r="C227" s="7">
         <v>-46.669594737380343</v>
       </c>
       <c r="D227" s="4" t="s">
@@ -4575,13 +4606,13 @@
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A228" s="3" t="s">
+      <c r="A228" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B228" s="4">
+      <c r="B228" s="7">
         <v>-23.562611189434861</v>
       </c>
-      <c r="C228" s="4">
+      <c r="C228" s="7">
         <v>-46.669594737380343</v>
       </c>
       <c r="D228" s="4" t="s">
@@ -4589,13 +4620,13 @@
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A229" s="3" t="s">
+      <c r="A229" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B229" s="4">
+      <c r="B229" s="7">
         <v>-23.96457981552652</v>
       </c>
-      <c r="C229" s="4">
+      <c r="C229" s="7">
         <v>-46.320583949793509</v>
       </c>
       <c r="D229" s="4" t="s">
@@ -4603,13 +4634,13 @@
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A230" s="3" t="s">
+      <c r="A230" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B230" s="4">
+      <c r="B230" s="7">
         <v>-23.5355715373036</v>
       </c>
-      <c r="C230" s="4">
+      <c r="C230" s="7">
         <v>-46.45559408977995</v>
       </c>
       <c r="D230" s="4" t="s">
@@ -4617,13 +4648,13 @@
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A231" s="3" t="s">
+      <c r="A231" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B231" s="4">
+      <c r="B231" s="7">
         <v>-23.527800819410349</v>
       </c>
-      <c r="C231" s="4">
+      <c r="C231" s="7">
         <v>-46.680122361921399</v>
       </c>
       <c r="D231" s="4" t="s">
@@ -4631,13 +4662,13 @@
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A232" s="3" t="s">
+      <c r="A232" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B232" s="4">
+      <c r="B232" s="7">
         <v>-23.528044367380261</v>
       </c>
-      <c r="C232" s="4">
+      <c r="C232" s="7">
         <v>-46.679590961921342</v>
       </c>
       <c r="D232" s="4" t="s">
@@ -4645,13 +4676,13 @@
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A233" s="3" t="s">
+      <c r="A233" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B233" s="4">
+      <c r="B233" s="7">
         <v>-23.527619560392001</v>
       </c>
-      <c r="C233" s="4">
+      <c r="C233" s="7">
         <v>-46.680234726725033</v>
       </c>
       <c r="D233" s="4" t="s">
@@ -4659,13 +4690,13 @@
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A234" s="3" t="s">
+      <c r="A234" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B234" s="4">
+      <c r="B234" s="7">
         <v>-23.527619560392001</v>
       </c>
-      <c r="C234" s="4">
+      <c r="C234" s="7">
         <v>-46.680234726725033</v>
       </c>
       <c r="D234" s="4" t="s">
@@ -4673,13 +4704,13 @@
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A235" s="3" t="s">
+      <c r="A235" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B235" s="4">
+      <c r="B235" s="7">
         <v>-23.47373735651383</v>
       </c>
-      <c r="C235" s="4">
+      <c r="C235" s="7">
         <v>-46.667459435988349</v>
       </c>
       <c r="D235" s="4" t="s">
@@ -4687,13 +4718,13 @@
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A236" s="3" t="s">
+      <c r="A236" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B236" s="4">
+      <c r="B236" s="7">
         <v>-23.472389208725719</v>
       </c>
-      <c r="C236" s="4">
+      <c r="C236" s="7">
         <v>-46.667181399824678</v>
       </c>
       <c r="D236" s="4" t="s">
@@ -4701,13 +4732,13 @@
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A237" s="3" t="s">
+      <c r="A237" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B237" s="4">
+      <c r="B237" s="7">
         <v>-23.47208363443902</v>
       </c>
-      <c r="C237" s="4">
+      <c r="C237" s="7">
         <v>-46.667051634938751</v>
       </c>
       <c r="D237" s="4" t="s">
@@ -4715,13 +4746,13 @@
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A238" s="3" t="s">
+      <c r="A238" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B238" s="4">
+      <c r="B238" s="7">
         <v>-23.490954847877688</v>
       </c>
-      <c r="C238" s="4">
+      <c r="C238" s="7">
         <v>-46.479214775414583</v>
       </c>
       <c r="D238" s="4" t="s">
@@ -4729,13 +4760,13 @@
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A239" s="3" t="s">
+      <c r="A239" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B239" s="4">
+      <c r="B239" s="7">
         <v>-23.534000573322189</v>
       </c>
-      <c r="C239" s="4">
+      <c r="C239" s="7">
         <v>-46.725843561752399</v>
       </c>
       <c r="D239" s="4" t="s">
@@ -4743,13 +4774,13 @@
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A240" s="3" t="s">
+      <c r="A240" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B240" s="4">
+      <c r="B240" s="7">
         <v>-23.522797692360928</v>
       </c>
-      <c r="C240" s="4">
+      <c r="C240" s="7">
         <v>-46.547501501665273</v>
       </c>
       <c r="D240" s="4" t="s">
@@ -4757,13 +4788,13 @@
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A241" s="3" t="s">
+      <c r="A241" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B241" s="4">
+      <c r="B241" s="7">
         <v>-23.462972452699638</v>
       </c>
-      <c r="C241" s="4">
+      <c r="C241" s="7">
         <v>-46.652803158827403</v>
       </c>
       <c r="D241" s="4" t="s">
@@ -4771,13 +4802,13 @@
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A242" s="3" t="s">
+      <c r="A242" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B242" s="4">
+      <c r="B242" s="7">
         <v>-23.528820458206329</v>
       </c>
-      <c r="C242" s="4">
+      <c r="C242" s="7">
         <v>-46.635663517741499</v>
       </c>
       <c r="D242" s="4" t="s">
@@ -4785,13 +4816,13 @@
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A243" s="3" t="s">
+      <c r="A243" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B243" s="4">
+      <c r="B243" s="7">
         <v>-23.950918851650581</v>
       </c>
-      <c r="C243" s="4">
+      <c r="C243" s="7">
         <v>-46.339795718900803</v>
       </c>
       <c r="D243" s="4" t="s">
@@ -4799,13 +4830,13 @@
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A244" s="3" t="s">
+      <c r="A244" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B244" s="4">
+      <c r="B244" s="7">
         <v>-23.497044917382269</v>
       </c>
-      <c r="C244" s="4">
+      <c r="C244" s="7">
         <v>-46.401397576608453</v>
       </c>
       <c r="D244" s="4" t="s">
@@ -4813,13 +4844,13 @@
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A245" s="3" t="s">
+      <c r="A245" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B245" s="4">
+      <c r="B245" s="7">
         <v>-23.541671550312291</v>
       </c>
-      <c r="C245" s="4">
+      <c r="C245" s="7">
         <v>-46.614646672825259</v>
       </c>
       <c r="D245" s="4" t="s">
@@ -4827,13 +4858,13 @@
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A246" s="3" t="s">
+      <c r="A246" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B246" s="4">
+      <c r="B246" s="7">
         <v>-23.600752161349821</v>
       </c>
-      <c r="C246" s="4">
+      <c r="C246" s="7">
         <v>-46.719996488903028</v>
       </c>
       <c r="D246" s="4" t="s">
@@ -4841,13 +4872,13 @@
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A247" s="3" t="s">
+      <c r="A247" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B247" s="4">
+      <c r="B247" s="7">
         <v>-23.596725180436309</v>
       </c>
-      <c r="C247" s="4">
+      <c r="C247" s="7">
         <v>-46.558841433083103</v>
       </c>
       <c r="D247" s="4" t="s">
@@ -4855,13 +4886,13 @@
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A248" s="3" t="s">
+      <c r="A248" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B248" s="4">
+      <c r="B248" s="7">
         <v>-23.555463612477961</v>
       </c>
-      <c r="C248" s="4">
+      <c r="C248" s="7">
         <v>-46.601079919592273</v>
       </c>
       <c r="D248" s="4" t="s">
@@ -4869,13 +4900,13 @@
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A249" s="3" t="s">
+      <c r="A249" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B249" s="4">
+      <c r="B249" s="7">
         <v>-23.522965806534671</v>
       </c>
-      <c r="C249" s="4">
+      <c r="C249" s="7">
         <v>-46.194952291158863</v>
       </c>
       <c r="D249" s="4" t="s">
@@ -4883,13 +4914,13 @@
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A250" s="3" t="s">
+      <c r="A250" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B250" s="4">
+      <c r="B250" s="7">
         <v>-23.80103844189879</v>
       </c>
-      <c r="C250" s="4">
+      <c r="C250" s="7">
         <v>-45.402060404645482</v>
       </c>
       <c r="D250" s="4" t="s">
@@ -4897,13 +4928,13 @@
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A251" s="3" t="s">
+      <c r="A251" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B251" s="4">
+      <c r="B251" s="7">
         <v>-23.536982093582449</v>
       </c>
-      <c r="C251" s="4">
+      <c r="C251" s="7">
         <v>-46.454761158222937</v>
       </c>
       <c r="D251" s="4" t="s">
@@ -4911,13 +4942,13 @@
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A252" s="3" t="s">
+      <c r="A252" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B252" s="4">
+      <c r="B252" s="7">
         <v>-23.602669558230499</v>
       </c>
-      <c r="C252" s="4">
+      <c r="C252" s="7">
         <v>-46.634041194267361</v>
       </c>
       <c r="D252" s="4" t="s">
@@ -4925,13 +4956,13 @@
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A253" s="3" t="s">
+      <c r="A253" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B253" s="4">
+      <c r="B253" s="7">
         <v>-23.88279945067486</v>
       </c>
-      <c r="C253" s="4">
+      <c r="C253" s="7">
         <v>-46.4219631554733</v>
       </c>
       <c r="D253" s="4" t="s">
@@ -4939,13 +4970,13 @@
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A254" s="3" t="s">
+      <c r="A254" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B254" s="4">
+      <c r="B254" s="7">
         <v>-23.491147709146979</v>
       </c>
-      <c r="C254" s="4">
+      <c r="C254" s="7">
         <v>-46.443645969332287</v>
       </c>
       <c r="D254" s="4" t="s">
@@ -4953,13 +4984,13 @@
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A255" s="3" t="s">
+      <c r="A255" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B255" s="4">
+      <c r="B255" s="7">
         <v>-23.491262606961261</v>
       </c>
-      <c r="C255" s="4">
+      <c r="C255" s="7">
         <v>-46.44393838890683</v>
       </c>
       <c r="D255" s="4" t="s">
@@ -4967,13 +4998,13 @@
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A256" s="3" t="s">
+      <c r="A256" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B256" s="4">
+      <c r="B256" s="7">
         <v>-23.546807598235649</v>
       </c>
-      <c r="C256" s="4">
+      <c r="C256" s="7">
         <v>-46.635826119592451</v>
       </c>
       <c r="D256" s="4" t="s">
@@ -4981,13 +5012,13 @@
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A257" s="3" t="s">
+      <c r="A257" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B257" s="4">
+      <c r="B257" s="7">
         <v>-23.433236185458419</v>
       </c>
-      <c r="C257" s="4">
+      <c r="C257" s="7">
         <v>-46.272289825929683</v>
       </c>
       <c r="D257" s="4" t="s">
@@ -4995,13 +5026,13 @@
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A258" s="3" t="s">
+      <c r="A258" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B258" s="4">
+      <c r="B258" s="7">
         <v>-23.526866352174331</v>
       </c>
-      <c r="C258" s="4">
+      <c r="C258" s="7">
         <v>-46.565511174396192</v>
       </c>
       <c r="D258" s="4" t="s">
@@ -5009,13 +5040,13 @@
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A259" s="3" t="s">
+      <c r="A259" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B259" s="4">
+      <c r="B259" s="7">
         <v>-23.62339270191459</v>
       </c>
-      <c r="C259" s="4">
+      <c r="C259" s="7">
         <v>-46.593668240133937</v>
       </c>
       <c r="D259" s="4" t="s">
@@ -5023,13 +5054,13 @@
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A260" s="3" t="s">
+      <c r="A260" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B260" s="4">
+      <c r="B260" s="7">
         <v>-23.596106515856121</v>
       </c>
-      <c r="C260" s="4">
+      <c r="C260" s="7">
         <v>-46.523696287051571</v>
       </c>
       <c r="D260" s="4" t="s">
@@ -5037,13 +5068,13 @@
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A261" s="3" t="s">
+      <c r="A261" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B261" s="4">
+      <c r="B261" s="7">
         <v>-23.712114488373409</v>
       </c>
-      <c r="C261" s="4">
+      <c r="C261" s="7">
         <v>-46.69846881422076</v>
       </c>
       <c r="D261" s="4" t="s">
@@ -5051,13 +5082,13 @@
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A262" s="3" t="s">
+      <c r="A262" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B262" s="4">
+      <c r="B262" s="7">
         <v>-23.592207972195741</v>
       </c>
-      <c r="C262" s="4">
+      <c r="C262" s="7">
         <v>-46.637403224058673</v>
       </c>
       <c r="D262" s="4" t="s">
@@ -5065,13 +5096,13 @@
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A263" s="3" t="s">
+      <c r="A263" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B263" s="4">
+      <c r="B263" s="7">
         <v>-23.492427192606801</v>
       </c>
-      <c r="C263" s="4">
+      <c r="C263" s="7">
         <v>-46.440570661922379</v>
       </c>
       <c r="D263" s="4" t="s">
@@ -5079,13 +5110,13 @@
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A264" s="3" t="s">
+      <c r="A264" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B264" s="4">
+      <c r="B264" s="7">
         <v>-23.492239529465941</v>
       </c>
-      <c r="C264" s="4">
+      <c r="C264" s="7">
         <v>-46.440901304250509</v>
       </c>
       <c r="D264" s="4" t="s">
@@ -5093,13 +5124,13 @@
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A265" s="3" t="s">
+      <c r="A265" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B265" s="4">
+      <c r="B265" s="7">
         <v>-23.49158759255425</v>
       </c>
-      <c r="C265" s="4">
+      <c r="C265" s="7">
         <v>-46.440875670984319</v>
       </c>
       <c r="D265" s="4" t="s">
@@ -5107,13 +5138,13 @@
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A266" s="3" t="s">
+      <c r="A266" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B266" s="4">
+      <c r="B266" s="7">
         <v>-23.182664866081709</v>
       </c>
-      <c r="C266" s="4">
+      <c r="C266" s="7">
         <v>-45.885691790768199</v>
       </c>
       <c r="D266" s="4" t="s">
@@ -5121,13 +5152,13 @@
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A267" s="3" t="s">
+      <c r="A267" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B267" s="4">
+      <c r="B267" s="7">
         <v>-23.598311348116411</v>
       </c>
-      <c r="C267" s="4">
+      <c r="C267" s="7">
         <v>-46.600309595663433</v>
       </c>
       <c r="D267" s="4" t="s">
@@ -5135,13 +5166,13 @@
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A268" s="3" t="s">
+      <c r="A268" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B268" s="4">
+      <c r="B268" s="7">
         <v>-23.57798572685445</v>
       </c>
-      <c r="C268" s="4">
+      <c r="C268" s="7">
         <v>-46.602564028637467</v>
       </c>
       <c r="D268" s="4" t="s">
@@ -5149,13 +5180,13 @@
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A269" s="3" t="s">
+      <c r="A269" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B269" s="4">
+      <c r="B269" s="7">
         <v>-23.566007427729311</v>
       </c>
-      <c r="C269" s="4">
+      <c r="C269" s="7">
         <v>-46.691701834935799</v>
       </c>
       <c r="D269" s="4" t="s">
@@ -5163,13 +5194,13 @@
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A270" s="3" t="s">
+      <c r="A270" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B270" s="4">
+      <c r="B270" s="7">
         <v>-23.566096195950461</v>
       </c>
-      <c r="C270" s="4">
+      <c r="C270" s="7">
         <v>-46.691930433084153</v>
       </c>
       <c r="D270" s="4" t="s">
@@ -5177,13 +5208,13 @@
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A271" s="3" t="s">
+      <c r="A271" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B271" s="4">
+      <c r="B271" s="7">
         <v>-23.940946334589292</v>
       </c>
-      <c r="C271" s="4">
+      <c r="C271" s="7">
         <v>-46.304872014612911</v>
       </c>
       <c r="D271" s="4" t="s">
@@ -5191,13 +5222,13 @@
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A272" s="3" t="s">
+      <c r="A272" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B272" s="4">
+      <c r="B272" s="7">
         <v>-23.55756190243449</v>
       </c>
-      <c r="C272" s="4">
+      <c r="C272" s="7">
         <v>-46.636306259493011</v>
       </c>
       <c r="D272" s="4" t="s">
@@ -5205,13 +5236,13 @@
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A273" s="3" t="s">
+      <c r="A273" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B273" s="4">
+      <c r="B273" s="7">
         <v>-23.530078214986531</v>
       </c>
-      <c r="C273" s="4">
+      <c r="C273" s="7">
         <v>-46.634488164906386</v>
       </c>
       <c r="D273" s="4" t="s">
@@ -5219,13 +5250,13 @@
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A274" s="3" t="s">
+      <c r="A274" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B274" s="4">
+      <c r="B274" s="7">
         <v>-23.52988561736511</v>
       </c>
-      <c r="C274" s="4">
+      <c r="C274" s="7">
         <v>-46.634709817741388</v>
       </c>
       <c r="D274" s="4" t="s">
@@ -5233,13 +5264,13 @@
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A275" s="3" t="s">
+      <c r="A275" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B275" s="4">
+      <c r="B275" s="7">
         <v>-23.479382328396909</v>
       </c>
-      <c r="C275" s="4">
+      <c r="C275" s="7">
         <v>-46.608265488749048</v>
       </c>
       <c r="D275" s="4" t="s">
@@ -5247,13 +5278,13 @@
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A276" s="3" t="s">
+      <c r="A276" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B276" s="4">
+      <c r="B276" s="7">
         <v>-23.543335294968749</v>
       </c>
-      <c r="C276" s="4">
+      <c r="C276" s="7">
         <v>-46.574988697957323</v>
       </c>
       <c r="D276" s="4" t="s">
@@ -5261,13 +5292,13 @@
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A277" s="3" t="s">
+      <c r="A277" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B277" s="4">
+      <c r="B277" s="7">
         <v>-23.484215915099838</v>
       </c>
-      <c r="C277" s="4">
+      <c r="C277" s="7">
         <v>-46.755477717742842</v>
       </c>
       <c r="D277" s="4" t="s">
@@ -5275,13 +5306,13 @@
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A278" s="3" t="s">
+      <c r="A278" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B278" s="4">
+      <c r="B278" s="7">
         <v>-23.543516708808191</v>
       </c>
-      <c r="C278" s="4">
+      <c r="C278" s="7">
         <v>-46.640149150249577</v>
       </c>
       <c r="D278" s="4" t="s">
@@ -5289,13 +5320,13 @@
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A279" s="3" t="s">
+      <c r="A279" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B279" s="4">
+      <c r="B279" s="7">
         <v>-23.638176815040818</v>
       </c>
-      <c r="C279" s="4">
+      <c r="C279" s="7">
         <v>-46.564604169226762</v>
       </c>
       <c r="D279" s="4" t="s">
@@ -5303,13 +5334,13 @@
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A280" s="3" t="s">
+      <c r="A280" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B280" s="4">
+      <c r="B280" s="7">
         <v>-23.501523519993501</v>
       </c>
-      <c r="C280" s="4">
+      <c r="C280" s="7">
         <v>-46.626011541097412</v>
       </c>
       <c r="D280" s="4" t="s">
@@ -5317,13 +5348,13 @@
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A281" s="3" t="s">
+      <c r="A281" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B281" s="4">
+      <c r="B281" s="7">
         <v>-23.503586107029871</v>
       </c>
-      <c r="C281" s="4">
+      <c r="C281" s="7">
         <v>-46.626211450999627</v>
       </c>
       <c r="D281" s="4" t="s">
@@ -5331,13 +5362,13 @@
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A282" s="3" t="s">
+      <c r="A282" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B282" s="4">
+      <c r="B282" s="7">
         <v>-23.502023857560459</v>
       </c>
-      <c r="C282" s="4">
+      <c r="C282" s="7">
         <v>-46.626390404250131</v>
       </c>
       <c r="D282" s="4" t="s">
@@ -5345,13 +5376,13 @@
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A283" s="3" t="s">
+      <c r="A283" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B283" s="4">
+      <c r="B283" s="7">
         <v>-23.501954985691299</v>
       </c>
-      <c r="C283" s="4">
+      <c r="C283" s="7">
         <v>-46.626422590757997</v>
       </c>
       <c r="D283" s="4" t="s">
@@ -5359,13 +5390,13 @@
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A284" s="3" t="s">
+      <c r="A284" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B284" s="4">
+      <c r="B284" s="7">
         <v>-23.500276599661639</v>
       </c>
-      <c r="C284" s="4">
+      <c r="C284" s="7">
         <v>-46.625969433086233</v>
       </c>
       <c r="D284" s="4" t="s">
@@ -5373,13 +5404,13 @@
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A285" s="3" t="s">
+      <c r="A285" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B285" s="4">
+      <c r="B285" s="7">
         <v>-23.54144490466987</v>
       </c>
-      <c r="C285" s="4">
+      <c r="C285" s="7">
         <v>-46.366536304248918</v>
       </c>
       <c r="D285" s="4" t="s">
@@ -5387,13 +5418,13 @@
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A286" s="3" t="s">
+      <c r="A286" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B286" s="4">
+      <c r="B286" s="7">
         <v>-23.99198113523585</v>
       </c>
-      <c r="C286" s="4">
+      <c r="C286" s="7">
         <v>-46.273385733070171</v>
       </c>
       <c r="D286" s="4" t="s">
@@ -5401,13 +5432,13 @@
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A287" s="3" t="s">
+      <c r="A287" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B287" s="4">
+      <c r="B287" s="7">
         <v>-23.57291730714336</v>
       </c>
-      <c r="C287" s="4">
+      <c r="C287" s="7">
         <v>-46.605762204247938</v>
       </c>
       <c r="D287" s="4" t="s">
@@ -5415,13 +5446,13 @@
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A288" s="3" t="s">
+      <c r="A288" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B288" s="4">
+      <c r="B288" s="7">
         <v>-23.22552730147973</v>
       </c>
-      <c r="C288" s="4">
+      <c r="C288" s="7">
         <v>-45.884401651259303</v>
       </c>
       <c r="D288" s="4" t="s">
@@ -5429,13 +5460,13 @@
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A289" s="3" t="s">
+      <c r="A289" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B289" s="4">
+      <c r="B289" s="7">
         <v>-23.664487792285641</v>
       </c>
-      <c r="C289" s="4">
+      <c r="C289" s="7">
         <v>-46.453451377260649</v>
       </c>
       <c r="D289" s="4" t="s">
@@ -5443,13 +5474,13 @@
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A290" s="3" t="s">
+      <c r="A290" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B290" s="4">
+      <c r="B290" s="7">
         <v>-23.47244907226656</v>
       </c>
-      <c r="C290" s="4">
+      <c r="C290" s="7">
         <v>-46.523299049226168</v>
       </c>
       <c r="D290" s="4" t="s">
@@ -5457,13 +5488,13 @@
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A291" s="3" t="s">
+      <c r="A291" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B291" s="4">
+      <c r="B291" s="7">
         <v>-23.963006237330362</v>
       </c>
-      <c r="C291" s="4">
+      <c r="C291" s="7">
         <v>-46.38050392855282</v>
       </c>
       <c r="D291" s="4" t="s">
@@ -5471,13 +5502,13 @@
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A292" s="3" t="s">
+      <c r="A292" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B292" s="4">
+      <c r="B292" s="7">
         <v>-23.584643793116971</v>
       </c>
-      <c r="C292" s="4">
+      <c r="C292" s="7">
         <v>-46.740342044258618</v>
       </c>
       <c r="D292" s="4" t="s">
@@ -5485,13 +5516,13 @@
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A293" s="3" t="s">
+      <c r="A293" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B293" s="4">
+      <c r="B293" s="7">
         <v>-23.567261987255041</v>
       </c>
-      <c r="C293" s="4">
+      <c r="C293" s="7">
         <v>-46.499815579652562</v>
       </c>
       <c r="D293" s="4" t="s">
@@ -5499,13 +5530,13 @@
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A294" s="3" t="s">
+      <c r="A294" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B294" s="4">
+      <c r="B294" s="7">
         <v>-23.567631399594031</v>
       </c>
-      <c r="C294" s="4">
+      <c r="C294" s="7">
         <v>-46.498992856461982</v>
       </c>
       <c r="D294" s="4" t="s">
@@ -5513,13 +5544,13 @@
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A295" s="3" t="s">
+      <c r="A295" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B295" s="4">
+      <c r="B295" s="7">
         <v>-23.666645793976659</v>
       </c>
-      <c r="C295" s="4">
+      <c r="C295" s="7">
         <v>-46.711714272797927</v>
       </c>
       <c r="D295" s="4" t="s">
@@ -5527,13 +5558,13 @@
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A296" s="3" t="s">
+      <c r="A296" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B296" s="4">
+      <c r="B296" s="7">
         <v>-23.614083248194159</v>
       </c>
-      <c r="C296" s="4">
+      <c r="C296" s="7">
         <v>-46.695307960066849</v>
       </c>
       <c r="D296" s="4" t="s">
@@ -5541,13 +5572,13 @@
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A297" s="3" t="s">
+      <c r="A297" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B297" s="4">
+      <c r="B297" s="7">
         <v>-23.527254972408471</v>
       </c>
-      <c r="C297" s="4">
+      <c r="C297" s="7">
         <v>-46.202499288905543</v>
       </c>
       <c r="D297" s="4" t="s">
@@ -5555,13 +5586,13 @@
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A298" s="3" t="s">
+      <c r="A298" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B298" s="4">
+      <c r="B298" s="7">
         <v>-23.51323748102979</v>
       </c>
-      <c r="C298" s="4">
+      <c r="C298" s="7">
         <v>-46.653889263773443</v>
       </c>
       <c r="D298" s="4" t="s">
@@ -5569,13 +5600,13 @@
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A299" s="3" t="s">
+      <c r="A299" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B299" s="4">
+      <c r="B299" s="7">
         <v>-23.52934061640649</v>
       </c>
-      <c r="C299" s="4">
+      <c r="C299" s="7">
         <v>-46.658492749147626</v>
       </c>
       <c r="D299" s="4" t="s">
@@ -5583,13 +5614,13 @@
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A300" s="3" t="s">
+      <c r="A300" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B300" s="4">
+      <c r="B300" s="7">
         <v>-23.571191967884289</v>
       </c>
-      <c r="C300" s="4">
+      <c r="C300" s="7">
         <v>-46.698936551526103</v>
       </c>
       <c r="D300" s="4" t="s">
@@ -5597,13 +5628,13 @@
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A301" s="3" t="s">
+      <c r="A301" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B301" s="4">
+      <c r="B301" s="7">
         <v>-23.523916509869309</v>
       </c>
-      <c r="C301" s="4">
+      <c r="C301" s="7">
         <v>-46.683559094777628</v>
       </c>
       <c r="D301" s="4" t="s">
@@ -5611,13 +5642,13 @@
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A302" s="3" t="s">
+      <c r="A302" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B302" s="4">
+      <c r="B302" s="7">
         <v>-23.535951452950741</v>
       </c>
-      <c r="C302" s="4">
+      <c r="C302" s="7">
         <v>-46.709406106100737</v>
       </c>
       <c r="D302" s="4" t="s">
@@ -5625,13 +5656,13 @@
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A303" s="3" t="s">
+      <c r="A303" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B303" s="4">
+      <c r="B303" s="7">
         <v>-23.024333952917061</v>
       </c>
-      <c r="C303" s="4">
+      <c r="C303" s="7">
         <v>-45.585270344514257</v>
       </c>
       <c r="D303" s="4" t="s">
@@ -5639,13 +5670,13 @@
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A304" s="3" t="s">
+      <c r="A304" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B304" s="4">
+      <c r="B304" s="7">
         <v>-23.21336676802931</v>
       </c>
-      <c r="C304" s="4">
+      <c r="C304" s="7">
         <v>-45.891913859195547</v>
       </c>
       <c r="D304" s="4" t="s">
@@ -5653,13 +5684,13 @@
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A305" s="3" t="s">
+      <c r="A305" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B305" s="4">
+      <c r="B305" s="7">
         <v>-23.586117093078261</v>
       </c>
-      <c r="C305" s="4">
+      <c r="C305" s="7">
         <v>-46.679653804247593</v>
       </c>
       <c r="D305" s="4" t="s">
@@ -5667,13 +5698,13 @@
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A306" s="3" t="s">
+      <c r="A306" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B306" s="4">
+      <c r="B306" s="7">
         <v>-23.733395299524659</v>
       </c>
-      <c r="C306" s="4">
+      <c r="C306" s="7">
         <v>-46.701505333078742</v>
       </c>
       <c r="D306" s="4" t="s">
@@ -5681,13 +5712,13 @@
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A307" s="3" t="s">
+      <c r="A307" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B307" s="4">
+      <c r="B307" s="7">
         <v>-23.513869889506811</v>
       </c>
-      <c r="C307" s="4">
+      <c r="C307" s="7">
         <v>-46.585346057487371</v>
       </c>
       <c r="D307" s="4" t="s">
@@ -5695,13 +5726,13 @@
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A308" s="3" t="s">
+      <c r="A308" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B308" s="4">
+      <c r="B308" s="7">
         <v>-23.56781656671237</v>
       </c>
-      <c r="C308" s="4">
+      <c r="C308" s="7">
         <v>-46.612498388904157</v>
       </c>
       <c r="D308" s="4" t="s">
@@ -5709,13 +5740,13 @@
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A309" s="3" t="s">
+      <c r="A309" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B309" s="4">
+      <c r="B309" s="7">
         <v>-23.670272961169111</v>
       </c>
-      <c r="C309" s="4">
+      <c r="C309" s="7">
         <v>-46.702838050350842</v>
       </c>
       <c r="D309" s="4" t="s">
@@ -5723,13 +5754,13 @@
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A310" s="3" t="s">
+      <c r="A310" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B310" s="4">
+      <c r="B310" s="7">
         <v>-23.657545580812879</v>
       </c>
-      <c r="C310" s="4">
+      <c r="C310" s="7">
         <v>-46.764037848424927</v>
       </c>
       <c r="D310" s="4" t="s">
@@ -5737,13 +5768,13 @@
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A311" s="3" t="s">
+      <c r="A311" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B311" s="4">
+      <c r="B311" s="7">
         <v>-23.974221764520141</v>
       </c>
-      <c r="C311" s="4">
+      <c r="C311" s="7">
         <v>-46.4680300135851</v>
       </c>
       <c r="D311" s="4" t="s">
@@ -5751,13 +5782,13 @@
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A312" s="3" t="s">
+      <c r="A312" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B312" s="4">
+      <c r="B312" s="7">
         <v>-23.621685846663429</v>
       </c>
-      <c r="C312" s="4">
+      <c r="C312" s="7">
         <v>-46.758842525890081</v>
       </c>
       <c r="D312" s="4" t="s">
@@ -5765,13 +5796,13 @@
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A313" s="3" t="s">
+      <c r="A313" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B313" s="4">
+      <c r="B313" s="7">
         <v>-23.68336079918269</v>
       </c>
-      <c r="C313" s="4">
+      <c r="C313" s="7">
         <v>-46.769038077260063</v>
       </c>
       <c r="D313" s="4" t="s">
@@ -5779,13 +5810,13 @@
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A314" s="3" t="s">
+      <c r="A314" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B314" s="4">
+      <c r="B314" s="7">
         <v>-23.56467922764649</v>
       </c>
-      <c r="C314" s="4">
+      <c r="C314" s="7">
         <v>-46.589846102396542</v>
       </c>
       <c r="D314" s="4" t="s">
@@ -5793,13 +5824,13 @@
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A315" s="3" t="s">
+      <c r="A315" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B315" s="4">
+      <c r="B315" s="7">
         <v>-23.95177826207555</v>
       </c>
-      <c r="C315" s="4">
+      <c r="C315" s="7">
         <v>-46.328872260377338</v>
       </c>
       <c r="D315" s="4" t="s">
@@ -5807,13 +5838,13 @@
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A316" s="3" t="s">
+      <c r="A316" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B316" s="4">
+      <c r="B316" s="7">
         <v>-23.951780915874689</v>
       </c>
-      <c r="C316" s="4">
+      <c r="C316" s="7">
         <v>-46.329198811777509</v>
       </c>
       <c r="D316" s="4" t="s">
@@ -5821,13 +5852,13 @@
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A317" s="3" t="s">
+      <c r="A317" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B317" s="4">
+      <c r="B317" s="7">
         <v>-23.19374151513227</v>
       </c>
-      <c r="C317" s="4">
+      <c r="C317" s="7">
         <v>-45.890978619603992</v>
       </c>
       <c r="D317" s="4" t="s">
@@ -5835,13 +5866,13 @@
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A318" s="3" t="s">
+      <c r="A318" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B318" s="4">
+      <c r="B318" s="7">
         <v>-23.536422883852001</v>
       </c>
-      <c r="C318" s="4">
+      <c r="C318" s="7">
         <v>-46.731629677568783</v>
       </c>
       <c r="D318" s="4" t="s">
@@ -5849,13 +5880,13 @@
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A319" s="3" t="s">
+      <c r="A319" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B319" s="4">
+      <c r="B319" s="7">
         <v>-23.46243720518612</v>
       </c>
-      <c r="C319" s="4">
+      <c r="C319" s="7">
         <v>-46.532448272842409</v>
       </c>
       <c r="D319" s="4" t="s">
@@ -5863,13 +5894,13 @@
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A320" s="3" t="s">
+      <c r="A320" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B320" s="4">
+      <c r="B320" s="7">
         <v>-23.213709260104249</v>
       </c>
-      <c r="C320" s="4">
+      <c r="C320" s="7">
         <v>-45.901231801732173</v>
       </c>
       <c r="D320" s="4" t="s">
@@ -5877,13 +5908,13 @@
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A321" s="3" t="s">
+      <c r="A321" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B321" s="4">
+      <c r="B321" s="7">
         <v>-23.53307858515771</v>
       </c>
-      <c r="C321" s="4">
+      <c r="C321" s="7">
         <v>-46.209464734936901</v>
       </c>
       <c r="D321" s="4" t="s">
@@ -5891,13 +5922,13 @@
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A322" s="3" t="s">
+      <c r="A322" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B322" s="4">
+      <c r="B322" s="7">
         <v>-23.494166854109171</v>
       </c>
-      <c r="C322" s="4">
+      <c r="C322" s="7">
         <v>-46.709350319594243</v>
       </c>
       <c r="D322" s="4" t="s">
@@ -5905,13 +5936,13 @@
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A323" s="3" t="s">
+      <c r="A323" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B323" s="4">
+      <c r="B323" s="7">
         <v>-23.501254184488172</v>
       </c>
-      <c r="C323" s="4">
+      <c r="C323" s="7">
         <v>-46.614778606101751</v>
       </c>
       <c r="D323" s="4" t="s">
@@ -5919,13 +5950,13 @@
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A324" s="3" t="s">
+      <c r="A324" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B324" s="4">
+      <c r="B324" s="7">
         <v>-23.502341431695271</v>
       </c>
-      <c r="C324" s="4">
+      <c r="C324" s="7">
         <v>-46.70700493226596</v>
       </c>
       <c r="D324" s="4" t="s">
@@ -5933,13 +5964,13 @@
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A325" s="3" t="s">
+      <c r="A325" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B325" s="4">
+      <c r="B325" s="7">
         <v>-23.612786223750859</v>
       </c>
-      <c r="C325" s="4">
+      <c r="C325" s="7">
         <v>-46.72955479075442</v>
       </c>
       <c r="D325" s="4" t="s">
@@ -5947,13 +5978,13 @@
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A326" s="3" t="s">
+      <c r="A326" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B326" s="4">
+      <c r="B326" s="7">
         <v>-23.616596103940939</v>
       </c>
-      <c r="C326" s="4">
+      <c r="C326" s="7">
         <v>-46.557167275410563</v>
       </c>
       <c r="D326" s="4" t="s">
@@ -5961,13 +5992,13 @@
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A327" s="3" t="s">
+      <c r="A327" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B327" s="4">
+      <c r="B327" s="7">
         <v>-23.522107559090529</v>
       </c>
-      <c r="C327" s="4">
+      <c r="C327" s="7">
         <v>-46.690903234937103</v>
       </c>
       <c r="D327" s="4" t="s">
@@ -5975,13 +6006,13 @@
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A328" s="3" t="s">
+      <c r="A328" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B328" s="4">
+      <c r="B328" s="7">
         <v>-23.485746517839861</v>
       </c>
-      <c r="C328" s="4">
+      <c r="C328" s="7">
         <v>-46.543038990758539</v>
       </c>
       <c r="D328" s="4" t="s">
@@ -5989,13 +6020,13 @@
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A329" s="3" t="s">
+      <c r="A329" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B329" s="4">
+      <c r="B329" s="7">
         <v>-23.613868312959969</v>
       </c>
-      <c r="C329" s="4">
+      <c r="C329" s="7">
         <v>-46.577668793484321</v>
       </c>
       <c r="D329" s="4" t="s">
@@ -6003,13 +6034,13 @@
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A330" s="3" t="s">
+      <c r="A330" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B330" s="4">
+      <c r="B330" s="7">
         <v>-23.518108826288859</v>
       </c>
-      <c r="C330" s="4">
+      <c r="C330" s="7">
         <v>-46.608959660069907</v>
       </c>
       <c r="D330" s="4" t="s">
@@ -6017,13 +6048,13 @@
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A331" s="3" t="s">
+      <c r="A331" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B331" s="4">
+      <c r="B331" s="7">
         <v>-23.518108826288859</v>
       </c>
-      <c r="C331" s="4">
+      <c r="C331" s="7">
         <v>-46.608959660069907</v>
       </c>
       <c r="D331" s="4" t="s">
@@ -6031,13 +6062,13 @@
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A332" s="3" t="s">
+      <c r="A332" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B332" s="4">
+      <c r="B332" s="7">
         <v>-23.607448374399329</v>
       </c>
-      <c r="C332" s="4">
+      <c r="C332" s="7">
         <v>-46.665512790754683</v>
       </c>
       <c r="D332" s="4" t="s">
@@ -6045,13 +6076,13 @@
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A333" s="3" t="s">
+      <c r="A333" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B333" s="4">
+      <c r="B333" s="7">
         <v>-23.608279669959281</v>
       </c>
-      <c r="C333" s="4">
+      <c r="C333" s="7">
         <v>-46.66724654657483</v>
       </c>
       <c r="D333" s="4" t="s">
@@ -6059,13 +6090,13 @@
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A334" s="3" t="s">
+      <c r="A334" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B334" s="4">
+      <c r="B334" s="7">
         <v>-23.036690281720009</v>
       </c>
-      <c r="C334" s="4">
+      <c r="C334" s="7">
         <v>-45.574915348444677</v>
       </c>
       <c r="D334" s="4" t="s">
@@ -6073,13 +6104,13 @@
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A335" s="3" t="s">
+      <c r="A335" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B335" s="4">
+      <c r="B335" s="7">
         <v>-23.541772461653249</v>
       </c>
-      <c r="C335" s="4">
+      <c r="C335" s="7">
         <v>-46.458498073561088</v>
       </c>
       <c r="D335" s="4" t="s">
@@ -6087,13 +6118,13 @@
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A336" s="3" t="s">
+      <c r="A336" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B336" s="4">
+      <c r="B336" s="7">
         <v>-23.615424335187939</v>
       </c>
-      <c r="C336" s="4">
+      <c r="C336" s="7">
         <v>-46.638387201645152</v>
       </c>
       <c r="D336" s="4" t="s">
@@ -6101,13 +6132,13 @@
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A337" s="3" t="s">
+      <c r="A337" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B337" s="4">
+      <c r="B337" s="7">
         <v>-23.623512079181619</v>
       </c>
-      <c r="C337" s="4">
+      <c r="C337" s="7">
         <v>-46.640178628547943</v>
       </c>
       <c r="D337" s="4" t="s">
@@ -6115,13 +6146,13 @@
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A338" s="3" t="s">
+      <c r="A338" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B338" s="4">
+      <c r="B338" s="7">
         <v>-23.645191048016638</v>
       </c>
-      <c r="C338" s="4">
+      <c r="C338" s="7">
         <v>-46.714445302393827</v>
       </c>
       <c r="D338" s="4" t="s">
@@ -6129,13 +6160,13 @@
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A339" s="3" t="s">
+      <c r="A339" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B339" s="4">
+      <c r="B339" s="7">
         <v>-23.944094145972159</v>
       </c>
-      <c r="C339" s="4">
+      <c r="C339" s="7">
         <v>-46.329292346563918</v>
       </c>
       <c r="D339" s="4" t="s">
@@ -6143,13 +6174,13 @@
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A340" s="3" t="s">
+      <c r="A340" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B340" s="4">
+      <c r="B340" s="7">
         <v>-22.816093146368321</v>
       </c>
-      <c r="C340" s="4">
+      <c r="C340" s="7">
         <v>-45.201361630338504</v>
       </c>
       <c r="D340" s="4" t="s">
@@ -6157,13 +6188,13 @@
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A341" s="3" t="s">
+      <c r="A341" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B341" s="4">
+      <c r="B341" s="7">
         <v>-23.93254040321106</v>
       </c>
-      <c r="C341" s="4">
+      <c r="C341" s="7">
         <v>-46.336479642432117</v>
       </c>
       <c r="D341" s="4" t="s">
@@ -6171,13 +6202,13 @@
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A342" s="3" t="s">
+      <c r="A342" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B342" s="4">
+      <c r="B342" s="7">
         <v>-23.702969355938251</v>
       </c>
-      <c r="C342" s="4">
+      <c r="C342" s="7">
         <v>-46.551696533079593</v>
       </c>
       <c r="D342" s="4" t="s">
@@ -6185,13 +6216,13 @@
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A343" s="3" t="s">
+      <c r="A343" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B343" s="4">
+      <c r="B343" s="7">
         <v>-23.484928217355751</v>
       </c>
-      <c r="C343" s="4">
+      <c r="C343" s="7">
         <v>-46.37970036192258</v>
       </c>
       <c r="D343" s="4" t="s">
@@ -6199,13 +6230,13 @@
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A344" s="3" t="s">
+      <c r="A344" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B344" s="4">
+      <c r="B344" s="7">
         <v>-23.59649802533605</v>
       </c>
-      <c r="C344" s="4">
+      <c r="C344" s="7">
         <v>-46.610188957469369</v>
       </c>
       <c r="D344" s="4" t="s">
@@ -6213,13 +6244,13 @@
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A345" s="3" t="s">
+      <c r="A345" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B345" s="4">
+      <c r="B345" s="7">
         <v>-23.894277129631991</v>
       </c>
-      <c r="C345" s="4">
+      <c r="C345" s="7">
         <v>-46.42114471772971</v>
       </c>
       <c r="D345" s="4" t="s">
@@ -6227,13 +6258,13 @@
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A346" s="3" t="s">
+      <c r="A346" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B346" s="4">
+      <c r="B346" s="7">
         <v>-23.443476570794861</v>
       </c>
-      <c r="C346" s="4">
+      <c r="C346" s="7">
         <v>-46.507905436144227</v>
       </c>
       <c r="D346" s="4" t="s">
@@ -6241,13 +6272,13 @@
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A347" s="3" t="s">
+      <c r="A347" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B347" s="4">
+      <c r="B347" s="7">
         <v>-23.566428332541928</v>
       </c>
-      <c r="C347" s="4">
+      <c r="C347" s="7">
         <v>-46.656969106099773</v>
       </c>
       <c r="D347" s="4" t="s">
@@ -6255,13 +6286,13 @@
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A348" s="3" t="s">
+      <c r="A348" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B348" s="4">
+      <c r="B348" s="7">
         <v>-23.61232569785766</v>
       </c>
-      <c r="C348" s="4">
+      <c r="C348" s="7">
         <v>-45.430425690754497</v>
       </c>
       <c r="D348" s="4" t="s">
@@ -6269,13 +6300,13 @@
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A349" s="3" t="s">
+      <c r="A349" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B349" s="4">
+      <c r="B349" s="7">
         <v>-24.004253161423481</v>
       </c>
-      <c r="C349" s="4">
+      <c r="C349" s="7">
         <v>-46.413312073546223</v>
       </c>
       <c r="D349" s="4" t="s">
@@ -6283,13 +6314,13 @@
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A350" s="3" t="s">
+      <c r="A350" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B350" s="4">
+      <c r="B350" s="7">
         <v>-23.685009525803121</v>
       </c>
-      <c r="C350" s="4">
+      <c r="C350" s="7">
         <v>-46.6269917754082</v>
       </c>
       <c r="D350" s="4" t="s">
@@ -6297,13 +6328,13 @@
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A351" s="3" t="s">
+      <c r="A351" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B351" s="4">
+      <c r="B351" s="7">
         <v>-24.011833368922819</v>
       </c>
-      <c r="C351" s="4">
+      <c r="C351" s="7">
         <v>-46.441429563757282</v>
       </c>
       <c r="D351" s="4" t="s">
@@ -6311,13 +6342,13 @@
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A352" s="3" t="s">
+      <c r="A352" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B352" s="4">
+      <c r="B352" s="7">
         <v>-23.66317225441589</v>
       </c>
-      <c r="C352" s="4">
+      <c r="C352" s="7">
         <v>-46.530690391607443</v>
       </c>
       <c r="D352" s="4" t="s">
@@ -6325,13 +6356,13 @@
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A353" s="3" t="s">
+      <c r="A353" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B353" s="4">
+      <c r="B353" s="7">
         <v>-23.588674699506551</v>
       </c>
-      <c r="C353" s="4">
+      <c r="C353" s="7">
         <v>-46.620450260067663</v>
       </c>
       <c r="D353" s="4" t="s">
@@ -6339,13 +6370,13 @@
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A354" s="3" t="s">
+      <c r="A354" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B354" s="4">
+      <c r="B354" s="7">
         <v>-23.583490763002349</v>
       </c>
-      <c r="C354" s="4">
+      <c r="C354" s="7">
         <v>-46.584146777686819</v>
       </c>
       <c r="D354" s="4" t="s">
@@ -6353,13 +6384,13 @@
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A355" s="3" t="s">
+      <c r="A355" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B355" s="4">
+      <c r="B355" s="7">
         <v>-23.545485202778</v>
       </c>
-      <c r="C355" s="4">
+      <c r="C355" s="7">
         <v>-46.55671526192075</v>
       </c>
       <c r="D355" s="4" t="s">
@@ -6367,13 +6398,13 @@
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A356" s="3" t="s">
+      <c r="A356" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B356" s="4">
+      <c r="B356" s="7">
         <v>-23.652891063049189</v>
       </c>
-      <c r="C356" s="4">
+      <c r="C356" s="7">
         <v>-46.657499748425117</v>
       </c>
       <c r="D356" s="4" t="s">
@@ -6381,13 +6412,13 @@
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A357" s="3" t="s">
+      <c r="A357" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B357" s="4">
+      <c r="B357" s="7">
         <v>-23.622402427377651</v>
       </c>
-      <c r="C357" s="4">
+      <c r="C357" s="7">
         <v>-46.536464146398266</v>
       </c>
       <c r="D357" s="4" t="s">
@@ -6395,13 +6426,13 @@
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A358" s="3" t="s">
+      <c r="A358" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B358" s="4">
+      <c r="B358" s="7">
         <v>-23.622402427377651</v>
       </c>
-      <c r="C358" s="4">
+      <c r="C358" s="7">
         <v>-46.536464146398266</v>
       </c>
       <c r="D358" s="4" t="s">
@@ -6409,13 +6440,13 @@
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A359" s="3" t="s">
+      <c r="A359" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B359" s="4">
+      <c r="B359" s="7">
         <v>-23.66537210008088</v>
       </c>
-      <c r="C359" s="4">
+      <c r="C359" s="7">
         <v>-46.516962461916798</v>
       </c>
       <c r="D359" s="4" t="s">
@@ -6423,13 +6454,13 @@
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A360" s="3" t="s">
+      <c r="A360" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B360" s="4">
+      <c r="B360" s="7">
         <v>-23.491469788481719</v>
       </c>
-      <c r="C360" s="4">
+      <c r="C360" s="7">
         <v>-46.447669188906701</v>
       </c>
       <c r="D360" s="4" t="s">
@@ -6437,13 +6468,13 @@
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A361" s="3" t="s">
+      <c r="A361" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B361" s="4">
+      <c r="B361" s="7">
         <v>-23.612033105677192</v>
       </c>
-      <c r="C361" s="4">
+      <c r="C361" s="7">
         <v>-46.478125306098462</v>
       </c>
       <c r="D361" s="4" t="s">
@@ -6451,13 +6482,13 @@
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A362" s="3" t="s">
+      <c r="A362" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B362" s="4">
+      <c r="B362" s="7">
         <v>-23.54075204457888</v>
       </c>
-      <c r="C362" s="4">
+      <c r="C362" s="7">
         <v>-46.575173961920832</v>
       </c>
       <c r="D362" s="4" t="s">
@@ -6465,13 +6496,13 @@
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A363" s="3" t="s">
+      <c r="A363" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B363" s="4">
+      <c r="B363" s="7">
         <v>-22.97256617449046</v>
       </c>
-      <c r="C363" s="4">
+      <c r="C363" s="7">
         <v>-45.46236491035225</v>
       </c>
       <c r="D363" s="4" t="s">
@@ -6479,13 +6510,13 @@
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A364" s="3" t="s">
+      <c r="A364" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B364" s="4">
+      <c r="B364" s="7">
         <v>-23.934076033986631</v>
       </c>
-      <c r="C364" s="4">
+      <c r="C364" s="7">
         <v>-46.33113269074412</v>
       </c>
       <c r="D364" s="4" t="s">
@@ -6493,13 +6524,13 @@
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A365" s="3" t="s">
+      <c r="A365" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B365" s="4">
+      <c r="B365" s="7">
         <v>-23.645712777091489</v>
       </c>
-      <c r="C365" s="4">
+      <c r="C365" s="7">
         <v>-46.674637033081531</v>
       </c>
       <c r="D365" s="4" t="s">
@@ -6507,13 +6538,13 @@
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A366" s="3" t="s">
+      <c r="A366" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B366" s="4">
+      <c r="B366" s="7">
         <v>-23.944847236431929</v>
       </c>
-      <c r="C366" s="4">
+      <c r="C366" s="7">
         <v>-46.325583061907672</v>
       </c>
       <c r="D366" s="4" t="s">
@@ -6521,13 +6552,13 @@
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A367" s="3" t="s">
+      <c r="A367" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B367" s="4">
+      <c r="B367" s="7">
         <v>-23.531849347808581</v>
       </c>
-      <c r="C367" s="4">
+      <c r="C367" s="7">
         <v>-46.735724065610007</v>
       </c>
       <c r="D367" s="4" t="s">
@@ -6535,13 +6566,13 @@
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A368" s="3" t="s">
+      <c r="A368" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B368" s="4">
+      <c r="B368" s="7">
         <v>-23.55294247630945</v>
       </c>
-      <c r="C368" s="4">
+      <c r="C368" s="7">
         <v>-46.619393166946679</v>
       </c>
       <c r="D368" s="4" t="s">
@@ -6549,13 +6580,13 @@
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A369" s="3" t="s">
+      <c r="A369" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B369" s="4">
+      <c r="B369" s="7">
         <v>-23.472979486390759</v>
       </c>
-      <c r="C369" s="4">
+      <c r="C369" s="7">
         <v>-46.523945212141733</v>
       </c>
       <c r="D369" s="4" t="s">
@@ -6563,13 +6594,13 @@
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A370" s="3" t="s">
+      <c r="A370" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B370" s="4">
+      <c r="B370" s="7">
         <v>-23.564769691418221</v>
       </c>
-      <c r="C370" s="4">
+      <c r="C370" s="7">
         <v>-46.501131225825851</v>
       </c>
       <c r="D370" s="4" t="s">
@@ -6577,13 +6608,13 @@
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A371" s="3" t="s">
+      <c r="A371" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B371" s="4">
+      <c r="B371" s="7">
         <v>-23.944992958284949</v>
       </c>
-      <c r="C371" s="4">
+      <c r="C371" s="7">
         <v>-46.325577395823011</v>
       </c>
       <c r="D371" s="4" t="s">
@@ -6591,13 +6622,13 @@
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A372" s="3" t="s">
+      <c r="A372" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B372" s="4">
+      <c r="B372" s="7">
         <v>-23.654672045553511</v>
       </c>
-      <c r="C372" s="4">
+      <c r="C372" s="7">
         <v>-46.532770484183843</v>
       </c>
       <c r="D372" s="4" t="s">
@@ -6605,13 +6636,13 @@
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A373" s="3" t="s">
+      <c r="A373" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B373" s="4">
+      <c r="B373" s="7">
         <v>-23.571564505363789</v>
       </c>
-      <c r="C373" s="4">
+      <c r="C373" s="7">
         <v>-46.674319619591728</v>
       </c>
       <c r="D373" s="4" t="s">
@@ -6619,13 +6650,13 @@
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A374" s="3" t="s">
+      <c r="A374" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B374" s="4">
+      <c r="B374" s="7">
         <v>-23.67088218599541</v>
       </c>
-      <c r="C374" s="4">
+      <c r="C374" s="7">
         <v>-46.703460322836527</v>
       </c>
       <c r="D374" s="4" t="s">
@@ -6633,13 +6664,13 @@
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A375" s="3" t="s">
+      <c r="A375" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B375" s="4">
+      <c r="B375" s="7">
         <v>-23.198517529504979</v>
       </c>
-      <c r="C375" s="4">
+      <c r="C375" s="7">
         <v>-45.878332076374498</v>
       </c>
       <c r="D375" s="4" t="s">
@@ -6647,13 +6678,13 @@
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A376" s="3" t="s">
+      <c r="A376" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B376" s="4">
+      <c r="B376" s="7">
         <v>-23.614815151746999</v>
       </c>
-      <c r="C376" s="4">
+      <c r="C376" s="7">
         <v>-46.667774402652867</v>
       </c>
       <c r="D376" s="4" t="s">
@@ -6661,13 +6692,13 @@
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A377" s="3" t="s">
+      <c r="A377" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B377" s="4">
+      <c r="B377" s="7">
         <v>-23.570646581729552</v>
       </c>
-      <c r="C377" s="4">
+      <c r="C377" s="7">
         <v>-46.700654586311067</v>
       </c>
       <c r="D377" s="4" t="s">
@@ -6675,13 +6706,13 @@
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A378" s="3" t="s">
+      <c r="A378" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B378" s="4">
+      <c r="B378" s="7">
         <v>-23.531889646879669</v>
       </c>
-      <c r="C378" s="4">
+      <c r="C378" s="7">
         <v>-46.735696404249197</v>
       </c>
       <c r="D378" s="4" t="s">
@@ -6689,13 +6720,13 @@
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A379" s="3" t="s">
+      <c r="A379" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B379" s="4">
+      <c r="B379" s="7">
         <v>-23.514655011467308</v>
       </c>
-      <c r="C379" s="4">
+      <c r="C379" s="7">
         <v>-46.69731055044749</v>
       </c>
       <c r="D379" s="4" t="s">
@@ -6703,13 +6734,13 @@
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A380" s="3" t="s">
+      <c r="A380" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B380" s="4">
+      <c r="B380" s="7">
         <v>-23.533991495405971</v>
       </c>
-      <c r="C380" s="4">
+      <c r="C380" s="7">
         <v>-46.213424755631287</v>
       </c>
       <c r="D380" s="4" t="s">
@@ -6717,13 +6748,13 @@
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A381" s="3" t="s">
+      <c r="A381" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B381" s="4">
+      <c r="B381" s="7">
         <v>-23.601480756898351</v>
       </c>
-      <c r="C381" s="4">
+      <c r="C381" s="7">
         <v>-46.660196519590862</v>
       </c>
       <c r="D381" s="4" t="s">
@@ -6731,13 +6762,13 @@
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A382" s="3" t="s">
+      <c r="A382" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B382" s="4">
+      <c r="B382" s="7">
         <v>-23.617863095353002</v>
       </c>
-      <c r="C382" s="4">
+      <c r="C382" s="7">
         <v>-46.703053701914143</v>
       </c>
       <c r="D382" s="4" t="s">
@@ -6745,13 +6776,13 @@
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A383" s="3" t="s">
+      <c r="A383" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B383" s="4">
+      <c r="B383" s="7">
         <v>-23.53076941855366</v>
       </c>
-      <c r="C383" s="4">
+      <c r="C383" s="7">
         <v>-46.661219004249162</v>
       </c>
       <c r="D383" s="4" t="s">
@@ -6759,13 +6790,13 @@
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A384" s="3" t="s">
+      <c r="A384" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B384" s="4">
+      <c r="B384" s="7">
         <v>-23.687290402466761</v>
       </c>
-      <c r="C384" s="4">
+      <c r="C384" s="7">
         <v>-46.547322733080051</v>
       </c>
       <c r="D384" s="4" t="s">
@@ -6773,13 +6804,13 @@
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A385" s="3" t="s">
+      <c r="A385" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B385" s="4">
+      <c r="B385" s="7">
         <v>-23.55050696354467</v>
       </c>
-      <c r="C385" s="4">
+      <c r="C385" s="7">
         <v>-46.567435488904863</v>
       </c>
       <c r="D385" s="4" t="s">
@@ -6787,13 +6818,13 @@
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A386" s="3" t="s">
+      <c r="A386" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B386" s="4">
+      <c r="B386" s="7">
         <v>-23.55050696354467</v>
       </c>
-      <c r="C386" s="4">
+      <c r="C386" s="7">
         <v>-46.567435488904863</v>
       </c>
       <c r="D386" s="4" t="s">
@@ -6801,13 +6832,13 @@
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A387" s="3" t="s">
+      <c r="A387" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B387" s="4">
+      <c r="B387" s="7">
         <v>-23.51602162022504</v>
       </c>
-      <c r="C387" s="4">
+      <c r="C387" s="7">
         <v>-46.60905822012348</v>
       </c>
       <c r="D387" s="4" t="s">
@@ -6815,13 +6846,13 @@
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A388" s="3" t="s">
+      <c r="A388" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B388" s="4">
+      <c r="B388" s="7">
         <v>-23.515997996484789</v>
       </c>
-      <c r="C388" s="4">
+      <c r="C388" s="7">
         <v>-46.609125690757487</v>
       </c>
       <c r="D388" s="4" t="s">
@@ -6829,13 +6860,13 @@
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A389" s="3" t="s">
+      <c r="A389" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B389" s="4">
+      <c r="B389" s="7">
         <v>-23.58698385549571</v>
       </c>
-      <c r="C389" s="4">
+      <c r="C389" s="7">
         <v>-46.671689406111518</v>
       </c>
       <c r="D389" s="4" t="s">
@@ -6843,13 +6874,13 @@
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A390" s="3" t="s">
+      <c r="A390" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B390" s="4">
+      <c r="B390" s="7">
         <v>-23.650150268594871</v>
       </c>
-      <c r="C390" s="4">
+      <c r="C390" s="7">
         <v>-46.677958860065658</v>
       </c>
       <c r="D390" s="4" t="s">
@@ -6857,13 +6888,13 @@
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A391" s="3" t="s">
+      <c r="A391" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B391" s="4">
+      <c r="B391" s="7">
         <v>-23.47289117254504</v>
       </c>
-      <c r="C391" s="4">
+      <c r="C391" s="7">
         <v>-46.52207849143646</v>
       </c>
       <c r="D391" s="4" t="s">
@@ -6871,13 +6902,13 @@
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A392" s="3" t="s">
+      <c r="A392" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B392" s="4">
+      <c r="B392" s="7">
         <v>-23.56536077118389</v>
       </c>
-      <c r="C392" s="4">
+      <c r="C392" s="7">
         <v>-46.500440332261029</v>
       </c>
       <c r="D392" s="4" t="s">
@@ -6885,13 +6916,13 @@
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A393" s="3" t="s">
+      <c r="A393" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B393" s="4">
+      <c r="B393" s="7">
         <v>-23.661359333585541</v>
       </c>
-      <c r="C393" s="4">
+      <c r="C393" s="7">
         <v>-46.520574457269959</v>
       </c>
       <c r="D393" s="4" t="s">
@@ -6899,13 +6930,13 @@
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A394" s="3" t="s">
+      <c r="A394" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B394" s="4">
+      <c r="B394" s="7">
         <v>-23.570707330093601</v>
       </c>
-      <c r="C394" s="4">
+      <c r="C394" s="7">
         <v>-46.720379967917701</v>
       </c>
       <c r="D394" s="4" t="s">
@@ -6913,13 +6944,13 @@
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A395" s="3" t="s">
+      <c r="A395" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B395" s="4">
+      <c r="B395" s="7">
         <v>-23.045459699579109</v>
       </c>
-      <c r="C395" s="4">
+      <c r="C395" s="7">
         <v>-45.583268119608519</v>
       </c>
       <c r="D395" s="4" t="s">
@@ -6927,13 +6958,13 @@
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A396" s="3" t="s">
+      <c r="A396" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B396" s="4">
+      <c r="B396" s="7">
         <v>-23.489014112668329</v>
       </c>
-      <c r="C396" s="4">
+      <c r="C396" s="7">
         <v>-46.654199878853412</v>
       </c>
       <c r="D396" s="4" t="s">
@@ -6941,13 +6972,13 @@
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A397" s="3" t="s">
+      <c r="A397" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B397" s="4">
+      <c r="B397" s="7">
         <v>-23.517930442486811</v>
       </c>
-      <c r="C397" s="4">
+      <c r="C397" s="7">
         <v>-46.609561860842398</v>
       </c>
       <c r="D397" s="4" t="s">
@@ -6955,13 +6986,13 @@
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A398" s="3" t="s">
+      <c r="A398" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B398" s="4">
+      <c r="B398" s="7">
         <v>-23.936341835223541</v>
       </c>
-      <c r="C398" s="4">
+      <c r="C398" s="7">
         <v>-46.330332980981289</v>
       </c>
       <c r="D398" s="4" t="s">
@@ -6969,13 +7000,13 @@
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A399" s="3" t="s">
+      <c r="A399" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B399" s="4">
+      <c r="B399" s="7">
         <v>-23.936241361134488</v>
       </c>
-      <c r="C399" s="4">
+      <c r="C399" s="7">
         <v>-46.329994816600603</v>
       </c>
       <c r="D399" s="4" t="s">
@@ -6983,13 +7014,13 @@
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A400" s="3" t="s">
+      <c r="A400" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B400" s="4">
+      <c r="B400" s="7">
         <v>-23.542180443534122</v>
       </c>
-      <c r="C400" s="4">
+      <c r="C400" s="7">
         <v>-46.547794314314849</v>
       </c>
       <c r="D400" s="4" t="s">
@@ -6997,13 +7028,13 @@
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A401" s="3" t="s">
+      <c r="A401" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B401" s="4">
+      <c r="B401" s="7">
         <v>-23.21299542490172</v>
       </c>
-      <c r="C401" s="4">
+      <c r="C401" s="7">
         <v>-45.891634145689373</v>
       </c>
       <c r="D401" s="4" t="s">
@@ -7011,13 +7042,13 @@
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A402" s="3" t="s">
+      <c r="A402" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B402" s="4">
+      <c r="B402" s="7">
         <v>-23.616689913358801</v>
       </c>
-      <c r="C402" s="4">
+      <c r="C402" s="7">
         <v>-46.73115851773855</v>
       </c>
       <c r="D402" s="4" t="s">
@@ -7025,13 +7056,13 @@
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A403" s="3" t="s">
+      <c r="A403" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B403" s="4">
+      <c r="B403" s="7">
         <v>-23.61617950543452</v>
       </c>
-      <c r="C403" s="4">
+      <c r="C403" s="7">
         <v>-46.55514996348554</v>
       </c>
       <c r="D403" s="4" t="s">
@@ -7039,13 +7070,13 @@
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A404" s="3" t="s">
+      <c r="A404" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B404" s="4">
+      <c r="B404" s="7">
         <v>-23.659527372292189</v>
       </c>
-      <c r="C404" s="4">
+      <c r="C404" s="7">
         <v>-46.679324804160899</v>
       </c>
       <c r="D404" s="4" t="s">
@@ -7053,13 +7084,13 @@
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A405" s="3" t="s">
+      <c r="A405" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B405" s="4">
+      <c r="B405" s="7">
         <v>-23.528986648887749</v>
       </c>
-      <c r="C405" s="4">
+      <c r="C405" s="7">
         <v>-46.202061720611603</v>
       </c>
       <c r="D405" s="4" t="s">
@@ -7067,13 +7098,13 @@
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A406" s="3" t="s">
+      <c r="A406" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B406" s="4">
+      <c r="B406" s="7">
         <v>-23.6165818644177</v>
       </c>
-      <c r="C406" s="4">
+      <c r="C406" s="7">
         <v>-46.609124019590261</v>
       </c>
       <c r="D406" s="4" t="s">
@@ -7081,13 +7112,13 @@
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A407" s="3" t="s">
+      <c r="A407" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B407" s="4">
+      <c r="B407" s="7">
         <v>-23.614889538343611</v>
       </c>
-      <c r="C407" s="4">
+      <c r="C407" s="7">
         <v>-45.43082713953082</v>
       </c>
       <c r="D407" s="4" t="s">
@@ -7095,13 +7126,13 @@
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A408" s="3" t="s">
+      <c r="A408" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B408" s="4">
+      <c r="B408" s="7">
         <v>-23.583207587411191</v>
       </c>
-      <c r="C408" s="4">
+      <c r="C408" s="7">
         <v>-46.575700250279112</v>
       </c>
       <c r="D408" s="4" t="s">
@@ -7109,13 +7140,13 @@
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A409" s="3" t="s">
+      <c r="A409" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B409" s="4">
+      <c r="B409" s="7">
         <v>-23.52333118643968</v>
       </c>
-      <c r="C409" s="4">
+      <c r="C409" s="7">
         <v>-46.687814811526337</v>
       </c>
       <c r="D409" s="4" t="s">
@@ -7123,13 +7154,13 @@
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A410" s="3" t="s">
+      <c r="A410" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B410" s="4">
+      <c r="B410" s="7">
         <v>-23.512812952205699</v>
       </c>
-      <c r="C410" s="4">
+      <c r="C410" s="7">
         <v>-46.703434205721571</v>
       </c>
       <c r="D410" s="4" t="s">
@@ -7137,13 +7168,13 @@
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A411" s="3" t="s">
+      <c r="A411" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B411" s="4">
+      <c r="B411" s="7">
         <v>-23.600163797091621</v>
       </c>
-      <c r="C411" s="4">
+      <c r="C411" s="7">
         <v>-46.647396065554943</v>
       </c>
       <c r="D411" s="4" t="s">
@@ -7151,13 +7182,13 @@
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A412" s="3" t="s">
+      <c r="A412" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B412" s="4">
+      <c r="B412" s="7">
         <v>-23.529221288285211</v>
       </c>
-      <c r="C412" s="4">
+      <c r="C412" s="7">
         <v>-46.202022417007768</v>
       </c>
       <c r="D412" s="4" t="s">
@@ -7165,13 +7196,13 @@
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A413" s="3" t="s">
+      <c r="A413" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B413" s="4">
+      <c r="B413" s="7">
         <v>-23.592473033312061</v>
       </c>
-      <c r="C413" s="4">
+      <c r="C413" s="7">
         <v>-46.621634868423968</v>
       </c>
       <c r="D413" s="4" t="s">
@@ -7179,13 +7210,13 @@
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A414" s="3" t="s">
+      <c r="A414" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B414" s="4">
+      <c r="B414" s="7">
         <v>-23.49786360950602</v>
       </c>
-      <c r="C414" s="4">
+      <c r="C414" s="7">
         <v>-46.455292573149649</v>
       </c>
       <c r="D414" s="4" t="s">
@@ -7193,13 +7224,13 @@
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A415" s="3" t="s">
+      <c r="A415" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B415" s="4">
+      <c r="B415" s="7">
         <v>-23.674672154258179</v>
       </c>
-      <c r="C415" s="4">
+      <c r="C415" s="7">
         <v>-46.55702542861637</v>
       </c>
       <c r="D415" s="4" t="s">
@@ -7207,13 +7238,13 @@
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A416" s="3" t="s">
+      <c r="A416" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B416" s="4">
-        <v>-23.66215145705554</v>
-      </c>
-      <c r="C416" s="4">
+      <c r="B416" s="7">
+        <v>-23.662151457055501</v>
+      </c>
+      <c r="C416" s="7">
         <v>-46.518995308408897</v>
       </c>
       <c r="D416" s="4" t="s">
@@ -7221,13 +7252,13 @@
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A417" s="5" t="s">
+      <c r="A417" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B417" s="4">
+      <c r="B417" s="7">
         <v>-23.469118999999999</v>
       </c>
-      <c r="C417" s="4">
+      <c r="C417" s="7">
         <v>-46.478465</v>
       </c>
       <c r="D417" s="4" t="s">
@@ -7235,10 +7266,592 @@
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A418" s="4"/>
-      <c r="B418" s="6"/>
-      <c r="C418" s="7"/>
-      <c r="D418" s="4"/>
+      <c r="A418" t="s">
+        <v>327</v>
+      </c>
+      <c r="B418" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="C418" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="D418" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>330</v>
+      </c>
+      <c r="B419" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C419" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>333</v>
+      </c>
+      <c r="B420" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C420" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="D420" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D421" s="4"/>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D422" s="4"/>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D423" s="4"/>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D424" s="4"/>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D425" s="4"/>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D426" s="4"/>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D427" s="4"/>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D428" s="4"/>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D429" s="4"/>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D430" s="4"/>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D431" s="4"/>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D432" s="4"/>
+    </row>
+    <row r="433" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D433" s="4"/>
+    </row>
+    <row r="434" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D434" s="4"/>
+    </row>
+    <row r="435" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D435" s="4"/>
+    </row>
+    <row r="436" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D436" s="4"/>
+    </row>
+    <row r="437" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D437" s="4"/>
+    </row>
+    <row r="438" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D438" s="4"/>
+    </row>
+    <row r="439" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D439" s="4"/>
+    </row>
+    <row r="440" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D440" s="4"/>
+    </row>
+    <row r="441" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D441" s="4"/>
+    </row>
+    <row r="442" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D442" s="4"/>
+    </row>
+    <row r="443" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D443" s="4"/>
+    </row>
+    <row r="444" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D444" s="4"/>
+    </row>
+    <row r="445" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D445" s="4"/>
+    </row>
+    <row r="446" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D446" s="4"/>
+    </row>
+    <row r="447" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D447" s="4"/>
+    </row>
+    <row r="448" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D448" s="4"/>
+    </row>
+    <row r="449" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D449" s="4"/>
+    </row>
+    <row r="450" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D450" s="4"/>
+    </row>
+    <row r="451" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D451" s="4"/>
+    </row>
+    <row r="452" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D452" s="4"/>
+    </row>
+    <row r="453" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D453" s="4"/>
+    </row>
+    <row r="454" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D454" s="4"/>
+    </row>
+    <row r="455" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D455" s="4"/>
+    </row>
+    <row r="456" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D456" s="4"/>
+    </row>
+    <row r="457" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D457" s="4"/>
+    </row>
+    <row r="458" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D458" s="4"/>
+    </row>
+    <row r="459" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D459" s="4"/>
+    </row>
+    <row r="460" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D460" s="4"/>
+    </row>
+    <row r="461" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D461" s="4"/>
+    </row>
+    <row r="462" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D462" s="4"/>
+    </row>
+    <row r="463" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D463" s="4"/>
+    </row>
+    <row r="464" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D464" s="4"/>
+    </row>
+    <row r="465" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D465" s="4"/>
+    </row>
+    <row r="466" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D466" s="4"/>
+    </row>
+    <row r="467" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D467" s="4"/>
+    </row>
+    <row r="468" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D468" s="4"/>
+    </row>
+    <row r="469" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D469" s="4"/>
+    </row>
+    <row r="470" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D470" s="4"/>
+    </row>
+    <row r="471" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D471" s="4"/>
+    </row>
+    <row r="472" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D472" s="4"/>
+    </row>
+    <row r="473" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D473" s="4"/>
+    </row>
+    <row r="474" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D474" s="4"/>
+    </row>
+    <row r="475" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D475" s="4"/>
+    </row>
+    <row r="476" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D476" s="4"/>
+    </row>
+    <row r="477" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D477" s="4"/>
+    </row>
+    <row r="478" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D478" s="4"/>
+    </row>
+    <row r="479" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D479" s="4"/>
+    </row>
+    <row r="480" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D480" s="4"/>
+    </row>
+    <row r="481" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D481" s="4"/>
+    </row>
+    <row r="482" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D482" s="4"/>
+    </row>
+    <row r="483" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D483" s="4"/>
+    </row>
+    <row r="484" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D484" s="4"/>
+    </row>
+    <row r="485" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D485" s="4"/>
+    </row>
+    <row r="486" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D486" s="4"/>
+    </row>
+    <row r="487" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D487" s="4"/>
+    </row>
+    <row r="488" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D488" s="4"/>
+    </row>
+    <row r="489" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D489" s="4"/>
+    </row>
+    <row r="490" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D490" s="4"/>
+    </row>
+    <row r="491" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D491" s="4"/>
+    </row>
+    <row r="492" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D492" s="4"/>
+    </row>
+    <row r="493" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D493" s="4"/>
+    </row>
+    <row r="494" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D494" s="4"/>
+    </row>
+    <row r="495" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D495" s="4"/>
+    </row>
+    <row r="496" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D496" s="4"/>
+    </row>
+    <row r="497" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D497" s="4"/>
+    </row>
+    <row r="498" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D498" s="4"/>
+    </row>
+    <row r="499" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D499" s="4"/>
+    </row>
+    <row r="500" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D500" s="4"/>
+    </row>
+    <row r="501" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D501" s="4"/>
+    </row>
+    <row r="502" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D502" s="4"/>
+    </row>
+    <row r="503" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D503" s="4"/>
+    </row>
+    <row r="504" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D504" s="4"/>
+    </row>
+    <row r="505" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D505" s="4"/>
+    </row>
+    <row r="506" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D506" s="4"/>
+    </row>
+    <row r="507" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D507" s="4"/>
+    </row>
+    <row r="508" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D508" s="4"/>
+    </row>
+    <row r="509" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D509" s="4"/>
+    </row>
+    <row r="510" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D510" s="4"/>
+    </row>
+    <row r="511" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D511" s="4"/>
+    </row>
+    <row r="512" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D512" s="4"/>
+    </row>
+    <row r="513" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D513" s="4"/>
+    </row>
+    <row r="514" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D514" s="4"/>
+    </row>
+    <row r="515" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D515" s="4"/>
+    </row>
+    <row r="516" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D516" s="4"/>
+    </row>
+    <row r="517" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D517" s="4"/>
+    </row>
+    <row r="518" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D518" s="4"/>
+    </row>
+    <row r="519" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D519" s="4"/>
+    </row>
+    <row r="520" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D520" s="4"/>
+    </row>
+    <row r="521" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D521" s="4"/>
+    </row>
+    <row r="522" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D522" s="4"/>
+    </row>
+    <row r="523" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D523" s="4"/>
+    </row>
+    <row r="524" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D524" s="4"/>
+    </row>
+    <row r="525" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D525" s="4"/>
+    </row>
+    <row r="526" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D526" s="4"/>
+    </row>
+    <row r="527" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D527" s="4"/>
+    </row>
+    <row r="528" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D528" s="4"/>
+    </row>
+    <row r="529" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D529" s="4"/>
+    </row>
+    <row r="530" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D530" s="4"/>
+    </row>
+    <row r="531" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D531" s="4"/>
+    </row>
+    <row r="532" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D532" s="4"/>
+    </row>
+    <row r="533" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D533" s="4"/>
+    </row>
+    <row r="534" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D534" s="4"/>
+    </row>
+    <row r="535" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D535" s="4"/>
+    </row>
+    <row r="536" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D536" s="4"/>
+    </row>
+    <row r="537" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D537" s="4"/>
+    </row>
+    <row r="538" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D538" s="4"/>
+    </row>
+    <row r="539" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D539" s="4"/>
+    </row>
+    <row r="540" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D540" s="4"/>
+    </row>
+    <row r="541" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D541" s="4"/>
+    </row>
+    <row r="542" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D542" s="4"/>
+    </row>
+    <row r="543" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D543" s="4"/>
+    </row>
+    <row r="544" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D544" s="4"/>
+    </row>
+    <row r="545" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D545" s="4"/>
+    </row>
+    <row r="546" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D546" s="4"/>
+    </row>
+    <row r="547" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D547" s="4"/>
+    </row>
+    <row r="548" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D548" s="4"/>
+    </row>
+    <row r="549" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D549" s="4"/>
+    </row>
+    <row r="550" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D550" s="4"/>
+    </row>
+    <row r="551" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D551" s="4"/>
+    </row>
+    <row r="552" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D552" s="4"/>
+    </row>
+    <row r="553" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D553" s="4"/>
+    </row>
+    <row r="554" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D554" s="4"/>
+    </row>
+    <row r="555" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D555" s="4"/>
+    </row>
+    <row r="556" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D556" s="4"/>
+    </row>
+    <row r="557" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D557" s="4"/>
+    </row>
+    <row r="558" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D558" s="4"/>
+    </row>
+    <row r="559" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D559" s="4"/>
+    </row>
+    <row r="560" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D560" s="4"/>
+    </row>
+    <row r="561" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D561" s="4"/>
+    </row>
+    <row r="562" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D562" s="4"/>
+    </row>
+    <row r="563" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D563" s="4"/>
+    </row>
+    <row r="564" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D564" s="4"/>
+    </row>
+    <row r="565" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D565" s="4"/>
+    </row>
+    <row r="566" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D566" s="4"/>
+    </row>
+    <row r="567" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D567" s="4"/>
+    </row>
+    <row r="568" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D568" s="4"/>
+    </row>
+    <row r="569" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D569" s="4"/>
+    </row>
+    <row r="570" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D570" s="4"/>
+    </row>
+    <row r="571" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D571" s="4"/>
+    </row>
+    <row r="572" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D572" s="4"/>
+    </row>
+    <row r="573" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D573" s="4"/>
+    </row>
+    <row r="574" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D574" s="4"/>
+    </row>
+    <row r="575" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D575" s="4"/>
+    </row>
+    <row r="576" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D576" s="4"/>
+    </row>
+    <row r="577" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D577" s="4"/>
+    </row>
+    <row r="578" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D578" s="4"/>
+    </row>
+    <row r="579" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D579" s="4"/>
+    </row>
+    <row r="580" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D580" s="4"/>
+    </row>
+    <row r="581" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D581" s="4"/>
+    </row>
+    <row r="582" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D582" s="4"/>
+    </row>
+    <row r="583" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D583" s="4"/>
+    </row>
+    <row r="584" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D584" s="4"/>
+    </row>
+    <row r="585" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D585" s="4"/>
+    </row>
+    <row r="586" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D586" s="4"/>
+    </row>
+    <row r="587" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D587" s="4"/>
+    </row>
+    <row r="588" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D588" s="4"/>
+    </row>
+    <row r="589" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D589" s="4"/>
+    </row>
+    <row r="590" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D590" s="4"/>
+    </row>
+    <row r="591" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D591" s="4"/>
+    </row>
+    <row r="592" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D592" s="4"/>
+    </row>
+    <row r="593" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D593" s="4"/>
+    </row>
+    <row r="594" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D594" s="4"/>
+    </row>
+    <row r="595" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D595" s="4"/>
+    </row>
+    <row r="596" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D596" s="4"/>
+    </row>
+    <row r="597" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D597" s="4"/>
+    </row>
+    <row r="598" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D598" s="4"/>
+    </row>
+    <row r="599" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D599" s="4"/>
+    </row>
+    <row r="600" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D600" s="4"/>
+    </row>
+    <row r="601" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D601" s="4"/>
+    </row>
+    <row r="602" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D602" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753C7EF0-9FF8-44C4-BD71-443314040C6E}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50E4E87E-71D0-4A14-91AA-4D405BAF86A4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="361">
   <si>
     <t>nome</t>
   </si>
@@ -1038,6 +1038,87 @@
   </si>
   <si>
     <t>Maisnove Med Diagnostica Ltda</t>
+  </si>
+  <si>
+    <t>-23.48657855930126</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.47016691774277</t>
+  </si>
+  <si>
+    <t>Bruna Oliveira Branco</t>
+  </si>
+  <si>
+    <t>-22.816959084641574</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.20179524679479</t>
+  </si>
+  <si>
+    <t>Cavalca Esp Gomes Med Diag Ltda</t>
+  </si>
+  <si>
+    <t>-23.612923085070907</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.443208104246565</t>
+  </si>
+  <si>
+    <t>Jailton Monteiro Dos Santos</t>
+  </si>
+  <si>
+    <t>-23.45758285539288</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.5878646114385</t>
+  </si>
+  <si>
+    <t>Sergio Luis Belem Ferreira Junior</t>
+  </si>
+  <si>
+    <t>-23.595336799409633</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.669321474611976</t>
+  </si>
+  <si>
+    <t>Duo Dermatologia Servicos Medicos L</t>
+  </si>
+  <si>
+    <t>-23.591768972267335</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.635527090755076</t>
+  </si>
+  <si>
+    <t>Joao Reis Com Prod Odonto Ltda Epp</t>
+  </si>
+  <si>
+    <t>-23.576331507748705</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64810419352019</t>
+  </si>
+  <si>
+    <t>Cdl - Central De Diagnosticos Labor</t>
+  </si>
+  <si>
+    <t>-23.957830534147675</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.32083131203267</t>
+  </si>
+  <si>
+    <t>General Doctors Sup Odonto Ltda Epp</t>
+  </si>
+  <si>
+    <t>-23.516799783036124</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.46528399614668</t>
+  </si>
+  <si>
+    <t>Bruno Campos Emidio</t>
   </si>
 </sst>
 </file>
@@ -7308,31 +7389,130 @@
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D421" s="4"/>
+      <c r="A421" t="s">
+        <v>336</v>
+      </c>
+      <c r="B421" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C421" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D422" s="4"/>
+      <c r="A422" t="s">
+        <v>339</v>
+      </c>
+      <c r="B422" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="C422" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D423" s="4"/>
+      <c r="A423" t="s">
+        <v>342</v>
+      </c>
+      <c r="B423" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="C423" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D424" s="4"/>
+      <c r="A424" t="s">
+        <v>345</v>
+      </c>
+      <c r="B424" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="C424" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D425" s="4"/>
+      <c r="A425" t="s">
+        <v>348</v>
+      </c>
+      <c r="B425" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C425" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D426" s="4"/>
+      <c r="A426" t="s">
+        <v>351</v>
+      </c>
+      <c r="B426" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C426" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="D426" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D427" s="4"/>
+      <c r="A427" t="s">
+        <v>354</v>
+      </c>
+      <c r="B427" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C427" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D428" s="4"/>
+      <c r="A428" t="s">
+        <v>357</v>
+      </c>
+      <c r="B428" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C428" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="D428" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D429" s="4"/>
+      <c r="A429" t="s">
+        <v>360</v>
+      </c>
+      <c r="B429" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C429" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="D429" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D430" s="4"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50E4E87E-71D0-4A14-91AA-4D405BAF86A4}"/>
+  <xr:revisionPtr revIDLastSave="364" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{655F0393-9D48-4415-B333-786207D06194}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="680">
   <si>
     <t>nome</t>
   </si>
@@ -1119,6 +1119,963 @@
   </si>
   <si>
     <t>Bruno Campos Emidio</t>
+  </si>
+  <si>
+    <t>-23.59924405841143</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.715295461918906</t>
+  </si>
+  <si>
+    <t>Soc Ben Israelita Bras H Albert Einstein</t>
+  </si>
+  <si>
+    <t>-23.59651378008784</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.7158458042471</t>
+  </si>
+  <si>
+    <t>ANDREA LAURATO SERTIE</t>
+  </si>
+  <si>
+    <t>-23.547535199432723</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.60001507726449</t>
+  </si>
+  <si>
+    <t>Inst. Brasileiro Controle Do Cancer</t>
+  </si>
+  <si>
+    <t>-23.596070315791028</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.677151817739265</t>
+  </si>
+  <si>
+    <t>Leandro Camacho Morant</t>
+  </si>
+  <si>
+    <t>-23.661617741271815</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.715714688901166</t>
+  </si>
+  <si>
+    <t>Janaina De Andrea Dernowsek</t>
+  </si>
+  <si>
+    <t>-23.661558779976502</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.71584343493269</t>
+  </si>
+  <si>
+    <t>Imd Medicina Diagnostica Ltda</t>
+  </si>
+  <si>
+    <t>-23.63016058540669</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.52182585561039</t>
+  </si>
+  <si>
+    <t>Rede Dor Sao Luiz Sa</t>
+  </si>
+  <si>
+    <t>-23.546548313897173</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.671234877264546</t>
+  </si>
+  <si>
+    <t>Valeria Marcondes Dermatologia Eire</t>
+  </si>
+  <si>
+    <t>-23.557817004541864</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67622860424828</t>
+  </si>
+  <si>
+    <t>Patricia Lerro De Paula Exuardo</t>
+  </si>
+  <si>
+    <t>-23.597340136000188</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68323016115303</t>
+  </si>
+  <si>
+    <t>Elisa Abreu Diniz Odontologia Ltda</t>
+  </si>
+  <si>
+    <t>-23.569092101107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.58561743308392</t>
+  </si>
+  <si>
+    <t>Assoc Benef Filantr S Cristovao</t>
+  </si>
+  <si>
+    <t>-23.965070068321157</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.33329386738097</t>
+  </si>
+  <si>
+    <t>Wagner Dental Viva Cosmetics Ltda M</t>
+  </si>
+  <si>
+    <t>-23.961701913215787</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.332504219591726</t>
+  </si>
+  <si>
+    <t>Instituto De Analises Clinicas De S</t>
+  </si>
+  <si>
+    <t>-23.95093714346995</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.331330617727794</t>
+  </si>
+  <si>
+    <t>Imuno Santos Onc E C D Infusao Ltda</t>
+  </si>
+  <si>
+    <t>-23.192718319867105</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.89721553309595</t>
+  </si>
+  <si>
+    <t>Centro De Imunobiologicos Imunecare</t>
+  </si>
+  <si>
+    <t>-23.594063676049423</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.47980020795055</t>
+  </si>
+  <si>
+    <t>Mariana Antunes Tresseno Dos Santos</t>
+  </si>
+  <si>
+    <t>-23.215261756442803</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.891789604259436</t>
+  </si>
+  <si>
+    <t>E-CONIC COMERCIO E IMPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t>-23.5531310336515</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66214364842842</t>
+  </si>
+  <si>
+    <t>Dra.Thais Tosta Clinica Medica Ltda</t>
+  </si>
+  <si>
+    <t>-23.49901386113877</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.755733269699434</t>
+  </si>
+  <si>
+    <t>Drs Adm De Estoques Ltda</t>
+  </si>
+  <si>
+    <t>-23.176415391367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.818532055708516</t>
+  </si>
+  <si>
+    <t>Renata Moreira Machado</t>
+  </si>
+  <si>
+    <t>-23.52789023347353</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.510201511813584</t>
+  </si>
+  <si>
+    <t>Dental Romano Ltda</t>
+  </si>
+  <si>
+    <t>-23.18702504354697</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.881652497590714</t>
+  </si>
+  <si>
+    <t>Serv. Hemot. Sao Jose Dos Campos Lt</t>
+  </si>
+  <si>
+    <t>-23.62689827756966</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.70181527541019</t>
+  </si>
+  <si>
+    <t>Amil Assistencia Medica Internacion</t>
+  </si>
+  <si>
+    <t>-23.166393765103336</t>
+  </si>
+  <si>
+    <t>Aigla Eduarda Lopes Soares</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.84131945360565</t>
+  </si>
+  <si>
+    <t>-23.48641055628623</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.63345386471398</t>
+  </si>
+  <si>
+    <t>Prevent Senior Atendimento</t>
+  </si>
+  <si>
+    <t>-23.66972770764289</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.56555417626507</t>
+  </si>
+  <si>
+    <t>Notre Dame Intermedica Saude S A</t>
+  </si>
+  <si>
+    <t>-23.52764865375098</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.69777192381932</t>
+  </si>
+  <si>
+    <t>Pensabio Instrumentos De Biotecnolo</t>
+  </si>
+  <si>
+    <t>-23.28122127901839</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.979860954102634</t>
+  </si>
+  <si>
+    <t>ROHM AND HAAS QUIMICA LTDA</t>
+  </si>
+  <si>
+    <t>-23.56253388406278</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.57968188890444</t>
+  </si>
+  <si>
+    <t>Luciane Barbaroto</t>
+  </si>
+  <si>
+    <t>-23.582149861587375</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64029348482453</t>
+  </si>
+  <si>
+    <t>Amico Saude Ltda</t>
+  </si>
+  <si>
+    <t>-23.582327601207936</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64039049064312</t>
+  </si>
+  <si>
+    <t>Allianca Saude E Participacoes S.A</t>
+  </si>
+  <si>
+    <t>-23.965697993833246</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.33183401438957</t>
+  </si>
+  <si>
+    <t>Sueli Anjos</t>
+  </si>
+  <si>
+    <t>-23.648414027751862</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.522554639113004</t>
+  </si>
+  <si>
+    <t>Dental Focus Com Prod Odonto Ltda E</t>
+  </si>
+  <si>
+    <t>-23.690509961247088</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.55895660424402</t>
+  </si>
+  <si>
+    <t>Tec Lab Medicina Diagnostica Sa</t>
+  </si>
+  <si>
+    <t>-23.501075215058357</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.63109362002816</t>
+  </si>
+  <si>
+    <t>Clinica Nr Ortopedia E Dermato Ltda</t>
+  </si>
+  <si>
+    <t>-23.584247215363956</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.676113119591264</t>
+  </si>
+  <si>
+    <t>Ligia Borges Novais Braga Saude Est</t>
+  </si>
+  <si>
+    <t>-23.585603892386334</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.675569760067646</t>
+  </si>
+  <si>
+    <t>Bclinique Medicina Ltda</t>
+  </si>
+  <si>
+    <t>-23.62888448010237</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.579405304246144</t>
+  </si>
+  <si>
+    <t>Rede D'or Sao Luiz S.A</t>
+  </si>
+  <si>
+    <t>-23.471475578892306</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.52853598633261</t>
+  </si>
+  <si>
+    <t>-23.61558623282507</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67551497726225</t>
+  </si>
+  <si>
+    <t>Clinica Paulista De Fisiatria Ltda</t>
+  </si>
+  <si>
+    <t>-23.51770801274468</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.6951863330857</t>
+  </si>
+  <si>
+    <t>Notre Dame Intermedica Saude S.A</t>
+  </si>
+  <si>
+    <t>-23.60640913468782</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.669497586303294</t>
+  </si>
+  <si>
+    <t>Clinica Ya. Serv. Medicos Ltda</t>
+  </si>
+  <si>
+    <t>-22.73320488166142</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.126635933110435</t>
+  </si>
+  <si>
+    <t>Municipio De Lorena</t>
+  </si>
+  <si>
+    <t>-23.53837173544398</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.31069715072797</t>
+  </si>
+  <si>
+    <t>Luizmed Artigos Medicos E Ortopedicos Ltda</t>
+  </si>
+  <si>
+    <t>-23.583794524535868</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66766783493534</t>
+  </si>
+  <si>
+    <t>Luciana Lourenco Dermatologia Ltda</t>
+  </si>
+  <si>
+    <t>-23.58134698798248</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66429701959141</t>
+  </si>
+  <si>
+    <t>Clinica Adriana Vilarinho Ltda</t>
+  </si>
+  <si>
+    <t>-23.20645697703737</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.89970022594616</t>
+  </si>
+  <si>
+    <t>Lessandra Oliveira Da Silva Me</t>
+  </si>
+  <si>
+    <t>-23.596090407837888</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.653860738623344</t>
+  </si>
+  <si>
+    <t>Inst Assist Med Serv Pub Est Iamspe</t>
+  </si>
+  <si>
+    <t>-23.597110481071418</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64315406006723</t>
+  </si>
+  <si>
+    <t>Spdm Associacao Paulista Desenv Med</t>
+  </si>
+  <si>
+    <t>-23.59599855673328</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64592944842705</t>
+  </si>
+  <si>
+    <t>Fund Oswaldo Ramos</t>
+  </si>
+  <si>
+    <t>-23.613576659444846</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.62514647516981</t>
+  </si>
+  <si>
+    <t>Dental Ricardo Tanaka Ltda</t>
+  </si>
+  <si>
+    <t>-23.613168701555775</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.62062897354862</t>
+  </si>
+  <si>
+    <t>Notre Dame Intermedica Saude Sa</t>
+  </si>
+  <si>
+    <t>-23.709262218316884</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.557071411413325</t>
+  </si>
+  <si>
+    <t>Jorge Santangelo</t>
+  </si>
+  <si>
+    <t>-23.176830565888835</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.8732009633132</t>
+  </si>
+  <si>
+    <t>Dra. Tassia Camargo Orlando</t>
+  </si>
+  <si>
+    <t>-23.546473462188814</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.60459559075667</t>
+  </si>
+  <si>
+    <t>-23.564545322568424</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64667116006839</t>
+  </si>
+  <si>
+    <t>Hosp Alvorada Taguatinga Ltd</t>
+  </si>
+  <si>
+    <t>-23.57228774158005</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.690345319591714</t>
+  </si>
+  <si>
+    <t>Guilherme Saavedra</t>
+  </si>
+  <si>
+    <t>-23.570195165800833</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65139727468047</t>
+  </si>
+  <si>
+    <t>Spdm Assoc Paulista Des Medicina</t>
+  </si>
+  <si>
+    <t>-23.579850554648978</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.663756461919505</t>
+  </si>
+  <si>
+    <t>Prevent Senior Atendimento A Saude</t>
+  </si>
+  <si>
+    <t>-23.582939124950776</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66823574842731</t>
+  </si>
+  <si>
+    <t>Inside Diagnosticos, Pesquisa E Des</t>
+  </si>
+  <si>
+    <t>-23.570581186393994</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65148093100067</t>
+  </si>
+  <si>
+    <t>Spdm Ass Paulista P O D Da Medicina</t>
+  </si>
+  <si>
+    <t>-23.652470289776474</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66803023122961</t>
+  </si>
+  <si>
+    <t>Adriana Rosa Da Silva</t>
+  </si>
+  <si>
+    <t>-23.537697485602877</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.40310419472534</t>
+  </si>
+  <si>
+    <t>Hospital E Pronto Socorro Comum</t>
+  </si>
+  <si>
+    <t>-23.675428729682377</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.50885712676452</t>
+  </si>
+  <si>
+    <t>Claudio Roberto Da Silva</t>
+  </si>
+  <si>
+    <t>-23.523654999757223</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.94053961774157</t>
+  </si>
+  <si>
+    <t>Diasorin Ltda</t>
+  </si>
+  <si>
+    <t>-23.663511603637836</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.56979579075276</t>
+  </si>
+  <si>
+    <t>-23.566448264561934</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.653629719592004</t>
+  </si>
+  <si>
+    <t>Dra. Gladys Mouessati Abud Mattei</t>
+  </si>
+  <si>
+    <t>-23.537000873491234</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.223068304249</t>
+  </si>
+  <si>
+    <t>Sancet Lab De Anal. Clinicas Ltda</t>
+  </si>
+  <si>
+    <t>-23.52267080395284</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.1906877421417</t>
+  </si>
+  <si>
+    <t>Lab De Protese Dentaria Cruz Ltda</t>
+  </si>
+  <si>
+    <t>-23.52189676928448</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.17909250239773</t>
+  </si>
+  <si>
+    <t>Dental Med Mogi Prod Odo E Med Ltda</t>
+  </si>
+  <si>
+    <t>-22.738235959553514</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.11589431961807</t>
+  </si>
+  <si>
+    <t>-22.574663215483596</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -44.957253182248934</t>
+  </si>
+  <si>
+    <t>Municipio De Cruzeiro</t>
+  </si>
+  <si>
+    <t>-23.613126598323237</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.63370748313514</t>
+  </si>
+  <si>
+    <t>Julio Cesar Bassi</t>
+  </si>
+  <si>
+    <t>-23.556536379499118</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67982864657644</t>
+  </si>
+  <si>
+    <t>Fleury S A</t>
+  </si>
+  <si>
+    <t>-23.56052072080297</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68740314842879</t>
+  </si>
+  <si>
+    <t>Matheus De Alencar Ichigi</t>
+  </si>
+  <si>
+    <t>-23.560491217411833</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68737096192091</t>
+  </si>
+  <si>
+    <t>Ph7 Com. Repr. Prod. P/ Diagn. Ltda</t>
+  </si>
+  <si>
+    <t>-23.224585613968976</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.90959150162788</t>
+  </si>
+  <si>
+    <t>Geia Clinica Medica Ltda</t>
+  </si>
+  <si>
+    <t>-23.205532664970143</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.895400342210095</t>
+  </si>
+  <si>
+    <t>Odontomed Do Vale De Pro Med E Od E</t>
+  </si>
+  <si>
+    <t>-23.55519803782628</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.5896179600687</t>
+  </si>
+  <si>
+    <t>G S H Corp Participacoes S.A</t>
+  </si>
+  <si>
+    <t>-23.224334290053843</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.91147251775115</t>
+  </si>
+  <si>
+    <t>Ariane Micaela Dantas Dos Santos</t>
+  </si>
+  <si>
+    <t>-23.652882728151074</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.53061561958913</t>
+  </si>
+  <si>
+    <t>Santa Helena A Me S A</t>
+  </si>
+  <si>
+    <t>-23.53751171061186</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68272130239733</t>
+  </si>
+  <si>
+    <t>Abbvie Farmaceutica Ltda</t>
+  </si>
+  <si>
+    <t>-23.542259962382044</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.5734937195927</t>
+  </si>
+  <si>
+    <t>Unen Servicos Medicos Ltda</t>
+  </si>
+  <si>
+    <t>-23.039068435154267</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.63579186639595</t>
+  </si>
+  <si>
+    <t>Daniele Cristina De Campos Mariano</t>
+  </si>
+  <si>
+    <t>-23.514613590727294</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.69483277468291</t>
+  </si>
+  <si>
+    <t>Kulzer South America Ltda</t>
+  </si>
+  <si>
+    <t>-23.56989096507761</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.644273506099765</t>
+  </si>
+  <si>
+    <t>Centro Dermatologico Sergio Talaric</t>
+  </si>
+  <si>
+    <t>-23.034993878497144</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.57249823495269</t>
+  </si>
+  <si>
+    <t>Adriana Franca Moreno</t>
+  </si>
+  <si>
+    <t>-23.870060842918182</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.41341858249727</t>
+  </si>
+  <si>
+    <t>Unipar Carbocloro Sa</t>
+  </si>
+  <si>
+    <t>-23.539573130396537</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66184984842871</t>
+  </si>
+  <si>
+    <t>Esho Empresa Serv Hospitalares S A</t>
+  </si>
+  <si>
+    <t>-23.952192550607972</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.32276425785174</t>
+  </si>
+  <si>
+    <t>Brunno Henrique Da Silva Miura35332054874</t>
+  </si>
+  <si>
+    <t>-23.620071006735152</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67676642499048</t>
+  </si>
+  <si>
+    <t>Vyvian Cristina Cassano</t>
+  </si>
+  <si>
+    <t>-23.10594057938862</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.70759493309873</t>
+  </si>
+  <si>
+    <t>Unimed De Cacapava C D Tra Medico</t>
+  </si>
+  <si>
+    <t>-23.106686044381412</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.707378733098714</t>
+  </si>
+  <si>
+    <t>Clinica Medica Vili Ltda</t>
+  </si>
+  <si>
+    <t>-23.53000747060739</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68315838890538</t>
+  </si>
+  <si>
+    <t>Sandra Kalil Bussadori</t>
+  </si>
+  <si>
+    <t>-23.55895809813347</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.6775717016574</t>
+  </si>
+  <si>
+    <t>Caio Bellinati</t>
+  </si>
+  <si>
+    <t>-23.555221446922896</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67962734842823</t>
+  </si>
+  <si>
+    <t>-23.55747763442108</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65428777726421</t>
+  </si>
+  <si>
+    <t>Soc Benef Sras Hosp Sirio Libanes</t>
+  </si>
+  <si>
+    <t>-23.366374238251097</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.229526785923355</t>
+  </si>
+  <si>
+    <t>Ultrafarma Saude Ltda</t>
+  </si>
+  <si>
+    <t>-23.55190490662209</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.624803646576645</t>
+  </si>
+  <si>
+    <t>-23.556506440469036</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.59396459075626</t>
+  </si>
+  <si>
+    <t>Zl Dental Produto Odontologico Ltda</t>
+  </si>
+  <si>
+    <t>-23.556440681440204</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65309690165781</t>
+  </si>
+  <si>
+    <t>-23.606796504105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.73703563123102</t>
+  </si>
+  <si>
+    <t>Fernando Rodrigues Costa</t>
+  </si>
+  <si>
+    <t>-23.643124770010438</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64182773122985</t>
+  </si>
+  <si>
+    <t>-23.660245103468323</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.77292558629147</t>
+  </si>
+  <si>
+    <t>SERRA MAYOR SERVICOS MEDICOS S A</t>
+  </si>
+  <si>
+    <t>-23.62228940333357</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.60461464842615</t>
+  </si>
+  <si>
+    <t>Mauro Itaru Honda</t>
+  </si>
+  <si>
+    <t>-23.031607838609396</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.57871766008529</t>
+  </si>
+  <si>
+    <t>Gustavo De Sousa Fortes Carvalho</t>
+  </si>
+  <si>
+    <t>-23.595734787861023</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.667305581955</t>
+  </si>
+  <si>
+    <t>Clinica Medica Conceito Ltda</t>
+  </si>
+  <si>
+    <t>-23.5696259357908</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.693084004247986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dra. Renata De Avila Silva | Avila Dermatologia E Clin. Medica | Jro Consultorio Medico S/C Ltda | 2Csj Medicos Associados Ltda </t>
+  </si>
+  <si>
+    <t>-23.213994054385118</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.907347602407484</t>
+  </si>
+  <si>
+    <t>Andreia Verri Silva</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +2132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1197,6 +2154,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1499,7 +2457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D602"/>
+  <dimension ref="A1:J602"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.77734375" customWidth="1"/>
@@ -7515,348 +8473,1549 @@
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D430" s="4"/>
+      <c r="A430" t="s">
+        <v>363</v>
+      </c>
+      <c r="B430" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C430" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="D430" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D431" s="4"/>
+      <c r="A431" t="s">
+        <v>366</v>
+      </c>
+      <c r="B431" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C431" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D432" s="4"/>
-    </row>
-    <row r="433" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D433" s="4"/>
-    </row>
-    <row r="434" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D434" s="4"/>
-    </row>
-    <row r="435" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D435" s="4"/>
-    </row>
-    <row r="436" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D436" s="4"/>
-    </row>
-    <row r="437" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D437" s="4"/>
-    </row>
-    <row r="438" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D438" s="4"/>
-    </row>
-    <row r="439" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D439" s="4"/>
-    </row>
-    <row r="440" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D440" s="4"/>
-    </row>
-    <row r="441" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D441" s="4"/>
-    </row>
-    <row r="442" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D442" s="4"/>
-    </row>
-    <row r="443" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D443" s="4"/>
-    </row>
-    <row r="444" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D444" s="4"/>
-    </row>
-    <row r="445" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D445" s="4"/>
-    </row>
-    <row r="446" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D446" s="4"/>
-    </row>
-    <row r="447" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D447" s="4"/>
-    </row>
-    <row r="448" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D448" s="4"/>
-    </row>
-    <row r="449" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D449" s="4"/>
-    </row>
-    <row r="450" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D450" s="4"/>
-    </row>
-    <row r="451" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D451" s="4"/>
-    </row>
-    <row r="452" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D452" s="4"/>
-    </row>
-    <row r="453" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D453" s="4"/>
-    </row>
-    <row r="454" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D454" s="4"/>
-    </row>
-    <row r="455" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D455" s="4"/>
-    </row>
-    <row r="456" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D456" s="4"/>
-    </row>
-    <row r="457" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D457" s="4"/>
-    </row>
-    <row r="458" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D458" s="4"/>
-    </row>
-    <row r="459" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D459" s="4"/>
-    </row>
-    <row r="460" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D460" s="4"/>
-    </row>
-    <row r="461" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D461" s="4"/>
-    </row>
-    <row r="462" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D462" s="4"/>
-    </row>
-    <row r="463" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D463" s="4"/>
-    </row>
-    <row r="464" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D464" s="4"/>
-    </row>
-    <row r="465" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D465" s="4"/>
-    </row>
-    <row r="466" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D466" s="4"/>
-    </row>
-    <row r="467" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D467" s="4"/>
-    </row>
-    <row r="468" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D468" s="4"/>
-    </row>
-    <row r="469" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D469" s="4"/>
-    </row>
-    <row r="470" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D470" s="4"/>
-    </row>
-    <row r="471" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D471" s="4"/>
-    </row>
-    <row r="472" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D472" s="4"/>
-    </row>
-    <row r="473" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D473" s="4"/>
-    </row>
-    <row r="474" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D474" s="4"/>
-    </row>
-    <row r="475" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D475" s="4"/>
-    </row>
-    <row r="476" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D476" s="4"/>
-    </row>
-    <row r="477" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D477" s="4"/>
-    </row>
-    <row r="478" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D478" s="4"/>
-    </row>
-    <row r="479" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D479" s="4"/>
-    </row>
-    <row r="480" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D480" s="4"/>
-    </row>
-    <row r="481" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D481" s="4"/>
-    </row>
-    <row r="482" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D482" s="4"/>
-    </row>
-    <row r="483" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D483" s="4"/>
-    </row>
-    <row r="484" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D484" s="4"/>
-    </row>
-    <row r="485" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D485" s="4"/>
-    </row>
-    <row r="486" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D486" s="4"/>
-    </row>
-    <row r="487" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D487" s="4"/>
-    </row>
-    <row r="488" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D488" s="4"/>
-    </row>
-    <row r="489" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D489" s="4"/>
-    </row>
-    <row r="490" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D490" s="4"/>
-    </row>
-    <row r="491" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D491" s="4"/>
-    </row>
-    <row r="492" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D492" s="4"/>
-    </row>
-    <row r="493" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D493" s="4"/>
-    </row>
-    <row r="494" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D494" s="4"/>
-    </row>
-    <row r="495" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D495" s="4"/>
-    </row>
-    <row r="496" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D496" s="4"/>
-    </row>
-    <row r="497" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D497" s="4"/>
-    </row>
-    <row r="498" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D498" s="4"/>
-    </row>
-    <row r="499" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D499" s="4"/>
-    </row>
-    <row r="500" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D500" s="4"/>
-    </row>
-    <row r="501" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D501" s="4"/>
-    </row>
-    <row r="502" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D502" s="4"/>
-    </row>
-    <row r="503" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D503" s="4"/>
-    </row>
-    <row r="504" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D504" s="4"/>
-    </row>
-    <row r="505" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D505" s="4"/>
-    </row>
-    <row r="506" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D506" s="4"/>
-    </row>
-    <row r="507" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D507" s="4"/>
-    </row>
-    <row r="508" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D508" s="4"/>
-    </row>
-    <row r="509" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D509" s="4"/>
-    </row>
-    <row r="510" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D510" s="4"/>
-    </row>
-    <row r="511" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D511" s="4"/>
-    </row>
-    <row r="512" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D512" s="4"/>
-    </row>
-    <row r="513" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D513" s="4"/>
-    </row>
-    <row r="514" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D514" s="4"/>
-    </row>
-    <row r="515" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D515" s="4"/>
-    </row>
-    <row r="516" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D516" s="4"/>
-    </row>
-    <row r="517" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D517" s="4"/>
-    </row>
-    <row r="518" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D518" s="4"/>
-    </row>
-    <row r="519" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D519" s="4"/>
-    </row>
-    <row r="520" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D520" s="4"/>
-    </row>
-    <row r="521" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D521" s="4"/>
-    </row>
-    <row r="522" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D522" s="4"/>
-    </row>
-    <row r="523" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D523" s="4"/>
-    </row>
-    <row r="524" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D524" s="4"/>
-    </row>
-    <row r="525" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D525" s="4"/>
-    </row>
-    <row r="526" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D526" s="4"/>
-    </row>
-    <row r="527" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D527" s="4"/>
-    </row>
-    <row r="528" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D528" s="4"/>
-    </row>
-    <row r="529" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D529" s="4"/>
-    </row>
-    <row r="530" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D530" s="4"/>
-    </row>
-    <row r="531" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D531" s="4"/>
-    </row>
-    <row r="532" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D532" s="4"/>
-    </row>
-    <row r="533" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D533" s="4"/>
-    </row>
-    <row r="534" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D534" s="4"/>
-    </row>
-    <row r="535" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D535" s="4"/>
-    </row>
-    <row r="536" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D536" s="4"/>
-    </row>
-    <row r="537" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D537" s="4"/>
-    </row>
-    <row r="538" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D538" s="4"/>
-    </row>
-    <row r="539" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>369</v>
+      </c>
+      <c r="B432" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C432" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="D432" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>372</v>
+      </c>
+      <c r="B433" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C433" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="D433" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>375</v>
+      </c>
+      <c r="B434" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C434" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D434" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>378</v>
+      </c>
+      <c r="B435" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C435" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D435" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>381</v>
+      </c>
+      <c r="B436" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="C436" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D436" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>384</v>
+      </c>
+      <c r="B437" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="C437" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="D437" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>387</v>
+      </c>
+      <c r="B438" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="C438" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>390</v>
+      </c>
+      <c r="B439" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C439" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="D439" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>393</v>
+      </c>
+      <c r="B440" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C440" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D440" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>396</v>
+      </c>
+      <c r="B441" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C441" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="D441" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>399</v>
+      </c>
+      <c r="B442" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C442" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D442" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="I442" s="9"/>
+      <c r="J442" s="9"/>
+    </row>
+    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>402</v>
+      </c>
+      <c r="B443" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C443" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="D443" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>405</v>
+      </c>
+      <c r="B444" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C444" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="D444" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>408</v>
+      </c>
+      <c r="B445" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C445" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="D445" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>411</v>
+      </c>
+      <c r="B446" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C446" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="D446" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>414</v>
+      </c>
+      <c r="B447" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="C447" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D447" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>417</v>
+      </c>
+      <c r="B448" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C448" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D448" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>420</v>
+      </c>
+      <c r="B449" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="C449" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D449" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>423</v>
+      </c>
+      <c r="B450" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="C450" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="D450" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>426</v>
+      </c>
+      <c r="B451" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="C451" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="D451" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>429</v>
+      </c>
+      <c r="B452" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="C452" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D452" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>431</v>
+      </c>
+      <c r="B453" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C453" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="D453" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>435</v>
+      </c>
+      <c r="B454" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="C454" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D454" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>438</v>
+      </c>
+      <c r="B455" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C455" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="D455" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>441</v>
+      </c>
+      <c r="B456" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="C456" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="D456" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>444</v>
+      </c>
+      <c r="B457" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C457" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="D457" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>447</v>
+      </c>
+      <c r="B458" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="C458" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D458" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>450</v>
+      </c>
+      <c r="B459" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="C459" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="D459" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>453</v>
+      </c>
+      <c r="B460" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="C460" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D460" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>456</v>
+      </c>
+      <c r="B461" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="C461" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="D461" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>459</v>
+      </c>
+      <c r="B462" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="C462" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="D462" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>462</v>
+      </c>
+      <c r="B463" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C463" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D463" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>465</v>
+      </c>
+      <c r="B464" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="C464" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="D464" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>468</v>
+      </c>
+      <c r="B465" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C465" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="D465" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>471</v>
+      </c>
+      <c r="B466" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="C466" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="D466" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>474</v>
+      </c>
+      <c r="B467" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="C467" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D467" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>450</v>
+      </c>
+      <c r="B468" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="C468" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="D468" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>479</v>
+      </c>
+      <c r="B469" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="C469" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="D469" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>482</v>
+      </c>
+      <c r="B470" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="C470" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="D470" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>485</v>
+      </c>
+      <c r="B471" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="C471" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="D471" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>488</v>
+      </c>
+      <c r="B472" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="C472" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="D472" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>491</v>
+      </c>
+      <c r="B473" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="C473" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="D473" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>494</v>
+      </c>
+      <c r="B474" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="C474" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="D474" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>497</v>
+      </c>
+      <c r="B475" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="C475" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="D475" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>500</v>
+      </c>
+      <c r="B476" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="C476" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="D476" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>503</v>
+      </c>
+      <c r="B477" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="C477" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="D477" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>506</v>
+      </c>
+      <c r="B478" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="C478" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="D478" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>509</v>
+      </c>
+      <c r="B479" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C479" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="D479" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>512</v>
+      </c>
+      <c r="B480" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="C480" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="D480" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>515</v>
+      </c>
+      <c r="B481" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="C481" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D481" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>518</v>
+      </c>
+      <c r="B482" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="C482" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="D482" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>521</v>
+      </c>
+      <c r="B483" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="C483" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="D483" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>438</v>
+      </c>
+      <c r="B484" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="C484" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="D484" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>526</v>
+      </c>
+      <c r="B485" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="C485" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D485" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>529</v>
+      </c>
+      <c r="B486" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="C486" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D486" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>532</v>
+      </c>
+      <c r="B487" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="C487" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="D487" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>535</v>
+      </c>
+      <c r="B488" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="C488" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="D488" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>538</v>
+      </c>
+      <c r="B489" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="C489" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="D489" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>541</v>
+      </c>
+      <c r="B490" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C490" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="D490" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>544</v>
+      </c>
+      <c r="B491" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="C491" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="D491" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>547</v>
+      </c>
+      <c r="B492" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="C492" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="D492" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>550</v>
+      </c>
+      <c r="B493" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="C493" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="D493" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>553</v>
+      </c>
+      <c r="B494" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="C494" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="D494" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>435</v>
+      </c>
+      <c r="B495" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="C495" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="D495" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>558</v>
+      </c>
+      <c r="B496" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="C496" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="D496" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>561</v>
+      </c>
+      <c r="B497" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="C497" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="D497" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>564</v>
+      </c>
+      <c r="B498" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="C498" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="D498" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>567</v>
+      </c>
+      <c r="B499" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="C499" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="D499" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A500" t="s">
+        <v>488</v>
+      </c>
+      <c r="B500" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="C500" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="D500" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A501" t="s">
+        <v>572</v>
+      </c>
+      <c r="B501" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="C501" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="D501" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
+        <v>575</v>
+      </c>
+      <c r="B502" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="C502" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="D502" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>578</v>
+      </c>
+      <c r="B503" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="C503" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D503" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A504" t="s">
+        <v>581</v>
+      </c>
+      <c r="B504" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="C504" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="D504" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A505" t="s">
+        <v>584</v>
+      </c>
+      <c r="B505" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="C505" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="D505" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A506" t="s">
+        <v>587</v>
+      </c>
+      <c r="B506" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="C506" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="D506" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A507" t="s">
+        <v>590</v>
+      </c>
+      <c r="B507" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="C507" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="D507" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A508" t="s">
+        <v>593</v>
+      </c>
+      <c r="B508" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="C508" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="D508" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A509" t="s">
+        <v>596</v>
+      </c>
+      <c r="B509" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="C509" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="D509" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A510" t="s">
+        <v>599</v>
+      </c>
+      <c r="B510" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="C510" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="D510" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A511" t="s">
+        <v>602</v>
+      </c>
+      <c r="B511" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="C511" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="D511" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A512" t="s">
+        <v>605</v>
+      </c>
+      <c r="B512" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="C512" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="D512" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A513" t="s">
+        <v>608</v>
+      </c>
+      <c r="B513" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="C513" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="D513" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A514" t="s">
+        <v>611</v>
+      </c>
+      <c r="B514" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="C514" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="D514" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A515" t="s">
+        <v>614</v>
+      </c>
+      <c r="B515" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="C515" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="D515" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A516" t="s">
+        <v>617</v>
+      </c>
+      <c r="B516" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="C516" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="D516" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A517" t="s">
+        <v>620</v>
+      </c>
+      <c r="B517" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="C517" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="D517" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A518" t="s">
+        <v>623</v>
+      </c>
+      <c r="B518" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="C518" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="D518" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A519" t="s">
+        <v>626</v>
+      </c>
+      <c r="B519" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="C519" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="D519" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A520" t="s">
+        <v>629</v>
+      </c>
+      <c r="B520" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C520" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="D520" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A521" t="s">
+        <v>632</v>
+      </c>
+      <c r="B521" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="C521" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="D521" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A522" t="s">
+        <v>635</v>
+      </c>
+      <c r="B522" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="C522" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="D522" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A523" t="s">
+        <v>638</v>
+      </c>
+      <c r="B523" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="C523" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="D523" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A524" t="s">
+        <v>641</v>
+      </c>
+      <c r="B524" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="C524" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="D524" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A525" t="s">
+        <v>435</v>
+      </c>
+      <c r="B525" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="C525" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="D525" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A526" t="s">
+        <v>646</v>
+      </c>
+      <c r="B526" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="C526" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="D526" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A527" t="s">
+        <v>649</v>
+      </c>
+      <c r="B527" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="C527" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="D527" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A528" t="s">
+        <v>435</v>
+      </c>
+      <c r="B528" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="C528" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="D528" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>654</v>
+      </c>
+      <c r="B529" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="C529" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="D529" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>646</v>
+      </c>
+      <c r="B530" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="C530" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="D530" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>659</v>
+      </c>
+      <c r="B531" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="C531" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="D531" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>474</v>
+      </c>
+      <c r="B532" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="C532" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="D532" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A533" t="s">
+        <v>664</v>
+      </c>
+      <c r="B533" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="C533" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="D533" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A534" t="s">
+        <v>667</v>
+      </c>
+      <c r="B534" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="C534" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="D534" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A535" t="s">
+        <v>670</v>
+      </c>
+      <c r="B535" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="C535" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="D535" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A536" t="s">
+        <v>673</v>
+      </c>
+      <c r="B536" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="C536" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="D536" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A537" t="s">
+        <v>676</v>
+      </c>
+      <c r="B537" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="C537" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="D537" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A538" t="s">
+        <v>679</v>
+      </c>
+      <c r="B538" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="C538" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="D538" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D539" s="4"/>
     </row>
-    <row r="540" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D540" s="4"/>
     </row>
-    <row r="541" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D541" s="4"/>
     </row>
-    <row r="542" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D542" s="4"/>
     </row>
-    <row r="543" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D543" s="4"/>
     </row>
-    <row r="544" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D544" s="4"/>
     </row>
     <row r="545" spans="4:4" x14ac:dyDescent="0.3">

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="364" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{655F0393-9D48-4415-B333-786207D06194}"/>
+  <xr:revisionPtr revIDLastSave="423" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52E6804A-B913-4403-9643-84DB35D2B326}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="757">
   <si>
     <t>nome</t>
   </si>
@@ -2076,6 +2076,237 @@
   </si>
   <si>
     <t>Andreia Verri Silva</t>
+  </si>
+  <si>
+    <t>-23.707592399768863</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.556303361915546</t>
+  </si>
+  <si>
+    <t>Regiane Ramires Vertemate</t>
+  </si>
+  <si>
+    <t>-23.505509075787977</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.597637786325336</t>
+  </si>
+  <si>
+    <t>Carlos Alberto Cordeiro</t>
+  </si>
+  <si>
+    <t>-22.57759653485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -44.964809361951225</t>
+  </si>
+  <si>
+    <t>-22.585272753002787</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -44.96790564660699</t>
+  </si>
+  <si>
+    <t>Araken Jose Monteiro Dos Reis Filho</t>
+  </si>
+  <si>
+    <t>-23.57662295196551</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.18257642510331</t>
+  </si>
+  <si>
+    <t>Vanessa Zanoni Okazaki</t>
+  </si>
+  <si>
+    <t>-23.712616902832277</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.52999866191533</t>
+  </si>
+  <si>
+    <t>Alexandre Ricardo Leite</t>
+  </si>
+  <si>
+    <t>-23.5906069512522</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.63561148630681</t>
+  </si>
+  <si>
+    <t>Transcendental Com Prod Odonto Ltda</t>
+  </si>
+  <si>
+    <t>-23.659139157192918</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.71893102369606</t>
+  </si>
+  <si>
+    <t>Caio Cesar Rubio Blum</t>
+  </si>
+  <si>
+    <t>-23.55758581597052</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65425559075632</t>
+  </si>
+  <si>
+    <t>-23.614589684856128</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66443042237601</t>
+  </si>
+  <si>
+    <t>Provet Inst. Brasil De Diag. E Esp</t>
+  </si>
+  <si>
+    <t>-23.88327559896266</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.422401470898556</t>
+  </si>
+  <si>
+    <t>Municipio De Cubatao</t>
+  </si>
+  <si>
+    <t>-23.60154288837846</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65459557541092</t>
+  </si>
+  <si>
+    <t>J.T.Gama Cirurgia Plastica S/C Ltda</t>
+  </si>
+  <si>
+    <t>-23.61270992894358</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.643656704246496</t>
+  </si>
+  <si>
+    <t>-23.59716040796751</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.403361575411154</t>
+  </si>
+  <si>
+    <t>Casa De Saude Sta Marcelina</t>
+  </si>
+  <si>
+    <t>-23.585384374456336</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.717646086307866</t>
+  </si>
+  <si>
+    <t>Hospital Leforte S A</t>
+  </si>
+  <si>
+    <t>-23.595987110752237</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.502000700900155</t>
+  </si>
+  <si>
+    <t>Killer Tapuy Sandy</t>
+  </si>
+  <si>
+    <t>-23.66497475793804</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.52184500865614</t>
+  </si>
+  <si>
+    <t>-23.589815072293284</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.673645548427054</t>
+  </si>
+  <si>
+    <t>Onco Star Sp Oncologia Ltda</t>
+  </si>
+  <si>
+    <t>-23.803977504165402</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.39939181958419</t>
+  </si>
+  <si>
+    <t>Fundacao De Saude Publica De Sao Sebastiao</t>
+  </si>
+  <si>
+    <t>-23.232703778884197</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.853409604258744</t>
+  </si>
+  <si>
+    <t>Cristiane Clemente De Faria Brito</t>
+  </si>
+  <si>
+    <t>-23.502154269609022</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.53436873123443</t>
+  </si>
+  <si>
+    <t>Sandro Morales</t>
+  </si>
+  <si>
+    <t>-23.597432416977483</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68606604397714</t>
+  </si>
+  <si>
+    <t>Ferreira P. Cli. De Der. E A. Ltda</t>
+  </si>
+  <si>
+    <t>-23.502230663773165</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.63148581959393</t>
+  </si>
+  <si>
+    <t>Clinica Padovan Eireli</t>
+  </si>
+  <si>
+    <t>-23.542426255228747</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.648893760069015</t>
+  </si>
+  <si>
+    <t>Hospital Santa Isabel S.A</t>
+  </si>
+  <si>
+    <t>-23.624565149469966</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.7015524151353</t>
+  </si>
+  <si>
+    <t>BIO-RAD LABORATORIOS BRASIL LTDA</t>
+  </si>
+  <si>
+    <t>-23.595265705412423</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64482546191913</t>
+  </si>
+  <si>
+    <t>-23.511397811320634</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.58389280424991</t>
+  </si>
+  <si>
+    <t>-23.556447944596872</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66882687541246</t>
   </si>
 </sst>
 </file>
@@ -10001,117 +10232,422 @@
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D539" s="4"/>
+      <c r="A539" t="s">
+        <v>682</v>
+      </c>
+      <c r="B539" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="C539" s="7" t="s">
+        <v>681</v>
+      </c>
+      <c r="D539" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D540" s="4"/>
+      <c r="A540" t="s">
+        <v>685</v>
+      </c>
+      <c r="B540" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="C540" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="D540" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D541" s="4"/>
+      <c r="A541" t="s">
+        <v>339</v>
+      </c>
+      <c r="B541" s="7" t="s">
+        <v>686</v>
+      </c>
+      <c r="C541" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="D541" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D542" s="4"/>
+      <c r="A542" t="s">
+        <v>690</v>
+      </c>
+      <c r="B542" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="C542" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="D542" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D543" s="4"/>
+      <c r="A543" t="s">
+        <v>693</v>
+      </c>
+      <c r="B543" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="C543" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="D543" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D544" s="4"/>
-    </row>
-    <row r="545" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D545" s="4"/>
-    </row>
-    <row r="546" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D546" s="4"/>
-    </row>
-    <row r="547" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D547" s="4"/>
-    </row>
-    <row r="548" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D548" s="4"/>
-    </row>
-    <row r="549" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D549" s="4"/>
-    </row>
-    <row r="550" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D550" s="4"/>
-    </row>
-    <row r="551" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D551" s="4"/>
-    </row>
-    <row r="552" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D552" s="4"/>
-    </row>
-    <row r="553" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D553" s="4"/>
-    </row>
-    <row r="554" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D554" s="4"/>
-    </row>
-    <row r="555" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D555" s="4"/>
-    </row>
-    <row r="556" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D556" s="4"/>
-    </row>
-    <row r="557" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D557" s="4"/>
-    </row>
-    <row r="558" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D558" s="4"/>
-    </row>
-    <row r="559" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D559" s="4"/>
-    </row>
-    <row r="560" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D560" s="4"/>
-    </row>
-    <row r="561" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D561" s="4"/>
-    </row>
-    <row r="562" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D562" s="4"/>
-    </row>
-    <row r="563" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D563" s="4"/>
-    </row>
-    <row r="564" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D564" s="4"/>
-    </row>
-    <row r="565" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D565" s="4"/>
-    </row>
-    <row r="566" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D566" s="4"/>
-    </row>
-    <row r="567" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="A544" t="s">
+        <v>696</v>
+      </c>
+      <c r="B544" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="C544" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="D544" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A545" t="s">
+        <v>699</v>
+      </c>
+      <c r="B545" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="C545" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="D545" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A546" t="s">
+        <v>702</v>
+      </c>
+      <c r="B546" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="C546" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="D546" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A547" t="s">
+        <v>646</v>
+      </c>
+      <c r="B547" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="C547" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="D547" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A548" t="s">
+        <v>707</v>
+      </c>
+      <c r="B548" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="C548" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="D548" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A549" t="s">
+        <v>710</v>
+      </c>
+      <c r="B549" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C549" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="D549" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A550" t="s">
+        <v>713</v>
+      </c>
+      <c r="B550" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="C550" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="D550" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A551" t="s">
+        <v>532</v>
+      </c>
+      <c r="B551" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="C551" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="D551" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A552" t="s">
+        <v>718</v>
+      </c>
+      <c r="B552" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="C552" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="D552" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A553" t="s">
+        <v>721</v>
+      </c>
+      <c r="B553" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="C553" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="D553" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A554" t="s">
+        <v>724</v>
+      </c>
+      <c r="B554" s="7" t="s">
+        <v>722</v>
+      </c>
+      <c r="C554" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="D554" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A555" t="s">
+        <v>482</v>
+      </c>
+      <c r="B555" s="7" t="s">
+        <v>725</v>
+      </c>
+      <c r="C555" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="D555" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A556" t="s">
+        <v>729</v>
+      </c>
+      <c r="B556" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="C556" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="D556" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A557" t="s">
+        <v>732</v>
+      </c>
+      <c r="B557" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="C557" s="7" t="s">
+        <v>731</v>
+      </c>
+      <c r="D557" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A558" t="s">
+        <v>735</v>
+      </c>
+      <c r="B558" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="C558" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="D558" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A559" t="s">
+        <v>738</v>
+      </c>
+      <c r="B559" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="C559" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="D559" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A560" t="s">
+        <v>741</v>
+      </c>
+      <c r="B560" s="7" t="s">
+        <v>739</v>
+      </c>
+      <c r="C560" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="D560" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>744</v>
+      </c>
+      <c r="B561" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="C561" s="7" t="s">
+        <v>743</v>
+      </c>
+      <c r="D561" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>747</v>
+      </c>
+      <c r="B562" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="C562" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="D562" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A563" t="s">
+        <v>750</v>
+      </c>
+      <c r="B563" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="C563" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="D563" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A564" t="s">
+        <v>506</v>
+      </c>
+      <c r="B564" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="C564" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="D564" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A565" t="s">
+        <v>482</v>
+      </c>
+      <c r="B565" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="C565" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="D565" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B566" s="7" t="s">
+        <v>755</v>
+      </c>
+      <c r="C566" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="D566" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D567" s="4"/>
     </row>
-    <row r="568" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D568" s="4"/>
     </row>
-    <row r="569" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D569" s="4"/>
     </row>
-    <row r="570" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D570" s="4"/>
     </row>
-    <row r="571" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D571" s="4"/>
     </row>
-    <row r="572" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D572" s="4"/>
     </row>
-    <row r="573" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D573" s="4"/>
     </row>
-    <row r="574" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D574" s="4"/>
     </row>
-    <row r="575" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D575" s="4"/>
     </row>
-    <row r="576" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D576" s="4"/>
     </row>
     <row r="577" spans="4:4" x14ac:dyDescent="0.3">

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\webidasi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="423" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52E6804A-B913-4403-9643-84DB35D2B326}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D466041-0E60-40A3-817A-4BFE8AD8E5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$524</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="632">
   <si>
     <t>nome</t>
   </si>
@@ -1013,15 +1016,6 @@
     <t>rosa</t>
   </si>
   <si>
-    <t>-23.453774345473747</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.558983148431594</t>
-  </si>
-  <si>
-    <t>Jorge Felix Monteiro</t>
-  </si>
-  <si>
     <t>-23.57251653927414</t>
   </si>
   <si>
@@ -1040,15 +1034,6 @@
     <t>Maisnove Med Diagnostica Ltda</t>
   </si>
   <si>
-    <t>-23.48657855930126</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.47016691774277</t>
-  </si>
-  <si>
-    <t>Bruna Oliveira Branco</t>
-  </si>
-  <si>
     <t>-22.816959084641574</t>
   </si>
   <si>
@@ -1058,24 +1043,6 @@
     <t>Cavalca Esp Gomes Med Diag Ltda</t>
   </si>
   <si>
-    <t>-23.612923085070907</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.443208104246565</t>
-  </si>
-  <si>
-    <t>Jailton Monteiro Dos Santos</t>
-  </si>
-  <si>
-    <t>-23.45758285539288</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.5878646114385</t>
-  </si>
-  <si>
-    <t>Sergio Luis Belem Ferreira Junior</t>
-  </si>
-  <si>
     <t>-23.595336799409633</t>
   </si>
   <si>
@@ -1112,15 +1079,6 @@
     <t>General Doctors Sup Odonto Ltda Epp</t>
   </si>
   <si>
-    <t>-23.516799783036124</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.46528399614668</t>
-  </si>
-  <si>
-    <t>Bruno Campos Emidio</t>
-  </si>
-  <si>
     <t>-23.59924405841143</t>
   </si>
   <si>
@@ -1130,15 +1088,6 @@
     <t>Soc Ben Israelita Bras H Albert Einstein</t>
   </si>
   <si>
-    <t>-23.59651378008784</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.7158458042471</t>
-  </si>
-  <si>
-    <t>ANDREA LAURATO SERTIE</t>
-  </si>
-  <si>
     <t>-23.547535199432723</t>
   </si>
   <si>
@@ -1148,24 +1097,6 @@
     <t>Inst. Brasileiro Controle Do Cancer</t>
   </si>
   <si>
-    <t>-23.596070315791028</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.677151817739265</t>
-  </si>
-  <si>
-    <t>Leandro Camacho Morant</t>
-  </si>
-  <si>
-    <t>-23.661617741271815</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.715714688901166</t>
-  </si>
-  <si>
-    <t>Janaina De Andrea Dernowsek</t>
-  </si>
-  <si>
     <t>-23.661558779976502</t>
   </si>
   <si>
@@ -1193,15 +1124,6 @@
     <t>Valeria Marcondes Dermatologia Eire</t>
   </si>
   <si>
-    <t>-23.557817004541864</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.67622860424828</t>
-  </si>
-  <si>
-    <t>Patricia Lerro De Paula Exuardo</t>
-  </si>
-  <si>
     <t>-23.597340136000188</t>
   </si>
   <si>
@@ -1256,15 +1178,6 @@
     <t>Centro De Imunobiologicos Imunecare</t>
   </si>
   <si>
-    <t>-23.594063676049423</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.47980020795055</t>
-  </si>
-  <si>
-    <t>Mariana Antunes Tresseno Dos Santos</t>
-  </si>
-  <si>
     <t>-23.215261756442803</t>
   </si>
   <si>
@@ -1292,15 +1205,6 @@
     <t>Drs Adm De Estoques Ltda</t>
   </si>
   <si>
-    <t>-23.176415391367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -45.818532055708516</t>
-  </si>
-  <si>
-    <t>Renata Moreira Machado</t>
-  </si>
-  <si>
     <t>-23.52789023347353</t>
   </si>
   <si>
@@ -1328,15 +1232,6 @@
     <t>Amil Assistencia Medica Internacion</t>
   </si>
   <si>
-    <t>-23.166393765103336</t>
-  </si>
-  <si>
-    <t>Aigla Eduarda Lopes Soares</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -45.84131945360565</t>
-  </si>
-  <si>
     <t>-23.48641055628623</t>
   </si>
   <si>
@@ -1373,15 +1268,6 @@
     <t>ROHM AND HAAS QUIMICA LTDA</t>
   </si>
   <si>
-    <t>-23.56253388406278</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.57968188890444</t>
-  </si>
-  <si>
-    <t>Luciane Barbaroto</t>
-  </si>
-  <si>
     <t>-23.582149861587375</t>
   </si>
   <si>
@@ -1400,15 +1286,6 @@
     <t>Allianca Saude E Participacoes S.A</t>
   </si>
   <si>
-    <t>-23.965697993833246</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.33183401438957</t>
-  </si>
-  <si>
-    <t>Sueli Anjos</t>
-  </si>
-  <si>
     <t>-23.648414027751862</t>
   </si>
   <si>
@@ -1586,24 +1463,6 @@
     <t>Notre Dame Intermedica Saude Sa</t>
   </si>
   <si>
-    <t>-23.709262218316884</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.557071411413325</t>
-  </si>
-  <si>
-    <t>Jorge Santangelo</t>
-  </si>
-  <si>
-    <t>-23.176830565888835</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -45.8732009633132</t>
-  </si>
-  <si>
-    <t>Dra. Tassia Camargo Orlando</t>
-  </si>
-  <si>
     <t>-23.546473462188814</t>
   </si>
   <si>
@@ -1619,15 +1478,6 @@
     <t>Hosp Alvorada Taguatinga Ltd</t>
   </si>
   <si>
-    <t>-23.57228774158005</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.690345319591714</t>
-  </si>
-  <si>
-    <t>Guilherme Saavedra</t>
-  </si>
-  <si>
     <t>-23.570195165800833</t>
   </si>
   <si>
@@ -1664,15 +1514,6 @@
     <t>Spdm Ass Paulista P O D Da Medicina</t>
   </si>
   <si>
-    <t>-23.652470289776474</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.66803023122961</t>
-  </si>
-  <si>
-    <t>Adriana Rosa Da Silva</t>
-  </si>
-  <si>
     <t>-23.537697485602877</t>
   </si>
   <si>
@@ -1682,15 +1523,6 @@
     <t>Hospital E Pronto Socorro Comum</t>
   </si>
   <si>
-    <t>-23.675428729682377</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.50885712676452</t>
-  </si>
-  <si>
-    <t>Claudio Roberto Da Silva</t>
-  </si>
-  <si>
     <t>-23.523654999757223</t>
   </si>
   <si>
@@ -1706,15 +1538,6 @@
     <t xml:space="preserve"> -46.56979579075276</t>
   </si>
   <si>
-    <t>-23.566448264561934</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.653629719592004</t>
-  </si>
-  <si>
-    <t>Dra. Gladys Mouessati Abud Mattei</t>
-  </si>
-  <si>
     <t>-23.537000873491234</t>
   </si>
   <si>
@@ -1757,15 +1580,6 @@
     <t>Municipio De Cruzeiro</t>
   </si>
   <si>
-    <t>-23.613126598323237</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.63370748313514</t>
-  </si>
-  <si>
-    <t>Julio Cesar Bassi</t>
-  </si>
-  <si>
     <t>-23.556536379499118</t>
   </si>
   <si>
@@ -1775,15 +1589,6 @@
     <t>Fleury S A</t>
   </si>
   <si>
-    <t>-23.56052072080297</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.68740314842879</t>
-  </si>
-  <si>
-    <t>Matheus De Alencar Ichigi</t>
-  </si>
-  <si>
     <t>-23.560491217411833</t>
   </si>
   <si>
@@ -1820,15 +1625,6 @@
     <t>G S H Corp Participacoes S.A</t>
   </si>
   <si>
-    <t>-23.224334290053843</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -45.91147251775115</t>
-  </si>
-  <si>
-    <t>Ariane Micaela Dantas Dos Santos</t>
-  </si>
-  <si>
     <t>-23.652882728151074</t>
   </si>
   <si>
@@ -1838,15 +1634,6 @@
     <t>Santa Helena A Me S A</t>
   </si>
   <si>
-    <t>-23.53751171061186</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.68272130239733</t>
-  </si>
-  <si>
-    <t>Abbvie Farmaceutica Ltda</t>
-  </si>
-  <si>
     <t>-23.542259962382044</t>
   </si>
   <si>
@@ -1856,15 +1643,6 @@
     <t>Unen Servicos Medicos Ltda</t>
   </si>
   <si>
-    <t>-23.039068435154267</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -45.63579186639595</t>
-  </si>
-  <si>
-    <t>Daniele Cristina De Campos Mariano</t>
-  </si>
-  <si>
     <t>-23.514613590727294</t>
   </si>
   <si>
@@ -1883,15 +1661,6 @@
     <t>Centro Dermatologico Sergio Talaric</t>
   </si>
   <si>
-    <t>-23.034993878497144</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -45.57249823495269</t>
-  </si>
-  <si>
-    <t>Adriana Franca Moreno</t>
-  </si>
-  <si>
     <t>-23.870060842918182</t>
   </si>
   <si>
@@ -1919,15 +1688,6 @@
     <t>Brunno Henrique Da Silva Miura35332054874</t>
   </si>
   <si>
-    <t>-23.620071006735152</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.67676642499048</t>
-  </si>
-  <si>
-    <t>Vyvian Cristina Cassano</t>
-  </si>
-  <si>
     <t>-23.10594057938862</t>
   </si>
   <si>
@@ -1946,24 +1706,6 @@
     <t>Clinica Medica Vili Ltda</t>
   </si>
   <si>
-    <t>-23.53000747060739</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.68315838890538</t>
-  </si>
-  <si>
-    <t>Sandra Kalil Bussadori</t>
-  </si>
-  <si>
-    <t>-23.55895809813347</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.6775717016574</t>
-  </si>
-  <si>
-    <t>Caio Bellinati</t>
-  </si>
-  <si>
     <t>-23.555221446922896</t>
   </si>
   <si>
@@ -2009,15 +1751,6 @@
     <t xml:space="preserve"> -46.65309690165781</t>
   </si>
   <si>
-    <t>-23.606796504105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.73703563123102</t>
-  </si>
-  <si>
-    <t>Fernando Rodrigues Costa</t>
-  </si>
-  <si>
     <t>-23.643124770010438</t>
   </si>
   <si>
@@ -2033,24 +1766,6 @@
     <t>SERRA MAYOR SERVICOS MEDICOS S A</t>
   </si>
   <si>
-    <t>-23.62228940333357</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.60461464842615</t>
-  </si>
-  <si>
-    <t>Mauro Itaru Honda</t>
-  </si>
-  <si>
-    <t>-23.031607838609396</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -45.57871766008529</t>
-  </si>
-  <si>
-    <t>Gustavo De Sousa Fortes Carvalho</t>
-  </si>
-  <si>
     <t>-23.595734787861023</t>
   </si>
   <si>
@@ -2069,66 +1784,12 @@
     <t xml:space="preserve">Dra. Renata De Avila Silva | Avila Dermatologia E Clin. Medica | Jro Consultorio Medico S/C Ltda | 2Csj Medicos Associados Ltda </t>
   </si>
   <si>
-    <t>-23.213994054385118</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -45.907347602407484</t>
-  </si>
-  <si>
-    <t>Andreia Verri Silva</t>
-  </si>
-  <si>
-    <t>-23.707592399768863</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.556303361915546</t>
-  </si>
-  <si>
-    <t>Regiane Ramires Vertemate</t>
-  </si>
-  <si>
-    <t>-23.505509075787977</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.597637786325336</t>
-  </si>
-  <si>
-    <t>Carlos Alberto Cordeiro</t>
-  </si>
-  <si>
     <t>-22.57759653485007</t>
   </si>
   <si>
     <t xml:space="preserve"> -44.964809361951225</t>
   </si>
   <si>
-    <t>-22.585272753002787</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -44.96790564660699</t>
-  </si>
-  <si>
-    <t>Araken Jose Monteiro Dos Reis Filho</t>
-  </si>
-  <si>
-    <t>-23.57662295196551</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.18257642510331</t>
-  </si>
-  <si>
-    <t>Vanessa Zanoni Okazaki</t>
-  </si>
-  <si>
-    <t>-23.712616902832277</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.52999866191533</t>
-  </si>
-  <si>
-    <t>Alexandre Ricardo Leite</t>
-  </si>
-  <si>
     <t>-23.5906069512522</t>
   </si>
   <si>
@@ -2138,15 +1799,6 @@
     <t>Transcendental Com Prod Odonto Ltda</t>
   </si>
   <si>
-    <t>-23.659139157192918</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.71893102369606</t>
-  </si>
-  <si>
-    <t>Caio Cesar Rubio Blum</t>
-  </si>
-  <si>
     <t>-23.55758581597052</t>
   </si>
   <si>
@@ -2204,15 +1856,6 @@
     <t>Hospital Leforte S A</t>
   </si>
   <si>
-    <t>-23.595987110752237</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.502000700900155</t>
-  </si>
-  <si>
-    <t>Killer Tapuy Sandy</t>
-  </si>
-  <si>
     <t>-23.66497475793804</t>
   </si>
   <si>
@@ -2237,24 +1880,6 @@
     <t>Fundacao De Saude Publica De Sao Sebastiao</t>
   </si>
   <si>
-    <t>-23.232703778884197</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -45.853409604258744</t>
-  </si>
-  <si>
-    <t>Cristiane Clemente De Faria Brito</t>
-  </si>
-  <si>
-    <t>-23.502154269609022</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.53436873123443</t>
-  </si>
-  <si>
-    <t>Sandro Morales</t>
-  </si>
-  <si>
     <t>-23.597432416977483</t>
   </si>
   <si>
@@ -2307,6 +1932,9 @@
   </si>
   <si>
     <t xml:space="preserve"> -46.66882687541246</t>
+  </si>
+  <si>
+    <t>Secretaria De Estado Da Saude</t>
   </si>
 </sst>
 </file>
@@ -2688,13 +2316,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J602"/>
+  <dimension ref="A1:J560"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.77734375" customWidth="1"/>
     <col min="2" max="2" width="21.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -8758,6 +8387,8 @@
       <c r="D433" s="4" t="s">
         <v>324</v>
       </c>
+      <c r="I433" s="9"/>
+      <c r="J433" s="9"/>
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
@@ -8884,8 +8515,6 @@
       <c r="D442" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="I442" s="9"/>
-      <c r="J442" s="9"/>
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
@@ -9029,13 +8658,13 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>430</v>
       </c>
       <c r="C453" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>324</v>
@@ -9043,7 +8672,7 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="B454" s="7" t="s">
         <v>433</v>
@@ -9057,13 +8686,13 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B455" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C455" s="7" t="s">
         <v>436</v>
-      </c>
-      <c r="C455" s="7" t="s">
-        <v>437</v>
       </c>
       <c r="D455" s="4" t="s">
         <v>324</v>
@@ -9071,13 +8700,13 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B456" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="C456" s="7" t="s">
         <v>439</v>
-      </c>
-      <c r="C456" s="7" t="s">
-        <v>440</v>
       </c>
       <c r="D456" s="4" t="s">
         <v>324</v>
@@ -9085,13 +8714,13 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B457" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="C457" s="7" t="s">
         <v>442</v>
-      </c>
-      <c r="C457" s="7" t="s">
-        <v>443</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>324</v>
@@ -9099,13 +8728,13 @@
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B458" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="C458" s="7" t="s">
         <v>445</v>
-      </c>
-      <c r="C458" s="7" t="s">
-        <v>446</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>324</v>
@@ -9113,13 +8742,13 @@
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B459" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C459" s="7" t="s">
         <v>448</v>
-      </c>
-      <c r="C459" s="7" t="s">
-        <v>449</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>324</v>
@@ -9127,13 +8756,13 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B460" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="C460" s="7" t="s">
         <v>451</v>
-      </c>
-      <c r="C460" s="7" t="s">
-        <v>452</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>324</v>
@@ -9141,13 +8770,13 @@
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B461" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="C461" s="7" t="s">
         <v>454</v>
-      </c>
-      <c r="C461" s="7" t="s">
-        <v>455</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>324</v>
@@ -9155,13 +8784,13 @@
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B462" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C462" s="7" t="s">
         <v>457</v>
-      </c>
-      <c r="C462" s="7" t="s">
-        <v>458</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>324</v>
@@ -9169,13 +8798,13 @@
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B463" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="C463" s="7" t="s">
         <v>460</v>
-      </c>
-      <c r="C463" s="7" t="s">
-        <v>461</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>324</v>
@@ -9183,13 +8812,13 @@
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B464" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="C464" s="7" t="s">
         <v>463</v>
-      </c>
-      <c r="C464" s="7" t="s">
-        <v>464</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>324</v>
@@ -9197,13 +8826,13 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B465" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="C465" s="7" t="s">
         <v>466</v>
-      </c>
-      <c r="C465" s="7" t="s">
-        <v>467</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>324</v>
@@ -9211,13 +8840,13 @@
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B466" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="C466" s="7" t="s">
         <v>469</v>
-      </c>
-      <c r="C466" s="7" t="s">
-        <v>470</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>324</v>
@@ -9225,13 +8854,13 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B467" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="C467" s="7" t="s">
         <v>472</v>
-      </c>
-      <c r="C467" s="7" t="s">
-        <v>473</v>
       </c>
       <c r="D467" s="4" t="s">
         <v>324</v>
@@ -9239,13 +8868,13 @@
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>450</v>
+        <v>402</v>
       </c>
       <c r="B468" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="C468" s="7" t="s">
         <v>475</v>
-      </c>
-      <c r="C468" s="7" t="s">
-        <v>476</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>324</v>
@@ -9253,13 +8882,13 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B469" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C469" s="7" t="s">
         <v>477</v>
-      </c>
-      <c r="C469" s="7" t="s">
-        <v>478</v>
       </c>
       <c r="D469" s="4" t="s">
         <v>324</v>
@@ -9267,13 +8896,13 @@
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B470" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="C470" s="7" t="s">
         <v>480</v>
-      </c>
-      <c r="C470" s="7" t="s">
-        <v>481</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>324</v>
@@ -9281,13 +8910,13 @@
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B471" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="C471" s="7" t="s">
         <v>483</v>
-      </c>
-      <c r="C471" s="7" t="s">
-        <v>484</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>324</v>
@@ -9295,13 +8924,13 @@
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B472" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="C472" s="7" t="s">
         <v>486</v>
-      </c>
-      <c r="C472" s="7" t="s">
-        <v>487</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>324</v>
@@ -9309,13 +8938,13 @@
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B473" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="C473" s="7" t="s">
         <v>489</v>
-      </c>
-      <c r="C473" s="7" t="s">
-        <v>490</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>324</v>
@@ -9323,13 +8952,13 @@
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B474" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="C474" s="7" t="s">
         <v>492</v>
-      </c>
-      <c r="C474" s="7" t="s">
-        <v>493</v>
       </c>
       <c r="D474" s="4" t="s">
         <v>324</v>
@@ -9337,13 +8966,13 @@
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B475" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="C475" s="7" t="s">
         <v>495</v>
-      </c>
-      <c r="C475" s="7" t="s">
-        <v>496</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>324</v>
@@ -9351,13 +8980,13 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>500</v>
+        <v>399</v>
       </c>
       <c r="B476" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="C476" s="7" t="s">
         <v>498</v>
-      </c>
-      <c r="C476" s="7" t="s">
-        <v>499</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>324</v>
@@ -9365,13 +8994,13 @@
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B477" s="7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C477" s="7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D477" s="4" t="s">
         <v>324</v>
@@ -9379,13 +9008,13 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C478" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D478" s="4" t="s">
         <v>324</v>
@@ -9393,13 +9022,13 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B479" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C479" s="7" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D479" s="4" t="s">
         <v>324</v>
@@ -9407,13 +9036,13 @@
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>512</v>
+        <v>446</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C480" s="7" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D480" s="4" t="s">
         <v>324</v>
@@ -9421,13 +9050,13 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B481" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C481" s="7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>324</v>
@@ -9435,13 +9064,13 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B482" s="7" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C482" s="7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>324</v>
@@ -9449,13 +9078,13 @@
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B483" s="7" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C483" s="7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>324</v>
@@ -9463,13 +9092,13 @@
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>438</v>
+        <v>521</v>
       </c>
       <c r="B484" s="7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C484" s="7" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>324</v>
@@ -9477,13 +9106,13 @@
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B485" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C485" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D485" s="4" t="s">
         <v>324</v>
@@ -9491,13 +9120,13 @@
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B486" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C486" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>324</v>
@@ -9505,13 +9134,13 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B487" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C487" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>324</v>
@@ -9519,13 +9148,13 @@
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B488" s="7" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C488" s="7" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>324</v>
@@ -9533,13 +9162,13 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B489" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C489" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D489" s="4" t="s">
         <v>324</v>
@@ -9547,13 +9176,13 @@
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B490" s="7" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C490" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D490" s="4" t="s">
         <v>324</v>
@@ -9561,13 +9190,13 @@
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B491" s="7" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C491" s="7" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D491" s="4" t="s">
         <v>324</v>
@@ -9575,13 +9204,13 @@
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B492" s="7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C492" s="7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>324</v>
@@ -9589,13 +9218,13 @@
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B493" s="7" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C493" s="7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D493" s="4" t="s">
         <v>324</v>
@@ -9603,13 +9232,13 @@
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B494" s="7" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C494" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D494" s="4" t="s">
         <v>324</v>
@@ -9617,13 +9246,13 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>435</v>
+        <v>554</v>
       </c>
       <c r="B495" s="7" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C495" s="7" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D495" s="4" t="s">
         <v>324</v>
@@ -9631,13 +9260,13 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>558</v>
+        <v>399</v>
       </c>
       <c r="B496" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="C496" s="7" t="s">
         <v>556</v>
-      </c>
-      <c r="C496" s="7" t="s">
-        <v>557</v>
       </c>
       <c r="D496" s="4" t="s">
         <v>324</v>
@@ -9645,13 +9274,13 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B497" s="7" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C497" s="7" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D497" s="4" t="s">
         <v>324</v>
@@ -9659,13 +9288,13 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B498" s="7" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C498" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D498" s="4" t="s">
         <v>324</v>
@@ -9673,13 +9302,13 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>567</v>
+        <v>399</v>
       </c>
       <c r="B499" s="7" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C499" s="7" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D499" s="4" t="s">
         <v>324</v>
@@ -9687,13 +9316,13 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>488</v>
+        <v>567</v>
       </c>
       <c r="B500" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C500" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D500" s="4" t="s">
         <v>324</v>
@@ -9701,13 +9330,13 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="B501" s="7" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C501" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D501" s="4" t="s">
         <v>324</v>
@@ -9715,13 +9344,13 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>575</v>
+        <v>432</v>
       </c>
       <c r="B502" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C502" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D502" s="4" t="s">
         <v>324</v>
@@ -9729,13 +9358,13 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B503" s="7" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C503" s="7" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D503" s="4" t="s">
         <v>324</v>
@@ -9743,13 +9372,13 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B504" s="7" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C504" s="7" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D504" s="4" t="s">
         <v>324</v>
@@ -9757,13 +9386,13 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B505" s="7" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C505" s="7" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="D505" s="4" t="s">
         <v>324</v>
@@ -9771,13 +9400,13 @@
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>587</v>
+        <v>333</v>
       </c>
       <c r="B506" s="7" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C506" s="7" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="D506" s="4" t="s">
         <v>324</v>
@@ -9785,13 +9414,13 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B507" s="7" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C507" s="7" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="D507" s="4" t="s">
         <v>324</v>
@@ -9799,13 +9428,13 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>593</v>
+        <v>559</v>
       </c>
       <c r="B508" s="7" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C508" s="7" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="D508" s="4" t="s">
         <v>324</v>
@@ -9813,13 +9442,13 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="B509" s="7" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C509" s="7" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D509" s="4" t="s">
         <v>324</v>
@@ -9827,13 +9456,13 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B510" s="7" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="C510" s="7" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="D510" s="4" t="s">
         <v>324</v>
@@ -9841,13 +9470,13 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="B511" s="7" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C511" s="7" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="D511" s="4" t="s">
         <v>324</v>
@@ -9855,13 +9484,13 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>605</v>
+        <v>481</v>
       </c>
       <c r="B512" s="7" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C512" s="7" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D512" s="4" t="s">
         <v>324</v>
@@ -9869,13 +9498,13 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="B513" s="7" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="C513" s="7" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="D513" s="4" t="s">
         <v>324</v>
@@ -9883,13 +9512,13 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="B514" s="7" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="C514" s="7" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="D514" s="4" t="s">
         <v>324</v>
@@ -9897,13 +9526,13 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>614</v>
+        <v>440</v>
       </c>
       <c r="B515" s="7" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="C515" s="7" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="D515" s="4" t="s">
         <v>324</v>
@@ -9911,13 +9540,13 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="B516" s="7" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C516" s="7" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="D516" s="4" t="s">
         <v>324</v>
@@ -9925,13 +9554,13 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B517" s="7" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="C517" s="7" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="D517" s="4" t="s">
         <v>324</v>
@@ -9939,13 +9568,13 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="B518" s="7" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C518" s="7" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="D518" s="4" t="s">
         <v>324</v>
@@ -9953,13 +9582,13 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B519" s="7" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="C519" s="7" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="D519" s="4" t="s">
         <v>324</v>
@@ -9967,13 +9596,13 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="B520" s="7" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="C520" s="7" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="D520" s="4" t="s">
         <v>324</v>
@@ -9981,13 +9610,13 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="B521" s="7" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="C521" s="7" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="D521" s="4" t="s">
         <v>324</v>
@@ -9995,13 +9624,13 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>635</v>
+        <v>464</v>
       </c>
       <c r="B522" s="7" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="C522" s="7" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="D522" s="4" t="s">
         <v>324</v>
@@ -10009,13 +9638,13 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>638</v>
+        <v>440</v>
       </c>
       <c r="B523" s="7" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="C523" s="7" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="D523" s="4" t="s">
         <v>324</v>
@@ -10023,710 +9652,125 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="B524" s="7" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="C524" s="7" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="D524" s="4" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A525" t="s">
-        <v>435</v>
-      </c>
-      <c r="B525" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="C525" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="D525" s="4" t="s">
-        <v>324</v>
-      </c>
+      <c r="D525" s="4"/>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A526" t="s">
-        <v>646</v>
-      </c>
-      <c r="B526" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="C526" s="7" t="s">
-        <v>645</v>
-      </c>
-      <c r="D526" s="4" t="s">
-        <v>324</v>
-      </c>
+      <c r="D526" s="4"/>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A527" t="s">
-        <v>649</v>
-      </c>
-      <c r="B527" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="C527" s="7" t="s">
-        <v>648</v>
-      </c>
-      <c r="D527" s="4" t="s">
-        <v>324</v>
-      </c>
+      <c r="D527" s="4"/>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A528" t="s">
-        <v>435</v>
-      </c>
-      <c r="B528" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="C528" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="D528" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A529" t="s">
-        <v>654</v>
-      </c>
-      <c r="B529" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="C529" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="D529" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A530" t="s">
-        <v>646</v>
-      </c>
-      <c r="B530" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="C530" s="7" t="s">
-        <v>656</v>
-      </c>
-      <c r="D530" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A531" t="s">
-        <v>659</v>
-      </c>
-      <c r="B531" s="7" t="s">
-        <v>657</v>
-      </c>
-      <c r="C531" s="7" t="s">
-        <v>658</v>
-      </c>
-      <c r="D531" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A532" t="s">
-        <v>474</v>
-      </c>
-      <c r="B532" s="7" t="s">
-        <v>660</v>
-      </c>
-      <c r="C532" s="7" t="s">
-        <v>661</v>
-      </c>
-      <c r="D532" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A533" t="s">
-        <v>664</v>
-      </c>
-      <c r="B533" s="7" t="s">
-        <v>662</v>
-      </c>
-      <c r="C533" s="7" t="s">
-        <v>663</v>
-      </c>
-      <c r="D533" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A534" t="s">
-        <v>667</v>
-      </c>
-      <c r="B534" s="7" t="s">
-        <v>665</v>
-      </c>
-      <c r="C534" s="7" t="s">
-        <v>666</v>
-      </c>
-      <c r="D534" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A535" t="s">
-        <v>670</v>
-      </c>
-      <c r="B535" s="7" t="s">
-        <v>668</v>
-      </c>
-      <c r="C535" s="7" t="s">
-        <v>669</v>
-      </c>
-      <c r="D535" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A536" t="s">
-        <v>673</v>
-      </c>
-      <c r="B536" s="7" t="s">
-        <v>671</v>
-      </c>
-      <c r="C536" s="7" t="s">
-        <v>672</v>
-      </c>
-      <c r="D536" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A537" t="s">
-        <v>676</v>
-      </c>
-      <c r="B537" s="7" t="s">
-        <v>674</v>
-      </c>
-      <c r="C537" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="D537" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A538" t="s">
-        <v>679</v>
-      </c>
-      <c r="B538" s="7" t="s">
-        <v>677</v>
-      </c>
-      <c r="C538" s="7" t="s">
-        <v>678</v>
-      </c>
-      <c r="D538" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A539" t="s">
-        <v>682</v>
-      </c>
-      <c r="B539" s="7" t="s">
-        <v>680</v>
-      </c>
-      <c r="C539" s="7" t="s">
-        <v>681</v>
-      </c>
-      <c r="D539" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A540" t="s">
-        <v>685</v>
-      </c>
-      <c r="B540" s="7" t="s">
-        <v>683</v>
-      </c>
-      <c r="C540" s="7" t="s">
-        <v>684</v>
-      </c>
-      <c r="D540" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A541" t="s">
-        <v>339</v>
-      </c>
-      <c r="B541" s="7" t="s">
-        <v>686</v>
-      </c>
-      <c r="C541" s="7" t="s">
-        <v>687</v>
-      </c>
-      <c r="D541" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A542" t="s">
-        <v>690</v>
-      </c>
-      <c r="B542" s="7" t="s">
-        <v>688</v>
-      </c>
-      <c r="C542" s="7" t="s">
-        <v>689</v>
-      </c>
-      <c r="D542" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A543" t="s">
-        <v>693</v>
-      </c>
-      <c r="B543" s="7" t="s">
-        <v>691</v>
-      </c>
-      <c r="C543" s="7" t="s">
-        <v>692</v>
-      </c>
-      <c r="D543" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A544" t="s">
-        <v>696</v>
-      </c>
-      <c r="B544" s="7" t="s">
-        <v>694</v>
-      </c>
-      <c r="C544" s="7" t="s">
-        <v>695</v>
-      </c>
-      <c r="D544" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A545" t="s">
-        <v>699</v>
-      </c>
-      <c r="B545" s="7" t="s">
-        <v>697</v>
-      </c>
-      <c r="C545" s="7" t="s">
-        <v>698</v>
-      </c>
-      <c r="D545" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A546" t="s">
-        <v>702</v>
-      </c>
-      <c r="B546" s="7" t="s">
-        <v>700</v>
-      </c>
-      <c r="C546" s="7" t="s">
-        <v>701</v>
-      </c>
-      <c r="D546" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A547" t="s">
-        <v>646</v>
-      </c>
-      <c r="B547" s="7" t="s">
-        <v>703</v>
-      </c>
-      <c r="C547" s="7" t="s">
-        <v>704</v>
-      </c>
-      <c r="D547" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A548" t="s">
-        <v>707</v>
-      </c>
-      <c r="B548" s="7" t="s">
-        <v>705</v>
-      </c>
-      <c r="C548" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="D548" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A549" t="s">
-        <v>710</v>
-      </c>
-      <c r="B549" s="7" t="s">
-        <v>708</v>
-      </c>
-      <c r="C549" s="7" t="s">
-        <v>709</v>
-      </c>
-      <c r="D549" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A550" t="s">
-        <v>713</v>
-      </c>
-      <c r="B550" s="7" t="s">
-        <v>711</v>
-      </c>
-      <c r="C550" s="7" t="s">
-        <v>712</v>
-      </c>
-      <c r="D550" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A551" t="s">
-        <v>532</v>
-      </c>
-      <c r="B551" s="7" t="s">
-        <v>714</v>
-      </c>
-      <c r="C551" s="7" t="s">
-        <v>715</v>
-      </c>
-      <c r="D551" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A552" t="s">
-        <v>718</v>
-      </c>
-      <c r="B552" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="C552" s="7" t="s">
-        <v>717</v>
-      </c>
-      <c r="D552" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A553" t="s">
-        <v>721</v>
-      </c>
-      <c r="B553" s="7" t="s">
-        <v>719</v>
-      </c>
-      <c r="C553" s="7" t="s">
-        <v>720</v>
-      </c>
-      <c r="D553" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A554" t="s">
-        <v>724</v>
-      </c>
-      <c r="B554" s="7" t="s">
-        <v>722</v>
-      </c>
-      <c r="C554" s="7" t="s">
-        <v>723</v>
-      </c>
-      <c r="D554" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A555" t="s">
-        <v>482</v>
-      </c>
-      <c r="B555" s="7" t="s">
-        <v>725</v>
-      </c>
-      <c r="C555" s="7" t="s">
-        <v>726</v>
-      </c>
-      <c r="D555" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A556" t="s">
-        <v>729</v>
-      </c>
-      <c r="B556" s="7" t="s">
-        <v>727</v>
-      </c>
-      <c r="C556" s="7" t="s">
-        <v>728</v>
-      </c>
-      <c r="D556" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A557" t="s">
-        <v>732</v>
-      </c>
-      <c r="B557" s="7" t="s">
-        <v>730</v>
-      </c>
-      <c r="C557" s="7" t="s">
-        <v>731</v>
-      </c>
-      <c r="D557" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A558" t="s">
-        <v>735</v>
-      </c>
-      <c r="B558" s="7" t="s">
-        <v>733</v>
-      </c>
-      <c r="C558" s="7" t="s">
-        <v>734</v>
-      </c>
-      <c r="D558" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A559" t="s">
-        <v>738</v>
-      </c>
-      <c r="B559" s="7" t="s">
-        <v>736</v>
-      </c>
-      <c r="C559" s="7" t="s">
-        <v>737</v>
-      </c>
-      <c r="D559" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A560" t="s">
-        <v>741</v>
-      </c>
-      <c r="B560" s="7" t="s">
-        <v>739</v>
-      </c>
-      <c r="C560" s="7" t="s">
-        <v>740</v>
-      </c>
-      <c r="D560" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A561" t="s">
-        <v>744</v>
-      </c>
-      <c r="B561" s="7" t="s">
-        <v>742</v>
-      </c>
-      <c r="C561" s="7" t="s">
-        <v>743</v>
-      </c>
-      <c r="D561" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A562" t="s">
-        <v>747</v>
-      </c>
-      <c r="B562" s="7" t="s">
-        <v>745</v>
-      </c>
-      <c r="C562" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="D562" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A563" t="s">
-        <v>750</v>
-      </c>
-      <c r="B563" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="C563" s="7" t="s">
-        <v>749</v>
-      </c>
-      <c r="D563" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A564" t="s">
-        <v>506</v>
-      </c>
-      <c r="B564" s="7" t="s">
-        <v>751</v>
-      </c>
-      <c r="C564" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="D564" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A565" t="s">
-        <v>482</v>
-      </c>
-      <c r="B565" s="7" t="s">
-        <v>753</v>
-      </c>
-      <c r="C565" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="D565" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B566" s="7" t="s">
-        <v>755</v>
-      </c>
-      <c r="C566" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="D566" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D567" s="4"/>
-    </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D568" s="4"/>
-    </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D569" s="4"/>
-    </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D570" s="4"/>
-    </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D571" s="4"/>
-    </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D572" s="4"/>
-    </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D573" s="4"/>
-    </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D574" s="4"/>
-    </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D575" s="4"/>
-    </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D576" s="4"/>
-    </row>
-    <row r="577" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D577" s="4"/>
-    </row>
-    <row r="578" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D578" s="4"/>
-    </row>
-    <row r="579" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D579" s="4"/>
-    </row>
-    <row r="580" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D580" s="4"/>
-    </row>
-    <row r="581" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D581" s="4"/>
-    </row>
-    <row r="582" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D582" s="4"/>
-    </row>
-    <row r="583" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D583" s="4"/>
-    </row>
-    <row r="584" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D584" s="4"/>
-    </row>
-    <row r="585" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D585" s="4"/>
-    </row>
-    <row r="586" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D586" s="4"/>
-    </row>
-    <row r="587" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D587" s="4"/>
-    </row>
-    <row r="588" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D588" s="4"/>
-    </row>
-    <row r="589" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D589" s="4"/>
-    </row>
-    <row r="590" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D590" s="4"/>
-    </row>
-    <row r="591" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D591" s="4"/>
-    </row>
-    <row r="592" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D592" s="4"/>
-    </row>
-    <row r="593" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D593" s="4"/>
-    </row>
-    <row r="594" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D594" s="4"/>
-    </row>
-    <row r="595" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D595" s="4"/>
-    </row>
-    <row r="596" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D596" s="4"/>
-    </row>
-    <row r="597" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D597" s="4"/>
-    </row>
-    <row r="598" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D598" s="4"/>
-    </row>
-    <row r="599" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D599" s="4"/>
-    </row>
-    <row r="600" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D600" s="4"/>
-    </row>
-    <row r="601" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D601" s="4"/>
-    </row>
-    <row r="602" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D602" s="4"/>
+      <c r="D528" s="4"/>
+    </row>
+    <row r="529" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D529" s="4"/>
+    </row>
+    <row r="530" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D530" s="4"/>
+    </row>
+    <row r="531" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D531" s="4"/>
+    </row>
+    <row r="532" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D532" s="4"/>
+    </row>
+    <row r="533" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D533" s="4"/>
+    </row>
+    <row r="534" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D534" s="4"/>
+    </row>
+    <row r="535" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D535" s="4"/>
+    </row>
+    <row r="536" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D536" s="4"/>
+    </row>
+    <row r="537" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D537" s="4"/>
+    </row>
+    <row r="538" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D538" s="4"/>
+    </row>
+    <row r="539" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D539" s="4"/>
+    </row>
+    <row r="540" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D540" s="4"/>
+    </row>
+    <row r="541" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D541" s="4"/>
+    </row>
+    <row r="542" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D542" s="4"/>
+    </row>
+    <row r="543" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D543" s="4"/>
+    </row>
+    <row r="544" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D544" s="4"/>
+    </row>
+    <row r="545" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D545" s="4"/>
+    </row>
+    <row r="546" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D546" s="4"/>
+    </row>
+    <row r="547" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D547" s="4"/>
+    </row>
+    <row r="548" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D548" s="4"/>
+    </row>
+    <row r="549" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D549" s="4"/>
+    </row>
+    <row r="550" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D550" s="4"/>
+    </row>
+    <row r="551" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D551" s="4"/>
+    </row>
+    <row r="552" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D552" s="4"/>
+    </row>
+    <row r="553" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D553" s="4"/>
+    </row>
+    <row r="554" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D554" s="4"/>
+    </row>
+    <row r="555" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D555" s="4"/>
+    </row>
+    <row r="556" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D556" s="4"/>
+    </row>
+    <row r="557" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D557" s="4"/>
+    </row>
+    <row r="558" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D558" s="4"/>
+    </row>
+    <row r="559" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D559" s="4"/>
+    </row>
+    <row r="560" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D560" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\webidasi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D466041-0E60-40A3-817A-4BFE8AD8E5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="514" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9836467E-729E-427B-BFD5-99F3AB8026C1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="685">
   <si>
     <t>nome</t>
   </si>
@@ -1935,6 +1935,165 @@
   </si>
   <si>
     <t>Secretaria De Estado Da Saude</t>
+  </si>
+  <si>
+    <t>-23.54153242542597</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.6488495330849</t>
+  </si>
+  <si>
+    <t>-23.624516001146592</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.7014987709555</t>
+  </si>
+  <si>
+    <t>-23.595226377965794</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.644718173559525</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.58392499075779</t>
+  </si>
+  <si>
+    <t>-23.556438109829077</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.6688161465765</t>
+  </si>
+  <si>
+    <t>-23.557472711764017</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66887086006866</t>
+  </si>
+  <si>
+    <t>Fund Facu De Medicina</t>
+  </si>
+  <si>
+    <t>-23.556098974420028</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.670293034936016</t>
+  </si>
+  <si>
+    <t>Hosp.Clin.Fac.Med.Univ.Sp</t>
+  </si>
+  <si>
+    <t>-23.97793606703386</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.311210601565385</t>
+  </si>
+  <si>
+    <t>Departamento Regional De Saude Da</t>
+  </si>
+  <si>
+    <t>-23.712026263227372</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.41375581958724</t>
+  </si>
+  <si>
+    <t>Dilavi Estetica E Beleza Ltda</t>
+  </si>
+  <si>
+    <t>-23.487732232930572</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.62712271780524</t>
+  </si>
+  <si>
+    <t>Sociedade Beneficente Sao Camilo</t>
+  </si>
+  <si>
+    <t>-23.969684930135767</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.32458840156706</t>
+  </si>
+  <si>
+    <t>-23.5332869314032</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.20536220424928</t>
+  </si>
+  <si>
+    <t>-23.55759964925302</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66996005213161</t>
+  </si>
+  <si>
+    <t>-22.739432202649798</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.11194048463755</t>
+  </si>
+  <si>
+    <t>Clinica Santa Rosa Ltda</t>
+  </si>
+  <si>
+    <t>-22.73942959667592</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.1118990889304</t>
+  </si>
+  <si>
+    <t>Liv Centro De Reuma E T Ass Ltda</t>
+  </si>
+  <si>
+    <t>-23.577691860704647</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64788274398148</t>
+  </si>
+  <si>
+    <t>Gsh Corp Participacoes S.A</t>
+  </si>
+  <si>
+    <t>-23.590099333979712</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.672806621442824</t>
+  </si>
+  <si>
+    <t>Dermoclin Clinica Dermatologica Eir</t>
+  </si>
+  <si>
+    <t>-23.414523662569568</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.03631550425287</t>
+  </si>
+  <si>
+    <t>Santa Casa De Misericordia De Guara</t>
+  </si>
+  <si>
+    <t>-23.556495175190648</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67018717726418</t>
+  </si>
+  <si>
+    <t>-23.668079692715132</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.52628453308078</t>
+  </si>
+  <si>
+    <t>Hosp Mat Dr Christ Da Gama S A</t>
+  </si>
+  <si>
+    <t>-23.670789833585772</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.53309888890087</t>
+  </si>
+  <si>
+    <t>Fundacao Do Abc</t>
   </si>
 </sst>
 </file>
@@ -9665,111 +9824,342 @@
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D525" s="4"/>
+      <c r="A525" t="s">
+        <v>621</v>
+      </c>
+      <c r="B525" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="C525" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="D525" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D526" s="4"/>
+      <c r="A526" t="s">
+        <v>624</v>
+      </c>
+      <c r="B526" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="C526" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="D526" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D527" s="4"/>
+      <c r="A527" t="s">
+        <v>464</v>
+      </c>
+      <c r="B527" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="C527" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="D527" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D528" s="4"/>
-    </row>
-    <row r="529" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D529" s="4"/>
-    </row>
-    <row r="530" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D530" s="4"/>
-    </row>
-    <row r="531" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D531" s="4"/>
-    </row>
-    <row r="532" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D532" s="4"/>
-    </row>
-    <row r="533" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D533" s="4"/>
-    </row>
-    <row r="534" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D534" s="4"/>
-    </row>
-    <row r="535" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D535" s="4"/>
-    </row>
-    <row r="536" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D536" s="4"/>
-    </row>
-    <row r="537" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D537" s="4"/>
-    </row>
-    <row r="538" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D538" s="4"/>
-    </row>
-    <row r="539" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D539" s="4"/>
-    </row>
-    <row r="540" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D540" s="4"/>
-    </row>
-    <row r="541" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D541" s="4"/>
-    </row>
-    <row r="542" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D542" s="4"/>
-    </row>
-    <row r="543" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D543" s="4"/>
-    </row>
-    <row r="544" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D544" s="4"/>
-    </row>
-    <row r="545" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D545" s="4"/>
-    </row>
-    <row r="546" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="A528" t="s">
+        <v>440</v>
+      </c>
+      <c r="B528" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C528" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="D528" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>631</v>
+      </c>
+      <c r="B529" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="C529" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="D529" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>643</v>
+      </c>
+      <c r="B530" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="C530" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="D530" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>646</v>
+      </c>
+      <c r="B531" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="C531" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="D531" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>649</v>
+      </c>
+      <c r="B532" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="C532" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="D532" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A533" t="s">
+        <v>652</v>
+      </c>
+      <c r="B533" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="C533" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="D533" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A534" t="s">
+        <v>655</v>
+      </c>
+      <c r="B534" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="C534" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="D534" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A535" t="s">
+        <v>440</v>
+      </c>
+      <c r="B535" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="C535" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="D535" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A536" t="s">
+        <v>473</v>
+      </c>
+      <c r="B536" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="C536" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="D536" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A537" t="s">
+        <v>646</v>
+      </c>
+      <c r="B537" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="C537" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="D537" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A538" t="s">
+        <v>664</v>
+      </c>
+      <c r="B538" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="C538" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="D538" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A539" t="s">
+        <v>667</v>
+      </c>
+      <c r="B539" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="C539" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="D539" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A540" t="s">
+        <v>670</v>
+      </c>
+      <c r="B540" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="C540" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="D540" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A541" t="s">
+        <v>673</v>
+      </c>
+      <c r="B541" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="C541" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="D541" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A542" t="s">
+        <v>676</v>
+      </c>
+      <c r="B542" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="C542" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="D542" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A543" t="s">
+        <v>646</v>
+      </c>
+      <c r="B543" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="C543" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="D543" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A544" t="s">
+        <v>681</v>
+      </c>
+      <c r="B544" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="C544" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="D544" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A545" t="s">
+        <v>684</v>
+      </c>
+      <c r="B545" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="C545" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="D545" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D546" s="4"/>
     </row>
-    <row r="547" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D547" s="4"/>
     </row>
-    <row r="548" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D548" s="4"/>
     </row>
-    <row r="549" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D549" s="4"/>
     </row>
-    <row r="550" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D550" s="4"/>
     </row>
-    <row r="551" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D551" s="4"/>
     </row>
-    <row r="552" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D552" s="4"/>
     </row>
-    <row r="553" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D553" s="4"/>
     </row>
-    <row r="554" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D554" s="4"/>
     </row>
-    <row r="555" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D555" s="4"/>
     </row>
-    <row r="556" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D556" s="4"/>
     </row>
-    <row r="557" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D557" s="4"/>
     </row>
-    <row r="558" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D558" s="4"/>
     </row>
-    <row r="559" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D559" s="4"/>
     </row>
-    <row r="560" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D560" s="4"/>
     </row>
   </sheetData>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="514" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9836467E-729E-427B-BFD5-99F3AB8026C1}"/>
+  <xr:revisionPtr revIDLastSave="526" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1584060-B9F6-4246-A2C0-9F4409A82A5E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="697">
   <si>
     <t>nome</t>
   </si>
@@ -2094,6 +2094,42 @@
   </si>
   <si>
     <t>Fundacao Do Abc</t>
+  </si>
+  <si>
+    <t>-22.74157299497972</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.594940333110074</t>
+  </si>
+  <si>
+    <t>Municipio De Campos Do Jordao</t>
+  </si>
+  <si>
+    <t>Clin Pediatrica E Vacin D P R Ltda</t>
+  </si>
+  <si>
+    <t>-23.02643835112516</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.57321244844508</t>
+  </si>
+  <si>
+    <t>-23.027432852726864</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.55902781960917</t>
+  </si>
+  <si>
+    <t>Ses Sp-Drsxvii-Taubate</t>
+  </si>
+  <si>
+    <t>-23.53264948380724</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.205591272827185</t>
+  </si>
+  <si>
+    <t>Centro Onco Mogi Cruzes Ltda / Mogi</t>
   </si>
 </sst>
 </file>
@@ -10118,16 +10154,60 @@
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D546" s="4"/>
+      <c r="A546" t="s">
+        <v>687</v>
+      </c>
+      <c r="B546" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="C546" s="7" t="s">
+        <v>686</v>
+      </c>
+      <c r="D546" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D547" s="4"/>
+      <c r="A547" t="s">
+        <v>688</v>
+      </c>
+      <c r="B547" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="C547" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="D547" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D548" s="4"/>
+      <c r="A548" t="s">
+        <v>693</v>
+      </c>
+      <c r="B548" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="C548" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="D548" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D549" s="4"/>
+      <c r="A549" t="s">
+        <v>696</v>
+      </c>
+      <c r="B549" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="C549" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="D549" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D550" s="4"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="526" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1584060-B9F6-4246-A2C0-9F4409A82A5E}"/>
+  <xr:revisionPtr revIDLastSave="541" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF9CC89E-F084-42F7-80B3-FB9637749134}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="703">
   <si>
     <t>nome</t>
   </si>
@@ -2130,6 +2130,24 @@
   </si>
   <si>
     <t>Centro Onco Mogi Cruzes Ltda / Mogi</t>
+  </si>
+  <si>
+    <t>-23.58477725863962</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67351613308339</t>
+  </si>
+  <si>
+    <t>Clinica Koza Dermat. Ltda</t>
+  </si>
+  <si>
+    <t>-23.59183017606718</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67392271959129</t>
+  </si>
+  <si>
+    <t>Mr Servicos Medicos Ltda</t>
   </si>
 </sst>
 </file>
@@ -10210,10 +10228,32 @@
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D550" s="4"/>
+      <c r="A550" t="s">
+        <v>699</v>
+      </c>
+      <c r="B550" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="C550" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="D550" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D551" s="4"/>
+      <c r="A551" t="s">
+        <v>702</v>
+      </c>
+      <c r="B551" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="C551" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="D551" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D552" s="4"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="541" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF9CC89E-F084-42F7-80B3-FB9637749134}"/>
+  <xr:revisionPtr revIDLastSave="554" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F7C61C8-CFD8-46AA-83A3-599131A8E3B8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10252,7 +10252,7 @@
         <v>701</v>
       </c>
       <c r="D551" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.3">

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="554" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F7C61C8-CFD8-46AA-83A3-599131A8E3B8}"/>
+  <xr:revisionPtr revIDLastSave="555" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{858CB8FF-56DB-4E8D-B114-1DB47D050E2B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10252,7 +10252,7 @@
         <v>701</v>
       </c>
       <c r="D551" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.3">

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="555" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{858CB8FF-56DB-4E8D-B114-1DB47D050E2B}"/>
+  <xr:revisionPtr revIDLastSave="558" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C66BD099-8B8F-4C5E-A666-BBDAE385A453}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="706">
   <si>
     <t>nome</t>
   </si>
@@ -2148,6 +2148,15 @@
   </si>
   <si>
     <t>Mr Servicos Medicos Ltda</t>
+  </si>
+  <si>
+    <t>-23.465511142446424</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.45197688688613</t>
+  </si>
+  <si>
+    <t>GLP 2</t>
   </si>
 </sst>
 </file>
@@ -10256,7 +10265,18 @@
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D552" s="4"/>
+      <c r="A552" t="s">
+        <v>705</v>
+      </c>
+      <c r="B552" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="C552" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="D552" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D553" s="4"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="558" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C66BD099-8B8F-4C5E-A666-BBDAE385A453}"/>
+  <xr:revisionPtr revIDLastSave="626" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CD3285B-E55C-49FD-AC22-517F9C708583}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="777">
   <si>
     <t>nome</t>
   </si>
@@ -2150,13 +2150,226 @@
     <t>Mr Servicos Medicos Ltda</t>
   </si>
   <si>
-    <t>-23.465511142446424</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.45197688688613</t>
-  </si>
-  <si>
-    <t>GLP 2</t>
+    <t>-23.588881667509305</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67555371773951</t>
+  </si>
+  <si>
+    <t>Dr. Fabio Carramaschi Ltda</t>
+  </si>
+  <si>
+    <t>-23.5984371629032</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.690104228449016</t>
+  </si>
+  <si>
+    <t>Abbvie Farmaceutica Ltda</t>
+  </si>
+  <si>
+    <t>-23.590726450983063</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.703679723054236</t>
+  </si>
+  <si>
+    <t>-23.461858000541632</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.53267561774368</t>
+  </si>
+  <si>
+    <t>-23.825227531464787</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.72859510794309</t>
+  </si>
+  <si>
+    <t>Spdm - Associacao Paulista Para O</t>
+  </si>
+  <si>
+    <t>-23.643848810985762</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.643393131729475</t>
+  </si>
+  <si>
+    <t>-23.594517798649118</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68543757547295</t>
+  </si>
+  <si>
+    <t>-23.522064654368574</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.56279822177888</t>
+  </si>
+  <si>
+    <t>Spdm - Associacao Paulista Para O D</t>
+  </si>
+  <si>
+    <t>-23.548741914814872</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.557962115722056</t>
+  </si>
+  <si>
+    <t>Hosp Mat Sao Luiz Sa</t>
+  </si>
+  <si>
+    <t>-23.185273120831813</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.88460660426029</t>
+  </si>
+  <si>
+    <t>Quaglia Laboratorio De Analises Cli</t>
+  </si>
+  <si>
+    <t>-23.714448830501738</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.41977916957931</t>
+  </si>
+  <si>
+    <t>-23.61683160790286</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.702064068620885</t>
+  </si>
+  <si>
+    <t>Prevent Senior Private Operadora De Saud</t>
+  </si>
+  <si>
+    <t>-23.57405314878834</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.685895417629496</t>
+  </si>
+  <si>
+    <t>Medicina Rmf Servicos Medicos Ltda</t>
+  </si>
+  <si>
+    <t>-23.61778811365637</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.63230473493409</t>
+  </si>
+  <si>
+    <t>-23.744824956368394</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.58171128841501</t>
+  </si>
+  <si>
+    <t>FLEURY S.A</t>
+  </si>
+  <si>
+    <t>-23.557686335249667</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.63498336865831</t>
+  </si>
+  <si>
+    <t>Hospital Leforte Liberdade Sa</t>
+  </si>
+  <si>
+    <t>-23.63860136542154</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.648424882543246</t>
+  </si>
+  <si>
+    <t>Tuv Sud Sfdk Laboratorio De Analise</t>
+  </si>
+  <si>
+    <t>-23.582145839521253</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.669545132239165</t>
+  </si>
+  <si>
+    <t>Dra. Bianca Lenci Viscomi</t>
+  </si>
+  <si>
+    <t>-23.570244297172593</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.33072664561862</t>
+  </si>
+  <si>
+    <t>Prefeitura De Suzano</t>
+  </si>
+  <si>
+    <t>-23.5702430679552</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.33073066893394</t>
+  </si>
+  <si>
+    <t>Fleury S.A</t>
+  </si>
+  <si>
+    <t>Dr. Rodrigo Martins Fuzaro</t>
+  </si>
+  <si>
+    <t>-23.57477661778818</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67270348610333</t>
+  </si>
+  <si>
+    <t>-23.56981775811766</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67658671458754</t>
+  </si>
+  <si>
+    <t>Clinica Dr. Otavio Roberti Macedo L</t>
+  </si>
+  <si>
+    <t>-23.578802662138948</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.668177744866334</t>
+  </si>
+  <si>
+    <t>Life Styling Consulting Ltda</t>
+  </si>
+  <si>
+    <t>-24.00704215984781</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.4316490581385</t>
+  </si>
+  <si>
+    <t>-23.494684951272227</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.54853934024136</t>
+  </si>
+  <si>
+    <t>ALLERGAN PRODUTOS FARMACEUTICOS LTD</t>
+  </si>
+  <si>
+    <t>-23.661611754116613</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.72475683385938</t>
+  </si>
+  <si>
+    <t>Abbvie Farmaceutica Ltda Laboratorio Guido Caloi</t>
+  </si>
+  <si>
+    <t>-23.661434754533737</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.72491404161047</t>
+  </si>
+  <si>
+    <t>Labinbraz Comercial Ltda</t>
   </si>
 </sst>
 </file>
@@ -2538,7 +2751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J560"/>
+  <dimension ref="A1:J588"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.77734375" customWidth="1"/>
@@ -10275,32 +10488,402 @@
         <v>704</v>
       </c>
       <c r="D552" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D553" s="4"/>
+      <c r="A553" t="s">
+        <v>708</v>
+      </c>
+      <c r="B553" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="C553" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="D553" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D554" s="4"/>
+      <c r="A554" t="s">
+        <v>432</v>
+      </c>
+      <c r="B554" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="C554" s="7" t="s">
+        <v>710</v>
+      </c>
+      <c r="D554" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D555" s="4"/>
+      <c r="A555" t="s">
+        <v>411</v>
+      </c>
+      <c r="B555" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="C555" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="D555" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D556" s="4"/>
+      <c r="A556" t="s">
+        <v>715</v>
+      </c>
+      <c r="B556" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="C556" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="D556" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D557" s="4"/>
+      <c r="A557" t="s">
+        <v>432</v>
+      </c>
+      <c r="B557" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="C557" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="D557" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D558" s="4"/>
+      <c r="A558" t="s">
+        <v>455</v>
+      </c>
+      <c r="B558" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="C558" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="D558" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D559" s="4"/>
+      <c r="A559" t="s">
+        <v>722</v>
+      </c>
+      <c r="B559" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="C559" s="7" t="s">
+        <v>721</v>
+      </c>
+      <c r="D559" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D560" s="4"/>
+      <c r="A560" t="s">
+        <v>725</v>
+      </c>
+      <c r="B560" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="C560" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="D560" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>728</v>
+      </c>
+      <c r="B561" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="C561" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="D561" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>432</v>
+      </c>
+      <c r="B562" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="C562" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="D562" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A563" t="s">
+        <v>733</v>
+      </c>
+      <c r="B563" s="7" t="s">
+        <v>731</v>
+      </c>
+      <c r="C563" s="7" t="s">
+        <v>732</v>
+      </c>
+      <c r="D563" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A564" t="s">
+        <v>736</v>
+      </c>
+      <c r="B564" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="C564" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="D564" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A565" t="s">
+        <v>399</v>
+      </c>
+      <c r="B565" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="C565" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="D565" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A566" t="s">
+        <v>741</v>
+      </c>
+      <c r="B566" s="7" t="s">
+        <v>739</v>
+      </c>
+      <c r="C566" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="D566" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
+        <v>744</v>
+      </c>
+      <c r="B567" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="C567" s="7" t="s">
+        <v>743</v>
+      </c>
+      <c r="D567" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>747</v>
+      </c>
+      <c r="B568" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="C568" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="D568" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>750</v>
+      </c>
+      <c r="B569" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="C569" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="D569" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>753</v>
+      </c>
+      <c r="B570" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="C570" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="D570" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>756</v>
+      </c>
+      <c r="B571" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="C571" s="7" t="s">
+        <v>755</v>
+      </c>
+      <c r="D571" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A572" t="s">
+        <v>757</v>
+      </c>
+      <c r="B572" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="C572" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="D572" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A573" t="s">
+        <v>762</v>
+      </c>
+      <c r="B573" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="C573" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="D573" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A574" t="s">
+        <v>765</v>
+      </c>
+      <c r="B574" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="C574" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="D574" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A575" t="s">
+        <v>354</v>
+      </c>
+      <c r="B575" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="C575" s="7" t="s">
+        <v>767</v>
+      </c>
+      <c r="D575" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A576" t="s">
+        <v>770</v>
+      </c>
+      <c r="B576" s="7" t="s">
+        <v>768</v>
+      </c>
+      <c r="C576" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="D576" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A577" t="s">
+        <v>773</v>
+      </c>
+      <c r="B577" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="C577" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="D577" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A578" t="s">
+        <v>776</v>
+      </c>
+      <c r="B578" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="C578" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="D578" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D579" s="4"/>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D580" s="4"/>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D581" s="4"/>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D582" s="4"/>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D583" s="4"/>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D584" s="4"/>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D585" s="4"/>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D586" s="4"/>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D587" s="4"/>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D588" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="626" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CD3285B-E55C-49FD-AC22-517F9C708583}"/>
+  <xr:revisionPtr revIDLastSave="691" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BF1A88B-7D16-4BDF-A43B-A797A3611D30}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="854">
   <si>
     <t>nome</t>
   </si>
@@ -2370,6 +2370,237 @@
   </si>
   <si>
     <t>Labinbraz Comercial Ltda</t>
+  </si>
+  <si>
+    <t>-23.55427039124284</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.46376637005731</t>
+  </si>
+  <si>
+    <t>-23.54947166153131</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.6841645061004</t>
+  </si>
+  <si>
+    <t>Casa De Saude Santa Marcelina</t>
+  </si>
+  <si>
+    <t>Clinica Medica Croce Ltda</t>
+  </si>
+  <si>
+    <t>-23.583078237732014</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64295037281621</t>
+  </si>
+  <si>
+    <t>Centro De Patologia Clinica Soares</t>
+  </si>
+  <si>
+    <t>-23.574998193315654</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.69601401315881</t>
+  </si>
+  <si>
+    <t>-23.6402734092189</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.80991811958961</t>
+  </si>
+  <si>
+    <t>-23.601470127663884</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66080071328859</t>
+  </si>
+  <si>
+    <t>Hospital Alvorada Taguatinga Ltda</t>
+  </si>
+  <si>
+    <t>-23.604475829432893</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.662569967790304</t>
+  </si>
+  <si>
+    <t>Dra. Caroline De Codes Crespo</t>
+  </si>
+  <si>
+    <t>-23.608634699384943</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66608315423682</t>
+  </si>
+  <si>
+    <t>-23.59517993479605</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65394977712234</t>
+  </si>
+  <si>
+    <t>-23.635912029907733</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66305065623297</t>
+  </si>
+  <si>
+    <t>Laboratorios Clinicos Associados Lt</t>
+  </si>
+  <si>
+    <t>-23.630368765466347</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.521548184351964</t>
+  </si>
+  <si>
+    <t>-23.620845495371942</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.63942498630003</t>
+  </si>
+  <si>
+    <t>Systempharma Com Prod Med Ltda</t>
+  </si>
+  <si>
+    <t>-23.541281039050137</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64927656532506</t>
+  </si>
+  <si>
+    <t>-23.613083551531076</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.655166773243714</t>
+  </si>
+  <si>
+    <t>Colsan - Assoc. Benef. Col. De San</t>
+  </si>
+  <si>
+    <t>-23.530946261789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.59957307288957</t>
+  </si>
+  <si>
+    <t>-23.607580874817003</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.72549500128221</t>
+  </si>
+  <si>
+    <t>Tecsa - Laboratorios Ltda</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.7020080830121</t>
+  </si>
+  <si>
+    <t>-23.64364718916537</t>
+  </si>
+  <si>
+    <t>-23.718293981174522</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.56064865744288</t>
+  </si>
+  <si>
+    <t>Rede Dor  Sao Luiz Sa</t>
+  </si>
+  <si>
+    <t>-23.590852999462637</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.666633788903454</t>
+  </si>
+  <si>
+    <t>Novu Clinica Integrada Ltda</t>
+  </si>
+  <si>
+    <t>-22.578494080699727</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -44.96370314899462</t>
+  </si>
+  <si>
+    <t>Clinica Med.Ort. Grossi Ltda</t>
+  </si>
+  <si>
+    <t>-23.585676566865907</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68064313123155</t>
+  </si>
+  <si>
+    <t>Jm Dermatologia - Eireli</t>
+  </si>
+  <si>
+    <t>-23.584566125691527</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67406696191939</t>
+  </si>
+  <si>
+    <t>Instituto E Clinica Matheus Arantes</t>
+  </si>
+  <si>
+    <t>-23.582707491767923</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.670895034935285</t>
+  </si>
+  <si>
+    <t>Clinica Dermatologica Denise Lage L</t>
+  </si>
+  <si>
+    <t>-23.948969149104652</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.33219078701671</t>
+  </si>
+  <si>
+    <t>Unimed De Santos Coop De Tra Medico</t>
+  </si>
+  <si>
+    <t>-23.949018174905465</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.332158600508826</t>
+  </si>
+  <si>
+    <t>Clariant Brasil Ltda-(2500050044</t>
+  </si>
+  <si>
+    <t>-23.966424938963716</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.329625386223995</t>
+  </si>
+  <si>
+    <t>Prevent Senior</t>
+  </si>
+  <si>
+    <t>-22.58136994299789</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -44.96020159216126</t>
+  </si>
+  <si>
+    <t>Clinica M. Pascoal&amp;Pen Ltda</t>
+  </si>
+  <si>
+    <t>-23.611619011478798</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.696808670958234</t>
+  </si>
+  <si>
+    <t>-23.704886403707125</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.60903983342616</t>
   </si>
 </sst>
 </file>
@@ -2751,7 +2982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J588"/>
+  <dimension ref="A1:J616"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.77734375" customWidth="1"/>
@@ -10856,34 +11087,437 @@
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D579" s="4"/>
+      <c r="A579" t="s">
+        <v>781</v>
+      </c>
+      <c r="B579" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="C579" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="D579" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D580" s="4"/>
+      <c r="A580" t="s">
+        <v>782</v>
+      </c>
+      <c r="B580" s="7" t="s">
+        <v>779</v>
+      </c>
+      <c r="C580" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="D580" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D581" s="4"/>
+      <c r="A581" t="s">
+        <v>785</v>
+      </c>
+      <c r="B581" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="C581" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="D581" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D582" s="4"/>
+      <c r="A582" t="s">
+        <v>455</v>
+      </c>
+      <c r="B582" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="C582" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="D582" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D583" s="4"/>
+      <c r="A583" t="s">
+        <v>481</v>
+      </c>
+      <c r="B583" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="C583" s="7" t="s">
+        <v>789</v>
+      </c>
+      <c r="D583" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D584" s="4"/>
+      <c r="A584" t="s">
+        <v>792</v>
+      </c>
+      <c r="B584" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="C584" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="D584" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D585" s="4"/>
+      <c r="A585" t="s">
+        <v>795</v>
+      </c>
+      <c r="B585" s="7" t="s">
+        <v>793</v>
+      </c>
+      <c r="C585" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="D585" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D586" s="4"/>
+      <c r="A586" t="s">
+        <v>708</v>
+      </c>
+      <c r="B586" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="C586" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="D586" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D587" s="4"/>
+      <c r="A587" t="s">
+        <v>461</v>
+      </c>
+      <c r="B587" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="C587" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="D587" s="4" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D588" s="4"/>
+      <c r="A588" t="s">
+        <v>802</v>
+      </c>
+      <c r="B588" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="C588" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="D588" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A589" t="s">
+        <v>357</v>
+      </c>
+      <c r="B589" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="C589" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="D589" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A590" t="s">
+        <v>807</v>
+      </c>
+      <c r="B590" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="C590" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="D590" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A591" t="s">
+        <v>733</v>
+      </c>
+      <c r="B591" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="C591" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="D591" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A592" t="s">
+        <v>812</v>
+      </c>
+      <c r="B592" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="C592" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="D592" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A593" t="s">
+        <v>481</v>
+      </c>
+      <c r="B593" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="C593" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="D593" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A594" t="s">
+        <v>817</v>
+      </c>
+      <c r="B594" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="C594" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="D594" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A595" t="s">
+        <v>473</v>
+      </c>
+      <c r="B595" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="C595" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="D595" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A596" t="s">
+        <v>822</v>
+      </c>
+      <c r="B596" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="C596" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="D596" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A597" t="s">
+        <v>825</v>
+      </c>
+      <c r="B597" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="C597" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="D597" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A598" t="s">
+        <v>828</v>
+      </c>
+      <c r="B598" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="C598" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="D598" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A599" t="s">
+        <v>831</v>
+      </c>
+      <c r="B599" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="C599" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="D599" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A600" t="s">
+        <v>834</v>
+      </c>
+      <c r="B600" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="C600" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="D600" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A601" t="s">
+        <v>837</v>
+      </c>
+      <c r="B601" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="C601" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D601" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A602" t="s">
+        <v>840</v>
+      </c>
+      <c r="B602" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="C602" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="D602" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A603" t="s">
+        <v>843</v>
+      </c>
+      <c r="B603" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="C603" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="D603" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A604" t="s">
+        <v>846</v>
+      </c>
+      <c r="B604" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="C604" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="D604" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A605" t="s">
+        <v>849</v>
+      </c>
+      <c r="B605" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="C605" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="D605" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A606" t="s">
+        <v>708</v>
+      </c>
+      <c r="B606" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="C606" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="D606" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A607" t="s">
+        <v>481</v>
+      </c>
+      <c r="B607" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="C607" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="D607" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D608" s="4"/>
+    </row>
+    <row r="609" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D609" s="4"/>
+    </row>
+    <row r="610" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D610" s="4"/>
+    </row>
+    <row r="611" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D611" s="4"/>
+    </row>
+    <row r="612" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D612" s="4"/>
+    </row>
+    <row r="613" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D613" s="4"/>
+    </row>
+    <row r="614" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D614" s="4"/>
+    </row>
+    <row r="615" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D615" s="4"/>
+    </row>
+    <row r="616" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D616" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="691" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BF1A88B-7D16-4BDF-A43B-A797A3611D30}"/>
+  <xr:revisionPtr revIDLastSave="719" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C331398-576E-48C3-AA5F-EBBFBA5A340F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="883">
   <si>
     <t>nome</t>
   </si>
@@ -2601,6 +2601,93 @@
   </si>
   <si>
     <t xml:space="preserve"> -46.60903983342616</t>
+  </si>
+  <si>
+    <t>-23.540207539160978</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.732760588905194</t>
+  </si>
+  <si>
+    <t>Evale Diagnosticos Ltda</t>
+  </si>
+  <si>
+    <t>-23.184545962734607</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.87859497494437</t>
+  </si>
+  <si>
+    <t>Municipio De S J Dos Campos</t>
+  </si>
+  <si>
+    <t>-23.766257360835233</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.58652729074939</t>
+  </si>
+  <si>
+    <t>Assoc Fund De Incentivo A Pesquisa</t>
+  </si>
+  <si>
+    <t>-23.557868723204894</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.56470305747786</t>
+  </si>
+  <si>
+    <t>-23.67346748505367</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.85732111958855</t>
+  </si>
+  <si>
+    <t>-23.470752083425708</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.53504193051256</t>
+  </si>
+  <si>
+    <t>Dr. Carlos Eduardo Nunes</t>
+  </si>
+  <si>
+    <t>-23.661132886740873</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.55683914842479</t>
+  </si>
+  <si>
+    <t>-23.672522031611862</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.5889158502763</t>
+  </si>
+  <si>
+    <t>Sgs Do Brasil Ltda</t>
+  </si>
+  <si>
+    <t>-23.197863195987285</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.917446785448526</t>
+  </si>
+  <si>
+    <t>-23.599630404432684</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.63753497281262</t>
+  </si>
+  <si>
+    <t>Associacao Fundo De Incentivo</t>
+  </si>
+  <si>
+    <t>-23.54994765929432</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65853121355729</t>
+  </si>
+  <si>
+    <t>Saha Serv Medic Hospitalares Ltda</t>
   </si>
 </sst>
 </file>
@@ -2982,7 +3069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J616"/>
+  <dimension ref="A1:J619"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.77734375" customWidth="1"/>
@@ -11493,31 +11580,161 @@
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D608" s="4"/>
-    </row>
-    <row r="609" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D609" s="4"/>
-    </row>
-    <row r="610" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D610" s="4"/>
-    </row>
-    <row r="611" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D611" s="4"/>
-    </row>
-    <row r="612" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D612" s="4"/>
-    </row>
-    <row r="613" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D613" s="4"/>
-    </row>
-    <row r="614" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D614" s="4"/>
-    </row>
-    <row r="615" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D615" s="4"/>
-    </row>
-    <row r="616" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D616" s="4"/>
+      <c r="A608" t="s">
+        <v>856</v>
+      </c>
+      <c r="B608" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="C608" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="D608" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A609" t="s">
+        <v>859</v>
+      </c>
+      <c r="B609" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="C609" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="D609" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A610" t="s">
+        <v>862</v>
+      </c>
+      <c r="B610" s="7" t="s">
+        <v>860</v>
+      </c>
+      <c r="C610" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="D610" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A611" t="s">
+        <v>455</v>
+      </c>
+      <c r="B611" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="C611" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="D611" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A612" t="s">
+        <v>559</v>
+      </c>
+      <c r="B612" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="C612" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="D612" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A613" t="s">
+        <v>869</v>
+      </c>
+      <c r="B613" s="7" t="s">
+        <v>867</v>
+      </c>
+      <c r="C613" s="7" t="s">
+        <v>868</v>
+      </c>
+      <c r="D613" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A614" t="s">
+        <v>684</v>
+      </c>
+      <c r="B614" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="C614" s="7" t="s">
+        <v>871</v>
+      </c>
+      <c r="D614" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A615" t="s">
+        <v>874</v>
+      </c>
+      <c r="B615" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="C615" s="7" t="s">
+        <v>873</v>
+      </c>
+      <c r="D615" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A616" t="s">
+        <v>357</v>
+      </c>
+      <c r="B616" s="7" t="s">
+        <v>875</v>
+      </c>
+      <c r="C616" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="D616" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A617" t="s">
+        <v>879</v>
+      </c>
+      <c r="B617" s="7" t="s">
+        <v>877</v>
+      </c>
+      <c r="C617" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="D617" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A618" t="s">
+        <v>882</v>
+      </c>
+      <c r="B618" s="7" t="s">
+        <v>880</v>
+      </c>
+      <c r="C618" s="7" t="s">
+        <v>881</v>
+      </c>
+      <c r="D618" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D619" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="719" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C331398-576E-48C3-AA5F-EBBFBA5A340F}"/>
+  <xr:revisionPtr revIDLastSave="735" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8397A2B-097C-4174-9D60-AB71E9CC223A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="900">
   <si>
     <t>nome</t>
   </si>
@@ -2688,6 +2688,57 @@
   </si>
   <si>
     <t>Saha Serv Medic Hospitalares Ltda</t>
+  </si>
+  <si>
+    <t>-23.597166476552783</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68524661299734</t>
+  </si>
+  <si>
+    <t>-23.68850653050148</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.55371064901907</t>
+  </si>
+  <si>
+    <t>-23.69235008263985</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.555069262329006</t>
+  </si>
+  <si>
+    <t>-23.555980745829135</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.56105012479932</t>
+  </si>
+  <si>
+    <t>CLINICA ANALIAMED SAUDE E BEM ESTAR</t>
+  </si>
+  <si>
+    <t>-23.619142747459193</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.40980961773843</t>
+  </si>
+  <si>
+    <t>Municipio De Caraguatatuba</t>
+  </si>
+  <si>
+    <t>-23.570565450048214</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64191990165489</t>
+  </si>
+  <si>
+    <t>-23.56739323211471</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.641747746576044</t>
+  </si>
+  <si>
+    <t>Real Benem Assoc Port Beneficencia Real Benem Assoc Port Ben</t>
   </si>
 </sst>
 </file>
@@ -3069,7 +3120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J619"/>
+  <dimension ref="A1:J626"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.77734375" customWidth="1"/>
@@ -11734,7 +11785,105 @@
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D619" s="4"/>
+      <c r="A619" t="s">
+        <v>399</v>
+      </c>
+      <c r="B619" s="7" t="s">
+        <v>883</v>
+      </c>
+      <c r="C619" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="D619" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A620" t="s">
+        <v>440</v>
+      </c>
+      <c r="B620" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="C620" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="D620" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A621" t="s">
+        <v>411</v>
+      </c>
+      <c r="B621" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="C621" s="7" t="s">
+        <v>888</v>
+      </c>
+      <c r="D621" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A622" t="s">
+        <v>891</v>
+      </c>
+      <c r="B622" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="C622" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="D622" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A623" t="s">
+        <v>894</v>
+      </c>
+      <c r="B623" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="C623" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="D623" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A624" t="s">
+        <v>399</v>
+      </c>
+      <c r="B624" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="C624" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="D624" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A625" t="s">
+        <v>899</v>
+      </c>
+      <c r="B625" s="7" t="s">
+        <v>897</v>
+      </c>
+      <c r="C625" s="7" t="s">
+        <v>898</v>
+      </c>
+      <c r="D625" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D626" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="735" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8397A2B-097C-4174-9D60-AB71E9CC223A}"/>
+  <xr:revisionPtr revIDLastSave="825" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{671DEC7E-A172-40C2-B180-2411FC486D0B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="1006">
   <si>
     <t>nome</t>
   </si>
@@ -2739,6 +2739,324 @@
   </si>
   <si>
     <t>Real Benem Assoc Port Beneficencia Real Benem Assoc Port Ben</t>
+  </si>
+  <si>
+    <t>-23.56430508977408</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64110322306412</t>
+  </si>
+  <si>
+    <t>-23.59898345939083</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.69727777623237</t>
+  </si>
+  <si>
+    <t>Er Servicos Medicos Ltda</t>
+  </si>
+  <si>
+    <t>-23.601870138150467</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.698123133082944</t>
+  </si>
+  <si>
+    <t>Clinica Katia Volpe Fogolin Serv Me</t>
+  </si>
+  <si>
+    <t>-23.1901132911918</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.88908801370077</t>
+  </si>
+  <si>
+    <t>Fernanda Navarro Loiola</t>
+  </si>
+  <si>
+    <t>-22.576655359904976</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -44.9614560772952</t>
+  </si>
+  <si>
+    <t>Coder Centro Ortopedico E Dermato Ss</t>
+  </si>
+  <si>
+    <t>-23.510141237960767</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.19491570424993</t>
+  </si>
+  <si>
+    <t>-23.530233553082994</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.697068057483776</t>
+  </si>
+  <si>
+    <t>-23.57952608511927</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.78203346191949</t>
+  </si>
+  <si>
+    <t>Sociedade Benef Israelita Bras</t>
+  </si>
+  <si>
+    <t>-23.480208327034223</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.642816919594594</t>
+  </si>
+  <si>
+    <t>Instituto Global Gestao</t>
+  </si>
+  <si>
+    <t>-23.66984076586461</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.44956930497305</t>
+  </si>
+  <si>
+    <t>Hospitais Integrados Da Gavea S A</t>
+  </si>
+  <si>
+    <t>-23.54981199768674</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.658616884803315</t>
+  </si>
+  <si>
+    <t>Sociedade Brasileira De Cirurgia De</t>
+  </si>
+  <si>
+    <t>-23.601086055251884</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.661382717565786</t>
+  </si>
+  <si>
+    <t>Dra. Renata Fogolin Violato Tagliaf</t>
+  </si>
+  <si>
+    <t>-23.564047429156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.559008788904464</t>
+  </si>
+  <si>
+    <t>-23.621128847322506</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.69183197095609</t>
+  </si>
+  <si>
+    <t>Genesis Analises Genomicas S A</t>
+  </si>
+  <si>
+    <t>-23.622726202038816</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68565000424619</t>
+  </si>
+  <si>
+    <t>-23.605448816182818</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.712767118344836</t>
+  </si>
+  <si>
+    <t>Lotten Eyes Oftalmologia Clinica E</t>
+  </si>
+  <si>
+    <t>-23.536499955524462</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.70356936366876</t>
+  </si>
+  <si>
+    <t>Mirian Suzana Gil Gewehr</t>
+  </si>
+  <si>
+    <t>-23.028769833413744</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.565181431249556</t>
+  </si>
+  <si>
+    <t>Artrocenter Clinica Medica Ltda</t>
+  </si>
+  <si>
+    <t>-23.59751491435573</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64366163719467</t>
+  </si>
+  <si>
+    <t>-23.519423942765474</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.19137548423811</t>
+  </si>
+  <si>
+    <t>Clin Infl Sao Nicolau S S Ltda</t>
+  </si>
+  <si>
+    <t>-23.552777457519305</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.55932786993428</t>
+  </si>
+  <si>
+    <t>-23.196143208935403</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.893890934431106</t>
+  </si>
+  <si>
+    <t>Policlin S A Servicos Medico Hospit</t>
+  </si>
+  <si>
+    <t>-23.57056763842754</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66294993308406</t>
+  </si>
+  <si>
+    <t>Fruges E Fontenele Estet Avancada L</t>
+  </si>
+  <si>
+    <t>-23.5716293735547</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.6635694889042</t>
+  </si>
+  <si>
+    <t>Centro De Infus Terapia Imuno Ltda</t>
+  </si>
+  <si>
+    <t>-23.577353848517475</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67293696588821</t>
+  </si>
+  <si>
+    <t>-23.953057116632465</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.329656130406846</t>
+  </si>
+  <si>
+    <t>Dra. Sonia Maria Voss Gonzalez</t>
+  </si>
+  <si>
+    <t>-23.601017524688153</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64746191959085</t>
+  </si>
+  <si>
+    <t>Marina Hayashida Dermatologia Ltda</t>
+  </si>
+  <si>
+    <t>-23.570253656125892</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.61433329684113</t>
+  </si>
+  <si>
+    <t>Hospital Militar De Area De Sao Paulo</t>
+  </si>
+  <si>
+    <t>-23.537168263954268</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.663344686318425</t>
+  </si>
+  <si>
+    <t>Imunolaboratorio Triagem De Doadore</t>
+  </si>
+  <si>
+    <t>-23.543877571883588</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.58557478890498</t>
+  </si>
+  <si>
+    <t>Rede D Or Sao Luiz S.A</t>
+  </si>
+  <si>
+    <t>-23.601690063177468</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.62651833493459</t>
+  </si>
+  <si>
+    <t>-23.623827867145778</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68745169116571</t>
+  </si>
+  <si>
+    <t>Food Intelligence Lab.Anal. De Alim</t>
+  </si>
+  <si>
+    <t>-23.569659005967274</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.645582317740015</t>
+  </si>
+  <si>
+    <t>Assoc Congr Santa Catarina</t>
+  </si>
+  <si>
+    <t>-23.956993995924027</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.3336622339688</t>
+  </si>
+  <si>
+    <t>Hospital Ana Costa</t>
+  </si>
+  <si>
+    <t>-23.596992549162813</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65443051959091</t>
+  </si>
+  <si>
+    <t>-23.559081046965716</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65553691722167</t>
+  </si>
+  <si>
+    <t>Serviço De Hemoterapia 9 De Julho L</t>
+  </si>
+  <si>
+    <t>-23.55922258412122</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.6557109177404</t>
+  </si>
+  <si>
+    <t>Impar Servicos Hospitalares Sa</t>
+  </si>
+  <si>
+    <t>-23.591738549608586</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68532045932214</t>
+  </si>
+  <si>
+    <t>Dr. Eduardo Gustavo Pires De Arruda</t>
+  </si>
+  <si>
+    <t>-23.69055280945754</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.54788670239236</t>
   </si>
 </sst>
 </file>
@@ -3120,7 +3438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J626"/>
+  <dimension ref="A1:J672"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.77734375" customWidth="1"/>
@@ -11883,7 +12201,574 @@
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D626" s="4"/>
+      <c r="A626" t="s">
+        <v>882</v>
+      </c>
+      <c r="B626" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="C626" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="D626" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A627" t="s">
+        <v>904</v>
+      </c>
+      <c r="B627" s="7" t="s">
+        <v>902</v>
+      </c>
+      <c r="C627" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="D627" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A628" t="s">
+        <v>907</v>
+      </c>
+      <c r="B628" s="7" t="s">
+        <v>905</v>
+      </c>
+      <c r="C628" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="D628" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A629" t="s">
+        <v>910</v>
+      </c>
+      <c r="B629" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="C629" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="D629" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A630" t="s">
+        <v>913</v>
+      </c>
+      <c r="B630" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="C630" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="D630" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A631" t="s">
+        <v>481</v>
+      </c>
+      <c r="B631" s="7" t="s">
+        <v>914</v>
+      </c>
+      <c r="C631" s="7" t="s">
+        <v>915</v>
+      </c>
+      <c r="D631" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A632" t="s">
+        <v>411</v>
+      </c>
+      <c r="B632" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="C632" s="7" t="s">
+        <v>917</v>
+      </c>
+      <c r="D632" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A633" t="s">
+        <v>920</v>
+      </c>
+      <c r="B633" s="7" t="s">
+        <v>918</v>
+      </c>
+      <c r="C633" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="D633" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A634" t="s">
+        <v>923</v>
+      </c>
+      <c r="B634" s="7" t="s">
+        <v>921</v>
+      </c>
+      <c r="C634" s="7" t="s">
+        <v>922</v>
+      </c>
+      <c r="D634" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A635" t="s">
+        <v>926</v>
+      </c>
+      <c r="B635" s="7" t="s">
+        <v>924</v>
+      </c>
+      <c r="C635" s="7" t="s">
+        <v>925</v>
+      </c>
+      <c r="D635" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A636" t="s">
+        <v>929</v>
+      </c>
+      <c r="B636" s="7" t="s">
+        <v>927</v>
+      </c>
+      <c r="C636" s="7" t="s">
+        <v>928</v>
+      </c>
+      <c r="D636" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A637" t="s">
+        <v>932</v>
+      </c>
+      <c r="B637" s="7" t="s">
+        <v>930</v>
+      </c>
+      <c r="C637" s="7" t="s">
+        <v>931</v>
+      </c>
+      <c r="D637" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A638" t="s">
+        <v>440</v>
+      </c>
+      <c r="B638" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="C638" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="D638" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A639" t="s">
+        <v>937</v>
+      </c>
+      <c r="B639" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="C639" s="7" t="s">
+        <v>936</v>
+      </c>
+      <c r="D639" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A640" t="s">
+        <v>741</v>
+      </c>
+      <c r="B640" s="7" t="s">
+        <v>938</v>
+      </c>
+      <c r="C640" s="7" t="s">
+        <v>939</v>
+      </c>
+      <c r="D640" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A641" t="s">
+        <v>942</v>
+      </c>
+      <c r="B641" s="7" t="s">
+        <v>940</v>
+      </c>
+      <c r="C641" s="7" t="s">
+        <v>941</v>
+      </c>
+      <c r="D641" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A642" t="s">
+        <v>945</v>
+      </c>
+      <c r="B642" s="7" t="s">
+        <v>943</v>
+      </c>
+      <c r="C642" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="D642" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A643" t="s">
+        <v>948</v>
+      </c>
+      <c r="B643" s="7" t="s">
+        <v>946</v>
+      </c>
+      <c r="C643" s="7" t="s">
+        <v>947</v>
+      </c>
+      <c r="D643" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A644" t="s">
+        <v>464</v>
+      </c>
+      <c r="B644" s="7" t="s">
+        <v>949</v>
+      </c>
+      <c r="C644" s="7" t="s">
+        <v>950</v>
+      </c>
+      <c r="D644" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A645" t="s">
+        <v>953</v>
+      </c>
+      <c r="B645" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="C645" s="7" t="s">
+        <v>952</v>
+      </c>
+      <c r="D645" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A646" t="s">
+        <v>708</v>
+      </c>
+      <c r="B646" s="7" t="s">
+        <v>954</v>
+      </c>
+      <c r="C646" s="7" t="s">
+        <v>955</v>
+      </c>
+      <c r="D646" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A647" t="s">
+        <v>958</v>
+      </c>
+      <c r="B647" s="7" t="s">
+        <v>956</v>
+      </c>
+      <c r="C647" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="D647" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A648" t="s">
+        <v>961</v>
+      </c>
+      <c r="B648" s="7" t="s">
+        <v>959</v>
+      </c>
+      <c r="C648" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="D648" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A649" t="s">
+        <v>964</v>
+      </c>
+      <c r="B649" s="7" t="s">
+        <v>962</v>
+      </c>
+      <c r="C649" s="7" t="s">
+        <v>963</v>
+      </c>
+      <c r="D649" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A650" t="s">
+        <v>708</v>
+      </c>
+      <c r="B650" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="C650" s="7" t="s">
+        <v>966</v>
+      </c>
+      <c r="D650" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A651" t="s">
+        <v>969</v>
+      </c>
+      <c r="B651" s="7" t="s">
+        <v>967</v>
+      </c>
+      <c r="C651" s="7" t="s">
+        <v>968</v>
+      </c>
+      <c r="D651" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A652" t="s">
+        <v>972</v>
+      </c>
+      <c r="B652" s="7" t="s">
+        <v>970</v>
+      </c>
+      <c r="C652" s="7" t="s">
+        <v>971</v>
+      </c>
+      <c r="D652" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A653" t="s">
+        <v>975</v>
+      </c>
+      <c r="B653" s="7" t="s">
+        <v>973</v>
+      </c>
+      <c r="C653" s="7" t="s">
+        <v>974</v>
+      </c>
+      <c r="D653" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A654" t="s">
+        <v>978</v>
+      </c>
+      <c r="B654" s="7" t="s">
+        <v>976</v>
+      </c>
+      <c r="C654" s="7" t="s">
+        <v>977</v>
+      </c>
+      <c r="D654" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A655" t="s">
+        <v>981</v>
+      </c>
+      <c r="B655" s="7" t="s">
+        <v>979</v>
+      </c>
+      <c r="C655" s="7" t="s">
+        <v>980</v>
+      </c>
+      <c r="D655" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A656" t="s">
+        <v>879</v>
+      </c>
+      <c r="B656" s="7" t="s">
+        <v>982</v>
+      </c>
+      <c r="C656" s="7" t="s">
+        <v>983</v>
+      </c>
+      <c r="D656" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A657" t="s">
+        <v>986</v>
+      </c>
+      <c r="B657" s="7" t="s">
+        <v>984</v>
+      </c>
+      <c r="C657" s="7" t="s">
+        <v>985</v>
+      </c>
+      <c r="D657" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A658" t="s">
+        <v>989</v>
+      </c>
+      <c r="B658" s="7" t="s">
+        <v>987</v>
+      </c>
+      <c r="C658" s="7" t="s">
+        <v>988</v>
+      </c>
+      <c r="D658" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A659" t="s">
+        <v>992</v>
+      </c>
+      <c r="B659" s="7" t="s">
+        <v>990</v>
+      </c>
+      <c r="C659" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="D659" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A660" t="s">
+        <v>812</v>
+      </c>
+      <c r="B660" s="7" t="s">
+        <v>993</v>
+      </c>
+      <c r="C660" s="7" t="s">
+        <v>994</v>
+      </c>
+      <c r="D660" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A661" t="s">
+        <v>997</v>
+      </c>
+      <c r="B661" s="7" t="s">
+        <v>995</v>
+      </c>
+      <c r="C661" s="7" t="s">
+        <v>996</v>
+      </c>
+      <c r="D661" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A662" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B662" s="7" t="s">
+        <v>998</v>
+      </c>
+      <c r="C662" s="7" t="s">
+        <v>999</v>
+      </c>
+      <c r="D662" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A663" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B663" s="7" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C663" s="7" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D663" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A664" t="s">
+        <v>440</v>
+      </c>
+      <c r="B664" s="7" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C664" s="7" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D664" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D665" s="4"/>
+    </row>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D666" s="4"/>
+    </row>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D667" s="4"/>
+    </row>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D668" s="4"/>
+    </row>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D669" s="4"/>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D670" s="4"/>
+    </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D671" s="4"/>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D672" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="825" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{671DEC7E-A172-40C2-B180-2411FC486D0B}"/>
+  <xr:revisionPtr revIDLastSave="838" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE5C611A-CF82-4965-90C7-4A601F46E036}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="1009">
   <si>
     <t>nome</t>
   </si>
@@ -3057,6 +3057,15 @@
   </si>
   <si>
     <t xml:space="preserve"> -46.54788670239236</t>
+  </si>
+  <si>
+    <t>TESTE</t>
+  </si>
+  <si>
+    <t>-23.441618712207582</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.41904920610375</t>
   </si>
 </sst>
 </file>
@@ -12747,7 +12756,18 @@
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D665" s="4"/>
+      <c r="A665" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B665" s="7" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C665" s="7" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D665" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D666" s="4"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="847" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{012D7C85-C920-43DF-8495-31CC28DE2827}"/>
+  <xr:revisionPtr revIDLastSave="848" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{511F99A3-8FF1-4CBA-8AD6-43C12690840B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve"> -46.41904920610375</t>
   </si>
   <si>
-    <t>descrição</t>
-  </si>
-  <si>
     <t>Com carrinho: das 22h às 11h, todos os dias | Em mãos: das 16h às 18h, de segunda a sexta-feira. | Em mãos: das 16h às 17h, aos finais de semana e feriados</t>
   </si>
   <si>
     <t>Shopping SP Market</t>
+  </si>
+  <si>
+    <t>descricao</t>
   </si>
 </sst>
 </file>
@@ -3488,7 +3488,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -3619,7 +3619,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B11" s="7">
         <v>-23.678487000000001</v>
@@ -3631,7 +3631,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="848" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{511F99A3-8FF1-4CBA-8AD6-43C12690840B}"/>
+  <xr:revisionPtr revIDLastSave="859" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{257ABEFB-68AF-4559-9566-FFC552300856}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="1026">
   <si>
     <t>nome</t>
   </si>
@@ -3056,15 +3056,6 @@
     <t xml:space="preserve"> -46.54788670239236</t>
   </si>
   <si>
-    <t>TESTE</t>
-  </si>
-  <si>
-    <t>-23.441618712207582</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -46.41904920610375</t>
-  </si>
-  <si>
     <t>Com carrinho: das 22h às 11h, todos os dias | Em mãos: das 16h às 18h, de segunda a sexta-feira. | Em mãos: das 16h às 17h, aos finais de semana e feriados</t>
   </si>
   <si>
@@ -3072,6 +3063,60 @@
   </si>
   <si>
     <t>descricao</t>
+  </si>
+  <si>
+    <t>06h às 10h - carrinho 4 rodas | 10h às 12h - carrinho 2 rodas</t>
+  </si>
+  <si>
+    <t>06h às 10h - carrinho 4 rodas | 10h às 12h - carrinho 2 rodas | 12h às 22h - apenas perecíveis</t>
+  </si>
+  <si>
+    <t>Apenas com agendamento via portal, dia todo</t>
+  </si>
+  <si>
+    <t>Até às 10h - Entregas somente fora do horário de funcionamento do shopping</t>
+  </si>
+  <si>
+    <t>Até às 10h pode utilizar carrinho, após o horário, apenas manualmente e sempre com lojista acompanhando</t>
+  </si>
+  <si>
+    <t>Com carrinho até às 10h| Itens de pequeno porte: 10h às 22h - apenas manualmente, sem carrinhos, caixas abaixo do ombro</t>
+  </si>
+  <si>
+    <t>Docas 24h, porém, das 23h às 6h sempre com lojista acompanhando | Até 9h40 permitido entrar com carrinho, após isso, apenas manualmente, caixas abaixo do ombro</t>
+  </si>
+  <si>
+    <t>Das 22h às 09h</t>
+  </si>
+  <si>
+    <t>Das 22h às 09h45 com carrinho | Das 10h às 12h apenas manualmente, caixas abaixo do ombro</t>
+  </si>
+  <si>
+    <t>Das 22h às 10h. Necessário alguém da loja para receber</t>
+  </si>
+  <si>
+    <t>Doca 1 (térreo): 24h | Doca 2: até 00h | Carrinho com 4 rodas até às 10h, carrinho com 2 rodas até 12h. | Caixas em mãos: dentro do horário de funcionamento, abaixo do ombro</t>
+  </si>
+  <si>
+    <t>Entregas liberadas durante o horário de funcionamento do Shopping/Loja | Horário: Seg a Sex 10h às 22h - Sáb 14h às 22h</t>
+  </si>
+  <si>
+    <t>Itens de grande porte: 22h às 09h30 | Itens de pequeno porte: 10h às 22h - apenas manualmente, sem carrinhos</t>
+  </si>
+  <si>
+    <t>Seg a Sáb: 06h às 11h</t>
+  </si>
+  <si>
+    <t>Seg a Sex 07h às 22h - Sáb 07h às 14h</t>
+  </si>
+  <si>
+    <t>Seg a Sex: 22h às 11h - 15h às 18h | Sáb: até às 11h</t>
+  </si>
+  <si>
+    <t>Seg a Sex: 8h30 às 11h30 e das 14h às 17h | Sáb: 8h30 às 12h | Doca 1: caminhões | Doca 2: veículos de pequeno porte</t>
+  </si>
+  <si>
+    <t>Dentro do horário de funcionamento do shopping, tratado diretamente com o lojista</t>
   </si>
 </sst>
 </file>
@@ -3464,14 +3509,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J672"/>
+  <dimension ref="A1:J671"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.77734375" customWidth="1"/>
     <col min="2" max="2" width="21.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="131.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="140.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -3488,7 +3533,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -3532,6 +3577,9 @@
       <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="E4" t="s">
+        <v>1008</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -3546,6 +3594,9 @@
       <c r="D5" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="E5" t="s">
+        <v>1009</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -3560,6 +3611,9 @@
       <c r="D6" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="E6" t="s">
+        <v>1010</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -3574,6 +3628,9 @@
       <c r="D7" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="E7" t="s">
+        <v>1011</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -3588,6 +3645,9 @@
       <c r="D8" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="E8" t="s">
+        <v>1012</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -3602,6 +3662,9 @@
       <c r="D9" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="E9" t="s">
+        <v>1013</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -3616,10 +3679,13 @@
       <c r="D10" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="E10" t="s">
+        <v>1013</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="B11" s="7">
         <v>-23.678487000000001</v>
@@ -3631,7 +3697,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -3704,7 +3770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -3718,7 +3784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -3732,7 +3798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
@@ -3745,8 +3811,11 @@
       <c r="D19" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
@@ -3760,7 +3829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
@@ -3774,7 +3843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
@@ -3788,7 +3857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
@@ -3801,8 +3870,11 @@
       <c r="D23" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
@@ -3816,7 +3888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
@@ -3830,7 +3902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
@@ -3844,7 +3916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
@@ -3858,7 +3930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
@@ -3871,8 +3943,11 @@
       <c r="D28" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>31</v>
       </c>
@@ -3885,8 +3960,11 @@
       <c r="D29" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -3899,8 +3977,11 @@
       <c r="D30" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>33</v>
       </c>
@@ -3913,8 +3994,11 @@
       <c r="D31" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>34</v>
       </c>
@@ -3927,8 +4011,11 @@
       <c r="D32" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
@@ -3941,8 +4028,11 @@
       <c r="D33" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>36</v>
       </c>
@@ -3955,8 +4045,11 @@
       <c r="D34" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
@@ -3969,8 +4062,11 @@
       <c r="D35" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>38</v>
       </c>
@@ -3983,8 +4079,11 @@
       <c r="D36" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>39</v>
       </c>
@@ -3997,8 +4096,11 @@
       <c r="D37" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
@@ -4011,8 +4113,11 @@
       <c r="D38" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>41</v>
       </c>
@@ -4026,7 +4131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>42</v>
       </c>
@@ -4040,7 +4145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>43</v>
       </c>
@@ -4054,7 +4159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>44</v>
       </c>
@@ -4068,7 +4173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>45</v>
       </c>
@@ -4082,7 +4187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>46</v>
       </c>
@@ -4096,7 +4201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>47</v>
       </c>
@@ -4110,7 +4215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>48</v>
       </c>
@@ -4124,7 +4229,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>49</v>
       </c>
@@ -4138,7 +4243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>50</v>
       </c>
@@ -12779,18 +12884,7 @@
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A665" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B665" s="7" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C665" s="7" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D665" s="4" t="s">
-        <v>322</v>
-      </c>
+      <c r="D665" s="4"/>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D666" s="4"/>
@@ -12809,9 +12903,6 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D671" s="4"/>
-    </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D672" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="859" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{257ABEFB-68AF-4559-9566-FFC552300856}"/>
+  <xr:revisionPtr revIDLastSave="862" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2178A8A6-1A3A-462C-A7AA-0EE3BB613529}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="1026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="1028">
   <si>
     <t>nome</t>
   </si>
@@ -3117,6 +3117,12 @@
   </si>
   <si>
     <t>Dentro do horário de funcionamento do shopping, tratado diretamente com o lojista</t>
+  </si>
+  <si>
+    <t>Loja não recebe aos sábados</t>
+  </si>
+  <si>
+    <t>verde escuro</t>
   </si>
 </sst>
 </file>
@@ -3515,7 +3521,7 @@
     <col min="1" max="1" width="85.77734375" customWidth="1"/>
     <col min="2" max="2" width="21.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="140.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5153,7 +5159,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>108</v>
       </c>
@@ -5167,7 +5173,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>109</v>
       </c>
@@ -5181,7 +5187,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>110</v>
       </c>
@@ -5195,7 +5201,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>111</v>
       </c>
@@ -5209,7 +5215,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>112</v>
       </c>
@@ -5223,7 +5229,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>113</v>
       </c>
@@ -5237,7 +5243,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>114</v>
       </c>
@@ -5251,7 +5257,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>115</v>
       </c>
@@ -5265,7 +5271,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>115</v>
       </c>
@@ -5279,7 +5285,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>116</v>
       </c>
@@ -5293,7 +5299,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>116</v>
       </c>
@@ -5307,7 +5313,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>117</v>
       </c>
@@ -5321,7 +5327,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>118</v>
       </c>
@@ -5332,10 +5338,13 @@
         <v>-46.624099999999999</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1027</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>119</v>
       </c>
@@ -5349,7 +5358,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>119</v>
       </c>
@@ -5363,7 +5372,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>120</v>
       </c>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="862" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2178A8A6-1A3A-462C-A7AA-0EE3BB613529}"/>
+  <xr:revisionPtr revIDLastSave="1006" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13155C6B-939C-40A3-90E2-06130949878D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="1191">
   <si>
     <t>nome</t>
   </si>
@@ -3123,6 +3123,495 @@
   </si>
   <si>
     <t>verde escuro</t>
+  </si>
+  <si>
+    <t>-23.491607906650273</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.8303128287055</t>
+  </si>
+  <si>
+    <t>Veritas Solucoes Diagnosticas Ltda</t>
+  </si>
+  <si>
+    <t>-23.58583928128466</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.672640553141285</t>
+  </si>
+  <si>
+    <t>Creta Centro Reumat Terap Avancada</t>
+  </si>
+  <si>
+    <t>-23.59115703002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68290408391284</t>
+  </si>
+  <si>
+    <t>Biohirata Servicos Medicos Ltda</t>
+  </si>
+  <si>
+    <t>-22.8109404152373</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.19300793111358</t>
+  </si>
+  <si>
+    <t>Clin Imunizacao E A Dom E E G Ltda</t>
+  </si>
+  <si>
+    <t>-23.622904815725118</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68336437573272</t>
+  </si>
+  <si>
+    <t>-23.565238995358513</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.637824760736045</t>
+  </si>
+  <si>
+    <t>Fundacao Antonio Prudente</t>
+  </si>
+  <si>
+    <t>-23.580239449878007</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.71082918784181</t>
+  </si>
+  <si>
+    <t>-23.57810551541359</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.70809454657586</t>
+  </si>
+  <si>
+    <t>J R P - Servico De Neuroc</t>
+  </si>
+  <si>
+    <t>-23.580948209971</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68531578789256</t>
+  </si>
+  <si>
+    <t>-23.59139410202751</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68042067843496</t>
+  </si>
+  <si>
+    <t>Rp Consultoria Medica E Hospitalar</t>
+  </si>
+  <si>
+    <t>-23.56488741676227</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.74059025724852</t>
+  </si>
+  <si>
+    <t>Universidade De Sao Paulo</t>
+  </si>
+  <si>
+    <t>-23.567266610720925</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.738906766717214</t>
+  </si>
+  <si>
+    <t>-23.557454108475696</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.666123779799676</t>
+  </si>
+  <si>
+    <t>-23.59525417508939</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66397409868103</t>
+  </si>
+  <si>
+    <t>Clinica Thais Pepe Ltda</t>
+  </si>
+  <si>
+    <t>Rebelo De Moraes Servicos Medicos L</t>
+  </si>
+  <si>
+    <t>-23.582273524974536</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.663798768798834</t>
+  </si>
+  <si>
+    <t>-23.41765028964514</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.3995451941182</t>
+  </si>
+  <si>
+    <t>Aqia Quimica Industrial Ltda</t>
+  </si>
+  <si>
+    <t>-23.766325358439147</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.58657428880948</t>
+  </si>
+  <si>
+    <t>-23.60137082955827</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.715166055446176</t>
+  </si>
+  <si>
+    <t>-23.600002705157458</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.7150809421247</t>
+  </si>
+  <si>
+    <t>Entrega Agendada</t>
+  </si>
+  <si>
+    <t>-23.303798508801876</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.96308424101065</t>
+  </si>
+  <si>
+    <t>Analice Souza Teixeira Pinto</t>
+  </si>
+  <si>
+    <t>-23.18081306063074</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.85561988678899</t>
+  </si>
+  <si>
+    <t>Spdm Assoc. Paulista P Desen. Da Me</t>
+  </si>
+  <si>
+    <t>-23.657255935448255</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.6537783144883</t>
+  </si>
+  <si>
+    <t>Soc Ben Isr Br Hosp Albert Einstein</t>
+  </si>
+  <si>
+    <t>-23.514690293386153</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.74526580912665</t>
+  </si>
+  <si>
+    <t>-23.553871360454092</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.46034874578499</t>
+  </si>
+  <si>
+    <t>-23.462915574159982</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.46722780221196</t>
+  </si>
+  <si>
+    <t>Llt Distribuicao Prod Medicos Ltda</t>
+  </si>
+  <si>
+    <t>-23.584037124899215</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.670540688903756</t>
+  </si>
+  <si>
+    <t>Prevent Senior Atendimento A Saude Ltda</t>
+  </si>
+  <si>
+    <t>-23.623116646564554</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68529916804948</t>
+  </si>
+  <si>
+    <t>-23.59029346411235</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67253025345803</t>
+  </si>
+  <si>
+    <t>Rede Dor Sao Luiz S A</t>
+  </si>
+  <si>
+    <t>-23.56726866221246</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65084158890422</t>
+  </si>
+  <si>
+    <t>-23.20130801315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.902349730502436</t>
+  </si>
+  <si>
+    <t>Clinica Vacinas Elis Camara Ltda</t>
+  </si>
+  <si>
+    <t>-23.685561203832545</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.62641837212703</t>
+  </si>
+  <si>
+    <t>Innova Hospitais Ass Ltda</t>
+  </si>
+  <si>
+    <t>-23.440595662870017</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.40992852207977</t>
+  </si>
+  <si>
+    <t>Assoc Fundo De Incentivo A Pesquis</t>
+  </si>
+  <si>
+    <t>-23.804677088978092</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.40166663492809</t>
+  </si>
+  <si>
+    <t>Municipio De Sao Sebastiao</t>
+  </si>
+  <si>
+    <t>-23.560207390018054</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65090470358774</t>
+  </si>
+  <si>
+    <t>Ronan Licinio De Araujo</t>
+  </si>
+  <si>
+    <t>-23.544375345612362</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.57399997390448</t>
+  </si>
+  <si>
+    <t>-23.583494401205378</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67053507504155</t>
+  </si>
+  <si>
+    <t>Impar Servicos Hospitalares S/A</t>
+  </si>
+  <si>
+    <t>-23.600513322674473</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.6946049093443</t>
+  </si>
+  <si>
+    <t>-23.564091947412805</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.591419625161954</t>
+  </si>
+  <si>
+    <t>-23.52359675688808</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.211731105445836</t>
+  </si>
+  <si>
+    <t>Cetal - Centro Tecnologico De</t>
+  </si>
+  <si>
+    <t>-23.19658441053305</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.89562088129015</t>
+  </si>
+  <si>
+    <t>Supreme Clinica Imunizacao Ltda</t>
+  </si>
+  <si>
+    <t>-23.465238694510592</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.53306954906003</t>
+  </si>
+  <si>
+    <t>NOTRE DAME INTERMEDICA SAUDE SA</t>
+  </si>
+  <si>
+    <t>-23.465230453715844</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.53307380902192</t>
+  </si>
+  <si>
+    <t>Pacifico Operacoes Hospitalares S.A</t>
+  </si>
+  <si>
+    <t>-23.208358330585508</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.89057103056921</t>
+  </si>
+  <si>
+    <t>ORTHOSERVICE LTDA</t>
+  </si>
+  <si>
+    <t>-23.20708539325637</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.88958526193157</t>
+  </si>
+  <si>
+    <t>Sao Camilo Clinica Medica Vale D</t>
+  </si>
+  <si>
+    <t>-23.414134703513536</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.34491112726881</t>
+  </si>
+  <si>
+    <t>Supermed Com Imp Prod Med E Hospit Ltda</t>
+  </si>
+  <si>
+    <t>Trindade E Almeida Med.Associados L</t>
+  </si>
+  <si>
+    <t>-23.54255436502904</t>
+  </si>
+  <si>
+    <t>-23.533057348624872</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.666733019593174</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.58298108631723</t>
+  </si>
+  <si>
+    <t>-23.584138496314093</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.67712126191948</t>
+  </si>
+  <si>
+    <t>Dra. Julia Ocampo Lyra Da Silva</t>
+  </si>
+  <si>
+    <t>-22.916157052564195</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.42562279604553</t>
+  </si>
+  <si>
+    <t>Adium S.A</t>
+  </si>
+  <si>
+    <t>-23.516862770450512</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.178527455079816</t>
+  </si>
+  <si>
+    <t>Ciat - Cent Inf Alto Tiete Ltda</t>
+  </si>
+  <si>
+    <t>-23.56213720240074</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.63858388659633</t>
+  </si>
+  <si>
+    <t>-23.5769001937721</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64047418630968</t>
+  </si>
+  <si>
+    <t>-23.579953021877305</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.63890296006778</t>
+  </si>
+  <si>
+    <t>Naga Medical Ltda</t>
+  </si>
+  <si>
+    <t>-23.62784934127493</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66338101643664</t>
+  </si>
+  <si>
+    <t>Dra. Silvania Barbosa Macedo</t>
+  </si>
+  <si>
+    <t>-23.645768784448368</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.71398787820983</t>
+  </si>
+  <si>
+    <t>Bioagri Analises De Alimentos Ltda</t>
+  </si>
+  <si>
+    <t>-23.186208322554833</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.88376874843998</t>
+  </si>
+  <si>
+    <t>Unimed Sao Jose Dos Campos - Cooper</t>
+  </si>
+  <si>
+    <t>-23.540252107647465</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.5737477735613</t>
+  </si>
+  <si>
+    <t>-23.56448247583954</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.72000743091553</t>
+  </si>
+  <si>
+    <t>FUNDACAO BUTANTAN</t>
+  </si>
+  <si>
+    <t>-23.49644469789858</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.626185943998955</t>
+  </si>
+  <si>
+    <t>INSTITUTO HERMES PARDINI S/A</t>
+  </si>
+  <si>
+    <t>-23.48454959827965</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.6305480418734</t>
+  </si>
+  <si>
+    <t>-23.66802405584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.53158202313826</t>
   </si>
 </sst>
 </file>
@@ -3515,7 +4004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J671"/>
+  <dimension ref="A1:J725"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.77734375" customWidth="1"/>
@@ -12893,25 +13382,867 @@
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D665" s="4"/>
+      <c r="A665" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B665" s="7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C665" s="7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D665" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D666" s="4"/>
+      <c r="A666" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B666" s="7" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C666" s="7" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D666" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D667" s="4"/>
+      <c r="A667" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B667" s="7" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C667" s="7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D667" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D668" s="4"/>
+      <c r="A668" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B668" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C668" s="7" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D668" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D669" s="4"/>
+      <c r="A669" t="s">
+        <v>480</v>
+      </c>
+      <c r="B669" s="7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C669" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D669" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D670" s="4"/>
+      <c r="A670" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B670" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C670" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D670" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D671" s="4"/>
+      <c r="A671" t="s">
+        <v>398</v>
+      </c>
+      <c r="B671" s="7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C671" s="7" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D671" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A672" t="s">
+        <v>410</v>
+      </c>
+      <c r="B672" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C672" s="7" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D672" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A673" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B673" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C673" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D673" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="674" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A674" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B674" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C674" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D674" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="675" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A675" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B675" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C675" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D675" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A676" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B676" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C676" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D676" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A677" t="s">
+        <v>642</v>
+      </c>
+      <c r="B677" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C677" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D677" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A678" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B678" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C678" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D678" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A679" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B679" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C679" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D679" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="680" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A680" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B680" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C680" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D680" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A681" t="s">
+        <v>878</v>
+      </c>
+      <c r="B681" s="7" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C681" s="7" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D681" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="682" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A682" t="s">
+        <v>347</v>
+      </c>
+      <c r="B682" s="7" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C682" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D682" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E682" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="683" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
+        <v>347</v>
+      </c>
+      <c r="B683" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C683" s="7" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D683" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E683" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="684" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A684" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B684" s="7" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C684" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D684" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="685" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A685" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B685" s="7" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C685" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D685" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="686" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A686" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B686" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C686" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D686" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E686" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A687" t="s">
+        <v>526</v>
+      </c>
+      <c r="B687" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C687" s="7" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D687" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="688" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A688" t="s">
+        <v>780</v>
+      </c>
+      <c r="B688" s="7" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C688" s="7" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D688" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A689" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B689" s="7" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C689" s="7" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D689" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A690" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B690" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C690" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D690" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A691" t="s">
+        <v>936</v>
+      </c>
+      <c r="B691" s="7" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C691" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D691" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A692" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B692" s="7" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C692" s="7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D692" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A693" t="s">
+        <v>398</v>
+      </c>
+      <c r="B693" s="7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C693" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D693" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A694" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B694" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C694" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D694" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A695" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B695" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C695" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D695" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A696" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B696" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C696" s="7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D696" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A697" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B697" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C697" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D697" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A698" t="s">
+        <v>353</v>
+      </c>
+      <c r="B698" s="7" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C698" s="7" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D698" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A699" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B699" s="7" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C699" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D699" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A700" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B700" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C700" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D700" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A701" t="s">
+        <v>707</v>
+      </c>
+      <c r="B701" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C701" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D701" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A702" t="s">
+        <v>398</v>
+      </c>
+      <c r="B702" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C702" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D702" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A703" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B703" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C703" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D703" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A704" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B704" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C704" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D704" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A705" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B705" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C705" s="7" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D705" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A706" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B706" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C706" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D706" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A707" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B707" s="7" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C707" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D707" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A708" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B708" s="7" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C708" s="7" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D708" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A709" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B709" s="7" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C709" s="7" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D709" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A710" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B710" s="7" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C710" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D710" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A711" t="s">
+        <v>398</v>
+      </c>
+      <c r="B711" s="7" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C711" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D711" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A712" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B712" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C712" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D712" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A713" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B713" s="7" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C713" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D713" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A714" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B714" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C714" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D714" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A715" t="s">
+        <v>483</v>
+      </c>
+      <c r="B715" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C715" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D715" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A716" t="s">
+        <v>483</v>
+      </c>
+      <c r="B716" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C716" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D716" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A717" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B717" s="7" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C717" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D717" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A718" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B718" s="7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C718" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D718" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A719" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B719" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C719" s="7" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D719" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A720" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B720" s="7" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C720" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D720" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A721" t="s">
+        <v>410</v>
+      </c>
+      <c r="B721" s="7" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C721" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D721" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A722" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B722" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C722" s="7" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D722" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A723" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B723" s="7" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C723" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D723" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A724" t="s">
+        <v>861</v>
+      </c>
+      <c r="B724" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C724" s="7" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D724" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A725" t="s">
+        <v>980</v>
+      </c>
+      <c r="B725" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C725" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D725" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1006" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13155C6B-939C-40A3-90E2-06130949878D}"/>
+  <xr:revisionPtr revIDLastSave="1037" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A1B0C50-085E-418A-ACE5-DE46774A9684}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="1191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="1220">
   <si>
     <t>nome</t>
   </si>
@@ -3612,6 +3612,93 @@
   </si>
   <si>
     <t xml:space="preserve"> -46.53158202313826</t>
+  </si>
+  <si>
+    <t>marrom</t>
+  </si>
+  <si>
+    <t>-23.41050058608194</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.36338527840866</t>
+  </si>
+  <si>
+    <t>Ffrr Distribuicao Ltda</t>
+  </si>
+  <si>
+    <t>DEDICADO - BEAM SUNTORY</t>
+  </si>
+  <si>
+    <t>-23.656805870279356</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.481131332213344</t>
+  </si>
+  <si>
+    <t>Dismax Distribuicao E Representacao De Produtos E Generos Al</t>
+  </si>
+  <si>
+    <t>DEDICADO - DURACELL</t>
+  </si>
+  <si>
+    <t>-23.522354445583566</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.52119926758678</t>
+  </si>
+  <si>
+    <t>WMS SUPERMERCADOS DO BRASIL LTDA</t>
+  </si>
+  <si>
+    <t>-23.551596211502304</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.51998999142315</t>
+  </si>
+  <si>
+    <t>COFEMA ATACADISTA LTDA</t>
+  </si>
+  <si>
+    <t>-23.552947213379987</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.51964641959238</t>
+  </si>
+  <si>
+    <t>ATACADAO S/A</t>
+  </si>
+  <si>
+    <t>-23.665845274250707</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.72293116436718</t>
+  </si>
+  <si>
+    <t>TENDA ATACADO LTDA</t>
+  </si>
+  <si>
+    <t>-23.674783665133408</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.71295388845304</t>
+  </si>
+  <si>
+    <t>-23.514294466307692</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.71502896602298</t>
+  </si>
+  <si>
+    <t>Arcoz Distribuidora Ltda Arcoz Distribuidora Ltda</t>
+  </si>
+  <si>
+    <t>-23.55344682022098</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.59960861719264</t>
+  </si>
+  <si>
+    <t>ARMARINHOS FERNANDO LTDA</t>
   </si>
 </sst>
 </file>
@@ -4004,7 +4091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J725"/>
+  <dimension ref="A1:J734"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.77734375" customWidth="1"/>
@@ -14174,7 +14261,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>410</v>
       </c>
@@ -14188,7 +14275,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="722" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>1183</v>
       </c>
@@ -14202,7 +14289,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="723" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>1186</v>
       </c>
@@ -14216,7 +14303,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="724" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>861</v>
       </c>
@@ -14230,7 +14317,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>980</v>
       </c>
@@ -14242,6 +14329,159 @@
       </c>
       <c r="D725" s="4" t="s">
         <v>323</v>
+      </c>
+    </row>
+    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A726" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B726" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C726" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D726" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E726" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A727" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B727" s="7" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C727" s="7" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D727" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E727" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A728" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B728" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C728" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D728" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E728" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A729" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B729" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C729" s="7" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D729" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E729" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A730" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B730" s="7" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C730" s="7" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D730" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E730" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A731" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B731" s="7" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C731" s="7" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D731" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E731" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A732" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B732" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C732" s="7" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D732" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E732" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A733" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B733" s="7" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C733" s="7" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D733" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E733" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A734" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B734" s="7" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C734" s="7" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D734" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E734" t="s">
+        <v>1199</v>
       </c>
     </row>
   </sheetData>

--- a/dados_mapa.xlsx
+++ b/dados_mapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/andre_alvesdossantos_dhl_com/Documents/Mapa de roteirização/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1037" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A1B0C50-085E-418A-ACE5-DE46774A9684}"/>
+  <xr:revisionPtr revIDLastSave="1169" documentId="8_{4AEB14AA-2EF0-4F07-BEAC-5E603C819C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB5C2D52-CBCC-4069-ADCA-E9FA5772EBD2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="1220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2314" uniqueCount="1315">
   <si>
     <t>nome</t>
   </si>
@@ -1778,9 +1778,6 @@
     <t xml:space="preserve"> -46.693084004247986</t>
   </si>
   <si>
-    <t xml:space="preserve">Dra. Renata De Avila Silva | Avila Dermatologia E Clin. Medica | Jro Consultorio Medico S/C Ltda | 2Csj Medicos Associados Ltda </t>
-  </si>
-  <si>
     <t>-22.57759653485007</t>
   </si>
   <si>
@@ -3699,6 +3696,294 @@
   </si>
   <si>
     <t>ARMARINHOS FERNANDO LTDA</t>
+  </si>
+  <si>
+    <t>-23.39490463631581</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.35323577726945</t>
+  </si>
+  <si>
+    <t>SENDAS DISTRIBUIDORA SA</t>
+  </si>
+  <si>
+    <t>-23.395262277131195</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.35138127541759</t>
+  </si>
+  <si>
+    <t>Comercial Esperanca Atac Importac E Exportacao Ltda</t>
+  </si>
+  <si>
+    <t>-23.46952521188216</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.428101754776954</t>
+  </si>
+  <si>
+    <t>Mult Bev Distribuicao Ltda</t>
+  </si>
+  <si>
+    <t>-23.669218442361917</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.736750017736874</t>
+  </si>
+  <si>
+    <t>ATACADAO S.A</t>
+  </si>
+  <si>
+    <t>-23.581093921772716</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.600732233083505</t>
+  </si>
+  <si>
+    <t>-23.559575648001942</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.447325993178715</t>
+  </si>
+  <si>
+    <t>-23.04814917572893</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.59339638892079</t>
+  </si>
+  <si>
+    <t>COMERCIAL ZARAGOZA IMP E EXP LTDA</t>
+  </si>
+  <si>
+    <t>-23.582075652726658</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.603034994294305</t>
+  </si>
+  <si>
+    <t>FRONT BEBIDAS LTDA</t>
+  </si>
+  <si>
+    <t>-23.599335838482162</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68208398176257</t>
+  </si>
+  <si>
+    <t>Gabrielly Gavassa Alves</t>
+  </si>
+  <si>
+    <t>-23.51145730265494</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.60725549742874</t>
+  </si>
+  <si>
+    <t>Renova Comercio De Produtos</t>
+  </si>
+  <si>
+    <t>-23.494927324457908</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.45616667544161</t>
+  </si>
+  <si>
+    <t>-23.442185476041512</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.499689041767716</t>
+  </si>
+  <si>
+    <t>DUFRY DO BRASIL DUTY FREE SHOP LTDA</t>
+  </si>
+  <si>
+    <t>-23.747133747128782</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.5657612129236</t>
+  </si>
+  <si>
+    <t>BMP UTILIDADES DOMESTICAS S.A.</t>
+  </si>
+  <si>
+    <t>-23.267924729580812</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.06131877542163</t>
+  </si>
+  <si>
+    <t>Sdb Comercio De Alimentos Ltda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jro Consultorio Medico S/C Ltda | 2Csj Medicos Associados Ltda </t>
+  </si>
+  <si>
+    <t>-23.685559362740722</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.69094908983349</t>
+  </si>
+  <si>
+    <t>-23.627747149240992</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.64393520424611</t>
+  </si>
+  <si>
+    <t>Wms Supermercados Do Brasil Ltda</t>
+  </si>
+  <si>
+    <t>-23.5219713232643</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.65780484107676</t>
+  </si>
+  <si>
+    <t>-23.76640933366652</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.58650636084093</t>
+  </si>
+  <si>
+    <t>BRS SUPRIMENTOS CORPORATIVOS S/A</t>
+  </si>
+  <si>
+    <t>-23.421441434056675</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.3889249788255</t>
+  </si>
+  <si>
+    <t>Imifarma Prod Farm Cosmet S A</t>
+  </si>
+  <si>
+    <t>-23.49484262435085</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.66536240452082</t>
+  </si>
+  <si>
+    <t>Paulo J. T. Ramos Distribuidora De Utens</t>
+  </si>
+  <si>
+    <t>-23.42623408709561</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.38322688875207</t>
+  </si>
+  <si>
+    <t>Raia Drogasil S A</t>
+  </si>
+  <si>
+    <t>-23.597526533201947</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.638609961021785</t>
+  </si>
+  <si>
+    <t>D'ARGENT COMERCIAL LTDA DARGENT</t>
+  </si>
+  <si>
+    <t>-23.62765071415904</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.633740472143494</t>
+  </si>
+  <si>
+    <t>FEMACELL COM REPRES LT FEMACELL</t>
+  </si>
+  <si>
+    <t>-23.51252685728442</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.698372211193636</t>
+  </si>
+  <si>
+    <t>-23.523841783763768</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.57412073437737</t>
+  </si>
+  <si>
+    <t>-23.486005585445078</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.73845184223361</t>
+  </si>
+  <si>
+    <t>-23.933673417390683</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.362680725421015</t>
+  </si>
+  <si>
+    <t>ATACADAO S A</t>
+  </si>
+  <si>
+    <t>-23.50538674931834</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.68994296272228</t>
+  </si>
+  <si>
+    <t>SENDAS DISTRIBUIDORA S/A</t>
+  </si>
+  <si>
+    <t>-23.443367896977662</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.445589965491955</t>
+  </si>
+  <si>
+    <t>Multiplica Atacado Ltda</t>
+  </si>
+  <si>
+    <t>-23.43188762153761</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.41421927727351</t>
+  </si>
+  <si>
+    <t>Tenda Atacado Sa</t>
+  </si>
+  <si>
+    <t>-23.436685368290004</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.71960321075231</t>
+  </si>
+  <si>
+    <t>ATACADAO SA</t>
+  </si>
+  <si>
+    <t>-23.53606284589343</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.582030246842265</t>
+  </si>
+  <si>
+    <t>-23.516969392908106</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.72657863065969</t>
+  </si>
+  <si>
+    <t>-23.766412681962112</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -46.718163070924454</t>
+  </si>
+  <si>
+    <t>ATACADAO S.A. COMERCIO E INDUSTRIA LTDA</t>
+  </si>
+  <si>
+    <t>-23.251675702243816</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -45.93031431006775</t>
+  </si>
+  <si>
+    <t>UNIVALE DISTRIBUIDORA DE ALIMENTOS E REPRESENTACAO COMERCIAL</t>
   </si>
 </sst>
 </file>
@@ -4091,14 +4376,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J734"/>
+  <dimension ref="A1:J773"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="85.77734375" customWidth="1"/>
+    <col min="1" max="1" width="52.21875" customWidth="1"/>
     <col min="2" max="2" width="21.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="140.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="100.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -4115,7 +4400,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -4160,7 +4445,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -4177,7 +4462,7 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -4194,7 +4479,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -4211,7 +4496,7 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -4228,7 +4513,7 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -4245,7 +4530,7 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -4262,12 +4547,12 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B11" s="7">
         <v>-23.678487000000001</v>
@@ -4279,7 +4564,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -4394,7 +4679,7 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -4453,7 +4738,7 @@
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -4526,7 +4811,7 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -4543,7 +4828,7 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -4560,7 +4845,7 @@
         <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -4577,7 +4862,7 @@
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -4594,7 +4879,7 @@
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -4611,7 +4896,7 @@
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -4628,7 +4913,7 @@
         <v>5</v>
       </c>
       <c r="E34" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -4645,7 +4930,7 @@
         <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -4662,7 +4947,7 @@
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -4679,7 +4964,7 @@
         <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -4696,7 +4981,7 @@
         <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -5914,10 +6199,10 @@
         <v>-46.624099999999999</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E125" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -11230,7 +11515,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>579</v>
+        <v>1258</v>
       </c>
       <c r="B505" s="7" t="s">
         <v>577</v>
@@ -11247,10 +11532,10 @@
         <v>332</v>
       </c>
       <c r="B506" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="C506" s="7" t="s">
         <v>580</v>
-      </c>
-      <c r="C506" s="7" t="s">
-        <v>581</v>
       </c>
       <c r="D506" s="4" t="s">
         <v>323</v>
@@ -11258,13 +11543,13 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B507" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="C507" s="7" t="s">
         <v>582</v>
-      </c>
-      <c r="C507" s="7" t="s">
-        <v>583</v>
       </c>
       <c r="D507" s="4" t="s">
         <v>323</v>
@@ -11275,10 +11560,10 @@
         <v>558</v>
       </c>
       <c r="B508" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="C508" s="7" t="s">
         <v>585</v>
-      </c>
-      <c r="C508" s="7" t="s">
-        <v>586</v>
       </c>
       <c r="D508" s="4" t="s">
         <v>323</v>
@@ -11286,13 +11571,13 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B509" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="C509" s="7" t="s">
         <v>587</v>
-      </c>
-      <c r="C509" s="7" t="s">
-        <v>588</v>
       </c>
       <c r="D509" s="4" t="s">
         <v>323</v>
@@ -11300,13 +11585,13 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B510" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="C510" s="7" t="s">
         <v>590</v>
-      </c>
-      <c r="C510" s="7" t="s">
-        <v>591</v>
       </c>
       <c r="D510" s="4" t="s">
         <v>323</v>
@@ -11314,13 +11599,13 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B511" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="C511" s="7" t="s">
         <v>593</v>
-      </c>
-      <c r="C511" s="7" t="s">
-        <v>594</v>
       </c>
       <c r="D511" s="4" t="s">
         <v>323</v>
@@ -11331,10 +11616,10 @@
         <v>480</v>
       </c>
       <c r="B512" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="C512" s="7" t="s">
         <v>596</v>
-      </c>
-      <c r="C512" s="7" t="s">
-        <v>597</v>
       </c>
       <c r="D512" s="4" t="s">
         <v>323</v>
@@ -11342,13 +11627,13 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B513" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="C513" s="7" t="s">
         <v>598</v>
-      </c>
-      <c r="C513" s="7" t="s">
-        <v>599</v>
       </c>
       <c r="D513" s="4" t="s">
         <v>323</v>
@@ -11356,13 +11641,13 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B514" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="C514" s="7" t="s">
         <v>601</v>
-      </c>
-      <c r="C514" s="7" t="s">
-        <v>602</v>
       </c>
       <c r="D514" s="4" t="s">
         <v>323</v>
@@ -11373,10 +11658,10 @@
         <v>439</v>
       </c>
       <c r="B515" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="C515" s="7" t="s">
         <v>604</v>
-      </c>
-      <c r="C515" s="7" t="s">
-        <v>605</v>
       </c>
       <c r="D515" s="4" t="s">
         <v>323</v>
@@ -11384,13 +11669,13 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B516" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="C516" s="7" t="s">
         <v>606</v>
-      </c>
-      <c r="C516" s="7" t="s">
-        <v>607</v>
       </c>
       <c r="D516" s="4" t="s">
         <v>323</v>
@@ -11398,13 +11683,13 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B517" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="C517" s="7" t="s">
         <v>609</v>
-      </c>
-      <c r="C517" s="7" t="s">
-        <v>610</v>
       </c>
       <c r="D517" s="4" t="s">
         <v>323</v>
@@ -11412,13 +11697,13 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B518" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="C518" s="7" t="s">
         <v>612</v>
-      </c>
-      <c r="C518" s="7" t="s">
-        <v>613</v>
       </c>
       <c r="D518" s="4" t="s">
         <v>323</v>
@@ -11426,13 +11711,13 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B519" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="C519" s="7" t="s">
         <v>615</v>
-      </c>
-      <c r="C519" s="7" t="s">
-        <v>616</v>
       </c>
       <c r="D519" s="4" t="s">
         <v>323</v>
@@ -11440,13 +11725,13 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B520" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="C520" s="7" t="s">
         <v>618</v>
-      </c>
-      <c r="C520" s="7" t="s">
-        <v>619</v>
       </c>
       <c r="D520" s="4" t="s">
         <v>323</v>
@@ -11454,13 +11739,13 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B521" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="C521" s="7" t="s">
         <v>621</v>
-      </c>
-      <c r="C521" s="7" t="s">
-        <v>622</v>
       </c>
       <c r="D521" s="4" t="s">
         <v>323</v>
@@ -11471,10 +11756,10 @@
         <v>463</v>
       </c>
       <c r="B522" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="C522" s="7" t="s">
         <v>624</v>
-      </c>
-      <c r="C522" s="7" t="s">
-        <v>625</v>
       </c>
       <c r="D522" s="4" t="s">
         <v>323</v>
@@ -11485,10 +11770,10 @@
         <v>439</v>
       </c>
       <c r="B523" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="C523" s="7" t="s">
         <v>626</v>
-      </c>
-      <c r="C523" s="7" t="s">
-        <v>627</v>
       </c>
       <c r="D523" s="4" t="s">
         <v>323</v>
@@ -11496,13 +11781,13 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B524" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C524" s="7" t="s">
         <v>628</v>
-      </c>
-      <c r="C524" s="7" t="s">
-        <v>629</v>
       </c>
       <c r="D524" s="4" t="s">
         <v>323</v>
@@ -11510,13 +11795,13 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B525" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="C525" s="7" t="s">
         <v>631</v>
-      </c>
-      <c r="C525" s="7" t="s">
-        <v>632</v>
       </c>
       <c r="D525" s="4" t="s">
         <v>323</v>
@@ -11524,13 +11809,13 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B526" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="C526" s="7" t="s">
         <v>633</v>
-      </c>
-      <c r="C526" s="7" t="s">
-        <v>634</v>
       </c>
       <c r="D526" s="4" t="s">
         <v>323</v>
@@ -11541,10 +11826,10 @@
         <v>463</v>
       </c>
       <c r="B527" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="C527" s="7" t="s">
         <v>635</v>
-      </c>
-      <c r="C527" s="7" t="s">
-        <v>636</v>
       </c>
       <c r="D527" s="4" t="s">
         <v>323</v>
@@ -11555,10 +11840,10 @@
         <v>439</v>
       </c>
       <c r="B528" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C528" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D528" s="4" t="s">
         <v>323</v>
@@ -11566,13 +11851,13 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B529" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="C529" s="7" t="s">
         <v>638</v>
-      </c>
-      <c r="C529" s="7" t="s">
-        <v>639</v>
       </c>
       <c r="D529" s="4" t="s">
         <v>323</v>
@@ -11580,13 +11865,13 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B530" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="C530" s="7" t="s">
         <v>640</v>
-      </c>
-      <c r="C530" s="7" t="s">
-        <v>641</v>
       </c>
       <c r="D530" s="4" t="s">
         <v>323</v>
@@ -11594,13 +11879,13 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B531" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="C531" s="7" t="s">
         <v>643</v>
-      </c>
-      <c r="C531" s="7" t="s">
-        <v>644</v>
       </c>
       <c r="D531" s="4" t="s">
         <v>323</v>
@@ -11608,13 +11893,13 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B532" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="C532" s="7" t="s">
         <v>646</v>
-      </c>
-      <c r="C532" s="7" t="s">
-        <v>647</v>
       </c>
       <c r="D532" s="4" t="s">
         <v>323</v>
@@ -11622,13 +11907,13 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B533" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="C533" s="7" t="s">
         <v>649</v>
-      </c>
-      <c r="C533" s="7" t="s">
-        <v>650</v>
       </c>
       <c r="D533" s="4" t="s">
         <v>323</v>
@@ -11636,13 +11921,13 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B534" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="C534" s="7" t="s">
         <v>652</v>
-      </c>
-      <c r="C534" s="7" t="s">
-        <v>653</v>
       </c>
       <c r="D534" s="4" t="s">
         <v>323</v>
@@ -11653,10 +11938,10 @@
         <v>439</v>
       </c>
       <c r="B535" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="C535" s="7" t="s">
         <v>655</v>
-      </c>
-      <c r="C535" s="7" t="s">
-        <v>656</v>
       </c>
       <c r="D535" s="4" t="s">
         <v>323</v>
@@ -11667,10 +11952,10 @@
         <v>472</v>
       </c>
       <c r="B536" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="C536" s="7" t="s">
         <v>657</v>
-      </c>
-      <c r="C536" s="7" t="s">
-        <v>658</v>
       </c>
       <c r="D536" s="4" t="s">
         <v>323</v>
@@ -11678,13 +11963,13 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B537" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="C537" s="7" t="s">
         <v>659</v>
-      </c>
-      <c r="C537" s="7" t="s">
-        <v>660</v>
       </c>
       <c r="D537" s="4" t="s">
         <v>323</v>
@@ -11692,13 +11977,13 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B538" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="C538" s="7" t="s">
         <v>661</v>
-      </c>
-      <c r="C538" s="7" t="s">
-        <v>662</v>
       </c>
       <c r="D538" s="4" t="s">
         <v>323</v>
@@ -11706,13 +11991,13 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B539" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="C539" s="7" t="s">
         <v>664</v>
-      </c>
-      <c r="C539" s="7" t="s">
-        <v>665</v>
       </c>
       <c r="D539" s="4" t="s">
         <v>323</v>
@@ -11720,13 +12005,13 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B540" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="C540" s="7" t="s">
         <v>667</v>
-      </c>
-      <c r="C540" s="7" t="s">
-        <v>668</v>
       </c>
       <c r="D540" s="4" t="s">
         <v>323</v>
@@ -11734,13 +12019,13 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B541" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="C541" s="7" t="s">
         <v>670</v>
-      </c>
-      <c r="C541" s="7" t="s">
-        <v>671</v>
       </c>
       <c r="D541" s="4" t="s">
         <v>323</v>
@@ -11748,13 +12033,13 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B542" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="C542" s="7" t="s">
         <v>673</v>
-      </c>
-      <c r="C542" s="7" t="s">
-        <v>674</v>
       </c>
       <c r="D542" s="4" t="s">
         <v>323</v>
@@ -11762,13 +12047,13 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B543" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="C543" s="7" t="s">
         <v>676</v>
-      </c>
-      <c r="C543" s="7" t="s">
-        <v>677</v>
       </c>
       <c r="D543" s="4" t="s">
         <v>323</v>
@@ -11776,13 +12061,13 @@
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B544" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="C544" s="7" t="s">
         <v>678</v>
-      </c>
-      <c r="C544" s="7" t="s">
-        <v>679</v>
       </c>
       <c r="D544" s="4" t="s">
         <v>323</v>
@@ -11790,13 +12075,13 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B545" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="C545" s="7" t="s">
         <v>681</v>
-      </c>
-      <c r="C545" s="7" t="s">
-        <v>682</v>
       </c>
       <c r="D545" s="4" t="s">
         <v>323</v>
@@ -11804,13 +12089,13 @@
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B546" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="C546" s="7" t="s">
         <v>684</v>
-      </c>
-      <c r="C546" s="7" t="s">
-        <v>685</v>
       </c>
       <c r="D546" s="4" t="s">
         <v>323</v>
@@ -11818,13 +12103,13 @@
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
+        <v>686</v>
+      </c>
+      <c r="B547" s="7" t="s">
         <v>687</v>
       </c>
-      <c r="B547" s="7" t="s">
+      <c r="C547" s="7" t="s">
         <v>688</v>
-      </c>
-      <c r="C547" s="7" t="s">
-        <v>689</v>
       </c>
       <c r="D547" s="4" t="s">
         <v>323</v>
@@ -11832,13 +12117,13 @@
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B548" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="C548" s="7" t="s">
         <v>690</v>
-      </c>
-      <c r="C548" s="7" t="s">
-        <v>691</v>
       </c>
       <c r="D548" s="4" t="s">
         <v>323</v>
@@ -11846,13 +12131,13 @@
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B549" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="C549" s="7" t="s">
         <v>693</v>
-      </c>
-      <c r="C549" s="7" t="s">
-        <v>694</v>
       </c>
       <c r="D549" s="4" t="s">
         <v>323</v>
@@ -11860,13 +12145,13 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B550" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="C550" s="7" t="s">
         <v>696</v>
-      </c>
-      <c r="C550" s="7" t="s">
-        <v>697</v>
       </c>
       <c r="D550" s="4" t="s">
         <v>323</v>
@@ -11874,13 +12159,13 @@
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B551" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="C551" s="7" t="s">
         <v>699</v>
-      </c>
-      <c r="C551" s="7" t="s">
-        <v>700</v>
       </c>
       <c r="D551" s="4" t="s">
         <v>323</v>
@@ -11888,13 +12173,13 @@
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B552" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="C552" s="7" t="s">
         <v>702</v>
-      </c>
-      <c r="C552" s="7" t="s">
-        <v>703</v>
       </c>
       <c r="D552" s="4" t="s">
         <v>323</v>
@@ -11902,13 +12187,13 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B553" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C553" s="7" t="s">
         <v>705</v>
-      </c>
-      <c r="C553" s="7" t="s">
-        <v>706</v>
       </c>
       <c r="D553" s="4" t="s">
         <v>323</v>
@@ -11919,10 +12204,10 @@
         <v>431</v>
       </c>
       <c r="B554" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="C554" s="7" t="s">
         <v>708</v>
-      </c>
-      <c r="C554" s="7" t="s">
-        <v>709</v>
       </c>
       <c r="D554" s="4" t="s">
         <v>323</v>
@@ -11933,10 +12218,10 @@
         <v>410</v>
       </c>
       <c r="B555" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="C555" s="7" t="s">
         <v>710</v>
-      </c>
-      <c r="C555" s="7" t="s">
-        <v>711</v>
       </c>
       <c r="D555" s="4" t="s">
         <v>323</v>
@@ -11944,13 +12229,13 @@
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B556" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="C556" s="7" t="s">
         <v>712</v>
-      </c>
-      <c r="C556" s="7" t="s">
-        <v>713</v>
       </c>
       <c r="D556" s="4" t="s">
         <v>323</v>
@@ -11961,10 +12246,10 @@
         <v>431</v>
       </c>
       <c r="B557" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="C557" s="7" t="s">
         <v>715</v>
-      </c>
-      <c r="C557" s="7" t="s">
-        <v>716</v>
       </c>
       <c r="D557" s="4" t="s">
         <v>323</v>
@@ -11975,10 +12260,10 @@
         <v>454</v>
       </c>
       <c r="B558" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="C558" s="7" t="s">
         <v>717</v>
-      </c>
-      <c r="C558" s="7" t="s">
-        <v>718</v>
       </c>
       <c r="D558" s="4" t="s">
         <v>323</v>
@@ -11986,13 +12271,13 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B559" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="C559" s="7" t="s">
         <v>719</v>
-      </c>
-      <c r="C559" s="7" t="s">
-        <v>720</v>
       </c>
       <c r="D559" s="4" t="s">
         <v>323</v>
@@ -12000,13 +12285,13 @@
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B560" s="7" t="s">
+        <v>721</v>
+      </c>
+      <c r="C560" s="7" t="s">
         <v>722</v>
-      </c>
-      <c r="C560" s="7" t="s">
-        <v>723</v>
       </c>
       <c r="D560" s="4" t="s">
         <v>323</v>
@@ -12014,13 +12299,13 @@
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B561" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="C561" s="7" t="s">
         <v>725</v>
-      </c>
-      <c r="C561" s="7" t="s">
-        <v>726</v>
       </c>
       <c r="D561" s="4" t="s">
         <v>323</v>
@@ -12031,10 +12316,10 @@
         <v>431</v>
       </c>
       <c r="B562" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="C562" s="7" t="s">
         <v>728</v>
-      </c>
-      <c r="C562" s="7" t="s">
-        <v>729</v>
       </c>
       <c r="D562" s="4" t="s">
         <v>323</v>
@@ -12042,13 +12327,13 @@
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B563" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="C563" s="7" t="s">
         <v>730</v>
-      </c>
-      <c r="C563" s="7" t="s">
-        <v>731</v>
       </c>
       <c r="D563" s="4" t="s">
         <v>323</v>
@@ -12056,13 +12341,13 @@
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B564" s="7" t="s">
+        <v>732</v>
+      </c>
+      <c r="C564" s="7" t="s">
         <v>733</v>
-      </c>
-      <c r="C564" s="7" t="s">
-        <v>734</v>
       </c>
       <c r="D564" s="4" t="s">
         <v>323</v>
@@ -12073,10 +12358,10 @@
         <v>398</v>
       </c>
       <c r="B565" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="C565" s="7" t="s">
         <v>736</v>
-      </c>
-      <c r="C565" s="7" t="s">
-        <v>737</v>
       </c>
       <c r="D565" s="4" t="s">
         <v>323</v>
@@ -12084,13 +12369,13 @@
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B566" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="C566" s="7" t="s">
         <v>738</v>
-      </c>
-      <c r="C566" s="7" t="s">
-        <v>739</v>
       </c>
       <c r="D566" s="4" t="s">
         <v>323</v>
@@ -12098,13 +12383,13 @@
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B567" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="C567" s="7" t="s">
         <v>741</v>
-      </c>
-      <c r="C567" s="7" t="s">
-        <v>742</v>
       </c>
       <c r="D567" s="4" t="s">
         <v>323</v>
@@ -12112,13 +12397,13 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B568" s="7" t="s">
+        <v>743</v>
+      </c>
+      <c r="C568" s="7" t="s">
         <v>744</v>
-      </c>
-      <c r="C568" s="7" t="s">
-        <v>745</v>
       </c>
       <c r="D568" s="4" t="s">
         <v>323</v>
@@ -12126,13 +12411,13 @@
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B569" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="C569" s="7" t="s">
         <v>747</v>
-      </c>
-      <c r="C569" s="7" t="s">
-        <v>748</v>
       </c>
       <c r="D569" s="4" t="s">
         <v>323</v>
@@ -12140,13 +12425,13 @@
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B570" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="C570" s="7" t="s">
         <v>750</v>
-      </c>
-      <c r="C570" s="7" t="s">
-        <v>751</v>
       </c>
       <c r="D570" s="4" t="s">
         <v>323</v>
@@ -12154,13 +12439,13 @@
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B571" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="C571" s="7" t="s">
         <v>753</v>
-      </c>
-      <c r="C571" s="7" t="s">
-        <v>754</v>
       </c>
       <c r="D571" s="4" t="s">
         <v>323</v>
@@ -12168,13 +12453,13 @@
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
+        <v>755</v>
+      </c>
+      <c r="B572" s="7" t="s">
         <v>756</v>
       </c>
-      <c r="B572" s="7" t="s">
+      <c r="C572" s="7" t="s">
         <v>757</v>
-      </c>
-      <c r="C572" s="7" t="s">
-        <v>758</v>
       </c>
       <c r="D572" s="4" t="s">
         <v>323</v>
@@ -12182,13 +12467,13 @@
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B573" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="C573" s="7" t="s">
         <v>759</v>
-      </c>
-      <c r="C573" s="7" t="s">
-        <v>760</v>
       </c>
       <c r="D573" s="4" t="s">
         <v>323</v>
@@ -12196,13 +12481,13 @@
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B574" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="C574" s="7" t="s">
         <v>762</v>
-      </c>
-      <c r="C574" s="7" t="s">
-        <v>763</v>
       </c>
       <c r="D574" s="4" t="s">
         <v>323</v>
@@ -12213,10 +12498,10 @@
         <v>353</v>
       </c>
       <c r="B575" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="C575" s="7" t="s">
         <v>765</v>
-      </c>
-      <c r="C575" s="7" t="s">
-        <v>766</v>
       </c>
       <c r="D575" s="4" t="s">
         <v>323</v>
@@ -12224,13 +12509,13 @@
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B576" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="C576" s="7" t="s">
         <v>767</v>
-      </c>
-      <c r="C576" s="7" t="s">
-        <v>768</v>
       </c>
       <c r="D576" s="4" t="s">
         <v>323</v>
@@ -12238,13 +12523,13 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B577" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="C577" s="7" t="s">
         <v>770</v>
-      </c>
-      <c r="C577" s="7" t="s">
-        <v>771</v>
       </c>
       <c r="D577" s="4" t="s">
         <v>323</v>
@@ -12252,13 +12537,13 @@
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B578" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="C578" s="7" t="s">
         <v>773</v>
-      </c>
-      <c r="C578" s="7" t="s">
-        <v>774</v>
       </c>
       <c r="D578" s="4" t="s">
         <v>323</v>
@@ -12266,13 +12551,13 @@
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B579" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="C579" s="7" t="s">
         <v>776</v>
-      </c>
-      <c r="C579" s="7" t="s">
-        <v>777</v>
       </c>
       <c r="D579" s="4" t="s">
         <v>323</v>
@@ -12280,13 +12565,13 @@
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B580" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="C580" s="7" t="s">
         <v>778</v>
-      </c>
-      <c r="C580" s="7" t="s">
-        <v>779</v>
       </c>
       <c r="D580" s="4" t="s">
         <v>323</v>
@@ -12294,13 +12579,13 @@
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B581" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="C581" s="7" t="s">
         <v>782</v>
-      </c>
-      <c r="C581" s="7" t="s">
-        <v>783</v>
       </c>
       <c r="D581" s="4" t="s">
         <v>323</v>
@@ -12311,10 +12596,10 @@
         <v>454</v>
       </c>
       <c r="B582" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="C582" s="7" t="s">
         <v>785</v>
-      </c>
-      <c r="C582" s="7" t="s">
-        <v>786</v>
       </c>
       <c r="D582" s="4" t="s">
         <v>323</v>
@@ -12325,10 +12610,10 @@
         <v>480</v>
       </c>
       <c r="B583" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="C583" s="7" t="s">
         <v>787</v>
-      </c>
-      <c r="C583" s="7" t="s">
-        <v>788</v>
       </c>
       <c r="D583" s="4" t="s">
         <v>323</v>
@@ -12336,13 +12621,13 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B584" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="C584" s="7" t="s">
         <v>789</v>
-      </c>
-      <c r="C584" s="7" t="s">
-        <v>790</v>
       </c>
       <c r="D584" s="4" t="s">
         <v>323</v>
@@ -12350,13 +12635,13 @@
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B585" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="C585" s="7" t="s">
         <v>792</v>
-      </c>
-      <c r="C585" s="7" t="s">
-        <v>793</v>
       </c>
       <c r="D585" s="4" t="s">
         <v>323</v>
@@ -12364,13 +12649,13 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B586" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="C586" s="7" t="s">
         <v>795</v>
-      </c>
-      <c r="C586" s="7" t="s">
-        <v>796</v>
       </c>
       <c r="D586" s="4" t="s">
         <v>323</v>
@@ -12381,10 +12666,10 @@
         <v>460</v>
       </c>
       <c r="B587" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="C587" s="7" t="s">
         <v>797</v>
-      </c>
-      <c r="C587" s="7" t="s">
-        <v>798</v>
       </c>
       <c r="D587" s="4" t="s">
         <v>323</v>
@@ -12392,13 +12677,13 @@
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B588" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="C588" s="7" t="s">
         <v>799</v>
-      </c>
-      <c r="C588" s="7" t="s">
-        <v>800</v>
       </c>
       <c r="D588" s="4" t="s">
         <v>323</v>
@@ -12409,10 +12694,10 @@
         <v>356</v>
       </c>
       <c r="B589" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="C589" s="7" t="s">
         <v>802</v>
-      </c>
-      <c r="C589" s="7" t="s">
-        <v>803</v>
       </c>
       <c r="D589" s="4" t="s">
         <v>323</v>
@@ -12420,13 +12705,13 @@
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B590" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="C590" s="7" t="s">
         <v>804</v>
-      </c>
-      <c r="C590" s="7" t="s">
-        <v>805</v>
       </c>
       <c r="D590" s="4" t="s">
         <v>323</v>
@@ -12434,13 +12719,13 @@
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B591" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="C591" s="7" t="s">
         <v>807</v>
-      </c>
-      <c r="C591" s="7" t="s">
-        <v>808</v>
       </c>
       <c r="D591" s="4" t="s">
         <v>323</v>
@@ -12448,13 +12733,13 @@
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B592" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="C592" s="7" t="s">
         <v>809</v>
-      </c>
-      <c r="C592" s="7" t="s">
-        <v>810</v>
       </c>
       <c r="D592" s="4" t="s">
         <v>323</v>
@@ -12465,10 +12750,10 @@
         <v>480</v>
       </c>
       <c r="B593" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="C593" s="7" t="s">
         <v>812</v>
-      </c>
-      <c r="C593" s="7" t="s">
-        <v>813</v>
       </c>
       <c r="D593" s="4" t="s">
         <v>323</v>
@@ -12476,13 +12761,13 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B594" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="C594" s="7" t="s">
         <v>814</v>
-      </c>
-      <c r="C594" s="7" t="s">
-        <v>815</v>
       </c>
       <c r="D594" s="4" t="s">
         <v>323</v>
@@ -12493,10 +12778,10 @@
         <v>472</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C595" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D595" s="4" t="s">
         <v>323</v>
@@ -12504,13 +12789,13 @@
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B596" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="C596" s="7" t="s">
         <v>819</v>
-      </c>
-      <c r="C596" s="7" t="s">
-        <v>820</v>
       </c>
       <c r="D596" s="4" t="s">
         <v>323</v>
@@ -12518,13 +12803,13 @@
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B597" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="C597" s="7" t="s">
         <v>822</v>
-      </c>
-      <c r="C597" s="7" t="s">
-        <v>823</v>
       </c>
       <c r="D597" s="4" t="s">
         <v>323</v>
@@ -12532,13 +12817,13 @@
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B598" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="C598" s="7" t="s">
         <v>825</v>
-      </c>
-      <c r="C598" s="7" t="s">
-        <v>826</v>
       </c>
       <c r="D598" s="4" t="s">
         <v>323</v>
@@ -12546,13 +12831,13 @@
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B599" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="C599" s="7" t="s">
         <v>828</v>
-      </c>
-      <c r="C599" s="7" t="s">
-        <v>829</v>
       </c>
       <c r="D599" s="4" t="s">
         <v>323</v>
@@ -12560,13 +12845,13 @@
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B600" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="C600" s="7" t="s">
         <v>831</v>
-      </c>
-      <c r="C600" s="7" t="s">
-        <v>832</v>
       </c>
       <c r="D600" s="4" t="s">
         <v>323</v>
@@ -12574,13 +12859,13 @@
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B601" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="C601" s="7" t="s">
         <v>834</v>
-      </c>
-      <c r="C601" s="7" t="s">
-        <v>835</v>
       </c>
       <c r="D601" s="4" t="s">
         <v>323</v>
@@ -12588,13 +12873,13 @@
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B602" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="C602" s="7" t="s">
         <v>837</v>
-      </c>
-      <c r="C602" s="7" t="s">
-        <v>838</v>
       </c>
       <c r="D602" s="4" t="s">
         <v>323</v>
@@ -12602,13 +12887,13 @@
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B603" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="C603" s="7" t="s">
         <v>840</v>
-      </c>
-      <c r="C603" s="7" t="s">
-        <v>841</v>
       </c>
       <c r="D603" s="4" t="s">
         <v>323</v>
@@ -12616,13 +12901,13 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B604" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="C604" s="7" t="s">
         <v>843</v>
-      </c>
-      <c r="C604" s="7" t="s">
-        <v>844</v>
       </c>
       <c r="D604" s="4" t="s">
         <v>323</v>
@@ -12630,13 +12915,13 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B605" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="C605" s="7" t="s">
         <v>846</v>
-      </c>
-      <c r="C605" s="7" t="s">
-        <v>847</v>
       </c>
       <c r="D605" s="4" t="s">
         <v>323</v>
@@ -12644,13 +12929,13 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B606" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="C606" s="7" t="s">
         <v>849</v>
-      </c>
-      <c r="C606" s="7" t="s">
-        <v>850</v>
       </c>
       <c r="D606" s="4" t="s">
         <v>323</v>
@@ -12661,10 +12946,10 @@
         <v>480</v>
       </c>
       <c r="B607" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="C607" s="7" t="s">
         <v>851</v>
-      </c>
-      <c r="C607" s="7" t="s">
-        <v>852</v>
       </c>
       <c r="D607" s="4" t="s">
         <v>323</v>
@@ -12672,13 +12957,13 @@
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B608" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="C608" s="7" t="s">
         <v>853</v>
-      </c>
-      <c r="C608" s="7" t="s">
-        <v>854</v>
       </c>
       <c r="D608" s="4" t="s">
         <v>323</v>
@@ -12686,13 +12971,13 @@
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B609" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="C609" s="7" t="s">
         <v>856</v>
-      </c>
-      <c r="C609" s="7" t="s">
-        <v>857</v>
       </c>
       <c r="D609" s="4" t="s">
         <v>323</v>
@@ -12700,13 +12985,13 @@
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B610" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="C610" s="7" t="s">
         <v>859</v>
-      </c>
-      <c r="C610" s="7" t="s">
-        <v>860</v>
       </c>
       <c r="D610" s="4" t="s">
         <v>323</v>
@@ -12717,10 +13002,10 @@
         <v>454</v>
       </c>
       <c r="B611" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="C611" s="7" t="s">
         <v>862</v>
-      </c>
-      <c r="C611" s="7" t="s">
-        <v>863</v>
       </c>
       <c r="D611" s="4" t="s">
         <v>323</v>
@@ -12731,10 +13016,10 @@
         <v>558</v>
       </c>
       <c r="B612" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="C612" s="7" t="s">
         <v>864</v>
-      </c>
-      <c r="C612" s="7" t="s">
-        <v>865</v>
       </c>
       <c r="D612" s="4" t="s">
         <v>323</v>
@@ -12742,13 +13027,13 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B613" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="C613" s="7" t="s">
         <v>866</v>
-      </c>
-      <c r="C613" s="7" t="s">
-        <v>867</v>
       </c>
       <c r="D613" s="4" t="s">
         <v>323</v>
@@ -12756,13 +13041,13 @@
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B614" s="7" t="s">
+        <v>868</v>
+      </c>
+      <c r="C614" s="7" t="s">
         <v>869</v>
-      </c>
-      <c r="C614" s="7" t="s">
-        <v>870</v>
       </c>
       <c r="D614" s="4" t="s">
         <v>323</v>
@@ -12770,13 +13055,13 @@
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B615" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="C615" s="7" t="s">
         <v>871</v>
-      </c>
-      <c r="C615" s="7" t="s">
-        <v>872</v>
       </c>
       <c r="D615" s="4" t="s">
         <v>323</v>
@@ -12787,10 +13072,10 @@
         <v>356</v>
       </c>
       <c r="B616" s="7" t="s">
+        <v>873</v>
+      </c>
+      <c r="C616" s="7" t="s">
         <v>874</v>
-      </c>
-      <c r="C616" s="7" t="s">
-        <v>875</v>
       </c>
       <c r="D616" s="4" t="s">
         <v>323</v>
@@ -12798,13 +13083,13 @@
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B617" s="7" t="s">
+        <v>875</v>
+      </c>
+      <c r="C617" s="7" t="s">
         <v>876</v>
-      </c>
-      <c r="C617" s="7" t="s">
-        <v>877</v>
       </c>
       <c r="D617" s="4" t="s">
         <v>323</v>
@@ -12812,13 +13097,13 @@
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B618" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="C618" s="7" t="s">
         <v>879</v>
-      </c>
-      <c r="C618" s="7" t="s">
-        <v>880</v>
       </c>
       <c r="D618" s="4" t="s">
         <v>323</v>
@@ -12829,10 +13114,10 @@
         <v>398</v>
       </c>
       <c r="B619" s="7" t="s">
+        <v>881</v>
+      </c>
+      <c r="C619" s="7" t="s">
         <v>882</v>
-      </c>
-      <c r="C619" s="7" t="s">
-        <v>883</v>
       </c>
       <c r="D619" s="4" t="s">
         <v>323</v>
@@ -12843,10 +13128,10 @@
         <v>439</v>
       </c>
       <c r="B620" s="7" t="s">
+        <v>883</v>
+      </c>
+      <c r="C620" s="7" t="s">
         <v>884</v>
-      </c>
-      <c r="C620" s="7" t="s">
-        <v>885</v>
       </c>
       <c r="D620" s="4" t="s">
         <v>323</v>
@@ -12857,10 +13142,10 @@
         <v>410</v>
       </c>
       <c r="B621" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="C621" s="7" t="s">
         <v>886</v>
-      </c>
-      <c r="C621" s="7" t="s">
-        <v>887</v>
       </c>
       <c r="D621" s="4" t="s">
         <v>323</v>
@@ -12868,13 +13153,13 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B622" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="C622" s="7" t="s">
         <v>888</v>
-      </c>
-      <c r="C622" s="7" t="s">
-        <v>889</v>
       </c>
       <c r="D622" s="4" t="s">
         <v>323</v>
@@ -12882,13 +13167,13 @@
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B623" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="C623" s="7" t="s">
         <v>891</v>
-      </c>
-      <c r="C623" s="7" t="s">
-        <v>892</v>
       </c>
       <c r="D623" s="4" t="s">
         <v>323</v>
@@ -12899,10 +13184,10 @@
         <v>398</v>
       </c>
       <c r="B624" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="C624" s="7" t="s">
         <v>894</v>
-      </c>
-      <c r="C624" s="7" t="s">
-        <v>895</v>
       </c>
       <c r="D624" s="4" t="s">
         <v>323</v>
@@ -12910,13 +13195,13 @@
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B625" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="C625" s="7" t="s">
         <v>896</v>
-      </c>
-      <c r="C625" s="7" t="s">
-        <v>897</v>
       </c>
       <c r="D625" s="4" t="s">
         <v>323</v>
@@ -12924,13 +13209,13 @@
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B626" s="7" t="s">
+        <v>898</v>
+      </c>
+      <c r="C626" s="7" t="s">
         <v>899</v>
-      </c>
-      <c r="C626" s="7" t="s">
-        <v>900</v>
       </c>
       <c r="D626" s="4" t="s">
         <v>323</v>
@@ -12938,13 +13223,13 @@
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B627" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="C627" s="7" t="s">
         <v>901</v>
-      </c>
-      <c r="C627" s="7" t="s">
-        <v>902</v>
       </c>
       <c r="D627" s="4" t="s">
         <v>323</v>
@@ -12952,13 +13237,13 @@
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B628" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="C628" s="7" t="s">
         <v>904</v>
-      </c>
-      <c r="C628" s="7" t="s">
-        <v>905</v>
       </c>
       <c r="D628" s="4" t="s">
         <v>323</v>
@@ -12966,13 +13251,13 @@
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B629" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="C629" s="7" t="s">
         <v>907</v>
-      </c>
-      <c r="C629" s="7" t="s">
-        <v>908</v>
       </c>
       <c r="D629" s="4" t="s">
         <v>323</v>
@@ -12980,13 +13265,13 @@
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B630" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="C630" s="7" t="s">
         <v>910</v>
-      </c>
-      <c r="C630" s="7" t="s">
-        <v>911</v>
       </c>
       <c r="D630" s="4" t="s">
         <v>323</v>
@@ -12997,10 +13282,10 @@
         <v>480</v>
       </c>
       <c r="B631" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="C631" s="7" t="s">
         <v>913</v>
-      </c>
-      <c r="C631" s="7" t="s">
-        <v>914</v>
       </c>
       <c r="D631" s="4" t="s">
         <v>323</v>
@@ -13011,10 +13296,10 @@
         <v>410</v>
       </c>
       <c r="B632" s="7" t="s">
+        <v>914</v>
+      </c>
+      <c r="C632" s="7" t="s">
         <v>915</v>
-      </c>
-      <c r="C632" s="7" t="s">
-        <v>916</v>
       </c>
       <c r="D632" s="4" t="s">
         <v>323</v>
@@ -13022,13 +13307,13 @@
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B633" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="C633" s="7" t="s">
         <v>917</v>
-      </c>
-      <c r="C633" s="7" t="s">
-        <v>918</v>
       </c>
       <c r="D633" s="4" t="s">
         <v>323</v>
@@ -13036,13 +13321,13 @@
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B634" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="C634" s="7" t="s">
         <v>920</v>
-      </c>
-      <c r="C634" s="7" t="s">
-        <v>921</v>
       </c>
       <c r="D634" s="4" t="s">
         <v>323</v>
@@ -13050,13 +13335,13 @@
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B635" s="7" t="s">
+        <v>922</v>
+      </c>
+      <c r="C635" s="7" t="s">
         <v>923</v>
-      </c>
-      <c r="C635" s="7" t="s">
-        <v>924</v>
       </c>
       <c r="D635" s="4" t="s">
         <v>323</v>
@@ -13064,13 +13349,13 @@
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B636" s="7" t="s">
+        <v>925</v>
+      </c>
+      <c r="C636" s="7" t="s">
         <v>926</v>
-      </c>
-      <c r="C636" s="7" t="s">
-        <v>927</v>
       </c>
       <c r="D636" s="4" t="s">
         <v>323</v>
@@ -13078,13 +13363,13 @@
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B637" s="7" t="s">
+        <v>928</v>
+      </c>
+      <c r="C637" s="7" t="s">
         <v>929</v>
-      </c>
-      <c r="C637" s="7" t="s">
-        <v>930</v>
       </c>
       <c r="D637" s="4" t="s">
         <v>323</v>
@@ -13095,10 +13380,10 @@
         <v>439</v>
       </c>
       <c r="B638" s="7" t="s">
+        <v>931</v>
+      </c>
+      <c r="C638" s="7" t="s">
         <v>932</v>
-      </c>
-      <c r="C638" s="7" t="s">
-        <v>933</v>
       </c>
       <c r="D638" s="4" t="s">
         <v>323</v>
@@ -13106,13 +13391,13 @@
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B639" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="C639" s="7" t="s">
         <v>934</v>
-      </c>
-      <c r="C639" s="7" t="s">
-        <v>935</v>
       </c>
       <c r="D639" s="4" t="s">
         <v>323</v>
@@ -13120,13 +13405,13 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B640" s="7" t="s">
+        <v>936</v>
+      </c>
+      <c r="C640" s="7" t="s">
         <v>937</v>
-      </c>
-      <c r="C640" s="7" t="s">
-        <v>938</v>
       </c>
       <c r="D640" s="4" t="s">
         <v>323</v>
@@ -13134,13 +13419,13 @@
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B641" s="7" t="s">
+        <v>938</v>
+      </c>
+      <c r="C641" s="7" t="s">
         <v>939</v>
-      </c>
-      <c r="C641" s="7" t="s">
-        <v>940</v>
       </c>
       <c r="D641" s="4" t="s">
         <v>323</v>
@@ -13148,13 +13433,13 @@
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B642" s="7" t="s">
+        <v>941</v>
+      </c>
+      <c r="C642" s="7" t="s">
         <v>942</v>
-      </c>
-      <c r="C642" s="7" t="s">
-        <v>943</v>
       </c>
       <c r="D642" s="4" t="s">
         <v>323</v>
@@ -13162,13 +13447,13 @@
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B643" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="C643" s="7" t="s">
         <v>945</v>
-      </c>
-      <c r="C643" s="7" t="s">
-        <v>946</v>
       </c>
       <c r="D643" s="4" t="s">
         <v>323</v>
@@ -13179,10 +13464,10 @@
         <v>463</v>
       </c>
       <c r="B644" s="7" t="s">
+        <v>947</v>
+      </c>
+      <c r="C644" s="7" t="s">
         <v>948</v>
-      </c>
-      <c r="C644" s="7" t="s">
-        <v>949</v>
       </c>
       <c r="D644" s="4" t="s">
         <v>323</v>
@@ -13190,13 +13475,13 @@
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B645" s="7" t="s">
+        <v>949</v>
+      </c>
+      <c r="C645" s="7" t="s">
         <v>950</v>
-      </c>
-      <c r="C645" s="7" t="s">
-        <v>951</v>
       </c>
       <c r="D645" s="4" t="s">
         <v>323</v>
@@ -13204,13 +13489,13 @@
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B646" s="7" t="s">
+        <v>952</v>
+      </c>
+      <c r="C646" s="7" t="s">
         <v>953</v>
-      </c>
-      <c r="C646" s="7" t="s">
-        <v>954</v>
       </c>
       <c r="D646" s="4" t="s">
         <v>323</v>
@@ -13218,13 +13503,13 @@
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B647" s="7" t="s">
+        <v>954</v>
+      </c>
+      <c r="C647" s="7" t="s">
         <v>955</v>
-      </c>
-      <c r="C647" s="7" t="s">
-        <v>956</v>
       </c>
       <c r="D647" s="4" t="s">
         <v>323</v>
@@ -13232,13 +13517,13 @@
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B648" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="C648" s="7" t="s">
         <v>958</v>
-      </c>
-      <c r="C648" s="7" t="s">
-        <v>959</v>
       </c>
       <c r="D648" s="4" t="s">
         <v>323</v>
@@ -13246,13 +13531,13 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B649" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="C649" s="7" t="s">
         <v>961</v>
-      </c>
-      <c r="C649" s="7" t="s">
-        <v>962</v>
       </c>
       <c r="D649" s="4" t="s">
         <v>323</v>
@@ -13260,13 +13545,13 @@
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B650" s="7" t="s">
+        <v>963</v>
+      </c>
+      <c r="C650" s="7" t="s">
         <v>964</v>
-      </c>
-      <c r="C650" s="7" t="s">
-        <v>965</v>
       </c>
       <c r="D650" s="4" t="s">
         <v>323</v>
@@ -13274,13 +13559,13 @@
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B651" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="C651" s="7" t="s">
         <v>966</v>
-      </c>
-      <c r="C651" s="7" t="s">
-        <v>967</v>
       </c>
       <c r="D651" s="4" t="s">
         <v>323</v>
@@ -13288,13 +13573,13 @@
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B652" s="7" t="s">
+        <v>968</v>
+      </c>
+      <c r="C652" s="7" t="s">
         <v>969</v>
-      </c>
-      <c r="C652" s="7" t="s">
-        <v>970</v>
       </c>
       <c r="D652" s="4" t="s">
         <v>323</v>
@@ -13302,13 +13587,13 @@
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B653" s="7" t="s">
+        <v>971</v>
+      </c>
+      <c r="C653" s="7" t="s">
         <v>972</v>
-      </c>
-      <c r="C653" s="7" t="s">
-        <v>973</v>
       </c>
       <c r="D653" s="4" t="s">
         <v>323</v>
@@ -13316,13 +13601,13 @@
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B654" s="7" t="s">
+        <v>974</v>
+      </c>
+      <c r="C654" s="7" t="s">
         <v>975</v>
-      </c>
-      <c r="C654" s="7" t="s">
-        <v>976</v>
       </c>
       <c r="D654" s="4" t="s">
         <v>323</v>
@@ -13330,13 +13615,13 @@
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B655" s="7" t="s">
+        <v>977</v>
+      </c>
+      <c r="C655" s="7" t="s">
         <v>978</v>
-      </c>
-      <c r="C655" s="7" t="s">
-        <v>979</v>
       </c>
       <c r="D655" s="4" t="s">
         <v>323</v>
@@ -13344,13 +13629,13 @@
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B656" s="7" t="s">
+        <v>980</v>
+      </c>
+      <c r="C656" s="7" t="s">
         <v>981</v>
-      </c>
-      <c r="C656" s="7" t="s">
-        <v>982</v>
       </c>
       <c r="D656" s="4" t="s">
         <v>323</v>
@@ -13358,13 +13643,13 @@
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B657" s="7" t="s">
+        <v>982</v>
+      </c>
+      <c r="C657" s="7" t="s">
         <v>983</v>
-      </c>
-      <c r="C657" s="7" t="s">
-        <v>984</v>
       </c>
       <c r="D657" s="4" t="s">
         <v>323</v>
@@ -13372,13 +13657,13 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B658" s="7" t="s">
+        <v>985</v>
+      </c>
+      <c r="C658" s="7" t="s">
         <v>986</v>
-      </c>
-      <c r="C658" s="7" t="s">
-        <v>987</v>
       </c>
       <c r="D658" s="4" t="s">
         <v>323</v>
@@ -13386,13 +13671,13 @@
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B659" s="7" t="s">
+        <v>988</v>
+      </c>
+      <c r="C659" s="7" t="s">
         <v>989</v>
-      </c>
-      <c r="C659" s="7" t="s">
-        <v>990</v>
       </c>
       <c r="D659" s="4" t="s">
         <v>323</v>
@@ -13400,13 +13685,13 @@
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B660" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="C660" s="7" t="s">
         <v>992</v>
-      </c>
-      <c r="C660" s="7" t="s">
-        <v>993</v>
       </c>
       <c r="D660" s="4" t="s">
         <v>323</v>
@@ -13414,13 +13699,13 @@
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B661" s="7" t="s">
+        <v>993</v>
+      </c>
+      <c r="C661" s="7" t="s">
         <v>994</v>
-      </c>
-      <c r="C661" s="7" t="s">
-        <v>995</v>
       </c>
       <c r="D661" s="4" t="s">
         <v>323</v>
@@ -13428,13 +13713,13 @@
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B662" s="7" t="s">
+        <v>996</v>
+      </c>
+      <c r="C662" s="7" t="s">
         <v>997</v>
-      </c>
-      <c r="C662" s="7" t="s">
-        <v>998</v>
       </c>
       <c r="D662" s="4" t="s">
         <v>323</v>
@@ -13442,13 +13727,13 @@
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B663" s="7" t="s">
+        <v>999</v>
+      </c>
+      <c r="C663" s="7" t="s">
         <v>1000</v>
-      </c>
-      <c r="C663" s="7" t="s">
-        <v>1001</v>
       </c>
       <c r="D663" s="4" t="s">
         <v>323</v>
@@ -13459,10 +13744,10 @@
         <v>439</v>
       </c>
       <c r="B664" s="7" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C664" s="7" t="s">
         <v>1003</v>
-      </c>
-      <c r="C664" s="7" t="s">
-        <v>1004</v>
       </c>
       <c r="D664" s="4" t="s">
         <v>323</v>
@@ -13470,13 +13755,13 @@
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B665" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C665" s="7" t="s">
         <v>1028</v>
-      </c>
-      <c r="C665" s="7" t="s">
-        <v>1029</v>
       </c>
       <c r="D665" s="4" t="s">
         <v>323</v>
@@ -13484,13 +13769,13 @@
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B666" s="7" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C666" s="7" t="s">
         <v>1031</v>
-      </c>
-      <c r="C666" s="7" t="s">
-        <v>1032</v>
       </c>
       <c r="D666" s="4" t="s">
         <v>323</v>
@@ -13498,13 +13783,13 @@
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B667" s="7" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C667" s="7" t="s">
         <v>1034</v>
-      </c>
-      <c r="C667" s="7" t="s">
-        <v>1035</v>
       </c>
       <c r="D667" s="4" t="s">
         <v>323</v>
@@ -13512,13 +13797,13 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B668" s="7" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C668" s="7" t="s">
         <v>1037</v>
-      </c>
-      <c r="C668" s="7" t="s">
-        <v>1038</v>
       </c>
       <c r="D668" s="4" t="s">
         <v>323</v>
@@ -13529,10 +13814,10 @@
         <v>480</v>
       </c>
       <c r="B669" s="7" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C669" s="7" t="s">
         <v>1040</v>
-      </c>
-      <c r="C669" s="7" t="s">
-        <v>1041</v>
       </c>
       <c r="D669" s="4" t="s">
         <v>323</v>
@@ -13540,13 +13825,13 @@
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B670" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C670" s="7" t="s">
         <v>1042</v>
-      </c>
-      <c r="C670" s="7" t="s">
-        <v>1043</v>
       </c>
       <c r="D670" s="4" t="s">
         <v>323</v>
@@ -13557,10 +13842,10 @@
         <v>398</v>
       </c>
       <c r="B671" s="7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C671" s="7" t="s">
         <v>1045</v>
-      </c>
-      <c r="C671" s="7" t="s">
-        <v>1046</v>
       </c>
       <c r="D671" s="4" t="s">
         <v>323</v>
@@ -13571,10 +13856,10 @@
         <v>410</v>
       </c>
       <c r="B672" s="7" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C672" s="7" t="s">
         <v>1047</v>
-      </c>
-      <c r="C672" s="7" t="s">
-        <v>1048</v>
       </c>
       <c r="D672" s="4" t="s">
         <v>323</v>
@@ -13582,13 +13867,13 @@
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B673" s="7" t="s">
         <v>1049</v>
       </c>
-      <c r="B673" s="7" t="s">
+      <c r="C673" s="7" t="s">
         <v>1050</v>
-      </c>
-      <c r="C673" s="7" t="s">
-        <v>1051</v>
       </c>
       <c r="D673" s="4" t="s">
         <v>323</v>
@@ -13596,13 +13881,13 @@
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B674" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C674" s="7" t="s">
         <v>1052</v>
-      </c>
-      <c r="C674" s="7" t="s">
-        <v>1053</v>
       </c>
       <c r="D674" s="4" t="s">
         <v>323</v>
@@ -13610,13 +13895,13 @@
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B675" s="7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C675" s="7" t="s">
         <v>1055</v>
-      </c>
-      <c r="C675" s="7" t="s">
-        <v>1056</v>
       </c>
       <c r="D675" s="4" t="s">
         <v>323</v>
@@ -13624,13 +13909,13 @@
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B676" s="7" t="s">
         <v>1057</v>
       </c>
-      <c r="B676" s="7" t="s">
+      <c r="C676" s="7" t="s">
         <v>1058</v>
-      </c>
-      <c r="C676" s="7" t="s">
-        <v>1059</v>
       </c>
       <c r="D676" s="4" t="s">
         <v>323</v>
@@ -13638,13 +13923,13 @@
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B677" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C677" s="7" t="s">
         <v>1060</v>
-      </c>
-      <c r="C677" s="7" t="s">
-        <v>1061</v>
       </c>
       <c r="D677" s="4" t="s">
         <v>323</v>
@@ -13652,13 +13937,13 @@
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B678" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C678" s="7" t="s">
         <v>1062</v>
-      </c>
-      <c r="C678" s="7" t="s">
-        <v>1063</v>
       </c>
       <c r="D678" s="4" t="s">
         <v>323</v>
@@ -13666,13 +13951,13 @@
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B679" s="7" t="s">
         <v>1065</v>
       </c>
-      <c r="B679" s="7" t="s">
+      <c r="C679" s="7" t="s">
         <v>1066</v>
-      </c>
-      <c r="C679" s="7" t="s">
-        <v>1067</v>
       </c>
       <c r="D679" s="4" t="s">
         <v>323</v>
@@ -13680,13 +13965,13 @@
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B680" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C680" s="7" t="s">
         <v>1068</v>
-      </c>
-      <c r="C680" s="7" t="s">
-        <v>1069</v>
       </c>
       <c r="D680" s="4" t="s">
         <v>323</v>
@@ -13694,13 +13979,13 @@
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B681" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C681" s="7" t="s">
         <v>1071</v>
-      </c>
-      <c r="C681" s="7" t="s">
-        <v>1072</v>
       </c>
       <c r="D681" s="4" t="s">
         <v>323</v>
@@ -13711,16 +13996,16 @@
         <v>347</v>
       </c>
       <c r="B682" s="7" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C682" s="7" t="s">
         <v>1073</v>
       </c>
-      <c r="C682" s="7" t="s">
-        <v>1074</v>
-      </c>
       <c r="D682" s="4" t="s">
         <v>323</v>
       </c>
       <c r="E682" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.3">
@@ -13728,27 +14013,27 @@
         <v>347</v>
       </c>
       <c r="B683" s="7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C683" s="7" t="s">
         <v>1075</v>
       </c>
-      <c r="C683" s="7" t="s">
+      <c r="D683" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E683" t="s">
         <v>1076</v>
-      </c>
-      <c r="D683" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="E683" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B684" s="7" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C684" s="7" t="s">
         <v>1078</v>
-      </c>
-      <c r="C684" s="7" t="s">
-        <v>1079</v>
       </c>
       <c r="D684" s="4" t="s">
         <v>323</v>
@@ -13756,13 +14041,13 @@
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B685" s="7" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C685" s="7" t="s">
         <v>1081</v>
-      </c>
-      <c r="C685" s="7" t="s">
-        <v>1082</v>
       </c>
       <c r="D685" s="4" t="s">
         <v>323</v>
@@ -13770,19 +14055,19 @@
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B686" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C686" s="7" t="s">
         <v>1084</v>
       </c>
-      <c r="C686" s="7" t="s">
-        <v>1085</v>
-      </c>
       <c r="D686" s="4" t="s">
         <v>323</v>
       </c>
       <c r="E686" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.3">
@@ -13790,10 +14075,10 @@
         <v>526</v>
       </c>
       <c r="B687" s="7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C687" s="7" t="s">
         <v>1087</v>
-      </c>
-      <c r="C687" s="7" t="s">
-        <v>1088</v>
       </c>
       <c r="D687" s="4" t="s">
         <v>323</v>
@@ -13801,13 +14086,13 @@
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B688" s="7" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C688" s="7" t="s">
         <v>1089</v>
-      </c>
-      <c r="C688" s="7" t="s">
-        <v>1090</v>
       </c>
       <c r="D688" s="4" t="s">
         <v>323</v>
@@ -13815,13 +14100,13 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B689" s="7" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C689" s="7" t="s">
         <v>1091</v>
-      </c>
-      <c r="C689" s="7" t="s">
-        <v>1092</v>
       </c>
       <c r="D689" s="4" t="s">
         <v>323</v>
@@ -13829,13 +14114,13 @@
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B690" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C690" s="7" t="s">
         <v>1094</v>
-      </c>
-      <c r="C690" s="7" t="s">
-        <v>1095</v>
       </c>
       <c r="D690" s="4" t="s">
         <v>323</v>
@@ -13843,13 +14128,13 @@
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B691" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C691" s="7" t="s">
         <v>1097</v>
-      </c>
-      <c r="C691" s="7" t="s">
-        <v>1098</v>
       </c>
       <c r="D691" s="4" t="s">
         <v>323</v>
@@ -13857,13 +14142,13 @@
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B692" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C692" s="7" t="s">
         <v>1099</v>
-      </c>
-      <c r="C692" s="7" t="s">
-        <v>1100</v>
       </c>
       <c r="D692" s="4" t="s">
         <v>323</v>
@@ -13874,10 +14159,10 @@
         <v>398</v>
       </c>
       <c r="B693" s="7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C693" s="7" t="s">
         <v>1102</v>
-      </c>
-      <c r="C693" s="7" t="s">
-        <v>1103</v>
       </c>
       <c r="D693" s="4" t="s">
         <v>323</v>
@@ -13885,13 +14170,13 @@
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B694" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C694" s="7" t="s">
         <v>1104</v>
-      </c>
-      <c r="C694" s="7" t="s">
-        <v>1105</v>
       </c>
       <c r="D694" s="4" t="s">
         <v>323</v>
@@ -13899,13 +14184,13 @@
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B695" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C695" s="7" t="s">
         <v>1107</v>
-      </c>
-      <c r="C695" s="7" t="s">
-        <v>1108</v>
       </c>
       <c r="D695" s="4" t="s">
         <v>323</v>
@@ -13913,13 +14198,13 @@
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B696" s="7" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C696" s="7" t="s">
         <v>1110</v>
-      </c>
-      <c r="C696" s="7" t="s">
-        <v>1111</v>
       </c>
       <c r="D696" s="4" t="s">
         <v>323</v>
@@ -13927,13 +14212,13 @@
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B697" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C697" s="7" t="s">
         <v>1113</v>
-      </c>
-      <c r="C697" s="7" t="s">
-        <v>1114</v>
       </c>
       <c r="D697" s="4" t="s">
         <v>323</v>
@@ -13944,10 +14229,10 @@
         <v>353</v>
       </c>
       <c r="B698" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C698" s="7" t="s">
         <v>1116</v>
-      </c>
-      <c r="C698" s="7" t="s">
-        <v>1117</v>
       </c>
       <c r="D698" s="4" t="s">
         <v>323</v>
@@ -13955,13 +14240,13 @@
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B699" s="7" t="s">
         <v>1118</v>
       </c>
-      <c r="B699" s="7" t="s">
+      <c r="C699" s="7" t="s">
         <v>1119</v>
-      </c>
-      <c r="C699" s="7" t="s">
-        <v>1120</v>
       </c>
       <c r="D699" s="4" t="s">
         <v>323</v>
@@ -13969,13 +14254,13 @@
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B700" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C700" s="7" t="s">
         <v>1121</v>
-      </c>
-      <c r="C700" s="7" t="s">
-        <v>1122</v>
       </c>
       <c r="D700" s="4" t="s">
         <v>323</v>
@@ -13983,13 +14268,13 @@
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B701" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C701" s="7" t="s">
         <v>1124</v>
-      </c>
-      <c r="C701" s="7" t="s">
-        <v>1125</v>
       </c>
       <c r="D701" s="4" t="s">
         <v>323</v>
@@ -14000,10 +14285,10 @@
         <v>398</v>
       </c>
       <c r="B702" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C702" s="7" t="s">
         <v>1126</v>
-      </c>
-      <c r="C702" s="7" t="s">
-        <v>1127</v>
       </c>
       <c r="D702" s="4" t="s">
         <v>323</v>
@@ -14011,13 +14296,13 @@
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B703" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C703" s="7" t="s">
         <v>1128</v>
-      </c>
-      <c r="C703" s="7" t="s">
-        <v>1129</v>
       </c>
       <c r="D703" s="4" t="s">
         <v>323</v>
@@ -14025,13 +14310,13 @@
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B704" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C704" s="7" t="s">
         <v>1131</v>
-      </c>
-      <c r="C704" s="7" t="s">
-        <v>1132</v>
       </c>
       <c r="D704" s="4" t="s">
         <v>323</v>
@@ -14039,13 +14324,13 @@
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B705" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C705" s="7" t="s">
         <v>1134</v>
-      </c>
-      <c r="C705" s="7" t="s">
-        <v>1135</v>
       </c>
       <c r="D705" s="4" t="s">
         <v>323</v>
@@ -14053,13 +14338,13 @@
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B706" s="7" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C706" s="7" t="s">
         <v>1137</v>
-      </c>
-      <c r="C706" s="7" t="s">
-        <v>1138</v>
       </c>
       <c r="D706" s="4" t="s">
         <v>323</v>
@@ -14067,13 +14352,13 @@
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B707" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C707" s="7" t="s">
         <v>1140</v>
-      </c>
-      <c r="C707" s="7" t="s">
-        <v>1141</v>
       </c>
       <c r="D707" s="4" t="s">
         <v>323</v>
@@ -14081,13 +14366,13 @@
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B708" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C708" s="7" t="s">
         <v>1143</v>
-      </c>
-      <c r="C708" s="7" t="s">
-        <v>1144</v>
       </c>
       <c r="D708" s="4" t="s">
         <v>323</v>
@@ -14095,13 +14380,13 @@
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B709" s="7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C709" s="7" t="s">
         <v>1146</v>
-      </c>
-      <c r="C709" s="7" t="s">
-        <v>1147</v>
       </c>
       <c r="D709" s="4" t="s">
         <v>323</v>
@@ -14109,13 +14394,13 @@
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B710" s="7" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C710" s="7" t="s">
         <v>1151</v>
-      </c>
-      <c r="C710" s="7" t="s">
-        <v>1152</v>
       </c>
       <c r="D710" s="4" t="s">
         <v>323</v>
@@ -14126,10 +14411,10 @@
         <v>398</v>
       </c>
       <c r="B711" s="7" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C711" s="7" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D711" s="4" t="s">
         <v>323</v>
@@ -14137,13 +14422,13 @@
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B712" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C712" s="7" t="s">
         <v>1154</v>
-      </c>
-      <c r="C712" s="7" t="s">
-        <v>1155</v>
       </c>
       <c r="D712" s="4" t="s">
         <v>323</v>
@@ -14151,13 +14436,13 @@
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B713" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C713" s="7" t="s">
         <v>1157</v>
-      </c>
-      <c r="C713" s="7" t="s">
-        <v>1158</v>
       </c>
       <c r="D713" s="4" t="s">
         <v>323</v>
@@ -14165,13 +14450,13 @@
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B714" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C714" s="7" t="s">
         <v>1160</v>
-      </c>
-      <c r="C714" s="7" t="s">
-        <v>1161</v>
       </c>
       <c r="D714" s="4" t="s">
         <v>323</v>
@@ -14182,10 +14467,10 @@
         <v>483</v>
       </c>
       <c r="B715" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C715" s="7" t="s">
         <v>1163</v>
-      </c>
-      <c r="C715" s="7" t="s">
-        <v>1164</v>
       </c>
       <c r="D715" s="4" t="s">
         <v>323</v>
@@ -14196,10 +14481,10 @@
         <v>483</v>
       </c>
       <c r="B716" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C716" s="7" t="s">
         <v>1165</v>
-      </c>
-      <c r="C716" s="7" t="s">
-        <v>1166</v>
       </c>
       <c r="D716" s="4" t="s">
         <v>323</v>
@@ -14207,13 +14492,13 @@
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B717" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C717" s="7" t="s">
         <v>1167</v>
-      </c>
-      <c r="C717" s="7" t="s">
-        <v>1168</v>
       </c>
       <c r="D717" s="4" t="s">
         <v>323</v>
@@ -14221,13 +14506,13 @@
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B718" s="7" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C718" s="7" t="s">
         <v>1170</v>
-      </c>
-      <c r="C718" s="7" t="s">
-        <v>1171</v>
       </c>
       <c r="D718" s="4" t="s">
         <v>323</v>
@@ -14235,13 +14520,13 @@
     </row>
     <row r="719" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B719" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C719" s="7" t="s">
         <v>1173</v>
-      </c>
-      <c r="C719" s="7" t="s">
-        <v>1174</v>
       </c>
       <c r="D719" s="4" t="s">
         <v>323</v>
@@ -14249,13 +14534,13 @@
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B720" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C720" s="7" t="s">
         <v>1176</v>
-      </c>
-      <c r="C720" s="7" t="s">
-        <v>1177</v>
       </c>
       <c r="D720" s="4" t="s">
         <v>323</v>
@@ -14266,10 +14551,10 @@
         <v>410</v>
       </c>
       <c r="B721" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C721" s="7" t="s">
         <v>1179</v>
-      </c>
-      <c r="C721" s="7" t="s">
-        <v>1180</v>
       </c>
       <c r="D721" s="4" t="s">
         <v>323</v>
@@ -14277,13 +14562,13 @@
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B722" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C722" s="7" t="s">
         <v>1181</v>
-      </c>
-      <c r="C722" s="7" t="s">
-        <v>1182</v>
       </c>
       <c r="D722" s="4" t="s">
         <v>323</v>
@@ -14291,13 +14576,13 @@
     </row>
     <row r="723" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B723" s="7" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C723" s="7" t="s">
         <v>1184</v>
-      </c>
-      <c r="C723" s="7" t="s">
-        <v>1185</v>
       </c>
       <c r="D723" s="4" t="s">
         <v>323</v>
@@ -14305,13 +14590,13 @@
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B724" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C724" s="7" t="s">
         <v>1187</v>
-      </c>
-      <c r="C724" s="7" t="s">
-        <v>1188</v>
       </c>
       <c r="D724" s="4" t="s">
         <v>323</v>
@@ -14319,13 +14604,13 @@
     </row>
     <row r="725" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B725" s="7" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C725" s="7" t="s">
         <v>1189</v>
-      </c>
-      <c r="C725" s="7" t="s">
-        <v>1190</v>
       </c>
       <c r="D725" s="4" t="s">
         <v>323</v>
@@ -14333,156 +14618,763 @@
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B726" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C726" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D726" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E726" t="s">
         <v>1194</v>
-      </c>
-      <c r="B726" s="7" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C726" s="7" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D726" s="4" t="s">
-        <v>1191</v>
-      </c>
-      <c r="E726" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B727" s="7" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C727" s="7" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D727" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E727" t="s">
         <v>1198</v>
-      </c>
-      <c r="B727" s="7" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C727" s="7" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D727" s="4" t="s">
-        <v>1191</v>
-      </c>
-      <c r="E727" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B728" s="7" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C728" s="7" t="s">
         <v>1200</v>
       </c>
-      <c r="C728" s="7" t="s">
-        <v>1201</v>
-      </c>
       <c r="D728" s="4" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E728" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B729" s="7" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C729" s="7" t="s">
         <v>1203</v>
       </c>
-      <c r="C729" s="7" t="s">
-        <v>1204</v>
-      </c>
       <c r="D729" s="4" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E729" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="730" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B730" s="7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C730" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="C730" s="7" t="s">
-        <v>1207</v>
-      </c>
       <c r="D730" s="4" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E730" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B731" s="7" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C731" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="C731" s="7" t="s">
-        <v>1210</v>
-      </c>
       <c r="D731" s="4" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E731" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B732" s="7" t="s">
         <v>1211</v>
       </c>
-      <c r="B732" s="7" t="s">
+      <c r="C732" s="7" t="s">
         <v>1212</v>
       </c>
-      <c r="C732" s="7" t="s">
-        <v>1213</v>
-      </c>
       <c r="D732" s="4" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E732" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B733" s="7" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C733" s="7" t="s">
         <v>1214</v>
       </c>
-      <c r="C733" s="7" t="s">
-        <v>1215</v>
-      </c>
       <c r="D733" s="4" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E733" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B734" s="7" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C734" s="7" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D734" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E734" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A735" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B735" s="7" t="s">
         <v>1219</v>
       </c>
-      <c r="B734" s="7" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C734" s="7" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D734" s="4" t="s">
-        <v>1191</v>
-      </c>
-      <c r="E734" t="s">
-        <v>1199</v>
-      </c>
+      <c r="C735" s="7" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D735" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E735" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A736" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B736" s="7" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C736" s="7" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D736" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E736" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="737" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A737" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B737" s="7" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C737" s="7" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D737" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E737" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="738" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A738" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B738" s="7" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C738" s="7" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D738" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E738" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="739" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A739" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B739" s="7" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C739" s="7" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D739" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E739" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="740" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A740" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B740" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C740" s="7" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D740" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E740" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="741" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A741" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B741" s="7" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C741" s="7" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D741" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E741" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="742" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A742" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B742" s="7" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C742" s="7" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D742" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E742" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="743" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A743" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B743" s="7" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C743" s="7" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D743" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E743" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="744" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A744" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B744" s="7" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C744" s="7" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D744" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E744" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="745" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A745" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B745" s="7" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C745" s="7" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D745" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E745" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="746" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A746" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B746" s="7" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C746" s="7" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D746" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E746" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="747" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A747" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B747" s="7" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C747" s="7" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D747" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E747" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="748" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A748" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B748" s="7" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C748" s="7" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D748" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E748" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="749" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A749" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B749" s="7" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C749" s="7" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D749" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E749" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="750" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A750" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B750" s="7" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C750" s="7" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D750" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E750" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="751" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A751" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B751" s="7" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C751" s="7" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D751" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E751" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="752" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A752" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B752" s="7" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C752" s="7" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D752" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E752" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="753" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A753" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B753" s="7" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C753" s="7" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D753" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E753" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="754" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A754" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B754" s="7" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C754" s="7" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D754" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E754" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="755" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A755" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B755" s="7" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C755" s="7" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D755" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E755" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="756" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A756" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B756" s="7" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C756" s="7" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D756" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E756" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="757" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A757" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B757" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C757" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D757" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E757" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="758" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A758" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B758" s="7" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C758" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D758" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E758" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="759" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A759" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B759" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C759" s="7" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D759" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E759" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="760" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A760" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B760" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C760" s="7" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D760" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E760" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="761" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A761" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B761" s="7" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C761" s="7" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D761" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E761" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="762" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A762" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B762" s="7" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C762" s="7" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D762" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E762" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="763" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A763" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B763" s="7" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C763" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D763" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E763" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="764" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A764" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B764" s="7" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C764" s="7" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D764" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E764" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="765" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A765" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B765" s="7" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C765" s="7" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D765" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E765" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="766" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A766" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B766" s="7" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C766" s="7" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D766" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E766" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="767" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A767" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B767" s="7" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C767" s="7" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D767" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E767" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="768" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A768" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B768" s="7" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C768" s="7" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D768" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E768" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="769" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A769" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B769" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C769" s="7" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D769" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E769" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="770" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D770" s="4"/>
+    </row>
+    <row r="771" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D771" s="4"/>
+    </row>
+    <row r="772" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D772" s="4"/>
+    </row>
+    <row r="773" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D773" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
